--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -545,34 +545,34 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46081.2034722222</v>
+        <v>46111.0972222222</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46081.2305555556</v>
+        <v>46111.1034722222</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46081.2215277778</v>
+        <v>46111.0993055556</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1</v>
+        <v>0.774</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
@@ -586,34 +586,34 @@
         <v>13</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46072.5097222222</v>
+        <v>46081.2034722222</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46072.5354166667</v>
+        <v>46081.2305555556</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46072.5236111111</v>
+        <v>46081.2215277778</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.154</v>
+        <v>0.1</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
       </c>
       <c r="I3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -624,81 +624,81 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46071.3876736111</v>
+        <v>46072.5097222222</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46071.4088541667</v>
+        <v>46072.5354166667</v>
       </c>
       <c r="D4" t="n">
         <v>3.1</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46071.4</v>
+        <v>46072.5236111111</v>
       </c>
       <c r="F4" t="n">
-        <v>30.5</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>0.174</v>
+        <v>0.154</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46070.6486111111</v>
+        <v>46071.3876736111</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46070.6548611111</v>
+        <v>46071.4088541667</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46070.6506944444</v>
+        <v>46071.4</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>30.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1.194</v>
+        <v>0.174</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="s">
         <v>17</v>
@@ -709,40 +709,40 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46069.4486111111</v>
+        <v>46070.6486111111</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46069.4833333333</v>
+        <v>46070.6548611111</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46069.4729166667</v>
+        <v>46070.6506944444</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>0.094</v>
+        <v>1.194</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -750,40 +750,40 @@
         <v>13</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46069.3868055556</v>
+        <v>46069.4486111111</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46069.4</v>
+        <v>46069.4833333333</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46069.3888888889</v>
+        <v>46069.4729166667</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>0.968</v>
+        <v>0.094</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I7" t="n">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -815,10 +815,10 @@
         <v>48</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -856,10 +856,10 @@
         <v>52</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -897,7 +897,7 @@
         <v>43</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
         <v>0.2</v>
@@ -938,10 +938,10 @@
         <v>13</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -979,10 +979,10 @@
         <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -1020,10 +1020,10 @@
         <v>44</v>
       </c>
       <c r="J13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.2</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -1061,16 +1061,16 @@
         <v>12</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -1102,7 +1102,7 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="K15" t="n">
         <v>0.1</v>
@@ -1143,7 +1143,7 @@
         <v>33</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K16" t="n">
         <v>0.3</v>
@@ -1184,10 +1184,10 @@
         <v>9</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -1225,7 +1225,7 @@
         <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K18" t="n">
         <v>0.4</v>
@@ -1426,10 +1426,10 @@
         <v>14</v>
       </c>
       <c r="G2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.2</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -1455,7 +1455,7 @@
         <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H3" t="n">
         <v>0.2</v>
@@ -1484,7 +1484,7 @@
         <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H4" t="n">
         <v>0.4</v>
@@ -1513,13 +1513,13 @@
         <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -1542,10 +1542,10 @@
         <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -1571,10 +1571,10 @@
         <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I7" t="s">
         <v>15</v>
@@ -1600,7 +1600,7 @@
         <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H8" t="n">
         <v>0.6</v>
@@ -1629,7 +1629,7 @@
         <v>14</v>
       </c>
       <c r="G9" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="H9" t="n">
         <v>1.5</v>
@@ -1672,28 +1672,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46069.3868055556</v>
+        <v>46069.2819444444</v>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.968</v>
+        <v>0.199</v>
       </c>
       <c r="F11" t="s">
         <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2</v>
+        <v>3.4</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="I11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -1701,25 +1701,25 @@
         <v>13</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46069.2819444444</v>
+        <v>46081.2034722222</v>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D12" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.199</v>
+        <v>0.1</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="I12" t="s">
         <v>15</v>
@@ -1730,25 +1730,25 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46081.2034722222</v>
+        <v>46111.0972222222</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1</v>
+        <v>0.774</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
@@ -1774,10 +1774,10 @@
         <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="I14" t="s">
         <v>15</v>
@@ -1803,7 +1803,7 @@
         <v>14</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H15" t="n">
         <v>0.3</v>
@@ -1832,10 +1832,10 @@
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="I16" t="s">
         <v>15</v>
@@ -1861,10 +1861,10 @@
         <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I17" t="s">
         <v>15</v>
@@ -1890,7 +1890,7 @@
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H18" t="n">
         <v>0.1</v>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -61,13 +61,13 @@
     <t xml:space="preserve">Sturzflut-Ereignis</t>
   </si>
   <si>
+    <t xml:space="preserve">Level 0 – Kein nennenswerter Regen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Level 1 – Leichter Regen (0.5–15 mm/h)</t>
   </si>
   <si>
     <t xml:space="preserve">Wasserbaulabor_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level 0 – Kein nennenswerter Regen</t>
   </si>
   <si>
     <t xml:space="preserve">Regenereignis / Natürlich</t>
@@ -147,8 +147,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M18" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M19" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M19"/>
   <tableColumns count="13">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -185,8 +185,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:I18" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:I19" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I19"/>
   <tableColumns count="9">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -545,34 +545,34 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46111.0972222222</v>
+        <v>46114.5555555556</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46111.1034722222</v>
+        <v>46114.5847222222</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4</v>
+        <v>17.3</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46111.0993055556</v>
+        <v>46114.5805555556</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>0.774</v>
+        <v>0.479</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4</v>
+        <v>0.1</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
@@ -586,40 +586,40 @@
         <v>13</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46081.2034722222</v>
+        <v>46111.0972222222</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46081.2305555556</v>
+        <v>46111.1034722222</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46081.2215277778</v>
+        <v>46111.0993055556</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1</v>
+        <v>0.774</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -627,122 +627,122 @@
         <v>13</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46072.5097222222</v>
+        <v>46081.2034722222</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46072.5354166667</v>
+        <v>46081.2305555556</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46072.5236111111</v>
+        <v>46081.2215277778</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>0.154</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46071.3876736111</v>
+        <v>46072.5097222222</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46071.4088541667</v>
+        <v>46072.5354166667</v>
       </c>
       <c r="D5" t="n">
         <v>3.1</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46071.4</v>
+        <v>46072.5236111111</v>
       </c>
       <c r="F5" t="n">
-        <v>30.5</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>0.174</v>
+        <v>0.154</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
       </c>
       <c r="I5" t="n">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46070.6486111111</v>
+        <v>46071.3876736111</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46070.6548611111</v>
+        <v>46071.4088541667</v>
       </c>
       <c r="D6" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46070.6506944444</v>
+        <v>46071.4</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>30.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1.194</v>
+        <v>0.174</v>
       </c>
       <c r="H6" t="s">
         <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -750,34 +750,34 @@
         <v>13</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46069.4486111111</v>
+        <v>46070.6486111111</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46069.4833333333</v>
+        <v>46070.6548611111</v>
       </c>
       <c r="D7" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46069.4729166667</v>
+        <v>46070.6506944444</v>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>0.094</v>
+        <v>1.194</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I7" t="n">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -791,40 +791,40 @@
         <v>13</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46069.2819444444</v>
+        <v>46069.4486111111</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46069.2979166667</v>
+        <v>46069.4833333333</v>
       </c>
       <c r="D8" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46069.2916666667</v>
+        <v>46069.4729166667</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>0.199</v>
+        <v>0.094</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I8" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -832,40 +832,40 @@
         <v>13</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46065.5597222222</v>
+        <v>46069.2819444444</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46065.5770833333</v>
+        <v>46069.2979166667</v>
       </c>
       <c r="D9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46069.2916666667</v>
+      </c>
+      <c r="F9" t="n">
+        <v>23</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" t="n">
+        <v>48</v>
+      </c>
+      <c r="J9" t="n">
         <v>3.4</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46065.56875</v>
-      </c>
-      <c r="F9" t="n">
-        <v>25</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="H9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" t="n">
-        <v>52</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.9</v>
-      </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -873,40 +873,40 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46038.7298611111</v>
+        <v>46065.5597222222</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46038.7590277778</v>
+        <v>46065.5770833333</v>
       </c>
       <c r="D10" t="n">
-        <v>23.7</v>
+        <v>3.4</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46038.7513888889</v>
+        <v>46065.56875</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>0.762</v>
+        <v>0.26</v>
       </c>
       <c r="H10" t="s">
         <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -914,34 +914,34 @@
         <v>13</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46034.8673611111</v>
+        <v>46038.7298611111</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46034.8770833333</v>
+        <v>46038.7590277778</v>
       </c>
       <c r="D11" t="n">
-        <v>2.3</v>
+        <v>23.7</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46034.8708333333</v>
+        <v>46038.7513888889</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>0.451</v>
+        <v>0.762</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="J11" t="n">
-        <v>6.3</v>
+        <v>0.6</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -955,40 +955,40 @@
         <v>13</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46031.5666666667</v>
+        <v>46034.8673611111</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46031.5923611111</v>
+        <v>46034.8770833333</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46031.5798611111</v>
+        <v>46034.8708333333</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.105</v>
+        <v>0.451</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7</v>
+        <v>6.3</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -996,72 +996,72 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46010.6055555556</v>
+        <v>46031.5666666667</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46010.6354166667</v>
+        <v>46031.5923611111</v>
       </c>
       <c r="D13" t="n">
-        <v>34.9</v>
+        <v>2</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46010.6229166667</v>
+        <v>46031.5798611111</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G13" t="n">
-        <v>1.39</v>
+        <v>0.105</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I13" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>45985.5916666667</v>
+        <v>46010.6055555556</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45985.6</v>
+        <v>46010.6354166667</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2</v>
+        <v>34.9</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>45985.5965277778</v>
+        <v>46010.6229166667</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="G14" t="n">
-        <v>0.592</v>
+        <v>1.39</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="n">
         <v>0.3</v>
@@ -1070,48 +1070,48 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>45980.5256944444</v>
+        <v>45985.5916666667</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45980.5625</v>
+        <v>45985.6</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>45980.5395833333</v>
+        <v>45985.5965277778</v>
       </c>
       <c r="F15" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1</v>
+        <v>0.592</v>
       </c>
       <c r="H15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -1119,40 +1119,40 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>45979.7826388889</v>
+        <v>45980.5256944444</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45979.80625</v>
+        <v>45980.5625</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>45979.7847222222</v>
+        <v>45980.5395833333</v>
       </c>
       <c r="F16" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>0.742</v>
+        <v>0.1</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I16" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -1160,34 +1160,34 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>45962.5118055556</v>
+        <v>45979.7826388889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45962.5340277778</v>
+        <v>45979.80625</v>
       </c>
       <c r="D17" t="n">
         <v>2.3</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>45962.5270833333</v>
+        <v>45979.7847222222</v>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G17" t="n">
-        <v>0.104</v>
+        <v>0.742</v>
       </c>
       <c r="H17" t="s">
         <v>14</v>
       </c>
       <c r="I17" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -1201,40 +1201,81 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="n">
+        <v>45962.5118055556</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>45962.5340277778</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>45962.5270833333</v>
+      </c>
+      <c r="F18" t="n">
+        <v>32</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="H18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="1" t="n">
         <v>45953.2340277778</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C19" s="1" t="n">
         <v>45953.2465277778</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D19" t="n">
         <v>5.2</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E19" s="1" t="n">
         <v>45953.2388888889</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>18</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G19" t="n">
         <v>0.732</v>
       </c>
-      <c r="H18" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="H19" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" t="n">
         <v>6</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J19" t="n">
         <v>0.9</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K19" t="n">
         <v>0.4</v>
       </c>
-      <c r="L18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" t="s">
-        <v>17</v>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1288,16 +1329,16 @@
         <v>13</v>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="D2" t="n">
         <v>34.9</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
@@ -1308,7 +1349,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -1432,7 +1473,7 @@
         <v>0.3</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1461,7 +1502,7 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -1469,86 +1510,86 @@
         <v>13</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>45953.2340277778</v>
+        <v>46114.5555555556</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2</v>
+        <v>17.3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.732</v>
+        <v>0.479</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>45985.5916666667</v>
+        <v>45953.2340277778</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.592</v>
+        <v>0.732</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46070.6486111111</v>
+        <v>45985.5916666667</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="E6" t="n">
-        <v>1.194</v>
+        <v>0.592</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -1556,25 +1597,25 @@
         <v>13</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46065.5597222222</v>
+        <v>46070.6486111111</v>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.26</v>
+        <v>1.194</v>
       </c>
       <c r="F7" t="s">
         <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I7" t="s">
         <v>15</v>
@@ -1585,28 +1626,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46069.4486111111</v>
+        <v>46065.5597222222</v>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="E8" t="n">
-        <v>0.094</v>
+        <v>0.26</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -1614,83 +1655,83 @@
         <v>13</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46072.5097222222</v>
+        <v>46069.4486111111</v>
       </c>
       <c r="C9" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="E9" t="n">
-        <v>0.154</v>
+        <v>0.094</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46071.3876736111</v>
+        <v>46072.5097222222</v>
       </c>
       <c r="C10" t="n">
-        <v>30.5</v>
+        <v>37</v>
       </c>
       <c r="D10" t="n">
         <v>3.1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.174</v>
+        <v>0.154</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46069.2819444444</v>
+        <v>46071.3876736111</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>30.5</v>
       </c>
       <c r="D11" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.199</v>
+        <v>0.174</v>
       </c>
       <c r="F11" t="s">
         <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
@@ -1701,28 +1742,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46081.2034722222</v>
+        <v>46069.2819444444</v>
       </c>
       <c r="C12" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1</v>
+        <v>0.199</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -1730,28 +1771,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46111.0972222222</v>
+        <v>46081.2034722222</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E13" t="n">
-        <v>0.774</v>
+        <v>0.1</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -1759,28 +1800,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46034.8673611111</v>
+        <v>46111.0972222222</v>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="E14" t="n">
-        <v>0.451</v>
+        <v>0.774</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>6.3</v>
+        <v>2.4</v>
       </c>
       <c r="H14" t="n">
         <v>2.2</v>
       </c>
       <c r="I14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -1788,28 +1829,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>45979.7826388889</v>
+        <v>46034.8673611111</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
         <v>2.3</v>
       </c>
       <c r="E15" t="n">
-        <v>0.742</v>
+        <v>0.451</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3</v>
+        <v>6.3</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -1817,25 +1858,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>45962.5118055556</v>
+        <v>45979.7826388889</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
         <v>2.3</v>
       </c>
       <c r="E16" t="n">
-        <v>0.104</v>
+        <v>0.742</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="I16" t="s">
         <v>15</v>
@@ -1846,28 +1887,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46031.5666666667</v>
+        <v>45962.5118055556</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="E17" t="n">
-        <v>0.105</v>
+        <v>0.104</v>
       </c>
       <c r="F17" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="I17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1875,28 +1916,57 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>45980.5256944444</v>
+        <v>46031.5666666667</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
       </c>
       <c r="G18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>45980.5256944444</v>
+      </c>
+      <c r="C19" t="n">
+        <v>53</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.1</v>
       </c>
-      <c r="H18" t="n">
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="n">
         <v>0.1</v>
       </c>
-      <c r="I18" t="s">
-        <v>17</v>
+      <c r="H19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -55,25 +55,34 @@
     <t xml:space="preserve">dwd_risk_level</t>
   </si>
   <si>
+    <t xml:space="preserve">Wasserstraße_Springorum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 0 – Kein nennenswerter Regen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Herzogstraße</t>
   </si>
   <si>
     <t xml:space="preserve">Sturzflut-Ereignis</t>
   </si>
   <si>
-    <t xml:space="preserve">Level 0 – Kein nennenswerter Regen</t>
+    <t xml:space="preserve">Königsallee_Springorum</t>
   </si>
   <si>
     <t xml:space="preserve">Level 1 – Leichter Regen (0.5–15 mm/h)</t>
   </si>
   <si>
-    <t xml:space="preserve">Wasserbaulabor_2</t>
+    <t xml:space="preserve">An_der_Kost</t>
   </si>
   <si>
     <t xml:space="preserve">Regenereignis / Natürlich</t>
   </si>
   <si>
-    <t xml:space="preserve">Wasserstraße_Springorum</t>
+    <t xml:space="preserve">Wasserbaulabor_2</t>
   </si>
   <si>
     <t xml:space="preserve">Ereignisse</t>
@@ -147,8 +156,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M19" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M79" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M79"/>
   <tableColumns count="13">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -169,8 +178,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:G4" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:G4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:G6" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:G6"/>
   <tableColumns count="7">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="Ereignisse"/>
@@ -185,8 +194,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:I19" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:I21" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I21"/>
   <tableColumns count="9">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -491,7 +500,7 @@
     <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="12.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="19.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="26.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="39.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="12.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="15.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
@@ -545,28 +554,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46114.5555555556</v>
+        <v>46116.6305555556</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46114.5847222222</v>
+        <v>46116.6503472222</v>
       </c>
       <c r="D2" t="n">
-        <v>17.3</v>
+        <v>0.6</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46114.5805555556</v>
+        <v>46116.6420138889</v>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>28.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.479</v>
+        <v>0.036</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
         <v>0.1</v>
@@ -586,160 +595,160 @@
         <v>13</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46111.0972222222</v>
+        <v>46114.8559027778</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46111.1034722222</v>
+        <v>46114.8770833333</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46111.0993055556</v>
+        <v>46114.865625</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>30.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.774</v>
+        <v>0.05</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46081.2034722222</v>
+        <v>46114.5555555556</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46081.2305555556</v>
+        <v>46114.5847222222</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6</v>
+        <v>17.3</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46081.2215277778</v>
+        <v>46114.5805555556</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="n">
+        <v>43</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.1</v>
       </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" t="n">
-        <v>20</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.6</v>
-      </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46072.5097222222</v>
+        <v>46110.1208333333</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46072.5354166667</v>
+        <v>46110.1395833333</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46072.5236111111</v>
+        <v>46110.1336805556</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>0.154</v>
+        <v>0.032</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
       </c>
       <c r="I5" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46071.3876736111</v>
+        <v>46106.290625</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46071.4088541667</v>
+        <v>46106.3069444444</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46071.4</v>
+        <v>46106.2989583333</v>
       </c>
       <c r="F6" t="n">
-        <v>30.5</v>
+        <v>23.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.174</v>
+        <v>0.066</v>
       </c>
       <c r="H6" t="s">
         <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>206</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="s">
         <v>15</v>
@@ -747,75 +756,75 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46070.6486111111</v>
+        <v>46095.1454861111</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46070.6548611111</v>
+        <v>46095.1604166667</v>
       </c>
       <c r="D7" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46070.6506944444</v>
+        <v>46095.1572916667</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>21.5</v>
       </c>
       <c r="G7" t="n">
-        <v>1.194</v>
+        <v>0.047</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46069.4486111111</v>
+        <v>46095.0517361111</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46069.4833333333</v>
+        <v>46095.0909722222</v>
       </c>
       <c r="D8" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46069.4729166667</v>
+        <v>46095.059375</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>56.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.094</v>
+        <v>0.081</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I8" t="n">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="K8" t="n">
         <v>0.6</v>
@@ -824,457 +833,2917 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46069.2819444444</v>
+        <v>46094.8979166667</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46069.2979166667</v>
+        <v>46094.9368055556</v>
       </c>
       <c r="D9" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46069.2916666667</v>
+        <v>46094.9322916667</v>
       </c>
       <c r="F9" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>0.199</v>
+        <v>0.014</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46065.5597222222</v>
+        <v>46094.6888888889</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46065.5770833333</v>
+        <v>46094.7201388889</v>
       </c>
       <c r="D10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46094.7069444444</v>
+      </c>
+      <c r="F10" t="n">
+        <v>45</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.4</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46065.56875</v>
-      </c>
-      <c r="F10" t="n">
-        <v>25</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="H10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" t="n">
-        <v>52</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.9</v>
-      </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46038.7298611111</v>
+        <v>46094.553125</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46038.7590277778</v>
+        <v>46094.5690972222</v>
       </c>
       <c r="D11" t="n">
-        <v>23.7</v>
+        <v>0.7</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46038.7513888889</v>
+        <v>46094.5559027778</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="G11" t="n">
-        <v>0.762</v>
+        <v>0.171</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46034.8673611111</v>
+        <v>46080.9958333333</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46034.8770833333</v>
+        <v>46081.0083333333</v>
       </c>
       <c r="D12" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46034.8708333333</v>
+        <v>46081.0013888889</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>0.451</v>
+        <v>0.074</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>6.3</v>
+        <v>1.2</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46031.5666666667</v>
+        <v>46076.9986111111</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46031.5923611111</v>
+        <v>46077.0152777778</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46031.5798611111</v>
+        <v>46077.0048611111</v>
       </c>
       <c r="F13" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G13" t="n">
-        <v>0.105</v>
+        <v>0.066</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46010.6055555556</v>
+        <v>46076.9590277778</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46010.6354166667</v>
+        <v>46076.9743055556</v>
       </c>
       <c r="D14" t="n">
-        <v>34.9</v>
+        <v>0.6</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46010.6229166667</v>
+        <v>46076.9666666667</v>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>1.39</v>
+        <v>0.054</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
       </c>
       <c r="I14" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>45985.5916666667</v>
+        <v>46075.9055555556</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45985.6</v>
+        <v>46075.9236111111</v>
       </c>
       <c r="D15" t="n">
         <v>4.2</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>45985.5965277778</v>
+        <v>46075.9138888889</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>0.592</v>
+        <v>0.347</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K15" t="n">
         <v>0.8</v>
       </c>
-      <c r="K15" t="n">
-        <v>0.3</v>
-      </c>
       <c r="L15" t="b">
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>45980.5256944444</v>
+        <v>46072.5090277778</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45980.5625</v>
+        <v>46072.5354166667</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>45980.5395833333</v>
+        <v>46072.5236111111</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1</v>
+        <v>0.147</v>
       </c>
       <c r="H16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>45979.7826388889</v>
+        <v>46072.45625</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45979.80625</v>
+        <v>46072.4736111111</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>45979.7847222222</v>
+        <v>46072.4631944444</v>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G17" t="n">
-        <v>0.742</v>
+        <v>0.059</v>
       </c>
       <c r="H17" t="s">
         <v>14</v>
       </c>
       <c r="I17" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>45962.5118055556</v>
+        <v>46072.4020833333</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45962.5340277778</v>
+        <v>46072.4097222222</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>45962.5270833333</v>
+        <v>46072.4076388889</v>
       </c>
       <c r="F18" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
-        <v>0.104</v>
+        <v>0.58</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46071.0847222222</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>46071.1173611111</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46071.1104166667</v>
+      </c>
+      <c r="F19" t="n">
+        <v>47</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="H19" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" t="n">
+        <v>70</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46070.6472222222</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>46070.6548611111</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46070.6506944444</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="H20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" t="n">
+        <v>24</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>46069.4486111111</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>46069.4833333333</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46069.4729166667</v>
+      </c>
+      <c r="F21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="H21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" t="n">
+        <v>102</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>46068.9430555556</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>46068.9555555556</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46068.9527777778</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="H22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>46067.4930555556</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>46067.50625</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46067.4958333333</v>
+      </c>
+      <c r="F23" t="n">
+        <v>19</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="H23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L23" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>46065.5520833333</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>46065.5770833333</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46065.56875</v>
+      </c>
+      <c r="F24" t="n">
+        <v>36</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="H24" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" t="n">
+        <v>62</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46056.6743055556</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>46056.7125</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46056.6763888889</v>
+      </c>
+      <c r="F25" t="n">
+        <v>55</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="H25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" t="n">
+        <v>14</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>46046.1458333333</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>46046.1729166667</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46046.1555555556</v>
+      </c>
+      <c r="F26" t="n">
+        <v>39</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="H26" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" t="n">
+        <v>62</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>46038.7298611111</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>46038.7590277778</v>
+      </c>
+      <c r="D27" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46038.7513888889</v>
+      </c>
+      <c r="F27" t="n">
+        <v>42</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="H27" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" t="n">
+        <v>43</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>46037.1930555556</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>46037.2333333333</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46037.2048611111</v>
+      </c>
+      <c r="F28" t="n">
+        <v>58</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="H28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>46036.4458333333</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>46036.4875</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46036.4493055556</v>
+      </c>
+      <c r="F29" t="n">
+        <v>60</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="H29" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" t="n">
+        <v>46</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="1" t="n">
-        <v>45953.2340277778</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>45953.2465277778</v>
-      </c>
-      <c r="D19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>45953.2388888889</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="B30" s="1" t="n">
+        <v>46034.2236111111</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>46034.2520833333</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46034.2326388889</v>
+      </c>
+      <c r="F30" t="n">
+        <v>41</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="H30" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" t="n">
+        <v>8</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>46031.6548611111</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>46031.6736111111</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46031.6597222222</v>
+      </c>
+      <c r="F31" t="n">
+        <v>27</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.085</v>
+      </c>
+      <c r="H31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>46031.4881944444</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>46031.5034722222</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46031.4965277778</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H32" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>46026.2631944444</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>46026.2770833333</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46026.2659722222</v>
+      </c>
+      <c r="F33" t="n">
+        <v>20</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="H33" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" t="n">
+        <v>21</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>46010.6055555556</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46010.6354166667</v>
+      </c>
+      <c r="D34" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46010.6229166667</v>
+      </c>
+      <c r="F34" t="n">
+        <v>43</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H34" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" t="n">
+        <v>44</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
         <v>18</v>
       </c>
-      <c r="G19" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="H19" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="B35" s="1" t="n">
+        <v>46010.3430555556</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46010.3534722222</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46010.3479166667</v>
+      </c>
+      <c r="F35" t="n">
+        <v>15</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="H35" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" t="n">
+        <v>8</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>46001.1465277778</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46001.1597222222</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46001.1506944444</v>
+      </c>
+      <c r="F36" t="n">
+        <v>19</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="H36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" t="n">
+        <v>11</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>45999.9777777778</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46000.00625</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>45999.9875</v>
+      </c>
+      <c r="F37" t="n">
+        <v>41</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="H37" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" t="n">
+        <v>27</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L37" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>45998.8833333333</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>45998.9118055556</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>45998.8979166667</v>
+      </c>
+      <c r="F38" t="n">
+        <v>41</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="H38" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" t="n">
+        <v>5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L38" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>45994.9763888889</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>45995.0069444444</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="F39" t="n">
+        <v>44</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="H39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" t="n">
+        <v>8</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L39" t="b">
+        <v>1</v>
+      </c>
+      <c r="M39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>45993.1833333333</v>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>45993.2048611111</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>45993.1923611111</v>
+      </c>
+      <c r="F40" t="n">
+        <v>31</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="H40" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" t="n">
+        <v>8</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L40" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>45991.2326388889</v>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>45991.2395833333</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>45991.2375</v>
+      </c>
+      <c r="F41" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="H41" t="s">
+        <v>14</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L41" t="b">
+        <v>1</v>
+      </c>
+      <c r="M41" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>45989.3763888889</v>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>45989.4041666667</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>45989.3993055556</v>
+      </c>
+      <c r="F42" t="n">
+        <v>40</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="H42" t="s">
+        <v>14</v>
+      </c>
+      <c r="I42" t="n">
+        <v>13</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L42" t="b">
+        <v>1</v>
+      </c>
+      <c r="M42" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>45986.3493055556</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>45986.3743055556</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>45986.3645833333</v>
+      </c>
+      <c r="F43" t="n">
+        <v>36</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="H43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L43" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>16</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>45986.0444444444</v>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>45986.05</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>45986.0479166667</v>
+      </c>
+      <c r="F44" t="n">
+        <v>8</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="H44" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" t="n">
+        <v>7</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>45985.60625</v>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>45985.6340277778</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>45985.6305555556</v>
+      </c>
+      <c r="F45" t="n">
+        <v>40</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="H45" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" t="n">
+        <v>10</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L45" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>45985.5916666667</v>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>45985.6</v>
+      </c>
+      <c r="D46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>45985.5965277778</v>
+      </c>
+      <c r="F46" t="n">
+        <v>12</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="H46" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" t="n">
+        <v>12</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L46" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>45980.9888888889</v>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>45981.0069444444</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>45981.0027777778</v>
+      </c>
+      <c r="F47" t="n">
+        <v>26</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H47" t="s">
+        <v>14</v>
+      </c>
+      <c r="I47" t="n">
+        <v>9</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L47" t="b">
+        <v>1</v>
+      </c>
+      <c r="M47" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>45980.9451388889</v>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>45980.9715277778</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>45980.9486111111</v>
+      </c>
+      <c r="F48" t="n">
+        <v>38</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="H48" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" t="n">
+        <v>12</v>
+      </c>
+      <c r="J48" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L48" t="b">
+        <v>1</v>
+      </c>
+      <c r="M48" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>45977.8520833333</v>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>45977.8861111111</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>45977.8638888889</v>
+      </c>
+      <c r="F49" t="n">
+        <v>49</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="H49" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" t="n">
         <v>6</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J49" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L49" t="b">
+        <v>1</v>
+      </c>
+      <c r="M49" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>45970.6055555556</v>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>45970.6333333333</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>45970.6284722222</v>
+      </c>
+      <c r="F50" t="n">
+        <v>40</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="H50" t="s">
+        <v>14</v>
+      </c>
+      <c r="I50" t="n">
+        <v>5</v>
+      </c>
+      <c r="J50" t="n">
         <v>0.9</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K50" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L50" t="b">
+        <v>1</v>
+      </c>
+      <c r="M50" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>45962.6513888889</v>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>45962.6715277778</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>45962.6583333333</v>
+      </c>
+      <c r="F51" t="n">
+        <v>29</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="H51" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2</v>
+      </c>
+      <c r="L51" t="b">
+        <v>1</v>
+      </c>
+      <c r="M51" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>45960.3222222222</v>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>45960.3430555556</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>45960.3319444444</v>
+      </c>
+      <c r="F52" t="n">
+        <v>30</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="H52" t="s">
+        <v>14</v>
+      </c>
+      <c r="I52" t="n">
+        <v>8</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L52" t="b">
+        <v>1</v>
+      </c>
+      <c r="M52" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>16</v>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>45958.5965277778</v>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>45958.6138888889</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>45958.6055555556</v>
+      </c>
+      <c r="F53" t="n">
+        <v>25</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="H53" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" t="n">
+        <v>8</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L53" t="b">
+        <v>1</v>
+      </c>
+      <c r="M53" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>45958.3965277778</v>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>45958.4298611111</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>45958.4201388889</v>
+      </c>
+      <c r="F54" t="n">
+        <v>48</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="H54" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54" t="n">
+        <v>10</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L54" t="b">
+        <v>1</v>
+      </c>
+      <c r="M54" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>16</v>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>45958.3354166667</v>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>45958.3555555556</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>45958.3513888889</v>
+      </c>
+      <c r="F55" t="n">
+        <v>29</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="H55" t="s">
+        <v>14</v>
+      </c>
+      <c r="I55" t="n">
+        <v>10</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L55" t="b">
+        <v>1</v>
+      </c>
+      <c r="M55" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>16</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>45958.3041666667</v>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>45958.3180555556</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>45958.3152777778</v>
+      </c>
+      <c r="F56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="H56" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" t="n">
+        <v>5</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L56" t="b">
+        <v>1</v>
+      </c>
+      <c r="M56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>45957.4340277778</v>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>45957.4534722222</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>45957.4451388889</v>
+      </c>
+      <c r="F57" t="n">
+        <v>28</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="H57" t="s">
+        <v>14</v>
+      </c>
+      <c r="I57" t="n">
+        <v>12</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L57" t="b">
+        <v>1</v>
+      </c>
+      <c r="M57" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>20</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>45957.1083333333</v>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>45957.1243055556</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>45957.1180555556</v>
+      </c>
+      <c r="F58" t="n">
+        <v>23</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="H58" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" t="n">
+        <v>9</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L58" t="b">
+        <v>1</v>
+      </c>
+      <c r="M58" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>16</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>45956.5763888889</v>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>45956.5909722222</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>45956.5875</v>
+      </c>
+      <c r="F59" t="n">
+        <v>21</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="H59" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" t="n">
+        <v>15</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L59" t="b">
+        <v>1</v>
+      </c>
+      <c r="M59" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>16</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>45953.7131944444</v>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>45953.7277777778</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>45953.7222222222</v>
+      </c>
+      <c r="F60" t="n">
+        <v>21</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="H60" t="s">
+        <v>14</v>
+      </c>
+      <c r="I60" t="n">
+        <v>10</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L60" t="b">
+        <v>1</v>
+      </c>
+      <c r="M60" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>20</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>45953.7097222222</v>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>45953.7395833333</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>45953.7201388889</v>
+      </c>
+      <c r="F61" t="n">
+        <v>43</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="H61" t="s">
+        <v>14</v>
+      </c>
+      <c r="I61" t="n">
+        <v>20</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L61" t="b">
+        <v>1</v>
+      </c>
+      <c r="M61" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>16</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>45953.5881944444</v>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>45953.5986111111</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>45953.5909722222</v>
+      </c>
+      <c r="F62" t="n">
+        <v>15</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="H62" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62" t="n">
+        <v>4</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L62" t="b">
+        <v>1</v>
+      </c>
+      <c r="M62" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>16</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>45953.1763888889</v>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>45953.2020833333</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>45953.1895833333</v>
+      </c>
+      <c r="F63" t="n">
+        <v>37</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="H63" t="s">
+        <v>17</v>
+      </c>
+      <c r="I63" t="n">
+        <v>20</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L63" t="b">
+        <v>1</v>
+      </c>
+      <c r="M63" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>45951.2659722222</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>45951.2895833333</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>45951.2680555556</v>
+      </c>
+      <c r="F64" t="n">
+        <v>34</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="H64" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64" t="n">
+        <v>4</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" t="b">
+        <v>1</v>
+      </c>
+      <c r="M64" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>13</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>45948.1659722222</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>45948.2069444444</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>45948.1777777778</v>
+      </c>
+      <c r="F65" t="n">
+        <v>59</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="H65" t="s">
+        <v>21</v>
+      </c>
+      <c r="I65" t="n">
+        <v>5</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L65" t="b">
+        <v>1</v>
+      </c>
+      <c r="M65" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>45948.1201388889</v>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>45948.1409722222</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E66" s="1" t="n">
+        <v>45948.1368055556</v>
+      </c>
+      <c r="F66" t="n">
+        <v>30</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="H66" t="s">
+        <v>14</v>
+      </c>
+      <c r="I66" t="n">
+        <v>5</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L66" t="b">
+        <v>1</v>
+      </c>
+      <c r="M66" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>13</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>45948.0152777778</v>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>45948.0430555556</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>45948.0243055556</v>
+      </c>
+      <c r="F67" t="n">
+        <v>40</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="H67" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L67" t="b">
+        <v>1</v>
+      </c>
+      <c r="M67" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>18</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>45946.8027777778</v>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>45946.8180555556</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E68" s="1" t="n">
+        <v>45946.8159722222</v>
+      </c>
+      <c r="F68" t="n">
+        <v>22</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="H68" t="s">
+        <v>14</v>
+      </c>
+      <c r="I68" t="n">
+        <v>4</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L68" t="b">
+        <v>1</v>
+      </c>
+      <c r="M68" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>18</v>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>45946.6076388889</v>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>45946.6354166667</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E69" s="1" t="n">
+        <v>45946.6194444444</v>
+      </c>
+      <c r="F69" t="n">
+        <v>40</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="H69" t="s">
+        <v>14</v>
+      </c>
+      <c r="I69" t="n">
+        <v>7</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L69" t="b">
+        <v>1</v>
+      </c>
+      <c r="M69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>13</v>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>45943.0444444444</v>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>45943.0583333333</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="1" t="n">
+        <v>45943.0555555556</v>
+      </c>
+      <c r="F70" t="n">
+        <v>20</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="H70" t="s">
+        <v>14</v>
+      </c>
+      <c r="I70" t="n">
+        <v>3</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L70" t="b">
+        <v>1</v>
+      </c>
+      <c r="M70" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>13</v>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>45942.2895833333</v>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>45942.3166666667</v>
+      </c>
+      <c r="D71" t="n">
+        <v>5</v>
+      </c>
+      <c r="E71" s="1" t="n">
+        <v>45942.3048611111</v>
+      </c>
+      <c r="F71" t="n">
+        <v>39</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="H71" t="s">
+        <v>17</v>
+      </c>
+      <c r="I71" t="n">
+        <v>12</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L71" t="b">
+        <v>1</v>
+      </c>
+      <c r="M71" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>18</v>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>45939.2444444444</v>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>45939.2652777778</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E72" s="1" t="n">
+        <v>45939.2548611111</v>
+      </c>
+      <c r="F72" t="n">
+        <v>30</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H72" t="s">
+        <v>14</v>
+      </c>
+      <c r="I72" t="n">
+        <v>7</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
         <v>0.4</v>
       </c>
-      <c r="L19" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" t="s">
+      <c r="L72" t="b">
+        <v>1</v>
+      </c>
+      <c r="M72" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>18</v>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>45939.1743055556</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>45939.1833333333</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>45939.1763888889</v>
+      </c>
+      <c r="F73" t="n">
+        <v>13</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="H73" t="s">
+        <v>14</v>
+      </c>
+      <c r="I73" t="n">
+        <v>6</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L73" t="b">
+        <v>1</v>
+      </c>
+      <c r="M73" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>16</v>
+      </c>
+      <c r="B74" s="1" t="n">
+        <v>45933.9763888889</v>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>45933.9902777778</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E74" s="1" t="n">
+        <v>45933.98125</v>
+      </c>
+      <c r="F74" t="n">
+        <v>20</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="H74" t="s">
+        <v>14</v>
+      </c>
+      <c r="I74" t="n">
+        <v>13</v>
+      </c>
+      <c r="J74" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L74" t="b">
+        <v>1</v>
+      </c>
+      <c r="M74" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>45930.2208333333</v>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>45930.2513888889</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" s="1" t="n">
+        <v>45930.2375</v>
+      </c>
+      <c r="F75" t="n">
+        <v>44</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="H75" t="s">
+        <v>17</v>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L75" t="b">
+        <v>1</v>
+      </c>
+      <c r="M75" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>13</v>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>45925.4902777778</v>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>45925.5319444444</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>45925.5201388889</v>
+      </c>
+      <c r="F76" t="n">
+        <v>60</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="H76" t="s">
+        <v>14</v>
+      </c>
+      <c r="I76" t="n">
+        <v>10</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L76" t="b">
+        <v>1</v>
+      </c>
+      <c r="M76" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>18</v>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>45921.4229166667</v>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>45921.4423611111</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>45921.4284722222</v>
+      </c>
+      <c r="F77" t="n">
+        <v>28</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="H77" t="s">
+        <v>14</v>
+      </c>
+      <c r="I77" t="n">
+        <v>5</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L77" t="b">
+        <v>1</v>
+      </c>
+      <c r="M77" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>13</v>
+      </c>
+      <c r="B78" s="1" t="n">
+        <v>45921.2979166667</v>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>45921.3111111111</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>45921.3034722222</v>
+      </c>
+      <c r="F78" t="n">
+        <v>19</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="H78" t="s">
+        <v>14</v>
+      </c>
+      <c r="I78" t="n">
+        <v>8</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L78" t="b">
+        <v>1</v>
+      </c>
+      <c r="M78" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>45710.3541666667</v>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>45710.3854166667</v>
+      </c>
+      <c r="D79" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>45710.375</v>
+      </c>
+      <c r="F79" t="n">
+        <v>45</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="H79" t="s">
+        <v>17</v>
+      </c>
+      <c r="I79" t="n">
+        <v>4</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="b">
+        <v>0</v>
+      </c>
+      <c r="M79" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1306,42 +3775,42 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="D2" t="n">
-        <v>34.9</v>
+        <v>1.2</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1349,22 +3818,22 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1</v>
+        <v>34.9</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1372,24 +3841,70 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1412,7 +3927,7 @@
     <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="19.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="26.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="39.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="18.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="42.71" hidden="0" customWidth="1"/>
@@ -1449,7 +3964,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>46010.6055555556</v>
@@ -1464,7 +3979,7 @@
         <v>1.39</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G2" t="n">
         <v>0.6</v>
@@ -1478,7 +3993,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>46038.7298611111</v>
@@ -1493,7 +4008,7 @@
         <v>0.762</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
         <v>0.6</v>
@@ -1507,28 +4022,28 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46114.5555555556</v>
+        <v>45710.3541666667</v>
       </c>
       <c r="C4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D4" t="n">
-        <v>17.3</v>
+        <v>19.6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.479</v>
+        <v>0.651</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="s">
         <v>15</v>
@@ -1536,28 +4051,28 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>45953.2340277778</v>
+        <v>46114.5555555556</v>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D5" t="n">
-        <v>5.2</v>
+        <v>17.3</v>
       </c>
       <c r="E5" t="n">
-        <v>0.732</v>
+        <v>0.479</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="I5" t="s">
         <v>15</v>
@@ -1565,28 +4080,28 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>45985.5916666667</v>
+        <v>45942.2895833333</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="D6" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.592</v>
+        <v>0.226</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I6" t="s">
         <v>15</v>
@@ -1594,31 +4109,31 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46070.6486111111</v>
+        <v>46072.4020833333</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="E7" t="n">
-        <v>1.194</v>
+        <v>0.58</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -1626,57 +4141,57 @@
         <v>13</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46065.5597222222</v>
+        <v>45948.1659722222</v>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="D8" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="E8" t="n">
-        <v>0.26</v>
+        <v>0.257</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46069.4486111111</v>
+        <v>46075.9055555556</v>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="E9" t="n">
-        <v>0.094</v>
+        <v>0.347</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.8</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.6</v>
-      </c>
       <c r="I9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -1684,54 +4199,54 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46072.5097222222</v>
+        <v>45985.5916666667</v>
       </c>
       <c r="C10" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.154</v>
+        <v>0.592</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46070.6472222222</v>
+      </c>
+      <c r="C11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="F11" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="1" t="n">
-        <v>46071.3876736111</v>
-      </c>
-      <c r="C11" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
@@ -1739,89 +4254,89 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46069.2819444444</v>
+        <v>46065.5520833333</v>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D12" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="E12" t="n">
-        <v>0.199</v>
+        <v>0.141</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46081.2034722222</v>
+        <v>46069.4486111111</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1</v>
+        <v>0.094</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46111.0972222222</v>
+        <v>46072.5090277778</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.774</v>
+        <v>0.147</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -1829,144 +4344,202 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46034.8673611111</v>
+        <v>45930.2208333333</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0.451</v>
+        <v>0.124</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>6.3</v>
+        <v>0.1</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>45979.7826388889</v>
+        <v>45953.1763888889</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="E16" t="n">
-        <v>0.742</v>
+        <v>0.141</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="I16" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>45962.5118055556</v>
+        <v>46036.4458333333</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.104</v>
+        <v>0.412</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="I17" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46031.5666666667</v>
+        <v>45953.5881944444</v>
       </c>
       <c r="C18" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.105</v>
+        <v>0.512</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>45980.5256944444</v>
+        <v>46026.2631944444</v>
       </c>
       <c r="C19" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>45956.5763888889</v>
+      </c>
+      <c r="C20" t="n">
+        <v>21</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H20" t="n">
         <v>0.1</v>
       </c>
-      <c r="F19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I19" t="s">
-        <v>15</v>
+      <c r="I20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>45953.7131944444</v>
+      </c>
+      <c r="C21" t="n">
+        <v>21</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I21" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -55,10 +55,19 @@
     <t xml:space="preserve">dwd_risk_level</t>
   </si>
   <si>
-    <t xml:space="preserve">Wasserstraße_Springorum</t>
+    <t xml:space="preserve">An_der_Kost</t>
   </si>
   <si>
     <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 1 – Leichter Regen (0.5–15 mm/h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Königsallee_Springorum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wasserstraße_Springorum</t>
   </si>
   <si>
     <t xml:space="preserve">Level 0 – Kein nennenswerter Regen</t>
@@ -68,15 +77,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sturzflut-Ereignis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Königsallee_Springorum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level 1 – Leichter Regen (0.5–15 mm/h)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An_der_Kost</t>
   </si>
   <si>
     <t xml:space="preserve">Regenereignis / Natürlich</t>
@@ -156,8 +156,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M79" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M79"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M81" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M81"/>
   <tableColumns count="13">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -554,34 +554,34 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46116.6305555556</v>
+        <v>46123.9034722222</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46116.6503472222</v>
+        <v>46123.9201388889</v>
       </c>
       <c r="D2" t="n">
         <v>0.6</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46116.6420138889</v>
+        <v>46123.9142361111</v>
       </c>
       <c r="F2" t="n">
-        <v>28.5</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>0.036</v>
+        <v>0.038</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1</v>
+        <v>5.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
@@ -592,37 +592,37 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46114.8559027778</v>
+        <v>46123.8131944444</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46114.8770833333</v>
+        <v>46123.8267361111</v>
       </c>
       <c r="D3" t="n">
         <v>0.7</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46114.865625</v>
+        <v>46123.8243055556</v>
       </c>
       <c r="F3" t="n">
-        <v>30.5</v>
+        <v>19.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05</v>
+        <v>0.043</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -633,31 +633,31 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46114.5555555556</v>
+        <v>46116.6305555556</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46114.5847222222</v>
+        <v>46116.6503472222</v>
       </c>
       <c r="D4" t="n">
-        <v>17.3</v>
+        <v>0.6</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46114.5805555556</v>
+        <v>46116.6420138889</v>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>28.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.479</v>
+        <v>0.036</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>0.1</v>
@@ -669,417 +669,417 @@
         <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46114.8559027778</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>46114.8770833333</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46114.865625</v>
+      </c>
+      <c r="F5" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" t="n">
+        <v>11</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
         <v>18</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>46110.1208333333</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>46110.1395833333</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46110.1336805556</v>
-      </c>
-      <c r="F5" t="n">
-        <v>27</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" t="n">
-        <v>14</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46106.290625</v>
+        <v>46114.5555555556</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46106.3069444444</v>
+        <v>46114.5847222222</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>17.3</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46106.2989583333</v>
+        <v>46114.5805555556</v>
       </c>
       <c r="F6" t="n">
-        <v>23.5</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.066</v>
+        <v>0.479</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46095.1454861111</v>
+        <v>46110.1208333333</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46095.1604166667</v>
+        <v>46110.1395833333</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46095.1572916667</v>
+        <v>46110.1336805556</v>
       </c>
       <c r="F7" t="n">
-        <v>21.5</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>0.047</v>
+        <v>0.032</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46106.290625</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>46106.3069444444</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46106.2989583333</v>
+      </c>
+      <c r="F8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
         <v>18</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>46095.0517361111</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>46095.0909722222</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46095.059375</v>
-      </c>
-      <c r="F8" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="H8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" t="n">
-        <v>9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L8" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46094.8979166667</v>
+        <v>46095.1454861111</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46094.9368055556</v>
+        <v>46095.1604166667</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46094.9322916667</v>
+        <v>46095.1572916667</v>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>21.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.014</v>
+        <v>0.047</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46094.6888888889</v>
+        <v>46095.0517361111</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46094.7201388889</v>
+        <v>46095.0909722222</v>
       </c>
       <c r="D10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46095.059375</v>
+      </c>
+      <c r="F10" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="H10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K10" t="n">
         <v>0.6</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46094.7069444444</v>
-      </c>
-      <c r="F10" t="n">
-        <v>45</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="H10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.6</v>
-      </c>
       <c r="L10" t="b">
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46094.553125</v>
+        <v>46094.8979166667</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46094.5690972222</v>
+        <v>46094.9368055556</v>
       </c>
       <c r="D11" t="n">
         <v>0.7</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46094.5559027778</v>
+        <v>46094.9322916667</v>
       </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="G11" t="n">
-        <v>0.171</v>
+        <v>0.014</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46080.9958333333</v>
+        <v>46094.6888888889</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46081.0083333333</v>
+        <v>46094.7201388889</v>
       </c>
       <c r="D12" t="n">
         <v>0.6</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46081.0013888889</v>
+        <v>46094.7069444444</v>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>0.074</v>
+        <v>0.023</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46076.9986111111</v>
+        <v>46094.553125</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46077.0152777778</v>
+        <v>46094.5690972222</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46077.0048611111</v>
+        <v>46094.5559027778</v>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.066</v>
+        <v>0.171</v>
       </c>
       <c r="H13" t="s">
         <v>14</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46076.9590277778</v>
+        <v>46080.9958333333</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46076.9743055556</v>
+        <v>46081.0083333333</v>
       </c>
       <c r="D14" t="n">
         <v>0.6</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46076.9666666667</v>
+        <v>46081.0013888889</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>0.054</v>
+        <v>0.074</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -1087,198 +1087,198 @@
         <v>16</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46075.9055555556</v>
+        <v>46076.9986111111</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46075.9236111111</v>
+        <v>46077.0152777778</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46075.9138888889</v>
+        <v>46077.0048611111</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>0.347</v>
+        <v>0.066</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46072.5090277778</v>
+        <v>46076.9590277778</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46072.5354166667</v>
+        <v>46076.9743055556</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46072.5236111111</v>
+        <v>46076.9666666667</v>
       </c>
       <c r="F16" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G16" t="n">
-        <v>0.147</v>
+        <v>0.054</v>
       </c>
       <c r="H16" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46075.9055555556</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>46075.9236111111</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46075.9138888889</v>
+      </c>
+      <c r="F17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="H17" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="1" t="n">
-        <v>46072.45625</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>46072.4736111111</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46072.4631944444</v>
-      </c>
-      <c r="F17" t="n">
-        <v>25</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="H17" t="s">
-        <v>14</v>
-      </c>
       <c r="I17" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46072.4020833333</v>
+        <v>46072.5090277778</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46072.4097222222</v>
+        <v>46072.5354166667</v>
       </c>
       <c r="D18" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46072.4076388889</v>
+        <v>46072.5236111111</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="G18" t="n">
-        <v>0.58</v>
+        <v>0.147</v>
       </c>
       <c r="H18" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K18" t="n">
         <v>1.5</v>
       </c>
-      <c r="K18" t="n">
-        <v>0.7</v>
-      </c>
       <c r="L18" t="b">
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46071.0847222222</v>
+        <v>46072.45625</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46071.1173611111</v>
+        <v>46072.4736111111</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46071.1104166667</v>
+        <v>46072.4631944444</v>
       </c>
       <c r="F19" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="G19" t="n">
-        <v>0.032</v>
+        <v>0.059</v>
       </c>
       <c r="H19" t="s">
         <v>14</v>
       </c>
       <c r="I19" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1</v>
+        <v>2.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="L19" t="b">
         <v>1</v>
@@ -1289,37 +1289,37 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46070.6472222222</v>
+        <v>46072.4020833333</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46070.6548611111</v>
+        <v>46072.4097222222</v>
       </c>
       <c r="D20" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46070.6506944444</v>
+        <v>46072.4076388889</v>
       </c>
       <c r="F20" t="n">
         <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>0.725</v>
+        <v>0.58</v>
       </c>
       <c r="H20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="L20" t="b">
         <v>1</v>
@@ -1330,119 +1330,119 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46069.4486111111</v>
+        <v>46071.0847222222</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46069.4833333333</v>
+        <v>46071.1173611111</v>
       </c>
       <c r="D21" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46069.4729166667</v>
+        <v>46071.1104166667</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G21" t="n">
-        <v>0.094</v>
+        <v>0.032</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I21" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="L21" t="b">
         <v>1</v>
       </c>
       <c r="M21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>46070.6472222222</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>46070.6548611111</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46070.6506944444</v>
+      </c>
+      <c r="F22" t="n">
+        <v>11</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="H22" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" t="n">
+        <v>24</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="s">
         <v>18</v>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>46068.9430555556</v>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>46068.9555555556</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46068.9527777778</v>
-      </c>
-      <c r="F22" t="n">
-        <v>18</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="H22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" t="n">
-        <v>10</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L22" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46067.4930555556</v>
+        <v>46069.4486111111</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46067.50625</v>
+        <v>46069.4833333333</v>
       </c>
       <c r="D23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46069.4729166667</v>
+      </c>
+      <c r="F23" t="n">
+        <v>50</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="H23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" t="n">
+        <v>102</v>
+      </c>
+      <c r="J23" t="n">
         <v>0.8</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46067.4958333333</v>
-      </c>
-      <c r="F23" t="n">
-        <v>19</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="H23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" t="n">
-        <v>10</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.3</v>
-      </c>
       <c r="K23" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="L23" t="b">
         <v>1</v>
@@ -1456,116 +1456,116 @@
         <v>16</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46065.5520833333</v>
+        <v>46068.9430555556</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46065.5770833333</v>
+        <v>46068.9555555556</v>
       </c>
       <c r="D24" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46065.56875</v>
+        <v>46068.9527777778</v>
       </c>
       <c r="F24" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G24" t="n">
-        <v>0.141</v>
+        <v>0.064</v>
       </c>
       <c r="H24" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I24" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L24" t="b">
         <v>1</v>
       </c>
       <c r="M24" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46067.4930555556</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>46067.50625</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46067.4958333333</v>
+      </c>
+      <c r="F25" t="n">
+        <v>19</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="H25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="s">
         <v>18</v>
-      </c>
-      <c r="B25" s="1" t="n">
-        <v>46056.6743055556</v>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>46056.7125</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46056.6763888889</v>
-      </c>
-      <c r="F25" t="n">
-        <v>55</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="H25" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" t="n">
-        <v>14</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L25" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46046.1458333333</v>
+        <v>46065.5520833333</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46046.1729166667</v>
+        <v>46065.5770833333</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46046.1555555556</v>
+        <v>46065.56875</v>
       </c>
       <c r="F26" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G26" t="n">
-        <v>0.064</v>
+        <v>0.141</v>
       </c>
       <c r="H26" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I26" t="n">
         <v>62</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
@@ -1579,34 +1579,34 @@
         <v>16</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46038.7298611111</v>
+        <v>46056.6743055556</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46038.7590277778</v>
+        <v>46056.7125</v>
       </c>
       <c r="D27" t="n">
-        <v>23.7</v>
+        <v>0.6</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46038.7513888889</v>
+        <v>46056.6763888889</v>
       </c>
       <c r="F27" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G27" t="n">
-        <v>0.762</v>
+        <v>0.194</v>
       </c>
       <c r="H27" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I27" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
@@ -1617,283 +1617,283 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>46046.1458333333</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>46046.1729166667</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46046.1555555556</v>
+      </c>
+      <c r="F28" t="n">
+        <v>39</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="H28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" t="n">
+        <v>62</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" t="s">
         <v>18</v>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>46037.1930555556</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>46037.2333333333</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46037.2048611111</v>
-      </c>
-      <c r="F28" t="n">
-        <v>58</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="H28" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" t="n">
-        <v>7</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L28" t="b">
-        <v>1</v>
-      </c>
-      <c r="M28" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46036.4458333333</v>
+        <v>46038.7298611111</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46036.4875</v>
+        <v>46038.7590277778</v>
       </c>
       <c r="D29" t="n">
-        <v>2.1</v>
+        <v>23.7</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46036.4493055556</v>
+        <v>46038.7513888889</v>
       </c>
       <c r="F29" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G29" t="n">
-        <v>0.412</v>
+        <v>0.762</v>
       </c>
       <c r="H29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I29" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="K29" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
       </c>
       <c r="M29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46034.2236111111</v>
+        <v>46037.1930555556</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46034.2520833333</v>
+        <v>46037.2333333333</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46034.2326388889</v>
+        <v>46037.2048611111</v>
       </c>
       <c r="F30" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="G30" t="n">
-        <v>0.061</v>
+        <v>0.035</v>
       </c>
       <c r="H30" t="s">
         <v>14</v>
       </c>
       <c r="I30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="L30" t="b">
         <v>1</v>
       </c>
       <c r="M30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46031.6548611111</v>
+        <v>46036.4458333333</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46031.6736111111</v>
+        <v>46036.4875</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46031.6597222222</v>
+        <v>46036.4493055556</v>
       </c>
       <c r="F31" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G31" t="n">
-        <v>0.085</v>
+        <v>0.412</v>
       </c>
       <c r="H31" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="J31" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="L31" t="b">
         <v>1</v>
       </c>
       <c r="M31" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46031.4881944444</v>
+        <v>46034.2236111111</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46031.5034722222</v>
+        <v>46034.2520833333</v>
       </c>
       <c r="D32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46034.2326388889</v>
+      </c>
+      <c r="F32" t="n">
+        <v>41</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="H32" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K32" t="n">
         <v>0.6</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>46031.4965277778</v>
-      </c>
-      <c r="F32" t="n">
-        <v>22</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H32" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" t="n">
-        <v>5</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.8</v>
-      </c>
       <c r="L32" t="b">
         <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46026.2631944444</v>
+        <v>46031.6548611111</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46026.2770833333</v>
+        <v>46031.6736111111</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46026.2659722222</v>
+        <v>46031.6597222222</v>
       </c>
       <c r="F33" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G33" t="n">
-        <v>0.488</v>
+        <v>0.085</v>
       </c>
       <c r="H33" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="K33" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="L33" t="b">
         <v>1</v>
       </c>
       <c r="M33" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46010.6055555556</v>
+        <v>46031.4881944444</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46010.6354166667</v>
+        <v>46031.5034722222</v>
       </c>
       <c r="D34" t="n">
-        <v>34.9</v>
+        <v>0.6</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46010.6229166667</v>
+        <v>46031.4965277778</v>
       </c>
       <c r="F34" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="G34" t="n">
-        <v>1.39</v>
+        <v>0.05</v>
       </c>
       <c r="H34" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I34" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K34" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="L34" t="b">
         <v>1</v>
@@ -1904,37 +1904,37 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46010.3430555556</v>
+        <v>46026.2631944444</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46010.3534722222</v>
+        <v>46026.2770833333</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46010.3479166667</v>
+        <v>46026.2659722222</v>
       </c>
       <c r="F35" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G35" t="n">
-        <v>0.113</v>
+        <v>0.488</v>
       </c>
       <c r="H35" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I35" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L35" t="b">
         <v>1</v>
@@ -1945,160 +1945,160 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>46010.6055555556</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46010.6354166667</v>
+      </c>
+      <c r="D36" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46010.6229166667</v>
+      </c>
+      <c r="F36" t="n">
+        <v>43</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H36" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" t="n">
+        <v>44</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" t="s">
         <v>18</v>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>46001.1465277778</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46001.1597222222</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46001.1506944444</v>
-      </c>
-      <c r="F36" t="n">
-        <v>19</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="H36" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" t="n">
-        <v>11</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L36" t="b">
-        <v>1</v>
-      </c>
-      <c r="M36" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>45999.9777777778</v>
+        <v>46010.3430555556</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46000.00625</v>
+        <v>46010.3534722222</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>45999.9875</v>
+        <v>46010.3479166667</v>
       </c>
       <c r="F37" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="G37" t="n">
-        <v>0.043</v>
+        <v>0.113</v>
       </c>
       <c r="H37" t="s">
         <v>14</v>
       </c>
       <c r="I37" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J37" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="K37" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="L37" t="b">
         <v>1</v>
       </c>
       <c r="M37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>45998.8833333333</v>
+        <v>46001.1465277778</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45998.9118055556</v>
+        <v>46001.1597222222</v>
       </c>
       <c r="D38" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>45998.8979166667</v>
+        <v>46001.1506944444</v>
       </c>
       <c r="F38" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G38" t="n">
-        <v>0.033</v>
+        <v>0.098</v>
       </c>
       <c r="H38" t="s">
         <v>14</v>
       </c>
       <c r="I38" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J38" t="n">
-        <v>7.1</v>
+        <v>0.5</v>
       </c>
       <c r="K38" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="L38" t="b">
         <v>1</v>
       </c>
       <c r="M38" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>45994.9763888889</v>
+        <v>45999.9777777778</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45995.0069444444</v>
+        <v>46000.00625</v>
       </c>
       <c r="D39" t="n">
         <v>0.6</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>45995</v>
+        <v>45999.9875</v>
       </c>
       <c r="F39" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G39" t="n">
-        <v>0.018</v>
+        <v>0.043</v>
       </c>
       <c r="H39" t="s">
         <v>14</v>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="K39" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="L39" t="b">
         <v>1</v>
@@ -2109,37 +2109,37 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>45993.1833333333</v>
+        <v>45998.8833333333</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45993.2048611111</v>
+        <v>45998.9118055556</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>45993.1923611111</v>
+        <v>45998.8979166667</v>
       </c>
       <c r="F40" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G40" t="n">
-        <v>0.046</v>
+        <v>0.033</v>
       </c>
       <c r="H40" t="s">
         <v>14</v>
       </c>
       <c r="I40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1</v>
+        <v>7.1</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1</v>
+        <v>3.4</v>
       </c>
       <c r="L40" t="b">
         <v>1</v>
@@ -2150,43 +2150,43 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>45991.2326388889</v>
+        <v>45994.9763888889</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45991.2395833333</v>
+        <v>45995.0069444444</v>
       </c>
       <c r="D41" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>45991.2375</v>
+        <v>45995</v>
       </c>
       <c r="F41" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="G41" t="n">
-        <v>0.099</v>
+        <v>0.018</v>
       </c>
       <c r="H41" t="s">
         <v>14</v>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="L41" t="b">
         <v>1</v>
       </c>
       <c r="M41" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
@@ -2194,72 +2194,72 @@
         <v>16</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>45989.3763888889</v>
+        <v>45993.1833333333</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45989.4041666667</v>
+        <v>45993.2048611111</v>
       </c>
       <c r="D42" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>45989.3993055556</v>
+        <v>45993.1923611111</v>
       </c>
       <c r="F42" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G42" t="n">
-        <v>0.039</v>
+        <v>0.046</v>
       </c>
       <c r="H42" t="s">
         <v>14</v>
       </c>
       <c r="I42" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J42" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="K42" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L42" t="b">
         <v>1</v>
       </c>
       <c r="M42" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>45986.3493055556</v>
+        <v>45991.2326388889</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45986.3743055556</v>
+        <v>45991.2395833333</v>
       </c>
       <c r="D43" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>45986.3645833333</v>
+        <v>45991.2375</v>
       </c>
       <c r="F43" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="G43" t="n">
-        <v>0.059</v>
+        <v>0.099</v>
       </c>
       <c r="H43" t="s">
         <v>14</v>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K43" t="n">
         <v>0.1</v>
@@ -2268,247 +2268,247 @@
         <v>1</v>
       </c>
       <c r="M43" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>45986.0444444444</v>
+        <v>45989.3763888889</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45986.05</v>
+        <v>45989.4041666667</v>
       </c>
       <c r="D44" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>45986.0479166667</v>
+        <v>45989.3993055556</v>
       </c>
       <c r="F44" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="G44" t="n">
-        <v>0.157</v>
+        <v>0.039</v>
       </c>
       <c r="H44" t="s">
         <v>14</v>
       </c>
       <c r="I44" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J44" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L44" t="b">
         <v>1</v>
       </c>
       <c r="M44" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>45985.60625</v>
+        <v>45986.3493055556</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45985.6340277778</v>
+        <v>45986.3743055556</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>45985.6305555556</v>
+        <v>45986.3645833333</v>
       </c>
       <c r="F45" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G45" t="n">
-        <v>0.017</v>
+        <v>0.059</v>
       </c>
       <c r="H45" t="s">
         <v>14</v>
       </c>
       <c r="I45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J45" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="K45" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
       </c>
       <c r="M45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>45985.5916666667</v>
+        <v>45986.0444444444</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45985.6</v>
+        <v>45986.05</v>
       </c>
       <c r="D46" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>45985.5965277778</v>
+        <v>45986.0479166667</v>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G46" t="n">
-        <v>0.592</v>
+        <v>0.157</v>
       </c>
       <c r="H46" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I46" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J46" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="K46" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="L46" t="b">
         <v>1</v>
       </c>
       <c r="M46" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>45980.9888888889</v>
+        <v>45985.60625</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45981.0069444444</v>
+        <v>45985.6340277778</v>
       </c>
       <c r="D47" t="n">
         <v>0.6</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>45981.0027777778</v>
+        <v>45985.6305555556</v>
       </c>
       <c r="F47" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G47" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="H47" t="s">
         <v>14</v>
       </c>
       <c r="I47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>45980.9451388889</v>
+        <v>45985.5916666667</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45980.9715277778</v>
+        <v>45985.6</v>
       </c>
       <c r="D48" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>45980.9486111111</v>
+        <v>45985.5965277778</v>
       </c>
       <c r="F48" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>0.118</v>
+        <v>0.592</v>
       </c>
       <c r="H48" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I48" t="n">
         <v>12</v>
       </c>
       <c r="J48" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="K48" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="L48" t="b">
         <v>1</v>
       </c>
       <c r="M48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>45977.8520833333</v>
+        <v>45980.9888888889</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45977.8861111111</v>
+        <v>45981.0069444444</v>
       </c>
       <c r="D49" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>45977.8638888889</v>
+        <v>45981.0027777778</v>
       </c>
       <c r="F49" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="G49" t="n">
-        <v>0.041</v>
+        <v>0.03</v>
       </c>
       <c r="H49" t="s">
         <v>14</v>
       </c>
       <c r="I49" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J49" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="K49" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="L49" t="b">
         <v>1</v>
@@ -2519,43 +2519,43 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>45970.6055555556</v>
+        <v>45980.9451388889</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45970.6333333333</v>
+        <v>45980.9715277778</v>
       </c>
       <c r="D50" t="n">
         <v>0.6</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>45970.6284722222</v>
+        <v>45980.9486111111</v>
       </c>
       <c r="F50" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G50" t="n">
-        <v>0.018</v>
+        <v>0.118</v>
       </c>
       <c r="H50" t="s">
         <v>14</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="K50" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
       </c>
       <c r="M50" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51">
@@ -2563,157 +2563,157 @@
         <v>16</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>45962.6513888889</v>
+        <v>45977.8520833333</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45962.6715277778</v>
+        <v>45977.8861111111</v>
       </c>
       <c r="D51" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>45962.6583333333</v>
+        <v>45977.8638888889</v>
       </c>
       <c r="F51" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="G51" t="n">
-        <v>0.109</v>
+        <v>0.041</v>
       </c>
       <c r="H51" t="s">
         <v>14</v>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
-        <v>5.5</v>
+        <v>0.2</v>
       </c>
       <c r="K51" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
       </c>
       <c r="M51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>45960.3222222222</v>
+        <v>45970.6055555556</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45960.3430555556</v>
+        <v>45970.6333333333</v>
       </c>
       <c r="D52" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>45960.3319444444</v>
+        <v>45970.6284722222</v>
       </c>
       <c r="F52" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G52" t="n">
-        <v>0.057</v>
+        <v>0.018</v>
       </c>
       <c r="H52" t="s">
         <v>14</v>
       </c>
       <c r="I52" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J52" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="K52" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L52" t="b">
         <v>1</v>
       </c>
       <c r="M52" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>45958.5965277778</v>
+        <v>45962.6513888889</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45958.6138888889</v>
+        <v>45962.6715277778</v>
       </c>
       <c r="D53" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>45958.6055555556</v>
+        <v>45962.6583333333</v>
       </c>
       <c r="F53" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G53" t="n">
-        <v>0.107</v>
+        <v>0.109</v>
       </c>
       <c r="H53" t="s">
         <v>14</v>
       </c>
       <c r="I53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="K53" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="L53" t="b">
         <v>1</v>
       </c>
       <c r="M53" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>45958.3965277778</v>
+        <v>45960.3222222222</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45958.4298611111</v>
+        <v>45960.3430555556</v>
       </c>
       <c r="D54" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>45958.4201388889</v>
+        <v>45960.3319444444</v>
       </c>
       <c r="F54" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G54" t="n">
-        <v>0.018</v>
+        <v>0.057</v>
       </c>
       <c r="H54" t="s">
         <v>14</v>
       </c>
       <c r="I54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J54" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="K54" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="L54" t="b">
         <v>1</v>
@@ -2724,201 +2724,201 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>45958.3354166667</v>
+        <v>45958.5965277778</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45958.3555555556</v>
+        <v>45958.6138888889</v>
       </c>
       <c r="D55" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>45958.3513888889</v>
+        <v>45958.6055555556</v>
       </c>
       <c r="F55" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G55" t="n">
-        <v>0.039</v>
+        <v>0.107</v>
       </c>
       <c r="H55" t="s">
         <v>14</v>
       </c>
       <c r="I55" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J55" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="K55" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="L55" t="b">
         <v>1</v>
       </c>
       <c r="M55" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>45958.3041666667</v>
+        <v>45958.3965277778</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45958.3180555556</v>
+        <v>45958.4298611111</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>45958.3152777778</v>
+        <v>45958.4201388889</v>
       </c>
       <c r="F56" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G56" t="n">
-        <v>0.062</v>
+        <v>0.018</v>
       </c>
       <c r="H56" t="s">
         <v>14</v>
       </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="K56" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
       </c>
       <c r="M56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>45957.4340277778</v>
+        <v>45958.3354166667</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45957.4534722222</v>
+        <v>45958.3555555556</v>
       </c>
       <c r="D57" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>45957.4451388889</v>
+        <v>45958.3513888889</v>
       </c>
       <c r="F57" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G57" t="n">
-        <v>0.043</v>
+        <v>0.039</v>
       </c>
       <c r="H57" t="s">
         <v>14</v>
       </c>
       <c r="I57" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K57" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="L57" t="b">
         <v>1</v>
       </c>
       <c r="M57" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
+        <v>19</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>45958.3041666667</v>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>45958.3180555556</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>45958.3152777778</v>
+      </c>
+      <c r="F58" t="n">
         <v>20</v>
       </c>
-      <c r="B58" s="1" t="n">
-        <v>45957.1083333333</v>
-      </c>
-      <c r="C58" s="1" t="n">
-        <v>45957.1243055556</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E58" s="1" t="n">
-        <v>45957.1180555556</v>
-      </c>
-      <c r="F58" t="n">
-        <v>23</v>
-      </c>
       <c r="G58" t="n">
-        <v>0.043</v>
+        <v>0.062</v>
       </c>
       <c r="H58" t="s">
         <v>14</v>
       </c>
       <c r="I58" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="K58" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
       </c>
       <c r="M58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>45956.5763888889</v>
+        <v>45957.4340277778</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45956.5909722222</v>
+        <v>45957.4534722222</v>
       </c>
       <c r="D59" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>45956.5875</v>
+        <v>45957.4451388889</v>
       </c>
       <c r="F59" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G59" t="n">
-        <v>0.118</v>
+        <v>0.043</v>
       </c>
       <c r="H59" t="s">
         <v>14</v>
       </c>
       <c r="I59" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J59" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="L59" t="b">
         <v>1</v>
@@ -2929,242 +2929,242 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>45953.7131944444</v>
+        <v>45957.1083333333</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45953.7277777778</v>
+        <v>45957.1243055556</v>
       </c>
       <c r="D60" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>45953.7222222222</v>
+        <v>45957.1180555556</v>
       </c>
       <c r="F60" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G60" t="n">
-        <v>0.122</v>
+        <v>0.043</v>
       </c>
       <c r="H60" t="s">
         <v>14</v>
       </c>
       <c r="I60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J60" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="K60" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="L60" t="b">
         <v>1</v>
       </c>
       <c r="M60" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>45953.7097222222</v>
+        <v>45956.5763888889</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45953.7395833333</v>
+        <v>45956.5909722222</v>
       </c>
       <c r="D61" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>45953.7201388889</v>
+        <v>45956.5875</v>
       </c>
       <c r="F61" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="G61" t="n">
-        <v>0.046</v>
+        <v>0.118</v>
       </c>
       <c r="H61" t="s">
         <v>14</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J61" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="K61" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="L61" t="b">
         <v>1</v>
       </c>
       <c r="M61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>45953.5881944444</v>
+        <v>45953.7131944444</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45953.5986111111</v>
+        <v>45953.7277777778</v>
       </c>
       <c r="D62" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>45953.5909722222</v>
+        <v>45953.7222222222</v>
       </c>
       <c r="F62" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G62" t="n">
-        <v>0.512</v>
+        <v>0.122</v>
       </c>
       <c r="H62" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J62" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="K62" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="L62" t="b">
         <v>1</v>
       </c>
       <c r="M62" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>45953.1763888889</v>
+        <v>45953.7097222222</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45953.2020833333</v>
+        <v>45953.7395833333</v>
       </c>
       <c r="D63" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>45953.1895833333</v>
+        <v>45953.7201388889</v>
       </c>
       <c r="F63" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G63" t="n">
-        <v>0.141</v>
+        <v>0.046</v>
       </c>
       <c r="H63" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I63" t="n">
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="K63" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
       </c>
       <c r="M63" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>45951.2659722222</v>
+        <v>45953.5881944444</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45951.2895833333</v>
+        <v>45953.5986111111</v>
       </c>
       <c r="D64" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>45951.2680555556</v>
+        <v>45953.5909722222</v>
       </c>
       <c r="F64" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G64" t="n">
-        <v>0.226</v>
+        <v>0.512</v>
       </c>
       <c r="H64" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I64" t="n">
         <v>4</v>
       </c>
       <c r="J64" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L64" t="b">
         <v>1</v>
       </c>
       <c r="M64" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>45948.1659722222</v>
+        <v>45953.1763888889</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45948.2069444444</v>
+        <v>45953.2020833333</v>
       </c>
       <c r="D65" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>45948.1777777778</v>
+        <v>45953.1895833333</v>
       </c>
       <c r="F65" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="G65" t="n">
-        <v>0.257</v>
+        <v>0.141</v>
       </c>
       <c r="H65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="K65" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
@@ -3175,37 +3175,37 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>45948.1201388889</v>
+        <v>45951.2659722222</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45948.1409722222</v>
+        <v>45951.2895833333</v>
       </c>
       <c r="D66" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>45948.1368055556</v>
+        <v>45951.2680555556</v>
       </c>
       <c r="F66" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G66" t="n">
-        <v>0.046</v>
+        <v>0.226</v>
       </c>
       <c r="H66" t="s">
         <v>14</v>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="K66" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="L66" t="b">
         <v>1</v>
@@ -3216,28 +3216,28 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>45948.0152777778</v>
+        <v>45948.1659722222</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45948.0430555556</v>
+        <v>45948.2069444444</v>
       </c>
       <c r="D67" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>45948.0243055556</v>
+        <v>45948.1777777778</v>
       </c>
       <c r="F67" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="G67" t="n">
-        <v>0.061</v>
+        <v>0.257</v>
       </c>
       <c r="H67" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I67" t="n">
         <v>5</v>
@@ -3252,36 +3252,36 @@
         <v>1</v>
       </c>
       <c r="M67" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>45946.8027777778</v>
+        <v>45948.1201388889</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45946.8180555556</v>
+        <v>45948.1409722222</v>
       </c>
       <c r="D68" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>45946.8159722222</v>
+        <v>45948.1368055556</v>
       </c>
       <c r="F68" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G68" t="n">
-        <v>0.063</v>
+        <v>0.046</v>
       </c>
       <c r="H68" t="s">
         <v>14</v>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J68" t="n">
         <v>0.1</v>
@@ -3293,77 +3293,77 @@
         <v>1</v>
       </c>
       <c r="M68" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>45946.6076388889</v>
+        <v>45948.0152777778</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45946.6354166667</v>
+        <v>45948.0430555556</v>
       </c>
       <c r="D69" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>45946.6194444444</v>
+        <v>45948.0243055556</v>
       </c>
       <c r="F69" t="n">
         <v>40</v>
       </c>
       <c r="G69" t="n">
-        <v>0.035</v>
+        <v>0.061</v>
       </c>
       <c r="H69" t="s">
         <v>14</v>
       </c>
       <c r="I69" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J69" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="K69" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L69" t="b">
         <v>1</v>
       </c>
       <c r="M69" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>45943.0444444444</v>
+        <v>45946.8027777778</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45943.0583333333</v>
+        <v>45946.8180555556</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>45943.0555555556</v>
+        <v>45946.8159722222</v>
       </c>
       <c r="F70" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G70" t="n">
-        <v>0.062</v>
+        <v>0.063</v>
       </c>
       <c r="H70" t="s">
         <v>14</v>
       </c>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J70" t="n">
         <v>0.1</v>
@@ -3375,130 +3375,130 @@
         <v>1</v>
       </c>
       <c r="M70" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>45942.2895833333</v>
+        <v>45946.6076388889</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45942.3166666667</v>
+        <v>45946.6354166667</v>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>45942.3048611111</v>
+        <v>45946.6194444444</v>
       </c>
       <c r="F71" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G71" t="n">
-        <v>0.226</v>
+        <v>0.035</v>
       </c>
       <c r="H71" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I71" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J71" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="K71" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L71" t="b">
         <v>1</v>
       </c>
       <c r="M71" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
+        <v>17</v>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>45943.0444444444</v>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>45943.0583333333</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="1" t="n">
+        <v>45943.0555555556</v>
+      </c>
+      <c r="F72" t="n">
+        <v>20</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="H72" t="s">
+        <v>14</v>
+      </c>
+      <c r="I72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L72" t="b">
+        <v>1</v>
+      </c>
+      <c r="M72" t="s">
         <v>18</v>
-      </c>
-      <c r="B72" s="1" t="n">
-        <v>45939.2444444444</v>
-      </c>
-      <c r="C72" s="1" t="n">
-        <v>45939.2652777778</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E72" s="1" t="n">
-        <v>45939.2548611111</v>
-      </c>
-      <c r="F72" t="n">
-        <v>30</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H72" t="s">
-        <v>14</v>
-      </c>
-      <c r="I72" t="n">
-        <v>7</v>
-      </c>
-      <c r="J72" t="n">
-        <v>1</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L72" t="b">
-        <v>1</v>
-      </c>
-      <c r="M72" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
+        <v>17</v>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>45942.2895833333</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>45942.3166666667</v>
+      </c>
+      <c r="D73" t="n">
+        <v>5</v>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>45942.3048611111</v>
+      </c>
+      <c r="F73" t="n">
+        <v>39</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="H73" t="s">
+        <v>20</v>
+      </c>
+      <c r="I73" t="n">
+        <v>12</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L73" t="b">
+        <v>1</v>
+      </c>
+      <c r="M73" t="s">
         <v>18</v>
-      </c>
-      <c r="B73" s="1" t="n">
-        <v>45939.1743055556</v>
-      </c>
-      <c r="C73" s="1" t="n">
-        <v>45939.1833333333</v>
-      </c>
-      <c r="D73" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E73" s="1" t="n">
-        <v>45939.1763888889</v>
-      </c>
-      <c r="F73" t="n">
-        <v>13</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="H73" t="s">
-        <v>14</v>
-      </c>
-      <c r="I73" t="n">
-        <v>6</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L73" t="b">
-        <v>1</v>
-      </c>
-      <c r="M73" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="74">
@@ -3506,116 +3506,116 @@
         <v>16</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>45933.9763888889</v>
+        <v>45939.2444444444</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45933.9902777778</v>
+        <v>45939.2652777778</v>
       </c>
       <c r="D74" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>45933.98125</v>
+        <v>45939.2548611111</v>
       </c>
       <c r="F74" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G74" t="n">
-        <v>0.211</v>
+        <v>0.04</v>
       </c>
       <c r="H74" t="s">
         <v>14</v>
       </c>
       <c r="I74" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J74" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="L74" t="b">
         <v>1</v>
       </c>
       <c r="M74" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
+        <v>16</v>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>45939.1743055556</v>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>45939.1833333333</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E75" s="1" t="n">
+        <v>45939.1763888889</v>
+      </c>
+      <c r="F75" t="n">
         <v>13</v>
       </c>
-      <c r="B75" s="1" t="n">
-        <v>45930.2208333333</v>
-      </c>
-      <c r="C75" s="1" t="n">
-        <v>45930.2513888889</v>
-      </c>
-      <c r="D75" t="n">
-        <v>3</v>
-      </c>
-      <c r="E75" s="1" t="n">
-        <v>45930.2375</v>
-      </c>
-      <c r="F75" t="n">
-        <v>44</v>
-      </c>
       <c r="G75" t="n">
-        <v>0.124</v>
+        <v>0.194</v>
       </c>
       <c r="H75" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J75" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="K75" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="L75" t="b">
         <v>1</v>
       </c>
       <c r="M75" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>19</v>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>45933.9763888889</v>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>45933.9902777778</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>45933.98125</v>
+      </c>
+      <c r="F76" t="n">
+        <v>20</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="H76" t="s">
+        <v>14</v>
+      </c>
+      <c r="I76" t="n">
         <v>13</v>
       </c>
-      <c r="B76" s="1" t="n">
-        <v>45925.4902777778</v>
-      </c>
-      <c r="C76" s="1" t="n">
-        <v>45925.5319444444</v>
-      </c>
-      <c r="D76" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E76" s="1" t="n">
-        <v>45925.5201388889</v>
-      </c>
-      <c r="F76" t="n">
-        <v>60</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="H76" t="s">
-        <v>14</v>
-      </c>
-      <c r="I76" t="n">
-        <v>10</v>
-      </c>
       <c r="J76" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="K76" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="L76" t="b">
         <v>1</v>
@@ -3626,125 +3626,207 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B77" s="1" t="n">
-        <v>45921.4229166667</v>
+        <v>45930.2208333333</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45921.4423611111</v>
+        <v>45930.2513888889</v>
       </c>
       <c r="D77" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>45921.4284722222</v>
+        <v>45930.2375</v>
       </c>
       <c r="F77" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G77" t="n">
-        <v>0.074</v>
+        <v>0.124</v>
       </c>
       <c r="H77" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I77" t="n">
         <v>5</v>
       </c>
       <c r="J77" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="K77" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="L77" t="b">
         <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>45921.2979166667</v>
+        <v>45925.4902777778</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45921.3111111111</v>
+        <v>45925.5319444444</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>45921.3034722222</v>
+        <v>45925.5201388889</v>
       </c>
       <c r="F78" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="G78" t="n">
-        <v>0.123</v>
+        <v>0.016</v>
       </c>
       <c r="H78" t="s">
         <v>14</v>
       </c>
       <c r="I78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="K78" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="L78" t="b">
         <v>1</v>
       </c>
       <c r="M78" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>16</v>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>45921.4229166667</v>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>45921.4423611111</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>45921.4284722222</v>
+      </c>
+      <c r="F79" t="n">
+        <v>28</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="H79" t="s">
+        <v>14</v>
+      </c>
+      <c r="I79" t="n">
+        <v>5</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L79" t="b">
+        <v>1</v>
+      </c>
+      <c r="M79" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>17</v>
+      </c>
+      <c r="B80" s="1" t="n">
+        <v>45921.2979166667</v>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>45921.3111111111</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="1" t="n">
+        <v>45921.3034722222</v>
+      </c>
+      <c r="F80" t="n">
+        <v>19</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="H80" t="s">
+        <v>14</v>
+      </c>
+      <c r="I80" t="n">
+        <v>8</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L80" t="b">
+        <v>1</v>
+      </c>
+      <c r="M80" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
         <v>22</v>
       </c>
-      <c r="B79" s="1" t="n">
+      <c r="B81" s="1" t="n">
         <v>45710.3541666667</v>
       </c>
-      <c r="C79" s="1" t="n">
+      <c r="C81" s="1" t="n">
         <v>45710.3854166667</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D81" t="n">
         <v>19.6</v>
       </c>
-      <c r="E79" s="1" t="n">
+      <c r="E81" s="1" t="n">
         <v>45710.375</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F81" t="n">
         <v>45</v>
       </c>
-      <c r="G79" t="n">
+      <c r="G81" t="n">
         <v>0.651</v>
       </c>
-      <c r="H79" t="s">
-        <v>17</v>
-      </c>
-      <c r="I79" t="n">
+      <c r="H81" t="s">
+        <v>20</v>
+      </c>
+      <c r="I81" t="n">
         <v>4</v>
       </c>
-      <c r="J79" t="n">
+      <c r="J81" t="n">
         <v>0</v>
       </c>
-      <c r="K79" t="n">
+      <c r="K81" t="n">
         <v>0</v>
       </c>
-      <c r="L79" t="b">
+      <c r="L81" t="b">
         <v>0</v>
       </c>
-      <c r="M79" t="s">
-        <v>15</v>
+      <c r="M81" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3795,10 +3877,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="n">
         <v>0.7</v>
@@ -3818,7 +3900,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>25</v>
@@ -3841,7 +3923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -3864,10 +3946,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
         <v>0.6</v>
@@ -3964,7 +4046,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>46010.6055555556</v>
@@ -3979,7 +4061,7 @@
         <v>1.39</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
         <v>0.6</v>
@@ -3988,12 +4070,12 @@
         <v>0.3</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>46038.7298611111</v>
@@ -4008,7 +4090,7 @@
         <v>0.762</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
         <v>0.6</v>
@@ -4017,7 +4099,7 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -4037,7 +4119,7 @@
         <v>0.651</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4046,12 +4128,12 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>46114.5555555556</v>
@@ -4066,7 +4148,7 @@
         <v>0.479</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
         <v>0.1</v>
@@ -4075,12 +4157,12 @@
         <v>0.1</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>45942.2895833333</v>
@@ -4095,7 +4177,7 @@
         <v>0.226</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
         <v>0.1</v>
@@ -4104,12 +4186,12 @@
         <v>0.1</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>46072.4020833333</v>
@@ -4124,7 +4206,7 @@
         <v>0.58</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G7" t="n">
         <v>1.5</v>
@@ -4133,12 +4215,12 @@
         <v>0.7</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>45948.1659722222</v>
@@ -4162,12 +4244,12 @@
         <v>0.1</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>46075.9055555556</v>
@@ -4182,7 +4264,7 @@
         <v>0.347</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G9" t="n">
         <v>1.6</v>
@@ -4191,12 +4273,12 @@
         <v>0.8</v>
       </c>
       <c r="I9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>45985.5916666667</v>
@@ -4211,7 +4293,7 @@
         <v>0.592</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G10" t="n">
         <v>0.8</v>
@@ -4220,12 +4302,12 @@
         <v>0.3</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>46070.6472222222</v>
@@ -4240,7 +4322,7 @@
         <v>0.725</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G11" t="n">
         <v>0.2</v>
@@ -4249,12 +4331,12 @@
         <v>0.1</v>
       </c>
       <c r="I11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>46065.5520833333</v>
@@ -4269,7 +4351,7 @@
         <v>0.141</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
         <v>1.9</v>
@@ -4278,12 +4360,12 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>46069.4486111111</v>
@@ -4307,12 +4389,12 @@
         <v>0.6</v>
       </c>
       <c r="I13" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>46072.5090277778</v>
@@ -4327,7 +4409,7 @@
         <v>0.147</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G14" t="n">
         <v>3.4</v>
@@ -4336,12 +4418,12 @@
         <v>1.5</v>
       </c>
       <c r="I14" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>45930.2208333333</v>
@@ -4356,7 +4438,7 @@
         <v>0.124</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G15" t="n">
         <v>0.1</v>
@@ -4365,12 +4447,12 @@
         <v>0.1</v>
       </c>
       <c r="I15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>45953.1763888889</v>
@@ -4385,7 +4467,7 @@
         <v>0.141</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G16" t="n">
         <v>1.9</v>
@@ -4394,12 +4476,12 @@
         <v>1.4</v>
       </c>
       <c r="I16" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>46036.4458333333</v>
@@ -4423,12 +4505,12 @@
         <v>1.5</v>
       </c>
       <c r="I17" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>45953.5881944444</v>
@@ -4443,7 +4525,7 @@
         <v>0.512</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G18" t="n">
         <v>0.6</v>
@@ -4452,12 +4534,12 @@
         <v>0.5</v>
       </c>
       <c r="I18" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>46026.2631944444</v>
@@ -4481,12 +4563,12 @@
         <v>0.5</v>
       </c>
       <c r="I19" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>45956.5763888889</v>
@@ -4510,12 +4592,12 @@
         <v>0.1</v>
       </c>
       <c r="I20" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>45953.7131944444</v>
@@ -4539,7 +4621,7 @@
         <v>1.3</v>
       </c>
       <c r="I21" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -55,16 +55,13 @@
     <t xml:space="preserve">dwd_risk_level</t>
   </si>
   <si>
-    <t xml:space="preserve">An_der_Kost</t>
+    <t xml:space="preserve">Königsallee_Springorum</t>
   </si>
   <si>
     <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
   </si>
   <si>
     <t xml:space="preserve">Level 1 – Leichter Regen (0.5–15 mm/h)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Königsallee_Springorum</t>
   </si>
   <si>
     <t xml:space="preserve">Wasserstraße_Springorum</t>
@@ -77,6 +74,9 @@
   </si>
   <si>
     <t xml:space="preserve">Sturzflut-Ereignis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An_der_Kost</t>
   </si>
   <si>
     <t xml:space="preserve">Regenereignis / Natürlich</t>
@@ -156,8 +156,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M81" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M81"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M80" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M80"/>
   <tableColumns count="13">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -554,22 +554,22 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46123.9034722222</v>
+        <v>46123.8034722222</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46123.9201388889</v>
+        <v>46123.8295138889</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46123.9142361111</v>
+        <v>46123.8243055556</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>37.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.038</v>
+        <v>0.027</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8</v>
+        <v>2.3</v>
       </c>
       <c r="K2" t="n">
         <v>2.2</v>
@@ -595,163 +595,163 @@
         <v>16</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46123.8131944444</v>
+        <v>46116.6305555556</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46123.8267361111</v>
+        <v>46116.6503472222</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46123.8243055556</v>
+        <v>46116.6420138889</v>
       </c>
       <c r="F3" t="n">
-        <v>19.5</v>
+        <v>28.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.043</v>
+        <v>0.036</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46114.8559027778</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>46114.8770833333</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46114.865625</v>
+      </c>
+      <c r="F4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
         <v>17</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>46116.6305555556</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>46116.6503472222</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46116.6420138889</v>
-      </c>
-      <c r="F4" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46114.5555555556</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>46114.5847222222</v>
+      </c>
+      <c r="D5" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46114.5805555556</v>
+      </c>
+      <c r="F5" t="n">
+        <v>42</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="H5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" t="n">
+        <v>43</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
         <v>17</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>46114.8559027778</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>46114.8770833333</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46114.865625</v>
-      </c>
-      <c r="F5" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" t="n">
-        <v>11</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46114.5555555556</v>
+        <v>46110.1208333333</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46114.5847222222</v>
+        <v>46110.1395833333</v>
       </c>
       <c r="D6" t="n">
-        <v>17.3</v>
+        <v>0.6</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46114.5805555556</v>
+        <v>46110.1336805556</v>
       </c>
       <c r="F6" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>0.479</v>
+        <v>0.032</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -759,63 +759,63 @@
         <v>16</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46110.1208333333</v>
+        <v>46106.290625</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46110.1395833333</v>
+        <v>46106.3069444444</v>
       </c>
       <c r="D7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46106.2989583333</v>
+      </c>
+      <c r="F7" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
         <v>0.6</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46110.1336805556</v>
-      </c>
-      <c r="F7" t="n">
-        <v>27</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" t="n">
-        <v>14</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.2</v>
-      </c>
       <c r="K7" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46106.290625</v>
+        <v>46095.1454861111</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46106.3069444444</v>
+        <v>46095.1604166667</v>
       </c>
       <c r="D8" t="n">
         <v>0.8</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46106.2989583333</v>
+        <v>46095.1572916667</v>
       </c>
       <c r="F8" t="n">
-        <v>23.5</v>
+        <v>21.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.066</v>
+        <v>0.047</v>
       </c>
       <c r="H8" t="s">
         <v>14</v>
@@ -824,48 +824,48 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K8" t="n">
         <v>0.6</v>
       </c>
-      <c r="K8" t="n">
-        <v>0.3</v>
-      </c>
       <c r="L8" t="b">
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46095.1454861111</v>
+        <v>46095.0517361111</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46095.1604166667</v>
+        <v>46095.0909722222</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46095.1572916667</v>
+        <v>46095.059375</v>
       </c>
       <c r="F9" t="n">
-        <v>21.5</v>
+        <v>56.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.047</v>
+        <v>0.081</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="K9" t="n">
         <v>0.6</v>
@@ -879,37 +879,37 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46095.0517361111</v>
+        <v>46094.8979166667</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46095.0909722222</v>
+        <v>46094.9368055556</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46095.059375</v>
+        <v>46094.9322916667</v>
       </c>
       <c r="F10" t="n">
-        <v>56.5</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>0.081</v>
+        <v>0.014</v>
       </c>
       <c r="H10" t="s">
         <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
@@ -920,37 +920,37 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46094.8979166667</v>
+        <v>46094.6888888889</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46094.9368055556</v>
+        <v>46094.7201388889</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46094.9322916667</v>
+        <v>46094.7069444444</v>
       </c>
       <c r="F11" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G11" t="n">
-        <v>0.014</v>
+        <v>0.023</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -961,37 +961,37 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46094.6888888889</v>
+        <v>46094.553125</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46094.7201388889</v>
+        <v>46094.5690972222</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46094.7069444444</v>
+        <v>46094.5559027778</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="G12" t="n">
-        <v>0.023</v>
+        <v>0.171</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -1005,34 +1005,34 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46094.553125</v>
+        <v>46080.9958333333</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46094.5690972222</v>
+        <v>46081.0083333333</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46094.5559027778</v>
+        <v>46081.0013888889</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G13" t="n">
-        <v>0.171</v>
+        <v>0.074</v>
       </c>
       <c r="H13" t="s">
         <v>14</v>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -1043,37 +1043,37 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46080.9958333333</v>
+        <v>46076.9986111111</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46081.0083333333</v>
+        <v>46077.0152777778</v>
       </c>
       <c r="D14" t="n">
         <v>0.6</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46081.0013888889</v>
+        <v>46077.0048611111</v>
       </c>
       <c r="F14" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G14" t="n">
-        <v>0.074</v>
+        <v>0.066</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
@@ -1084,34 +1084,34 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46076.9986111111</v>
+        <v>46076.9590277778</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46077.0152777778</v>
+        <v>46076.9743055556</v>
       </c>
       <c r="D15" t="n">
         <v>0.6</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46077.0048611111</v>
+        <v>46076.9666666667</v>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
-        <v>0.066</v>
+        <v>0.054</v>
       </c>
       <c r="H15" t="s">
         <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="K15" t="n">
         <v>1.4</v>
@@ -1125,37 +1125,37 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46076.9590277778</v>
+        <v>46075.9055555556</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46076.9743055556</v>
+        <v>46075.9236111111</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46076.9666666667</v>
+        <v>46075.9138888889</v>
       </c>
       <c r="F16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G16" t="n">
-        <v>0.054</v>
+        <v>0.347</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
@@ -1166,37 +1166,37 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46072.5090277778</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>46072.5354166667</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46072.5236111111</v>
+      </c>
+      <c r="F17" t="n">
+        <v>38</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="H17" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="1" t="n">
-        <v>46075.9055555556</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>46075.9236111111</v>
-      </c>
-      <c r="D17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46075.9138888889</v>
-      </c>
-      <c r="F17" t="n">
-        <v>26</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="H17" t="s">
-        <v>20</v>
-      </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -1207,37 +1207,37 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46072.5090277778</v>
+        <v>46072.45625</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46072.5354166667</v>
+        <v>46072.4736111111</v>
       </c>
       <c r="D18" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46072.5236111111</v>
+        <v>46072.4631944444</v>
       </c>
       <c r="F18" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G18" t="n">
-        <v>0.147</v>
+        <v>0.059</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -1248,37 +1248,37 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46072.45625</v>
+        <v>46072.4020833333</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46072.4736111111</v>
+        <v>46072.4097222222</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46072.4631944444</v>
+        <v>46072.4076388889</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>0.059</v>
+        <v>0.58</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="L19" t="b">
         <v>1</v>
@@ -1289,75 +1289,75 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46072.4020833333</v>
+        <v>46071.0847222222</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46072.4097222222</v>
+        <v>46071.1173611111</v>
       </c>
       <c r="D20" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46072.4076388889</v>
+        <v>46071.1104166667</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="G20" t="n">
-        <v>0.58</v>
+        <v>0.032</v>
       </c>
       <c r="H20" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I20" t="n">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="L20" t="b">
         <v>1</v>
       </c>
       <c r="M20" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>46070.6472222222</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>46070.6548611111</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46070.6506944444</v>
+      </c>
+      <c r="F21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="H21" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="1" t="n">
-        <v>46071.0847222222</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>46071.1173611111</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46071.1104166667</v>
-      </c>
-      <c r="F21" t="n">
-        <v>47</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H21" t="s">
-        <v>14</v>
-      </c>
       <c r="I21" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="K21" t="n">
         <v>0.1</v>
@@ -1366,83 +1366,83 @@
         <v>1</v>
       </c>
       <c r="M21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46070.6472222222</v>
+        <v>46069.4486111111</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46070.6548611111</v>
+        <v>46069.4833333333</v>
       </c>
       <c r="D22" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46070.6506944444</v>
+        <v>46069.4729166667</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="G22" t="n">
-        <v>0.725</v>
+        <v>0.094</v>
       </c>
       <c r="H22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="L22" t="b">
         <v>1</v>
       </c>
       <c r="M22" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46069.4486111111</v>
+        <v>46068.9430555556</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46069.4833333333</v>
+        <v>46068.9555555556</v>
       </c>
       <c r="D23" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46069.4729166667</v>
+        <v>46068.9527777778</v>
       </c>
       <c r="F23" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G23" t="n">
-        <v>0.094</v>
+        <v>0.064</v>
       </c>
       <c r="H23" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I23" t="n">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="L23" t="b">
         <v>1</v>
@@ -1453,25 +1453,25 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46068.9430555556</v>
+        <v>46067.4930555556</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46068.9555555556</v>
+        <v>46067.50625</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46068.9527777778</v>
+        <v>46067.4958333333</v>
       </c>
       <c r="F24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G24" t="n">
-        <v>0.064</v>
+        <v>0.195</v>
       </c>
       <c r="H24" t="s">
         <v>14</v>
@@ -1480,92 +1480,92 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L24" t="b">
         <v>1</v>
       </c>
       <c r="M24" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46065.5520833333</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>46065.5770833333</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46065.56875</v>
+      </c>
+      <c r="F25" t="n">
+        <v>36</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="H25" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="1" t="n">
-        <v>46067.4930555556</v>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>46067.50625</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46067.4958333333</v>
-      </c>
-      <c r="F25" t="n">
-        <v>19</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="H25" t="s">
-        <v>14</v>
-      </c>
       <c r="I25" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="L25" t="b">
         <v>1</v>
       </c>
       <c r="M25" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46065.5520833333</v>
+        <v>46056.6743055556</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46065.5770833333</v>
+        <v>46056.7125</v>
       </c>
       <c r="D26" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46065.56875</v>
+        <v>46056.6763888889</v>
       </c>
       <c r="F26" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="G26" t="n">
-        <v>0.141</v>
+        <v>0.194</v>
       </c>
       <c r="H26" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I26" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="J26" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
@@ -1576,201 +1576,201 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46056.6743055556</v>
+        <v>46046.1458333333</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46056.7125</v>
+        <v>46046.1729166667</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46056.6763888889</v>
+        <v>46046.1555555556</v>
       </c>
       <c r="F27" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G27" t="n">
-        <v>0.194</v>
+        <v>0.064</v>
       </c>
       <c r="H27" t="s">
         <v>14</v>
       </c>
       <c r="I27" t="n">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="J27" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="K27" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
       </c>
       <c r="M27" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46046.1458333333</v>
+        <v>46038.7298611111</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46046.1729166667</v>
+        <v>46038.7590277778</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9</v>
+        <v>23.7</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46046.1555555556</v>
+        <v>46038.7513888889</v>
       </c>
       <c r="F28" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G28" t="n">
-        <v>0.064</v>
+        <v>0.762</v>
       </c>
       <c r="H28" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I28" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L28" t="b">
         <v>1</v>
       </c>
       <c r="M28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46038.7298611111</v>
+        <v>46037.1930555556</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46038.7590277778</v>
+        <v>46037.2333333333</v>
       </c>
       <c r="D29" t="n">
-        <v>23.7</v>
+        <v>0.6</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46038.7513888889</v>
+        <v>46037.2048611111</v>
       </c>
       <c r="F29" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="G29" t="n">
-        <v>0.762</v>
+        <v>0.035</v>
       </c>
       <c r="H29" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I29" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
       </c>
       <c r="M29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46037.1930555556</v>
+        <v>46036.4458333333</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46037.2333333333</v>
+        <v>46036.4875</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46037.2048611111</v>
+        <v>46036.4493055556</v>
       </c>
       <c r="F30" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G30" t="n">
-        <v>0.035</v>
+        <v>0.412</v>
       </c>
       <c r="H30" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="L30" t="b">
         <v>1</v>
       </c>
       <c r="M30" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46036.4458333333</v>
+        <v>46034.2236111111</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46036.4875</v>
+        <v>46034.2520833333</v>
       </c>
       <c r="D31" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46036.4493055556</v>
+        <v>46034.2326388889</v>
       </c>
       <c r="F31" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="G31" t="n">
-        <v>0.412</v>
+        <v>0.061</v>
       </c>
       <c r="H31" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I31" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="K31" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="L31" t="b">
         <v>1</v>
@@ -1781,37 +1781,37 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46034.2236111111</v>
+        <v>46031.6548611111</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46034.2520833333</v>
+        <v>46031.6736111111</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46034.2326388889</v>
+        <v>46031.6597222222</v>
       </c>
       <c r="F32" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G32" t="n">
-        <v>0.061</v>
+        <v>0.085</v>
       </c>
       <c r="H32" t="s">
         <v>14</v>
       </c>
       <c r="I32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="L32" t="b">
         <v>1</v>
@@ -1822,25 +1822,25 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46031.6548611111</v>
+        <v>46031.4881944444</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46031.6736111111</v>
+        <v>46031.5034722222</v>
       </c>
       <c r="D33" t="n">
         <v>0.6</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46031.6597222222</v>
+        <v>46031.4965277778</v>
       </c>
       <c r="F33" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G33" t="n">
-        <v>0.085</v>
+        <v>0.05</v>
       </c>
       <c r="H33" t="s">
         <v>14</v>
@@ -1849,10 +1849,10 @@
         <v>5</v>
       </c>
       <c r="J33" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="K33" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="L33" t="b">
         <v>1</v>
@@ -1863,37 +1863,37 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46031.4881944444</v>
+        <v>46026.2631944444</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46031.5034722222</v>
+        <v>46026.2770833333</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46031.4965277778</v>
+        <v>46026.2659722222</v>
       </c>
       <c r="F34" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G34" t="n">
-        <v>0.05</v>
+        <v>0.488</v>
       </c>
       <c r="H34" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="L34" t="b">
         <v>1</v>
@@ -1904,75 +1904,75 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>46010.6055555556</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46010.6354166667</v>
+      </c>
+      <c r="D35" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46010.6229166667</v>
+      </c>
+      <c r="F35" t="n">
+        <v>43</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H35" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="1" t="n">
-        <v>46026.2631944444</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46026.2770833333</v>
-      </c>
-      <c r="D35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46026.2659722222</v>
-      </c>
-      <c r="F35" t="n">
-        <v>20</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="H35" t="s">
-        <v>21</v>
-      </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="J35" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L35" t="b">
         <v>1</v>
       </c>
       <c r="M35" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46010.6055555556</v>
+        <v>46010.3430555556</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46010.6354166667</v>
+        <v>46010.3534722222</v>
       </c>
       <c r="D36" t="n">
-        <v>34.9</v>
+        <v>0.8</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46010.6229166667</v>
+        <v>46010.3479166667</v>
       </c>
       <c r="F36" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="G36" t="n">
-        <v>1.39</v>
+        <v>0.113</v>
       </c>
       <c r="H36" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I36" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="J36" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K36" t="n">
         <v>0.3</v>
@@ -1981,83 +1981,83 @@
         <v>1</v>
       </c>
       <c r="M36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46010.3430555556</v>
+        <v>46001.1465277778</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46010.3534722222</v>
+        <v>46001.1597222222</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46010.3479166667</v>
+        <v>46001.1506944444</v>
       </c>
       <c r="F37" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G37" t="n">
-        <v>0.113</v>
+        <v>0.098</v>
       </c>
       <c r="H37" t="s">
         <v>14</v>
       </c>
       <c r="I37" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J37" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K37" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L37" t="b">
         <v>1</v>
       </c>
       <c r="M37" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46001.1465277778</v>
+        <v>45999.9777777778</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46001.1597222222</v>
+        <v>46000.00625</v>
       </c>
       <c r="D38" t="n">
         <v>0.6</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46001.1506944444</v>
+        <v>45999.9875</v>
       </c>
       <c r="F38" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="G38" t="n">
-        <v>0.098</v>
+        <v>0.043</v>
       </c>
       <c r="H38" t="s">
         <v>14</v>
       </c>
       <c r="I38" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L38" t="b">
         <v>1</v>
@@ -2071,34 +2071,34 @@
         <v>13</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>45999.9777777778</v>
+        <v>45998.8833333333</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46000.00625</v>
+        <v>45998.9118055556</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>45999.9875</v>
+        <v>45998.8979166667</v>
       </c>
       <c r="F39" t="n">
         <v>41</v>
       </c>
       <c r="G39" t="n">
-        <v>0.043</v>
+        <v>0.033</v>
       </c>
       <c r="H39" t="s">
         <v>14</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="J39" t="n">
-        <v>2.4</v>
+        <v>7.1</v>
       </c>
       <c r="K39" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="L39" t="b">
         <v>1</v>
@@ -2109,66 +2109,66 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>45998.8833333333</v>
+        <v>45994.9763888889</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45998.9118055556</v>
+        <v>45995.0069444444</v>
       </c>
       <c r="D40" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>45998.8979166667</v>
+        <v>45995</v>
       </c>
       <c r="F40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G40" t="n">
-        <v>0.033</v>
+        <v>0.018</v>
       </c>
       <c r="H40" t="s">
         <v>14</v>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J40" t="n">
-        <v>7.1</v>
+        <v>1.1</v>
       </c>
       <c r="K40" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="L40" t="b">
         <v>1</v>
       </c>
       <c r="M40" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>45994.9763888889</v>
+        <v>45993.1833333333</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45995.0069444444</v>
+        <v>45993.2048611111</v>
       </c>
       <c r="D41" t="n">
         <v>0.6</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>45995</v>
+        <v>45993.1923611111</v>
       </c>
       <c r="F41" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G41" t="n">
-        <v>0.018</v>
+        <v>0.046</v>
       </c>
       <c r="H41" t="s">
         <v>14</v>
@@ -2177,16 +2177,16 @@
         <v>8</v>
       </c>
       <c r="J41" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="K41" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L41" t="b">
         <v>1</v>
       </c>
       <c r="M41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42">
@@ -2194,31 +2194,31 @@
         <v>16</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>45993.1833333333</v>
+        <v>45991.2326388889</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45993.2048611111</v>
+        <v>45991.2395833333</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>45993.1923611111</v>
+        <v>45991.2375</v>
       </c>
       <c r="F42" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G42" t="n">
-        <v>0.046</v>
+        <v>0.099</v>
       </c>
       <c r="H42" t="s">
         <v>14</v>
       </c>
       <c r="I42" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="K42" t="n">
         <v>0.1</v>
@@ -2227,121 +2227,121 @@
         <v>1</v>
       </c>
       <c r="M42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>45989.3763888889</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>45989.4041666667</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>45989.3993055556</v>
+      </c>
+      <c r="F43" t="n">
+        <v>40</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="H43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" t="n">
+        <v>13</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L43" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" t="s">
         <v>17</v>
-      </c>
-      <c r="B43" s="1" t="n">
-        <v>45991.2326388889</v>
-      </c>
-      <c r="C43" s="1" t="n">
-        <v>45991.2395833333</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E43" s="1" t="n">
-        <v>45991.2375</v>
-      </c>
-      <c r="F43" t="n">
-        <v>10</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="H43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I43" t="n">
-        <v>4</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L43" t="b">
-        <v>1</v>
-      </c>
-      <c r="M43" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>45989.3763888889</v>
+        <v>45986.3493055556</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45989.4041666667</v>
+        <v>45986.3743055556</v>
       </c>
       <c r="D44" t="n">
         <v>1.3</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>45989.3993055556</v>
+        <v>45986.3645833333</v>
       </c>
       <c r="F44" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G44" t="n">
-        <v>0.039</v>
+        <v>0.059</v>
       </c>
       <c r="H44" t="s">
         <v>14</v>
       </c>
       <c r="I44" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J44" t="n">
         <v>0.3</v>
       </c>
       <c r="K44" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L44" t="b">
         <v>1</v>
       </c>
       <c r="M44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>45986.3493055556</v>
+        <v>45986.0444444444</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45986.3743055556</v>
+        <v>45986.05</v>
       </c>
       <c r="D45" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>45986.3645833333</v>
+        <v>45986.0479166667</v>
       </c>
       <c r="F45" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="G45" t="n">
-        <v>0.059</v>
+        <v>0.157</v>
       </c>
       <c r="H45" t="s">
         <v>14</v>
       </c>
       <c r="I45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J45" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="K45" t="n">
         <v>0.1</v>
@@ -2350,162 +2350,162 @@
         <v>1</v>
       </c>
       <c r="M45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>45986.0444444444</v>
+        <v>45985.60625</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45986.05</v>
+        <v>45985.6340277778</v>
       </c>
       <c r="D46" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>45986.0479166667</v>
+        <v>45985.6305555556</v>
       </c>
       <c r="F46" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="G46" t="n">
-        <v>0.157</v>
+        <v>0.017</v>
       </c>
       <c r="H46" t="s">
         <v>14</v>
       </c>
       <c r="I46" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="L46" t="b">
         <v>1</v>
       </c>
       <c r="M46" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>45985.60625</v>
+        <v>45985.5916666667</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45985.6340277778</v>
+        <v>45985.6</v>
       </c>
       <c r="D47" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>45985.6305555556</v>
+        <v>45985.5965277778</v>
       </c>
       <c r="F47" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G47" t="n">
-        <v>0.017</v>
+        <v>0.592</v>
       </c>
       <c r="H47" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I47" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J47" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>45985.5916666667</v>
+        <v>45980.9888888889</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45985.6</v>
+        <v>45981.0069444444</v>
       </c>
       <c r="D48" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>45985.5965277778</v>
+        <v>45981.0027777778</v>
       </c>
       <c r="F48" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G48" t="n">
-        <v>0.592</v>
+        <v>0.03</v>
       </c>
       <c r="H48" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I48" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="K48" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="L48" t="b">
         <v>1</v>
       </c>
       <c r="M48" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>45980.9888888889</v>
+        <v>45980.9451388889</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45981.0069444444</v>
+        <v>45980.9715277778</v>
       </c>
       <c r="D49" t="n">
         <v>0.6</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>45981.0027777778</v>
+        <v>45980.9486111111</v>
       </c>
       <c r="F49" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="G49" t="n">
-        <v>0.03</v>
+        <v>0.118</v>
       </c>
       <c r="H49" t="s">
         <v>14</v>
       </c>
       <c r="I49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K49" t="n">
         <v>1.3</v>
@@ -2519,107 +2519,107 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>45980.9451388889</v>
+        <v>45977.8520833333</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45980.9715277778</v>
+        <v>45977.8861111111</v>
       </c>
       <c r="D50" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>45980.9486111111</v>
+        <v>45977.8638888889</v>
       </c>
       <c r="F50" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G50" t="n">
-        <v>0.118</v>
+        <v>0.041</v>
       </c>
       <c r="H50" t="s">
         <v>14</v>
       </c>
       <c r="I50" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="K50" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
       </c>
       <c r="M50" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>45977.8520833333</v>
+        <v>45970.6055555556</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45977.8861111111</v>
+        <v>45970.6333333333</v>
       </c>
       <c r="D51" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>45970.6284722222</v>
+      </c>
+      <c r="F51" t="n">
+        <v>40</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="H51" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K51" t="n">
         <v>0.7</v>
       </c>
-      <c r="E51" s="1" t="n">
-        <v>45977.8638888889</v>
-      </c>
-      <c r="F51" t="n">
-        <v>49</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="H51" t="s">
-        <v>14</v>
-      </c>
-      <c r="I51" t="n">
-        <v>6</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0.1</v>
-      </c>
       <c r="L51" t="b">
         <v>1</v>
       </c>
       <c r="M51" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>45970.6055555556</v>
+        <v>45962.6513888889</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45970.6333333333</v>
+        <v>45962.6715277778</v>
       </c>
       <c r="D52" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>45970.6284722222</v>
+        <v>45962.6583333333</v>
       </c>
       <c r="F52" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G52" t="n">
-        <v>0.018</v>
+        <v>0.109</v>
       </c>
       <c r="H52" t="s">
         <v>14</v>
@@ -2628,10 +2628,10 @@
         <v>5</v>
       </c>
       <c r="J52" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="K52" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="L52" t="b">
         <v>1</v>
@@ -2642,37 +2642,37 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>45962.6513888889</v>
+        <v>45960.3222222222</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45962.6715277778</v>
+        <v>45960.3430555556</v>
       </c>
       <c r="D53" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>45960.3319444444</v>
+      </c>
+      <c r="F53" t="n">
+        <v>30</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="H53" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" t="n">
+        <v>8</v>
+      </c>
+      <c r="J53" t="n">
         <v>1.1</v>
       </c>
-      <c r="E53" s="1" t="n">
-        <v>45962.6583333333</v>
-      </c>
-      <c r="F53" t="n">
-        <v>29</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="H53" t="s">
-        <v>14</v>
-      </c>
-      <c r="I53" t="n">
-        <v>5</v>
-      </c>
-      <c r="J53" t="n">
-        <v>5.5</v>
-      </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="L53" t="b">
         <v>1</v>
@@ -2683,25 +2683,25 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>45960.3222222222</v>
+        <v>45958.5965277778</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45960.3430555556</v>
+        <v>45958.6138888889</v>
       </c>
       <c r="D54" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>45960.3319444444</v>
+        <v>45958.6055555556</v>
       </c>
       <c r="F54" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G54" t="n">
-        <v>0.057</v>
+        <v>0.107</v>
       </c>
       <c r="H54" t="s">
         <v>14</v>
@@ -2710,10 +2710,10 @@
         <v>8</v>
       </c>
       <c r="J54" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="K54" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="L54" t="b">
         <v>1</v>
@@ -2724,66 +2724,66 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>45958.5965277778</v>
+        <v>45958.3965277778</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45958.6138888889</v>
+        <v>45958.4298611111</v>
       </c>
       <c r="D55" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>45958.6055555556</v>
+        <v>45958.4201388889</v>
       </c>
       <c r="F55" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="G55" t="n">
-        <v>0.107</v>
+        <v>0.018</v>
       </c>
       <c r="H55" t="s">
         <v>14</v>
       </c>
       <c r="I55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="K55" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="L55" t="b">
         <v>1</v>
       </c>
       <c r="M55" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>45958.3965277778</v>
+        <v>45958.3354166667</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45958.4298611111</v>
+        <v>45958.3555555556</v>
       </c>
       <c r="D56" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>45958.4201388889</v>
+        <v>45958.3513888889</v>
       </c>
       <c r="F56" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="G56" t="n">
-        <v>0.018</v>
+        <v>0.039</v>
       </c>
       <c r="H56" t="s">
         <v>14</v>
@@ -2792,45 +2792,45 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="K56" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
       </c>
       <c r="M56" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>45958.3354166667</v>
+        <v>45958.3041666667</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45958.3555555556</v>
+        <v>45958.3180555556</v>
       </c>
       <c r="D57" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>45958.3513888889</v>
+        <v>45958.3152777778</v>
       </c>
       <c r="F57" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G57" t="n">
-        <v>0.039</v>
+        <v>0.062</v>
       </c>
       <c r="H57" t="s">
         <v>14</v>
       </c>
       <c r="I57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J57" t="n">
         <v>1.8</v>
@@ -2847,37 +2847,37 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>45958.3041666667</v>
+        <v>45957.4340277778</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45958.3180555556</v>
+        <v>45957.4534722222</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>45958.3152777778</v>
+        <v>45957.4451388889</v>
       </c>
       <c r="F58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G58" t="n">
-        <v>0.062</v>
+        <v>0.043</v>
       </c>
       <c r="H58" t="s">
         <v>14</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J58" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K58" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
@@ -2888,22 +2888,22 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>45957.4340277778</v>
+        <v>45957.1083333333</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45957.4534722222</v>
+        <v>45957.1243055556</v>
       </c>
       <c r="D59" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>45957.4451388889</v>
+        <v>45957.1180555556</v>
       </c>
       <c r="F59" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G59" t="n">
         <v>0.043</v>
@@ -2912,13 +2912,13 @@
         <v>14</v>
       </c>
       <c r="I59" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K59" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="L59" t="b">
         <v>1</v>
@@ -2929,113 +2929,113 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>45957.1083333333</v>
+        <v>45956.5763888889</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45957.1243055556</v>
+        <v>45956.5909722222</v>
       </c>
       <c r="D60" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>45957.1180555556</v>
+        <v>45956.5875</v>
       </c>
       <c r="F60" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G60" t="n">
-        <v>0.043</v>
+        <v>0.118</v>
       </c>
       <c r="H60" t="s">
         <v>14</v>
       </c>
       <c r="I60" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J60" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="K60" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="L60" t="b">
         <v>1</v>
       </c>
       <c r="M60" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>45956.5763888889</v>
+        <v>45953.7131944444</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45956.5909722222</v>
+        <v>45953.7277777778</v>
       </c>
       <c r="D61" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>45956.5875</v>
+        <v>45953.7222222222</v>
       </c>
       <c r="F61" t="n">
         <v>21</v>
       </c>
       <c r="G61" t="n">
-        <v>0.118</v>
+        <v>0.122</v>
       </c>
       <c r="H61" t="s">
         <v>14</v>
       </c>
       <c r="I61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="L61" t="b">
         <v>1</v>
       </c>
       <c r="M61" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>45953.7131944444</v>
+        <v>45953.7097222222</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45953.7277777778</v>
+        <v>45953.7395833333</v>
       </c>
       <c r="D62" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>45953.7222222222</v>
+        <v>45953.7201388889</v>
       </c>
       <c r="F62" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="G62" t="n">
-        <v>0.122</v>
+        <v>0.046</v>
       </c>
       <c r="H62" t="s">
         <v>14</v>
       </c>
       <c r="I62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J62" t="n">
         <v>2.5</v>
@@ -3052,37 +3052,37 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>45953.7097222222</v>
+        <v>45953.5881944444</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45953.7395833333</v>
+        <v>45953.5986111111</v>
       </c>
       <c r="D63" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>45953.7201388889</v>
+        <v>45953.5909722222</v>
       </c>
       <c r="F63" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="G63" t="n">
-        <v>0.046</v>
+        <v>0.512</v>
       </c>
       <c r="H63" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J63" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="K63" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
@@ -3093,37 +3093,37 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>45953.1763888889</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>45953.2020833333</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>45953.1895833333</v>
+      </c>
+      <c r="F64" t="n">
+        <v>37</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="H64" t="s">
         <v>19</v>
       </c>
-      <c r="B64" s="1" t="n">
-        <v>45953.5881944444</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>45953.5986111111</v>
-      </c>
-      <c r="D64" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E64" s="1" t="n">
-        <v>45953.5909722222</v>
-      </c>
-      <c r="F64" t="n">
-        <v>15</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0.512</v>
-      </c>
-      <c r="H64" t="s">
+      <c r="I64" t="n">
         <v>20</v>
       </c>
-      <c r="I64" t="n">
-        <v>4</v>
-      </c>
       <c r="J64" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="K64" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="L64" t="b">
         <v>1</v>
@@ -3134,37 +3134,37 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>45953.1763888889</v>
+        <v>45951.2659722222</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45953.2020833333</v>
+        <v>45951.2895833333</v>
       </c>
       <c r="D65" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>45953.1895833333</v>
+        <v>45951.2680555556</v>
       </c>
       <c r="F65" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G65" t="n">
-        <v>0.141</v>
+        <v>0.226</v>
       </c>
       <c r="H65" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J65" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="K65" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
@@ -3178,66 +3178,66 @@
         <v>16</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>45951.2659722222</v>
+        <v>45948.1659722222</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45951.2895833333</v>
+        <v>45948.2069444444</v>
       </c>
       <c r="D66" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>45951.2680555556</v>
+        <v>45948.1777777778</v>
       </c>
       <c r="F66" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="G66" t="n">
-        <v>0.226</v>
+        <v>0.257</v>
       </c>
       <c r="H66" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="L66" t="b">
         <v>1</v>
       </c>
       <c r="M66" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>45948.1659722222</v>
+        <v>45948.1201388889</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45948.2069444444</v>
+        <v>45948.1409722222</v>
       </c>
       <c r="D67" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>45948.1777777778</v>
+        <v>45948.1368055556</v>
       </c>
       <c r="F67" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="G67" t="n">
-        <v>0.257</v>
+        <v>0.046</v>
       </c>
       <c r="H67" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I67" t="n">
         <v>5</v>
@@ -3252,30 +3252,30 @@
         <v>1</v>
       </c>
       <c r="M67" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>45948.1201388889</v>
+        <v>45948.0152777778</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45948.1409722222</v>
+        <v>45948.0430555556</v>
       </c>
       <c r="D68" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>45948.1368055556</v>
+        <v>45948.0243055556</v>
       </c>
       <c r="F68" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G68" t="n">
-        <v>0.046</v>
+        <v>0.061</v>
       </c>
       <c r="H68" t="s">
         <v>14</v>
@@ -3293,36 +3293,36 @@
         <v>1</v>
       </c>
       <c r="M68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>45948.0152777778</v>
+        <v>45946.8027777778</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45948.0430555556</v>
+        <v>45946.8180555556</v>
       </c>
       <c r="D69" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>45948.0243055556</v>
+        <v>45946.8159722222</v>
       </c>
       <c r="F69" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G69" t="n">
-        <v>0.061</v>
+        <v>0.063</v>
       </c>
       <c r="H69" t="s">
         <v>14</v>
       </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
         <v>0.1</v>
@@ -3334,48 +3334,48 @@
         <v>1</v>
       </c>
       <c r="M69" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>45946.8027777778</v>
+        <v>45946.6076388889</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45946.8180555556</v>
+        <v>45946.6354166667</v>
       </c>
       <c r="D70" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>45946.8159722222</v>
+        <v>45946.6194444444</v>
       </c>
       <c r="F70" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G70" t="n">
-        <v>0.063</v>
+        <v>0.035</v>
       </c>
       <c r="H70" t="s">
         <v>14</v>
       </c>
       <c r="I70" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J70" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L70" t="b">
         <v>1</v>
       </c>
       <c r="M70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71">
@@ -3383,69 +3383,69 @@
         <v>16</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>45946.6076388889</v>
+        <v>45943.0444444444</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45946.6354166667</v>
+        <v>45943.0583333333</v>
       </c>
       <c r="D71" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>45946.6194444444</v>
+        <v>45943.0555555556</v>
       </c>
       <c r="F71" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G71" t="n">
-        <v>0.035</v>
+        <v>0.062</v>
       </c>
       <c r="H71" t="s">
         <v>14</v>
       </c>
       <c r="I71" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="K71" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L71" t="b">
         <v>1</v>
       </c>
       <c r="M71" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>45943.0444444444</v>
+        <v>45942.2895833333</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45943.0583333333</v>
+        <v>45942.3166666667</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>45943.0555555556</v>
+        <v>45942.3048611111</v>
       </c>
       <c r="F72" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G72" t="n">
-        <v>0.062</v>
+        <v>0.226</v>
       </c>
       <c r="H72" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J72" t="n">
         <v>0.1</v>
@@ -3457,253 +3457,253 @@
         <v>1</v>
       </c>
       <c r="M72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
+        <v>13</v>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>45939.2444444444</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>45939.2652777778</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>45939.2548611111</v>
+      </c>
+      <c r="F73" t="n">
+        <v>30</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H73" t="s">
+        <v>14</v>
+      </c>
+      <c r="I73" t="n">
+        <v>7</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L73" t="b">
+        <v>1</v>
+      </c>
+      <c r="M73" t="s">
         <v>17</v>
-      </c>
-      <c r="B73" s="1" t="n">
-        <v>45942.2895833333</v>
-      </c>
-      <c r="C73" s="1" t="n">
-        <v>45942.3166666667</v>
-      </c>
-      <c r="D73" t="n">
-        <v>5</v>
-      </c>
-      <c r="E73" s="1" t="n">
-        <v>45942.3048611111</v>
-      </c>
-      <c r="F73" t="n">
-        <v>39</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="H73" t="s">
-        <v>20</v>
-      </c>
-      <c r="I73" t="n">
-        <v>12</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L73" t="b">
-        <v>1</v>
-      </c>
-      <c r="M73" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>45939.2444444444</v>
+        <v>45939.1743055556</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45939.2652777778</v>
+        <v>45939.1833333333</v>
       </c>
       <c r="D74" t="n">
         <v>0.6</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>45939.2548611111</v>
+        <v>45939.1763888889</v>
       </c>
       <c r="F74" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G74" t="n">
-        <v>0.04</v>
+        <v>0.194</v>
       </c>
       <c r="H74" t="s">
         <v>14</v>
       </c>
       <c r="I74" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="K74" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L74" t="b">
         <v>1</v>
       </c>
       <c r="M74" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>45939.1743055556</v>
+        <v>45933.9763888889</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45939.1833333333</v>
+        <v>45933.9902777778</v>
       </c>
       <c r="D75" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>45939.1763888889</v>
+        <v>45933.98125</v>
       </c>
       <c r="F75" t="n">
+        <v>20</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="H75" t="s">
+        <v>14</v>
+      </c>
+      <c r="I75" t="n">
         <v>13</v>
       </c>
-      <c r="G75" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="H75" t="s">
-        <v>14</v>
-      </c>
-      <c r="I75" t="n">
-        <v>6</v>
-      </c>
       <c r="J75" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="K75" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="L75" t="b">
         <v>1</v>
       </c>
       <c r="M75" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>16</v>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>45930.2208333333</v>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>45930.2513888889</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>45930.2375</v>
+      </c>
+      <c r="F76" t="n">
+        <v>44</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="H76" t="s">
         <v>19</v>
       </c>
-      <c r="B76" s="1" t="n">
-        <v>45933.9763888889</v>
-      </c>
-      <c r="C76" s="1" t="n">
-        <v>45933.9902777778</v>
-      </c>
-      <c r="D76" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E76" s="1" t="n">
-        <v>45933.98125</v>
-      </c>
-      <c r="F76" t="n">
-        <v>20</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="H76" t="s">
-        <v>14</v>
-      </c>
       <c r="I76" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J76" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="K76" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="L76" t="b">
         <v>1</v>
       </c>
       <c r="M76" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
+        <v>16</v>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>45925.4902777778</v>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>45925.5319444444</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>45925.5201388889</v>
+      </c>
+      <c r="F77" t="n">
+        <v>60</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="H77" t="s">
+        <v>14</v>
+      </c>
+      <c r="I77" t="n">
+        <v>10</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L77" t="b">
+        <v>1</v>
+      </c>
+      <c r="M77" t="s">
         <v>17</v>
-      </c>
-      <c r="B77" s="1" t="n">
-        <v>45930.2208333333</v>
-      </c>
-      <c r="C77" s="1" t="n">
-        <v>45930.2513888889</v>
-      </c>
-      <c r="D77" t="n">
-        <v>3</v>
-      </c>
-      <c r="E77" s="1" t="n">
-        <v>45930.2375</v>
-      </c>
-      <c r="F77" t="n">
-        <v>44</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="H77" t="s">
-        <v>20</v>
-      </c>
-      <c r="I77" t="n">
-        <v>5</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L77" t="b">
-        <v>1</v>
-      </c>
-      <c r="M77" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>45925.4902777778</v>
+        <v>45921.4229166667</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45925.5319444444</v>
+        <v>45921.4423611111</v>
       </c>
       <c r="D78" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>45925.5201388889</v>
+        <v>45921.4284722222</v>
       </c>
       <c r="F78" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="G78" t="n">
-        <v>0.016</v>
+        <v>0.074</v>
       </c>
       <c r="H78" t="s">
         <v>14</v>
       </c>
       <c r="I78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J78" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="K78" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="L78" t="b">
         <v>1</v>
       </c>
       <c r="M78" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79">
@@ -3711,34 +3711,34 @@
         <v>16</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>45921.4229166667</v>
+        <v>45921.2979166667</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45921.4423611111</v>
+        <v>45921.3111111111</v>
       </c>
       <c r="D79" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>45921.4284722222</v>
+        <v>45921.3034722222</v>
       </c>
       <c r="F79" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G79" t="n">
-        <v>0.074</v>
+        <v>0.123</v>
       </c>
       <c r="H79" t="s">
         <v>14</v>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J79" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="K79" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="L79" t="b">
         <v>1</v>
@@ -3749,84 +3749,43 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80" s="1" t="n">
+        <v>45710.3541666667</v>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>45710.3854166667</v>
+      </c>
+      <c r="D80" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="E80" s="1" t="n">
+        <v>45710.375</v>
+      </c>
+      <c r="F80" t="n">
+        <v>45</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="H80" t="s">
+        <v>19</v>
+      </c>
+      <c r="I80" t="n">
+        <v>4</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="b">
+        <v>0</v>
+      </c>
+      <c r="M80" t="s">
         <v>17</v>
-      </c>
-      <c r="B80" s="1" t="n">
-        <v>45921.2979166667</v>
-      </c>
-      <c r="C80" s="1" t="n">
-        <v>45921.3111111111</v>
-      </c>
-      <c r="D80" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="1" t="n">
-        <v>45921.3034722222</v>
-      </c>
-      <c r="F80" t="n">
-        <v>19</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="H80" t="s">
-        <v>14</v>
-      </c>
-      <c r="I80" t="n">
-        <v>8</v>
-      </c>
-      <c r="J80" t="n">
-        <v>1</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L80" t="b">
-        <v>1</v>
-      </c>
-      <c r="M80" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>22</v>
-      </c>
-      <c r="B81" s="1" t="n">
-        <v>45710.3541666667</v>
-      </c>
-      <c r="C81" s="1" t="n">
-        <v>45710.3854166667</v>
-      </c>
-      <c r="D81" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="E81" s="1" t="n">
-        <v>45710.375</v>
-      </c>
-      <c r="F81" t="n">
-        <v>45</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0.651</v>
-      </c>
-      <c r="H81" t="s">
-        <v>20</v>
-      </c>
-      <c r="I81" t="n">
-        <v>4</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="b">
-        <v>0</v>
-      </c>
-      <c r="M81" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3877,7 +3836,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B2" t="n">
         <v>28</v>
@@ -3900,7 +3859,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" t="n">
         <v>25</v>
@@ -3923,7 +3882,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -3946,10 +3905,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
         <v>0.6</v>
@@ -4046,7 +4005,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>46010.6055555556</v>
@@ -4061,7 +4020,7 @@
         <v>1.39</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
         <v>0.6</v>
@@ -4070,12 +4029,12 @@
         <v>0.3</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>46038.7298611111</v>
@@ -4090,7 +4049,7 @@
         <v>0.762</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
         <v>0.6</v>
@@ -4099,7 +4058,7 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -4119,7 +4078,7 @@
         <v>0.651</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4128,12 +4087,12 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>46114.5555555556</v>
@@ -4148,7 +4107,7 @@
         <v>0.479</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
         <v>0.1</v>
@@ -4157,12 +4116,12 @@
         <v>0.1</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>45942.2895833333</v>
@@ -4177,7 +4136,7 @@
         <v>0.226</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" t="n">
         <v>0.1</v>
@@ -4186,12 +4145,12 @@
         <v>0.1</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>46072.4020833333</v>
@@ -4206,7 +4165,7 @@
         <v>0.58</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
         <v>1.5</v>
@@ -4220,7 +4179,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>45948.1659722222</v>
@@ -4244,12 +4203,12 @@
         <v>0.1</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>46075.9055555556</v>
@@ -4264,7 +4223,7 @@
         <v>0.347</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G9" t="n">
         <v>1.6</v>
@@ -4278,7 +4237,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>45985.5916666667</v>
@@ -4293,7 +4252,7 @@
         <v>0.592</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G10" t="n">
         <v>0.8</v>
@@ -4302,12 +4261,12 @@
         <v>0.3</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>46070.6472222222</v>
@@ -4322,7 +4281,7 @@
         <v>0.725</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11" t="n">
         <v>0.2</v>
@@ -4331,12 +4290,12 @@
         <v>0.1</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>46065.5520833333</v>
@@ -4351,7 +4310,7 @@
         <v>0.141</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G12" t="n">
         <v>1.9</v>
@@ -4365,7 +4324,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>46069.4486111111</v>
@@ -4394,7 +4353,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>46072.5090277778</v>
@@ -4409,7 +4368,7 @@
         <v>0.147</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G14" t="n">
         <v>3.4</v>
@@ -4423,7 +4382,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>45930.2208333333</v>
@@ -4438,7 +4397,7 @@
         <v>0.124</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G15" t="n">
         <v>0.1</v>
@@ -4447,12 +4406,12 @@
         <v>0.1</v>
       </c>
       <c r="I15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>45953.1763888889</v>
@@ -4467,7 +4426,7 @@
         <v>0.141</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G16" t="n">
         <v>1.9</v>
@@ -4481,7 +4440,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>46036.4458333333</v>
@@ -4510,7 +4469,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>45953.5881944444</v>
@@ -4525,7 +4484,7 @@
         <v>0.512</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G18" t="n">
         <v>0.6</v>
@@ -4539,7 +4498,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>46026.2631944444</v>
@@ -4568,7 +4527,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>45956.5763888889</v>
@@ -4592,12 +4551,12 @@
         <v>0.1</v>
       </c>
       <c r="I20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>45953.7131944444</v>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -52,6 +52,21 @@
     <t xml:space="preserve">points_count</t>
   </si>
   <si>
+    <t xml:space="preserve">Königsallee_Springorum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/13 18:05:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/13 18:58:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/13 18:26:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wasserstraße_Springorum</t>
   </si>
   <si>
@@ -64,25 +79,10 @@
     <t xml:space="preserve">2026/04/13 11:19:30</t>
   </si>
   <si>
-    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Königsallee_Springorum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/12 02:34:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/12 03:20:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/12 03:07:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/11 19:17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/11 19:54:30</t>
+    <t xml:space="preserve">2026/04/11 19:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 19:50:30</t>
   </si>
   <si>
     <t xml:space="preserve">2026/04/11 19:47:00</t>
@@ -2598,16 +2598,16 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>33.5</v>
+        <v>53</v>
       </c>
       <c r="G2" t="n">
-        <v>0.088</v>
+        <v>0.028</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
@@ -2616,7 +2616,7 @@
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -2630,16 +2630,16 @@
         <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>46</v>
+        <v>33.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.025</v>
+        <v>0.088</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
@@ -2648,12 +2648,12 @@
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -2662,16 +2662,16 @@
         <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E4" t="s">
         <v>23</v>
       </c>
       <c r="F4" t="n">
-        <v>37.5</v>
+        <v>19.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.027</v>
+        <v>0.043</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -2680,12 +2680,12 @@
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -2717,7 +2717,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
@@ -2749,7 +2749,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
@@ -2813,7 +2813,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
@@ -2845,7 +2845,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>40</v>
@@ -2877,7 +2877,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
         <v>43</v>
@@ -2909,7 +2909,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>46</v>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
         <v>49</v>
@@ -2973,7 +2973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>52</v>
@@ -3037,7 +3037,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
         <v>59</v>
@@ -3101,7 +3101,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
         <v>65</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
         <v>68</v>
@@ -3165,7 +3165,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
         <v>71</v>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
         <v>74</v>
@@ -3229,7 +3229,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
         <v>77</v>
@@ -3261,7 +3261,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
         <v>80</v>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
         <v>83</v>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
         <v>86</v>
@@ -3357,7 +3357,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
         <v>89</v>
@@ -3389,7 +3389,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
         <v>92</v>
@@ -3421,7 +3421,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
         <v>95</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
         <v>98</v>
@@ -3517,7 +3517,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
         <v>104</v>
@@ -3549,7 +3549,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
         <v>107</v>
@@ -3581,7 +3581,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
         <v>110</v>
@@ -3613,7 +3613,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
         <v>113</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
         <v>120</v>
@@ -3709,7 +3709,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
         <v>123</v>
@@ -3741,7 +3741,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
         <v>126</v>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
         <v>129</v>
@@ -3805,7 +3805,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
         <v>132</v>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
         <v>135</v>
@@ -3869,7 +3869,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
         <v>138</v>
@@ -3901,7 +3901,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
         <v>141</v>
@@ -3933,7 +3933,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
         <v>144</v>
@@ -3965,7 +3965,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
         <v>147</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
         <v>150</v>
@@ -4093,7 +4093,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
         <v>160</v>
@@ -4125,7 +4125,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
         <v>163</v>
@@ -4157,7 +4157,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
         <v>166</v>
@@ -4189,7 +4189,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
         <v>169</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
         <v>172</v>
@@ -4253,7 +4253,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
         <v>175</v>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
         <v>178</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
         <v>181</v>
@@ -4349,7 +4349,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
         <v>184</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
         <v>187</v>
@@ -4413,7 +4413,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
         <v>190</v>
@@ -4445,7 +4445,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
         <v>193</v>
@@ -4477,7 +4477,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B61" t="s">
         <v>196</v>
@@ -4509,7 +4509,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
         <v>199</v>
@@ -4541,7 +4541,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
         <v>202</v>
@@ -4893,7 +4893,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B74" t="s">
         <v>235</v>
@@ -5021,7 +5021,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
         <v>247</v>
@@ -5053,7 +5053,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
         <v>250</v>
@@ -5085,7 +5085,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B80" t="s">
         <v>253</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B81" t="s">
         <v>256</v>
@@ -5149,7 +5149,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B82" t="s">
         <v>259</v>
@@ -5181,7 +5181,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B83" t="s">
         <v>262</v>
@@ -5213,7 +5213,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B84" t="s">
         <v>265</v>
@@ -5277,7 +5277,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B86" t="s">
         <v>271</v>
@@ -5373,7 +5373,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B89" t="s">
         <v>280</v>
@@ -5405,7 +5405,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B90" t="s">
         <v>283</v>
@@ -5437,7 +5437,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B91" t="s">
         <v>286</v>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B92" t="s">
         <v>289</v>
@@ -5533,7 +5533,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B94" t="s">
         <v>295</v>
@@ -5629,7 +5629,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B97" t="s">
         <v>304</v>
@@ -5661,7 +5661,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B98" t="s">
         <v>307</v>
@@ -5821,7 +5821,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
         <v>322</v>
@@ -5853,7 +5853,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B104" t="s">
         <v>325</v>
@@ -5885,7 +5885,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B105" t="s">
         <v>328</v>
@@ -5917,7 +5917,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B106" t="s">
         <v>331</v>
@@ -5949,7 +5949,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B107" t="s">
         <v>334</v>
@@ -5981,7 +5981,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B108" t="s">
         <v>337</v>
@@ -6045,7 +6045,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B110" t="s">
         <v>343</v>
@@ -6173,7 +6173,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B114" t="s">
         <v>355</v>
@@ -6205,7 +6205,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B115" t="s">
         <v>358</v>
@@ -6237,7 +6237,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B116" t="s">
         <v>361</v>
@@ -6269,7 +6269,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B117" t="s">
         <v>364</v>
@@ -6301,7 +6301,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B118" t="s">
         <v>367</v>
@@ -6365,7 +6365,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B120" t="s">
         <v>373</v>
@@ -6397,7 +6397,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B121" t="s">
         <v>376</v>
@@ -6429,7 +6429,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B122" t="s">
         <v>379</v>
@@ -6461,7 +6461,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B123" t="s">
         <v>382</v>
@@ -6493,7 +6493,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B124" t="s">
         <v>385</v>
@@ -6525,7 +6525,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B125" t="s">
         <v>388</v>
@@ -6557,7 +6557,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B126" t="s">
         <v>391</v>
@@ -6589,7 +6589,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B127" t="s">
         <v>394</v>
@@ -6621,7 +6621,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B128" t="s">
         <v>397</v>
@@ -6653,7 +6653,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B129" t="s">
         <v>400</v>
@@ -6685,7 +6685,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B130" t="s">
         <v>403</v>
@@ -6717,7 +6717,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B131" t="s">
         <v>406</v>
@@ -6781,7 +6781,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B133" t="s">
         <v>412</v>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B137" t="s">
         <v>424</v>
@@ -6973,7 +6973,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B139" t="s">
         <v>430</v>
@@ -7005,7 +7005,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B140" t="s">
         <v>433</v>
@@ -7037,7 +7037,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B141" t="s">
         <v>436</v>
@@ -7069,7 +7069,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B142" t="s">
         <v>439</v>
@@ -7101,7 +7101,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B143" t="s">
         <v>442</v>
@@ -7133,7 +7133,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B144" t="s">
         <v>445</v>
@@ -7165,7 +7165,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B145" t="s">
         <v>448</v>
@@ -7197,7 +7197,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B146" t="s">
         <v>451</v>
@@ -7229,7 +7229,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B147" t="s">
         <v>454</v>
@@ -7261,7 +7261,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B148" t="s">
         <v>457</v>
@@ -7293,7 +7293,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B149" t="s">
         <v>460</v>
@@ -7325,7 +7325,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B150" t="s">
         <v>463</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B151" t="s">
         <v>466</v>
@@ -7389,7 +7389,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B152" t="s">
         <v>469</v>
@@ -7421,7 +7421,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B153" t="s">
         <v>472</v>
@@ -7453,7 +7453,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B154" t="s">
         <v>475</v>
@@ -7485,7 +7485,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B155" t="s">
         <v>478</v>
@@ -7517,7 +7517,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B156" t="s">
         <v>481</v>
@@ -7549,7 +7549,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B157" t="s">
         <v>484</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B158" t="s">
         <v>487</v>
@@ -7613,7 +7613,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B159" t="s">
         <v>490</v>
@@ -7645,7 +7645,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B160" t="s">
         <v>493</v>
@@ -7677,7 +7677,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B161" t="s">
         <v>496</v>
@@ -7741,7 +7741,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B163" t="s">
         <v>502</v>
@@ -7773,7 +7773,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B164" t="s">
         <v>505</v>
@@ -7805,7 +7805,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B165" t="s">
         <v>508</v>
@@ -7837,7 +7837,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B166" t="s">
         <v>511</v>
@@ -7869,7 +7869,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B167" t="s">
         <v>514</v>
@@ -7901,7 +7901,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B168" t="s">
         <v>517</v>
@@ -8317,7 +8317,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B181" t="s">
         <v>556</v>
@@ -8349,7 +8349,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B182" t="s">
         <v>559</v>
@@ -8381,7 +8381,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B183" t="s">
         <v>562</v>
@@ -8413,7 +8413,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B184" t="s">
         <v>565</v>
@@ -8445,7 +8445,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B185" t="s">
         <v>568</v>
@@ -8477,7 +8477,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B186" t="s">
         <v>571</v>
@@ -8509,7 +8509,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B187" t="s">
         <v>574</v>
@@ -8541,7 +8541,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B188" t="s">
         <v>577</v>
@@ -8573,7 +8573,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B189" t="s">
         <v>580</v>
@@ -8605,7 +8605,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B190" t="s">
         <v>583</v>
@@ -8637,7 +8637,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B191" t="s">
         <v>586</v>
@@ -8669,7 +8669,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B192" t="s">
         <v>589</v>
@@ -8701,7 +8701,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B193" t="s">
         <v>592</v>
@@ -8733,7 +8733,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B194" t="s">
         <v>595</v>
@@ -8765,7 +8765,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B195" t="s">
         <v>598</v>
@@ -8797,7 +8797,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B196" t="s">
         <v>601</v>
@@ -8829,7 +8829,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B197" t="s">
         <v>604</v>
@@ -8861,7 +8861,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B198" t="s">
         <v>607</v>
@@ -8893,7 +8893,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B199" t="s">
         <v>610</v>
@@ -8957,7 +8957,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B201" t="s">
         <v>616</v>
@@ -8989,7 +8989,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B202" t="s">
         <v>619</v>
@@ -9021,7 +9021,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B203" t="s">
         <v>622</v>
@@ -9053,7 +9053,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B204" t="s">
         <v>625</v>
@@ -9117,7 +9117,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B206" t="s">
         <v>631</v>
@@ -9149,7 +9149,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B207" t="s">
         <v>634</v>
@@ -9181,7 +9181,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B208" t="s">
         <v>637</v>
@@ -9213,7 +9213,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B209" t="s">
         <v>640</v>
@@ -9245,7 +9245,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B210" t="s">
         <v>643</v>
@@ -9277,7 +9277,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B211" t="s">
         <v>646</v>
@@ -9309,7 +9309,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B212" t="s">
         <v>649</v>
@@ -9341,7 +9341,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B213" t="s">
         <v>652</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B214" t="s">
         <v>655</v>
@@ -9405,7 +9405,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B215" t="s">
         <v>658</v>
@@ -9437,7 +9437,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B216" t="s">
         <v>661</v>
@@ -9469,7 +9469,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B217" t="s">
         <v>664</v>
@@ -9501,7 +9501,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B218" t="s">
         <v>667</v>
@@ -9533,7 +9533,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B219" t="s">
         <v>670</v>
@@ -9565,7 +9565,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B220" t="s">
         <v>673</v>
@@ -9597,7 +9597,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B221" t="s">
         <v>676</v>
@@ -9629,7 +9629,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B222" t="s">
         <v>679</v>
@@ -9661,7 +9661,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B223" t="s">
         <v>682</v>
@@ -9693,7 +9693,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B224" t="s">
         <v>685</v>
@@ -9725,7 +9725,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B225" t="s">
         <v>688</v>
@@ -9757,7 +9757,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B226" t="s">
         <v>691</v>
@@ -9789,7 +9789,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B227" t="s">
         <v>694</v>
@@ -9821,7 +9821,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B228" t="s">
         <v>697</v>
@@ -9853,7 +9853,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B229" t="s">
         <v>700</v>
@@ -9963,7 +9963,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B2" t="n">
         <v>130</v>
@@ -9986,7 +9986,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B3" t="n">
         <v>44</v>
@@ -10458,7 +10458,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
         <v>160</v>
@@ -10502,7 +10502,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>604</v>
@@ -10524,7 +10524,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
         <v>616</v>
@@ -10546,7 +10546,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
         <v>697</v>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -106,21 +106,6 @@
     <t xml:space="preserve">2026/03/25 08:32:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Wasserbaulabor_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/02/18 09:06:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/02/18 11:56:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/02/18 09:36:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verdächtig / Kein Regen</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026/02/12 01:18:00</t>
   </si>
   <si>
@@ -194,24 +179,6 @@
   </si>
   <si>
     <t xml:space="preserve">2025/10/04 00:26:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/03/05 22:15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/03/06 01:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/03/05 23:15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/02/26 21:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/02/27 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/02/26 23:45:00</t>
   </si>
   <si>
     <t xml:space="preserve">Ereignisse</t>
@@ -277,8 +244,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L17" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L14" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L14"/>
   <tableColumns count="12">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -298,8 +265,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:G5" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:G5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:G4" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:G4"/>
   <tableColumns count="7">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="Ereignisse"/>
@@ -314,8 +281,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:H17" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:H14" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H14"/>
   <tableColumns count="8">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -856,40 +823,40 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
-      </c>
       <c r="F7" t="n">
-        <v>169.5</v>
+        <v>139</v>
       </c>
       <c r="G7" t="n">
-        <v>0.105</v>
+        <v>0.017</v>
       </c>
       <c r="H7" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="K7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>644</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -897,75 +864,75 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E8" t="s">
         <v>35</v>
       </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E8" t="s">
-        <v>37</v>
-      </c>
       <c r="F8" t="n">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>0.017</v>
+        <v>0.064</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="J8" t="n">
-        <v>1.56</v>
+        <v>0.84</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E9" t="s">
         <v>38</v>
       </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>40</v>
-      </c>
       <c r="F9" t="n">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="G9" t="n">
-        <v>0.064</v>
+        <v>0.01</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="J9" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -973,104 +940,104 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E10" t="s">
         <v>41</v>
       </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E10" t="s">
-        <v>43</v>
-      </c>
       <c r="F10" t="n">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01</v>
+        <v>0.085</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
       </c>
       <c r="I10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J10" t="n">
         <v>0.36</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.96</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D11" t="n">
         <v>0.6</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
-        <v>0.085</v>
+        <v>0.194</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>0.12</v>
+        <v>1.39</v>
       </c>
       <c r="J11" t="n">
-        <v>0.36</v>
+        <v>2.4</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E12" t="s">
         <v>47</v>
       </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E12" t="s">
-        <v>49</v>
-      </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.194</v>
+        <v>0.115</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>1.39</v>
+        <v>0.52</v>
       </c>
       <c r="J12" t="n">
         <v>2.4</v>
@@ -1079,197 +1046,83 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
         <v>50</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E13" t="s">
         <v>51</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E13" t="s">
-        <v>52</v>
-      </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="G13" t="n">
-        <v>0.115</v>
+        <v>0.039</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4</v>
+        <v>1.68</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s">
         <v>53</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E14" t="s">
         <v>54</v>
       </c>
-      <c r="C14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>56</v>
-      </c>
       <c r="F14" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G14" t="n">
-        <v>0.039</v>
+        <v>0.074</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.62</v>
+        <v>1.82</v>
       </c>
       <c r="J14" t="n">
-        <v>1.68</v>
+        <v>3.36</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" t="n">
-        <v>132</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="H15" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="K15" t="b">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
         <v>120</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" t="n">
-        <v>165</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="H16" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E17" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" t="n">
-        <v>150</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="H17" t="s">
-        <v>34</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1300,22 +1153,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D1" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E1" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F1" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G1" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2">
@@ -1366,16 +1219,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>20.4</v>
+        <v>1.1</v>
       </c>
       <c r="D4" t="n">
-        <v>29.2</v>
+        <v>1.1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1384,29 +1237,6 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1462,158 +1292,158 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="D2" t="n">
-        <v>29.2</v>
+        <v>1.1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.216</v>
+        <v>0.039</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n">
-        <v>165</v>
+        <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>28.9</v>
+        <v>0.9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.481</v>
+        <v>0.064</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C4" t="n">
-        <v>169.5</v>
+        <v>132</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.105</v>
+        <v>0.074</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.039</v>
+        <v>0.01</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.62</v>
+        <v>0.36</v>
       </c>
       <c r="H5" t="n">
-        <v>1.68</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>39</v>
+        <v>77.5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.064</v>
+        <v>0.053</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>0.46</v>
+        <v>2.2</v>
       </c>
       <c r="H6" t="n">
-        <v>0.84</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C7" t="n">
-        <v>132</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.074</v>
+        <v>0.115</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>1.82</v>
+        <v>0.52</v>
       </c>
       <c r="H7" t="n">
-        <v>3.36</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="8">
@@ -1621,103 +1451,103 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>83</v>
+        <v>60.5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01</v>
+        <v>0.107</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>0.36</v>
+        <v>2.91</v>
       </c>
       <c r="H8" t="n">
-        <v>0.96</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>77.5</v>
+        <v>129.5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E9" t="n">
-        <v>0.053</v>
+        <v>0.04</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="H9" t="n">
-        <v>2.04</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E10" t="n">
-        <v>0.115</v>
+        <v>0.05</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.52</v>
+        <v>0.16</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>60.5</v>
+        <v>24.5</v>
       </c>
       <c r="D11" t="n">
         <v>0.6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.107</v>
+        <v>0.091</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>2.91</v>
+        <v>0.34</v>
       </c>
       <c r="H11" t="n">
-        <v>7.8</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="12">
@@ -1725,51 +1555,51 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>129.5</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
         <v>0.6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04</v>
+        <v>0.017</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>1.92</v>
+        <v>0.5</v>
       </c>
       <c r="H12" t="n">
-        <v>3.36</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D13" t="n">
         <v>0.6</v>
       </c>
       <c r="E13" t="n">
-        <v>0.05</v>
+        <v>0.085</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
       </c>
       <c r="G13" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="H13" t="n">
-        <v>0.84</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="14">
@@ -1777,102 +1607,24 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C14" t="n">
-        <v>24.5</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
         <v>0.6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.091</v>
+        <v>0.194</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.34</v>
+        <v>1.39</v>
       </c>
       <c r="H14" t="n">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="n">
-        <v>139</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="F15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" t="n">
-        <v>33</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.085</v>
-      </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" t="n">
-        <v>21</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="F17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="H17" t="n">
         <v>2.4</v>
       </c>
     </row>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -52,133 +52,325 @@
     <t xml:space="preserve">points_count</t>
   </si>
   <si>
+    <t xml:space="preserve">Königsallee_Springorum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/13 18:32:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/13 18:59:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/13 18:47:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
     <t xml:space="preserve">An_der_Kost</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/04/11 19:15:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/11 20:16:00</t>
+    <t xml:space="preserve">2026/04/11 21:48:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 22:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 21:54:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 19:14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 20:25:00</t>
   </si>
   <si>
     <t xml:space="preserve">2026/04/11 19:21:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/29 22:31:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/29 23:48:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/29 22:44:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Königsallee_Springorum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 20:24:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 22:33:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 20:39:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 11:14:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 11:50:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 11:26:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 08:25:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 08:50:00</t>
+    <t xml:space="preserve">2026/03/28 08:04:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/28 08:17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/28 08:11:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wasserstraße_Springorum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 08:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 09:25:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 09:00:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sturzflut-Ereignis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 08:19:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 08:53:30</t>
   </si>
   <si>
     <t xml:space="preserve">2026/03/25 08:32:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/02/12 01:18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/02/12 03:37:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/02/12 01:54:00</t>
+    <t xml:space="preserve">2026/03/14 04:18:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/14 04:39:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/14 04:24:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/13 13:16:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/13 13:36:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/13 13:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 12:03:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 12:22:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 12:17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/24 03:18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/24 03:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/24 03:24:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 03:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 04:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 03:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/17 10:02:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/17 10:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/17 10:05:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/16 14:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/16 16:01:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/16 14:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/16 07:50:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/16 08:23:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/16 07:54:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/11 17:49:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/11 18:28:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/11 17:55:00</t>
   </si>
   <si>
     <t xml:space="preserve">2026/01/24 03:30:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/01/24 04:09:00</t>
+    <t xml:space="preserve">2026/01/24 04:11:00</t>
   </si>
   <si>
     <t xml:space="preserve">2026/01/24 03:44:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/01/14 05:12:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/01/14 06:35:00</t>
+    <t xml:space="preserve">2026/01/14 04:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/14 06:45:00</t>
   </si>
   <si>
     <t xml:space="preserve">2026/01/14 06:29:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2025/12/08 23:35:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/12/09 00:08:00</t>
+    <t xml:space="preserve">2025/12/10 03:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/10 04:36:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/10 03:35:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/08 23:18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/09 00:14:00</t>
   </si>
   <si>
     <t xml:space="preserve">2025/12/08 23:42:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2025/12/02 06:15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/12/02 06:36:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/12/02 06:18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/10/23 17:14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/10/23 17:36:00</t>
+    <t xml:space="preserve">2025/12/06 04:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/06 04:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/06 04:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/03 23:45:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/04 00:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/04 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/28 11:39:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/28 11:48:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/28 11:45:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/24 13:49:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/24 15:17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/24 13:54:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/19 23:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/20 00:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/20 00:05:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/16 16:36:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/16 18:41:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/16 18:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/29 21:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/29 22:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/29 21:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/27 00:28:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/27 01:23:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/27 00:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 16:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 17:46:00</t>
   </si>
   <si>
     <t xml:space="preserve">2025/10/23 17:20:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Wasserstraße_Springorum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/10/04 13:06:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/10/04 15:14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/10/04 13:34:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/10/04 00:14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/10/04 02:26:00</t>
+    <t xml:space="preserve">2025/10/23 06:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 06:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 06:41:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 04:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 04:49:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 04:45:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 03:37:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 03:47:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 03:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 01:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 02:02:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 01:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 00:05:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 02:31:00</t>
   </si>
   <si>
     <t xml:space="preserve">2025/10/04 00:26:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/03 20:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/03 20:56:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/03 20:50:00</t>
   </si>
   <si>
     <t xml:space="preserve">Ereignisse</t>
@@ -244,8 +436,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L14" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L35" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L35"/>
   <tableColumns count="12">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -281,8 +473,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:H14" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:H21" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H21"/>
   <tableColumns count="8">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -642,74 +834,74 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>60.5</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>0.107</v>
+        <v>0.033</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>2.91</v>
+        <v>1.2</v>
       </c>
       <c r="J2" t="n">
-        <v>7.8</v>
+        <v>0.36</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>77.5</v>
+        <v>19.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.053</v>
+        <v>0.089</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="J3" t="n">
-        <v>2.04</v>
+        <v>7.8</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>121</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -724,30 +916,30 @@
         <v>23</v>
       </c>
       <c r="F4" t="n">
-        <v>129.5</v>
+        <v>71</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04</v>
+        <v>0.085</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>1.92</v>
+        <v>2.91</v>
       </c>
       <c r="J4" t="n">
-        <v>3.36</v>
+        <v>7.8</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>95</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -756,57 +948,57 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="s">
         <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>0.16</v>
+        <v>3.38</v>
       </c>
       <c r="J5" t="n">
-        <v>0.84</v>
+        <v>4.8</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>24.5</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>0.091</v>
+        <v>0.331</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="I6" t="n">
         <v>0.34</v>
@@ -818,121 +1010,121 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>42</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" t="n">
         <v>0.6</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7" t="n">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>0.017</v>
+        <v>0.048</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>0.34</v>
       </c>
       <c r="J7" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>0.064</v>
+        <v>0.089</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.46</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
-        <v>0.84</v>
+        <v>1.44</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01</v>
+        <v>0.167</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.36</v>
+        <v>0.51</v>
       </c>
       <c r="J9" t="n">
-        <v>0.96</v>
+        <v>3.12</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -940,75 +1132,75 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" t="n">
         <v>0.6</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>18.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.085</v>
+        <v>0.043</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.12</v>
+        <v>0.39</v>
       </c>
       <c r="J10" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.194</v>
+        <v>0.082</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>1.39</v>
+        <v>1.14</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4</v>
+        <v>1.08</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -1016,113 +1208,911 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="G12" t="n">
-        <v>0.115</v>
+        <v>0.024</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>0.52</v>
+        <v>1.13</v>
       </c>
       <c r="J12" t="n">
-        <v>2.4</v>
+        <v>1.32</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>0.039</v>
+        <v>0.194</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>0.62</v>
+        <v>0.44</v>
       </c>
       <c r="J13" t="n">
-        <v>1.68</v>
+        <v>2.52</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" t="n">
+        <v>78</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" t="n">
+        <v>33</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="H15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" t="n">
+        <v>39</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="H16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" t="n">
         <v>0.9</v>
       </c>
-      <c r="E14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" t="n">
-        <v>132</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="H14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="E17" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="H17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" t="n">
+        <v>138</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" t="n">
+        <v>65</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="H19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" t="n">
+        <v>56</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" t="n">
+        <v>13</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" t="n">
+        <v>36</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="H22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>82</v>
+      </c>
+      <c r="F23" t="n">
+        <v>9</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="H23" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" t="n">
+        <v>88</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E25" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" t="n">
+        <v>40</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E26" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" t="n">
+        <v>125</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E27" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" t="n">
+        <v>28</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="H27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E28" t="s">
+        <v>97</v>
+      </c>
+      <c r="F28" t="n">
+        <v>55</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" t="s">
+        <v>99</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E29" t="s">
+        <v>100</v>
+      </c>
+      <c r="F29" t="n">
+        <v>48</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="H29" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E30" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30" t="n">
+        <v>12</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="H30" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J30" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" t="s">
+        <v>105</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E31" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" t="n">
+        <v>7</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>9.12</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E32" t="s">
+        <v>109</v>
+      </c>
+      <c r="F32" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="J32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" t="s">
+        <v>111</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E33" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33" t="n">
+        <v>35</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="H33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E34" t="s">
+        <v>115</v>
+      </c>
+      <c r="F34" t="n">
+        <v>146</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="H34" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J34" t="n">
         <v>3.36</v>
       </c>
-      <c r="K14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>120</v>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E35" t="s">
+        <v>118</v>
+      </c>
+      <c r="F35" t="n">
+        <v>25</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1153,33 +2143,33 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="D1" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="E1" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="F1" t="s">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="G1" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D2" t="n">
         <v>0.9</v>
@@ -1196,13 +2186,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D3" t="n">
         <v>0.8</v>
@@ -1219,19 +2209,19 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1292,80 +2282,80 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.039</v>
+        <v>0.331</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>0.62</v>
+        <v>0.34</v>
       </c>
       <c r="H2" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D3" t="n">
         <v>0.9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.064</v>
+        <v>0.024</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>0.46</v>
+        <v>1.13</v>
       </c>
       <c r="H3" t="n">
-        <v>0.84</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C4" t="n">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="D4" t="n">
         <v>0.9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.074</v>
+        <v>0.064</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>1.82</v>
+        <v>0.46</v>
       </c>
       <c r="H4" t="n">
-        <v>3.36</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="5">
@@ -1373,51 +2363,51 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="C5" t="n">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01</v>
+        <v>0.043</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.36</v>
+        <v>1.91</v>
       </c>
       <c r="H5" t="n">
-        <v>0.96</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="C6" t="n">
-        <v>77.5</v>
+        <v>138</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.053</v>
+        <v>0.007</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2</v>
+        <v>0.38</v>
       </c>
       <c r="H6" t="n">
-        <v>2.04</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="7">
@@ -1425,207 +2415,389 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.115</v>
+        <v>0.195</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>60.5</v>
+        <v>78</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.107</v>
+        <v>0.226</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>2.91</v>
+        <v>0.46</v>
       </c>
       <c r="H8" t="n">
-        <v>7.8</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>129.5</v>
+        <v>48</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04</v>
+        <v>0.032</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>1.92</v>
+        <v>0.52</v>
       </c>
       <c r="H9" t="n">
-        <v>3.36</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C10" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05</v>
+        <v>0.037</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.16</v>
+        <v>1.33</v>
       </c>
       <c r="H10" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>24.5</v>
+        <v>71</v>
       </c>
       <c r="D11" t="n">
         <v>0.6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.091</v>
+        <v>0.085</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.34</v>
+        <v>2.91</v>
       </c>
       <c r="H11" t="n">
-        <v>1.44</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="D12" t="n">
         <v>0.6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.017</v>
+        <v>0.048</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5</v>
+        <v>0.34</v>
       </c>
       <c r="H12" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
         <v>0.6</v>
       </c>
       <c r="E13" t="n">
-        <v>0.085</v>
+        <v>0.167</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
       </c>
       <c r="G13" t="n">
-        <v>0.12</v>
+        <v>0.51</v>
       </c>
       <c r="H13" t="n">
-        <v>0.36</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="D14" t="n">
         <v>0.6</v>
       </c>
       <c r="E14" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E15" t="n">
         <v>0.194</v>
       </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" t="n">
+        <v>56</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="n">
+        <v>125</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" t="n">
         <v>2.4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>9.12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="n">
+        <v>27</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="F20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H20" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="n">
+        <v>13</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="F21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -76,6 +76,54 @@
     <t xml:space="preserve">2026/04/11 19:21:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/03/30 01:34:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/30 05:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/30 02:15:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 22:09:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/30 00:06:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 22:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Königsallee_Springorum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 21:02:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/30 07:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 23:14:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/28 06:47:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/28 09:42:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/28 06:59:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/26 15:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/26 15:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/26 15:23:30</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/03/26 11:39:30</t>
   </si>
   <si>
@@ -85,6 +133,24 @@
     <t xml:space="preserve">2026/03/26 11:44:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/03/25 19:59:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/26 07:46:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 20:39:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 10:24:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 12:30:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 11:26:30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wasserstraße_Springorum</t>
   </si>
   <si>
@@ -100,9 +166,6 @@
     <t xml:space="preserve">Sturzflut-Ereignis</t>
   </si>
   <si>
-    <t xml:space="preserve">Königsallee_Springorum</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026/03/25 08:19:30</t>
   </si>
   <si>
@@ -112,6 +175,81 @@
     <t xml:space="preserve">2026/03/25 08:32:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/03/16 00:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/16 08:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/16 00:48:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 11:20:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 12:06:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 11:31:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/23 22:16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/24 03:36:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/24 03:24:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 09:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 11:51:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 11:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/14 04:18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/14 07:54:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/14 06:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/10 04:52:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/10 08:02:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/10 07:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regenereignis / Natürlich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/10 03:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/10 05:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/10 03:35:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/06 03:28:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/06 06:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/06 04:40:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025/11/24 17:27:00</t>
   </si>
   <si>
@@ -121,6 +259,15 @@
     <t xml:space="preserve">2025/11/24 18:05:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2025/11/19 21:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/20 02:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/19 22:45:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025/11/16 16:21:00</t>
   </si>
   <si>
@@ -130,6 +277,60 @@
     <t xml:space="preserve">2025/11/16 18:21:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2025/11/15 00:23:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/15 03:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/15 00:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/10 21:25:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/11 05:12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/10 21:28:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/02 15:16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/02 23:09:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/02 18:13:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/29 21:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/30 08:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/29 21:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 17:04:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/24 00:39:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 20:07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 16:51:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 18:45:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 17:20:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025/10/23 03:37:00</t>
   </si>
   <si>
@@ -139,6 +340,42 @@
     <t xml:space="preserve">2025/10/23 03:40:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2025/10/05 02:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/05 07:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/05 05:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/03 20:37:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 04:18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 00:26:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 18:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 23:51:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 20:25:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 16:05:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 17:09:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 16:36:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025/09/21 07:16:00</t>
   </si>
   <si>
@@ -146,6 +383,24 @@
   </si>
   <si>
     <t xml:space="preserve">2025/09/21 07:22:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 01:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 05:59:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 05:10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/20 22:55:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 10:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 00:49:00</t>
   </si>
   <si>
     <t xml:space="preserve">Ereignisse</t>
@@ -211,8 +466,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L10" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L38" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L38"/>
   <tableColumns count="12">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -248,8 +503,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:H10" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:H21" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H21"/>
   <tableColumns count="8">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -685,107 +940,107 @@
         <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>248.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.109</v>
+        <v>0.019</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>0.83</v>
+        <v>2.63</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>33</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
       <c r="F5" t="n">
-        <v>41</v>
+        <v>117.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.331</v>
+        <v>0.02</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>0.34</v>
+        <v>2.29</v>
       </c>
       <c r="J5" t="n">
-        <v>1.44</v>
+        <v>2.04</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>83</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
         <v>28</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
-      </c>
       <c r="F6" t="n">
-        <v>41.5</v>
+        <v>644</v>
       </c>
       <c r="G6" t="n">
-        <v>0.048</v>
+        <v>0.007</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>0.34</v>
+        <v>3.77</v>
       </c>
       <c r="J6" t="n">
-        <v>1.44</v>
+        <v>7.08</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>84</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="7">
@@ -793,75 +1048,75 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7" t="n">
         <v>0.5</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>175</v>
       </c>
       <c r="G7" t="n">
-        <v>0.013</v>
+        <v>0.041</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03</v>
+        <v>4.17</v>
       </c>
       <c r="J7" t="n">
-        <v>0.36</v>
+        <v>3.48</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>56</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E8" t="s">
         <v>35</v>
       </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E8" t="s">
-        <v>37</v>
-      </c>
       <c r="F8" t="n">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005</v>
+        <v>0.139</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="J8" t="n">
-        <v>0.84</v>
+        <v>2.52</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>141</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -869,75 +1124,1139 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D9" t="n">
         <v>0.5</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.161</v>
+        <v>0.109</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>3.47</v>
+        <v>0.83</v>
       </c>
       <c r="J9" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E10" t="s">
         <v>41</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="n">
+        <v>707</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
         <v>42</v>
       </c>
-      <c r="D10" t="n">
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" t="n">
+        <v>126</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" t="n">
+        <v>41</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="H12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" t="n">
+        <v>485</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="H15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" t="n">
+        <v>320</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E17" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" t="n">
+        <v>140</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" t="n">
+        <v>216</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" t="n">
+        <v>190</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H19" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" t="n">
+        <v>131</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" t="n">
+        <v>196</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" t="n">
+        <v>55</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="H22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" t="n">
+        <v>321</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H23" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" t="n">
+        <v>140</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E25" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25" t="n">
+        <v>165</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" t="n">
         <v>0.9</v>
       </c>
-      <c r="E10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="E26" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" t="n">
+        <v>467</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" t="n">
+        <v>473</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="H27" t="s">
+        <v>71</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="J27" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E28" t="s">
+        <v>98</v>
+      </c>
+      <c r="F28" t="n">
+        <v>647</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>101</v>
+      </c>
+      <c r="F29" t="n">
+        <v>455</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="H29" t="s">
+        <v>71</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" t="s">
+        <v>103</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E30" t="s">
+        <v>104</v>
+      </c>
+      <c r="F30" t="n">
+        <v>114</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="H30" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E31" t="s">
+        <v>107</v>
+      </c>
+      <c r="F31" t="n">
+        <v>12</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E32" t="s">
+        <v>110</v>
+      </c>
+      <c r="F32" t="n">
+        <v>323</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E33" t="s">
+        <v>113</v>
+      </c>
+      <c r="F33" t="n">
+        <v>461</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" t="s">
+        <v>115</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E34" t="s">
+        <v>116</v>
+      </c>
+      <c r="F34" t="n">
+        <v>319</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H34" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E35" t="s">
+        <v>119</v>
+      </c>
+      <c r="F35" t="n">
+        <v>64</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" t="s">
+        <v>120</v>
+      </c>
+      <c r="C36" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E36" t="s">
+        <v>122</v>
+      </c>
+      <c r="F36" t="n">
         <v>27</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G36" t="n">
         <v>0.148</v>
       </c>
-      <c r="H10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="H36" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" t="n">
         <v>2.14</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J36" t="n">
         <v>3.72</v>
       </c>
-      <c r="K10" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
         <v>28</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E37" t="s">
+        <v>125</v>
+      </c>
+      <c r="F37" t="n">
+        <v>278</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="H37" t="s">
+        <v>71</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E38" t="s">
+        <v>128</v>
+      </c>
+      <c r="F38" t="n">
+        <v>699</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="H38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>700</v>
       </c>
     </row>
   </sheetData>
@@ -968,42 +2287,42 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>46</v>
+        <v>131</v>
       </c>
       <c r="E1" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="F1" t="s">
-        <v>48</v>
+        <v>133</v>
       </c>
       <c r="G1" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1011,16 +2330,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
         <v>0.6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1034,22 +2353,22 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1107,100 +2426,100 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>278</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.331</v>
+        <v>0.033</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G2" t="n">
-        <v>0.34</v>
+        <v>1.07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.44</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>473</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9</v>
+        <v>6.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.148</v>
+        <v>0.034</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>3.14</v>
       </c>
       <c r="H3" t="n">
-        <v>3.72</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="C4" t="n">
-        <v>79.5</v>
+        <v>45.5</v>
       </c>
       <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="F4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="H4" t="n">
-        <v>7.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C5" t="n">
-        <v>41.5</v>
+        <v>41</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.048</v>
+        <v>0.331</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
         <v>0.34</v>
@@ -1211,132 +2530,418 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C6" t="n">
-        <v>140</v>
+        <v>455</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005</v>
+        <v>0.017</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="H6" t="n">
-        <v>0.84</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>190</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="E7" t="n">
-        <v>0.031</v>
+        <v>0.015</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>2.29</v>
+        <v>0.55</v>
       </c>
       <c r="H7" t="n">
-        <v>7.8</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>485</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="E8" t="n">
-        <v>0.109</v>
+        <v>0.068</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="C9" t="n">
-        <v>55</v>
+        <v>699</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="E9" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03</v>
+        <v>2.55</v>
       </c>
       <c r="H9" t="n">
-        <v>0.36</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="n">
+        <v>644</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7.08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" t="n">
+        <v>467</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" t="n">
+        <v>461</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" t="n">
+        <v>27</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" t="n">
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="D10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="H10" t="n">
-        <v>6.6</v>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" t="n">
+        <v>216</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" t="n">
+        <v>647</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" t="n">
+        <v>114</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" t="n">
+        <v>323</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" t="n">
+        <v>319</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="F21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -55,6 +55,18 @@
     <t xml:space="preserve">An_der_Kost</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/04/19 00:23:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/19 02:28:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/19 00:45:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/04/11 21:38:00</t>
   </si>
   <si>
@@ -62,9 +74,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026/04/11 21:54:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
   </si>
   <si>
     <t xml:space="preserve">2026/04/11 19:10:30</t>
@@ -466,8 +475,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L38" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L39" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L39"/>
   <tableColumns count="12">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -864,31 +873,31 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="G2" t="n">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>2.29</v>
+        <v>0.25</v>
       </c>
       <c r="J2" t="n">
-        <v>7.8</v>
+        <v>2.52</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>73</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3">
@@ -902,22 +911,22 @@
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>79.5</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>0.057</v>
+        <v>0.031</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>2.91</v>
+        <v>2.29</v>
       </c>
       <c r="J3" t="n">
         <v>7.8</v>
@@ -926,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>160</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
@@ -940,31 +949,31 @@
         <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>248.5</v>
+        <v>79.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.019</v>
+        <v>0.057</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>2.63</v>
+        <v>2.91</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>498</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5">
@@ -978,74 +987,74 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="s">
         <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>117.5</v>
+        <v>248.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="J5" t="n">
-        <v>2.04</v>
+        <v>4.8</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>236</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>29</v>
-      </c>
       <c r="F6" t="n">
-        <v>644</v>
+        <v>117.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007</v>
+        <v>0.02</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>3.77</v>
+        <v>2.29</v>
       </c>
       <c r="J6" t="n">
-        <v>7.08</v>
+        <v>2.04</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1289</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
@@ -1054,31 +1063,31 @@
         <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E7" t="s">
         <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>175</v>
+        <v>644</v>
       </c>
       <c r="G7" t="n">
-        <v>0.041</v>
+        <v>0.007</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>4.17</v>
+        <v>3.77</v>
       </c>
       <c r="J7" t="n">
-        <v>3.48</v>
+        <v>7.08</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>351</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="8">
@@ -1098,25 +1107,25 @@
         <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="G8" t="n">
-        <v>0.139</v>
+        <v>0.041</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.38</v>
+        <v>4.17</v>
       </c>
       <c r="J8" t="n">
-        <v>2.52</v>
+        <v>3.48</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>49</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -1136,30 +1145,30 @@
         <v>38</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>0.109</v>
+        <v>0.139</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.83</v>
+        <v>0.38</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>39</v>
@@ -1168,36 +1177,36 @@
         <v>40</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E10" t="s">
         <v>41</v>
       </c>
       <c r="F10" t="n">
-        <v>707</v>
+        <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.015</v>
+        <v>0.109</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>2.19</v>
+        <v>0.83</v>
       </c>
       <c r="J10" t="n">
-        <v>3.36</v>
+        <v>2.4</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1415</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
         <v>42</v>
@@ -1212,89 +1221,89 @@
         <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>126</v>
+        <v>707</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>0.75</v>
+        <v>2.19</v>
       </c>
       <c r="J11" t="n">
-        <v>2.16</v>
+        <v>3.36</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>253</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
         <v>45</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>46</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E12" t="s">
         <v>47</v>
       </c>
-      <c r="D12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E12" t="s">
-        <v>48</v>
-      </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="G12" t="n">
-        <v>0.331</v>
+        <v>0.01</v>
       </c>
       <c r="H12" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>0.34</v>
+        <v>0.75</v>
       </c>
       <c r="J12" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>83</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
         <v>50</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E13" t="s">
         <v>51</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="n">
+        <v>41</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="H13" t="s">
         <v>52</v>
-      </c>
-      <c r="F13" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="H13" t="s">
-        <v>16</v>
       </c>
       <c r="I13" t="n">
         <v>0.34</v>
@@ -1306,12 +1315,12 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
         <v>53</v>
@@ -1320,36 +1329,36 @@
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="E14" t="s">
         <v>55</v>
       </c>
       <c r="F14" t="n">
-        <v>485</v>
+        <v>41.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.068</v>
+        <v>0.048</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.85</v>
+        <v>0.34</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>1.44</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>971</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
         <v>56</v>
@@ -1358,36 +1367,36 @@
         <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="E15" t="s">
         <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>45.5</v>
+        <v>485</v>
       </c>
       <c r="G15" t="n">
-        <v>0.541</v>
+        <v>0.068</v>
       </c>
       <c r="H15" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>0.35</v>
+        <v>0.85</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>92</v>
+        <v>971</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
         <v>59</v>
@@ -1396,31 +1405,31 @@
         <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="s">
         <v>61</v>
       </c>
       <c r="F16" t="n">
-        <v>320</v>
+        <v>45.5</v>
       </c>
       <c r="G16" t="n">
-        <v>0.002</v>
+        <v>0.541</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="I16" t="n">
-        <v>1.71</v>
+        <v>0.35</v>
       </c>
       <c r="J16" t="n">
-        <v>1.56</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>321</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -1434,31 +1443,31 @@
         <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E17" t="s">
         <v>64</v>
       </c>
       <c r="F17" t="n">
-        <v>140</v>
+        <v>320</v>
       </c>
       <c r="G17" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>0.21</v>
+        <v>1.71</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>1.56</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>141</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18">
@@ -1472,13 +1481,13 @@
         <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E18" t="s">
         <v>67</v>
       </c>
       <c r="F18" t="n">
-        <v>216</v>
+        <v>140</v>
       </c>
       <c r="G18" t="n">
         <v>0.006</v>
@@ -1487,21 +1496,21 @@
         <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.44</v>
+        <v>0.21</v>
       </c>
       <c r="J18" t="n">
-        <v>0.96</v>
+        <v>0.6</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>217</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
         <v>68</v>
@@ -1510,60 +1519,60 @@
         <v>69</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="E19" t="s">
         <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="G19" t="n">
-        <v>0.015</v>
+        <v>0.006</v>
       </c>
       <c r="H19" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.55</v>
+        <v>0.44</v>
       </c>
       <c r="J19" t="n">
-        <v>1.44</v>
+        <v>0.96</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>191</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="s">
         <v>72</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E20" t="s">
         <v>73</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="F20" t="n">
+        <v>190</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H20" t="s">
         <v>74</v>
       </c>
-      <c r="F20" t="n">
-        <v>131</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="H20" t="s">
-        <v>16</v>
-      </c>
       <c r="I20" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="J20" t="n">
         <v>1.44</v>
@@ -1572,12 +1581,12 @@
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>132</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
         <v>75</v>
@@ -1592,30 +1601,30 @@
         <v>77</v>
       </c>
       <c r="F21" t="n">
-        <v>196</v>
+        <v>131</v>
       </c>
       <c r="G21" t="n">
-        <v>0.007</v>
+        <v>0.122</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="J21" t="n">
-        <v>2.52</v>
+        <v>1.44</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>197</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
         <v>78</v>
@@ -1630,30 +1639,30 @@
         <v>80</v>
       </c>
       <c r="F22" t="n">
-        <v>55</v>
+        <v>196</v>
       </c>
       <c r="G22" t="n">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0.36</v>
+        <v>2.52</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>56</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
         <v>81</v>
@@ -1668,30 +1677,30 @@
         <v>83</v>
       </c>
       <c r="F23" t="n">
-        <v>321</v>
+        <v>55</v>
       </c>
       <c r="G23" t="n">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>3.37</v>
+        <v>0.03</v>
       </c>
       <c r="J23" t="n">
-        <v>3.6</v>
+        <v>0.36</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>322</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B24" t="s">
         <v>84</v>
@@ -1700,13 +1709,13 @@
         <v>85</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E24" t="s">
         <v>86</v>
       </c>
       <c r="F24" t="n">
-        <v>140</v>
+        <v>321</v>
       </c>
       <c r="G24" t="n">
         <v>0.005</v>
@@ -1715,21 +1724,21 @@
         <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.21</v>
+        <v>3.37</v>
       </c>
       <c r="J24" t="n">
-        <v>0.84</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>141</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B25" t="s">
         <v>87</v>
@@ -1738,36 +1747,36 @@
         <v>88</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E25" t="s">
         <v>89</v>
       </c>
       <c r="F25" t="n">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="G25" t="n">
-        <v>0.07</v>
+        <v>0.005</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
       </c>
       <c r="I25" t="n">
-        <v>0.92</v>
+        <v>0.21</v>
       </c>
       <c r="J25" t="n">
-        <v>2.04</v>
+        <v>0.84</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>166</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
         <v>90</v>
@@ -1776,36 +1785,36 @@
         <v>91</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="E26" t="s">
         <v>92</v>
       </c>
       <c r="F26" t="n">
-        <v>467</v>
+        <v>165</v>
       </c>
       <c r="G26" t="n">
-        <v>0.29</v>
+        <v>0.07</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>1.26</v>
+        <v>0.92</v>
       </c>
       <c r="J26" t="n">
-        <v>8.4</v>
+        <v>2.04</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>468</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
         <v>93</v>
@@ -1814,36 +1823,36 @@
         <v>94</v>
       </c>
       <c r="D27" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="E27" t="s">
         <v>95</v>
       </c>
       <c r="F27" t="n">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="G27" t="n">
-        <v>0.034</v>
+        <v>0.29</v>
       </c>
       <c r="H27" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="I27" t="n">
-        <v>3.14</v>
+        <v>1.26</v>
       </c>
       <c r="J27" t="n">
-        <v>7.44</v>
+        <v>8.4</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
         <v>96</v>
@@ -1852,36 +1861,36 @@
         <v>97</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="E28" t="s">
         <v>98</v>
       </c>
       <c r="F28" t="n">
-        <v>647</v>
+        <v>473</v>
       </c>
       <c r="G28" t="n">
-        <v>0.195</v>
+        <v>0.034</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>3.14</v>
       </c>
       <c r="J28" t="n">
-        <v>8.16</v>
+        <v>7.44</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>648</v>
+        <v>474</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
         <v>99</v>
@@ -1890,36 +1899,36 @@
         <v>100</v>
       </c>
       <c r="D29" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="E29" t="s">
         <v>101</v>
       </c>
       <c r="F29" t="n">
-        <v>455</v>
+        <v>647</v>
       </c>
       <c r="G29" t="n">
-        <v>0.017</v>
+        <v>0.195</v>
       </c>
       <c r="H29" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="I29" t="n">
-        <v>0.26</v>
+        <v>5.2</v>
       </c>
       <c r="J29" t="n">
-        <v>1.32</v>
+        <v>8.16</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>456</v>
+        <v>648</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
         <v>102</v>
@@ -1928,31 +1937,31 @@
         <v>103</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="E30" t="s">
         <v>104</v>
       </c>
       <c r="F30" t="n">
-        <v>114</v>
+        <v>455</v>
       </c>
       <c r="G30" t="n">
-        <v>0.024</v>
+        <v>0.017</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="I30" t="n">
-        <v>0.52</v>
+        <v>0.26</v>
       </c>
       <c r="J30" t="n">
-        <v>2.4</v>
+        <v>1.32</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>115</v>
+        <v>456</v>
       </c>
     </row>
     <row r="31">
@@ -1966,36 +1975,36 @@
         <v>106</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E31" t="s">
         <v>107</v>
       </c>
       <c r="F31" t="n">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G31" t="n">
-        <v>0.161</v>
+        <v>0.024</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>3.47</v>
+        <v>0.52</v>
       </c>
       <c r="J31" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>13</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
         <v>108</v>
@@ -2004,36 +2013,36 @@
         <v>109</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E32" t="s">
         <v>110</v>
       </c>
       <c r="F32" t="n">
-        <v>323</v>
+        <v>12</v>
       </c>
       <c r="G32" t="n">
-        <v>0.003</v>
+        <v>0.161</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>0.19</v>
+        <v>3.47</v>
       </c>
       <c r="J32" t="n">
-        <v>2.16</v>
+        <v>6.6</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>324</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
         <v>111</v>
@@ -2042,36 +2051,36 @@
         <v>112</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E33" t="s">
         <v>113</v>
       </c>
       <c r="F33" t="n">
-        <v>461</v>
+        <v>323</v>
       </c>
       <c r="G33" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
       </c>
       <c r="I33" t="n">
-        <v>3.21</v>
+        <v>0.19</v>
       </c>
       <c r="J33" t="n">
-        <v>3.36</v>
+        <v>2.16</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>462</v>
+        <v>324</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B34" t="s">
         <v>114</v>
@@ -2080,36 +2089,36 @@
         <v>115</v>
       </c>
       <c r="D34" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="E34" t="s">
         <v>116</v>
       </c>
       <c r="F34" t="n">
-        <v>319</v>
+        <v>461</v>
       </c>
       <c r="G34" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
       </c>
       <c r="I34" t="n">
-        <v>0.56</v>
+        <v>3.21</v>
       </c>
       <c r="J34" t="n">
-        <v>2.28</v>
+        <v>3.36</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>320</v>
+        <v>462</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
         <v>117</v>
@@ -2118,16 +2127,16 @@
         <v>118</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E35" t="s">
         <v>119</v>
       </c>
       <c r="F35" t="n">
-        <v>64</v>
+        <v>319</v>
       </c>
       <c r="G35" t="n">
-        <v>0.016</v>
+        <v>0.006</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -2142,12 +2151,12 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>65</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B36" t="s">
         <v>120</v>
@@ -2156,36 +2165,36 @@
         <v>121</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="E36" t="s">
         <v>122</v>
       </c>
       <c r="F36" t="n">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="G36" t="n">
-        <v>0.148</v>
+        <v>0.016</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>2.14</v>
+        <v>0.56</v>
       </c>
       <c r="J36" t="n">
-        <v>3.72</v>
+        <v>2.28</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
         <v>123</v>
@@ -2194,22 +2203,22 @@
         <v>124</v>
       </c>
       <c r="D37" t="n">
-        <v>7.5</v>
+        <v>0.9</v>
       </c>
       <c r="E37" t="s">
         <v>125</v>
       </c>
       <c r="F37" t="n">
-        <v>278</v>
+        <v>27</v>
       </c>
       <c r="G37" t="n">
-        <v>0.033</v>
+        <v>0.148</v>
       </c>
       <c r="H37" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="I37" t="n">
-        <v>1.07</v>
+        <v>2.14</v>
       </c>
       <c r="J37" t="n">
         <v>3.72</v>
@@ -2218,12 +2227,12 @@
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>279</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B38" t="s">
         <v>126</v>
@@ -2232,22 +2241,22 @@
         <v>127</v>
       </c>
       <c r="D38" t="n">
-        <v>1.3</v>
+        <v>7.5</v>
       </c>
       <c r="E38" t="s">
         <v>128</v>
       </c>
       <c r="F38" t="n">
-        <v>699</v>
+        <v>278</v>
       </c>
       <c r="G38" t="n">
-        <v>0.011</v>
+        <v>0.033</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="I38" t="n">
-        <v>2.55</v>
+        <v>1.07</v>
       </c>
       <c r="J38" t="n">
         <v>3.72</v>
@@ -2256,6 +2265,44 @@
         <v>1</v>
       </c>
       <c r="L38" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" t="s">
+        <v>129</v>
+      </c>
+      <c r="C39" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E39" t="s">
+        <v>131</v>
+      </c>
+      <c r="F39" t="n">
+        <v>699</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="H39" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
         <v>700</v>
       </c>
     </row>
@@ -2287,27 +2334,27 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B2" t="n">
         <v>18</v>
@@ -2333,7 +2380,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
         <v>0.6</v>
@@ -2353,7 +2400,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B4" t="n">
         <v>6</v>
@@ -2426,10 +2473,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C2" t="n">
         <v>278</v>
@@ -2441,7 +2488,7 @@
         <v>0.033</v>
       </c>
       <c r="F2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G2" t="n">
         <v>1.07</v>
@@ -2452,10 +2499,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C3" t="n">
         <v>473</v>
@@ -2467,7 +2514,7 @@
         <v>0.034</v>
       </c>
       <c r="F3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
         <v>3.14</v>
@@ -2478,10 +2525,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C4" t="n">
         <v>45.5</v>
@@ -2493,7 +2540,7 @@
         <v>0.541</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
         <v>0.35</v>
@@ -2504,10 +2551,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C5" t="n">
         <v>41</v>
@@ -2519,7 +2566,7 @@
         <v>0.331</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G5" t="n">
         <v>0.34</v>
@@ -2530,10 +2577,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C6" t="n">
         <v>455</v>
@@ -2545,7 +2592,7 @@
         <v>0.017</v>
       </c>
       <c r="F6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G6" t="n">
         <v>0.26</v>
@@ -2556,10 +2603,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
         <v>190</v>
@@ -2571,7 +2618,7 @@
         <v>0.015</v>
       </c>
       <c r="F7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
         <v>0.55</v>
@@ -2582,10 +2629,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
         <v>485</v>
@@ -2608,10 +2655,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C9" t="n">
         <v>699</v>
@@ -2634,10 +2681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
         <v>644</v>
@@ -2660,10 +2707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C11" t="n">
         <v>467</v>
@@ -2686,10 +2733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C12" t="n">
         <v>461</v>
@@ -2712,10 +2759,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C13" t="n">
         <v>27</v>
@@ -2741,7 +2788,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
         <v>248.5</v>
@@ -2767,7 +2814,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C15" t="n">
         <v>216</v>
@@ -2790,10 +2837,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C16" t="n">
         <v>647</v>
@@ -2819,25 +2866,25 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>117.5</v>
+        <v>125</v>
       </c>
       <c r="D17" t="n">
         <v>0.7</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02</v>
+        <v>0.032</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>2.29</v>
+        <v>0.25</v>
       </c>
       <c r="H17" t="n">
-        <v>2.04</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="18">
@@ -2845,103 +2892,103 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="C18" t="n">
-        <v>114</v>
+        <v>117.5</v>
       </c>
       <c r="D18" t="n">
         <v>0.7</v>
       </c>
       <c r="E18" t="n">
-        <v>0.024</v>
+        <v>0.02</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>0.52</v>
+        <v>2.29</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C19" t="n">
-        <v>323</v>
+        <v>114</v>
       </c>
       <c r="D19" t="n">
         <v>0.7</v>
       </c>
       <c r="E19" t="n">
-        <v>0.003</v>
+        <v>0.024</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>0.19</v>
+        <v>0.52</v>
       </c>
       <c r="H19" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C20" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D20" t="n">
         <v>0.7</v>
       </c>
       <c r="E20" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>0.56</v>
+        <v>0.19</v>
       </c>
       <c r="H20" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="C21" t="n">
-        <v>79.5</v>
+        <v>319</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E21" t="n">
-        <v>0.057</v>
+        <v>0.006</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>2.91</v>
+        <v>0.56</v>
       </c>
       <c r="H21" t="n">
-        <v>7.8</v>
+        <v>2.28</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -52,156 +52,111 @@
     <t xml:space="preserve">points_count</t>
   </si>
   <si>
+    <t xml:space="preserve">Königsallee_Springorum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/18 15:25:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/19 05:22:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/19 00:35:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/13 15:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/14 07:14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/13 18:47:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 21:15:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/30 07:33:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 23:14:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wasserstraße_Springorum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 11:16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 21:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 12:47:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/28 00:17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/28 12:38:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/28 03:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 19:59:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/26 07:46:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 20:39:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 10:24:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 12:30:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 11:26:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 08:19:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 09:01:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/25 08:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/16 00:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/16 08:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/16 00:48:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 05:51:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 12:06:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 11:31:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regenereignis / Natürlich</t>
+  </si>
+  <si>
     <t xml:space="preserve">An_der_Kost</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/04/19 00:23:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/19 02:28:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/19 00:45:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/11 21:38:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/11 22:14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/11 21:54:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/11 19:10:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/11 20:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/11 19:21:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/30 01:34:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/30 05:43:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/30 02:15:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/29 22:09:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/30 00:06:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/29 22:44:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Königsallee_Springorum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/29 21:02:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/30 07:46:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/29 23:14:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/28 06:47:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/28 09:42:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/28 06:59:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/26 15:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/26 15:44:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/26 15:23:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/26 11:39:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/26 11:55:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/26 11:44:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 19:59:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/26 07:46:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 20:39:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 10:24:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 12:30:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 11:26:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wasserstraße_Springorum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 08:44:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 09:25:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 09:00:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sturzflut-Ereignis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 08:19:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 09:01:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/25 08:32:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/16 00:29:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/16 08:34:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/16 00:48:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/11 11:20:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/11 12:06:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/11 11:31:30</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026/02/23 22:16:00</t>
   </si>
   <si>
@@ -211,34 +166,103 @@
     <t xml:space="preserve">2026/02/24 03:24:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/02/19 09:31:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/02/19 11:51:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/02/19 11:08:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/01/14 04:18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/01/14 07:54:00</t>
+    <t xml:space="preserve">2026/02/23 21:53:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/24 06:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/23 21:56:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/21 16:22:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/21 19:56:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/21 16:51:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 04:48:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 11:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 08:24:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 00:55:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 14:15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 03:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/18 13:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 02:52:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/18 13:41:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/15 19:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/16 10:54:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/15 22:52:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/14 04:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/14 07:35:00</t>
   </si>
   <si>
     <t xml:space="preserve">2026/01/14 06:29:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2025/12/10 04:52:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/12/10 08:02:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/12/10 07:27:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regenereignis / Natürlich</t>
+    <t xml:space="preserve">2026/01/08 06:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/09 00:38:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/08 15:38:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/07 18:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/08 04:39:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/07 19:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/05 15:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/06 12:23:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/06 08:39:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/01 22:25:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/02 10:48:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/02 00:46:00</t>
   </si>
   <si>
     <t xml:space="preserve">2025/12/10 03:31:00</t>
@@ -250,15 +274,51 @@
     <t xml:space="preserve">2025/12/10 03:35:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2025/12/06 03:28:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/12/06 06:44:00</t>
+    <t xml:space="preserve">2025/12/07 20:33:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/08 02:25:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/07 21:06:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/06 03:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/06 06:46:00</t>
   </si>
   <si>
     <t xml:space="preserve">2025/12/06 04:40:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2025/12/05 04:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/05 08:37:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/05 05:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/03 22:06:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/04 09:04:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/03 22:10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/02 02:59:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/02 13:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/02 06:18:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025/11/24 17:27:00</t>
   </si>
   <si>
@@ -268,49 +328,22 @@
     <t xml:space="preserve">2025/11/24 18:05:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2025/11/19 21:08:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/11/20 02:29:00</t>
+    <t xml:space="preserve">2025/11/19 16:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/20 09:13:00</t>
   </si>
   <si>
     <t xml:space="preserve">2025/11/19 22:45:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2025/11/16 16:21:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/11/16 18:41:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/11/16 18:21:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/11/15 00:23:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/11/15 03:08:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/11/15 00:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/11/10 21:25:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/11/11 05:12:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/11/10 21:28:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/11/02 15:16:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/11/02 23:09:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/11/02 18:13:00</t>
+    <t xml:space="preserve">2025/11/18 16:22:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/18 22:24:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/18 16:25:00</t>
   </si>
   <si>
     <t xml:space="preserve">2025/10/29 21:40:00</t>
@@ -322,31 +355,49 @@
     <t xml:space="preserve">2025/10/29 21:44:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2025/10/23 17:04:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/10/24 00:39:00</t>
+    <t xml:space="preserve">2025/10/27 11:14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/28 01:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/27 17:13:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/26 22:17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/27 02:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/27 00:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 17:14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 17:36:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 17:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 15:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/24 05:29:00</t>
   </si>
   <si>
     <t xml:space="preserve">2025/10/23 20:07:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2025/10/23 16:51:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/10/23 18:45:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/10/23 17:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/10/23 03:37:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/10/23 03:49:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/10/23 03:40:00</t>
+    <t xml:space="preserve">2025/10/23 13:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 13:52:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 13:49:00</t>
   </si>
   <si>
     <t xml:space="preserve">2025/10/05 02:21:00</t>
@@ -367,49 +418,22 @@
     <t xml:space="preserve">2025/10/04 00:26:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2025/09/21 18:32:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/09/21 23:51:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/09/21 20:25:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/09/21 16:05:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/09/21 17:09:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/09/21 16:36:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/09/21 07:16:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/09/21 07:43:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/09/21 07:22:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/09/21 01:21:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/09/21 05:59:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/09/21 05:10:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/09/20 22:55:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/09/21 10:34:00</t>
+    <t xml:space="preserve">2025/09/21 00:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 08:46:00</t>
   </si>
   <si>
     <t xml:space="preserve">2025/09/21 00:49:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/15 04:22:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/15 14:24:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/15 10:02:00</t>
   </si>
   <si>
     <t xml:space="preserve">Ereignisse</t>
@@ -475,8 +499,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L39" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L42" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L42"/>
   <tableColumns count="12">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -873,31 +897,31 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>125</v>
+        <v>837</v>
       </c>
       <c r="G2" t="n">
-        <v>0.032</v>
+        <v>0.003</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>0.25</v>
+        <v>13.24</v>
       </c>
       <c r="J2" t="n">
-        <v>2.52</v>
+        <v>19.44</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>251</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="3">
@@ -911,31 +935,31 @@
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>940</v>
       </c>
       <c r="G3" t="n">
-        <v>0.031</v>
+        <v>0.003</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>2.29</v>
+        <v>1.5</v>
       </c>
       <c r="J3" t="n">
-        <v>7.8</v>
+        <v>0.36</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>73</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="4">
@@ -949,69 +973,69 @@
         <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>79.5</v>
+        <v>617.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.057</v>
+        <v>0.007</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>2.91</v>
+        <v>3.77</v>
       </c>
       <c r="J4" t="n">
-        <v>7.8</v>
+        <v>7.08</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>160</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>248.5</v>
+        <v>630</v>
       </c>
       <c r="G5" t="n">
-        <v>0.019</v>
+        <v>0.014</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>2.63</v>
+        <v>0.77</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8</v>
+        <v>0.96</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>498</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="6">
@@ -1019,42 +1043,42 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
         <v>0.7</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>117.5</v>
+        <v>740.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>2.29</v>
+        <v>7.27</v>
       </c>
       <c r="J6" t="n">
-        <v>2.04</v>
+        <v>4.8</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>236</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
@@ -1063,31 +1087,31 @@
         <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E7" t="s">
         <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>644</v>
+        <v>707</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007</v>
+        <v>0.015</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>3.77</v>
+        <v>2.19</v>
       </c>
       <c r="J7" t="n">
-        <v>7.08</v>
+        <v>3.36</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1289</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="8">
@@ -1101,31 +1125,31 @@
         <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E8" t="s">
         <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>175</v>
+        <v>126</v>
       </c>
       <c r="G8" t="n">
-        <v>0.041</v>
+        <v>0.01</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>4.17</v>
+        <v>0.75</v>
       </c>
       <c r="J8" t="n">
-        <v>3.48</v>
+        <v>2.16</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>351</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9">
@@ -1139,31 +1163,31 @@
         <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
       </c>
       <c r="F9" t="n">
-        <v>24</v>
+        <v>41.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.139</v>
+        <v>0.048</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="J9" t="n">
-        <v>2.52</v>
+        <v>1.44</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>49</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -1177,36 +1201,36 @@
         <v>40</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="E10" t="s">
         <v>41</v>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
+        <v>485</v>
       </c>
       <c r="G10" t="n">
-        <v>0.109</v>
+        <v>0.068</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>33</v>
+        <v>971</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
         <v>42</v>
@@ -1215,112 +1239,112 @@
         <v>43</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>707</v>
+        <v>374.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="I11" t="n">
-        <v>2.19</v>
+        <v>1.01</v>
       </c>
       <c r="J11" t="n">
-        <v>3.36</v>
+        <v>4.8</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1415</v>
+        <v>750</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>126</v>
+        <v>320</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>0.75</v>
+        <v>1.71</v>
       </c>
       <c r="J12" t="n">
-        <v>2.16</v>
+        <v>1.56</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>253</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>521</v>
       </c>
       <c r="G13" t="n">
-        <v>0.331</v>
+        <v>0.194</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>0.34</v>
+        <v>2.82</v>
       </c>
       <c r="J13" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>83</v>
+        <v>522</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>53</v>
@@ -1329,36 +1353,36 @@
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E14" t="s">
         <v>55</v>
       </c>
       <c r="F14" t="n">
-        <v>41.5</v>
+        <v>214</v>
       </c>
       <c r="G14" t="n">
-        <v>0.048</v>
+        <v>0.017</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.34</v>
+        <v>0.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1.44</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>84</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
         <v>56</v>
@@ -1367,36 +1391,36 @@
         <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="E15" t="s">
         <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>485</v>
+        <v>412</v>
       </c>
       <c r="G15" t="n">
-        <v>0.068</v>
+        <v>0.02</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="I15" t="n">
-        <v>0.85</v>
+        <v>1.91</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>971</v>
+        <v>413</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
         <v>59</v>
@@ -1405,36 +1429,36 @@
         <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="E16" t="s">
         <v>61</v>
       </c>
       <c r="F16" t="n">
-        <v>45.5</v>
+        <v>800</v>
       </c>
       <c r="G16" t="n">
-        <v>0.541</v>
+        <v>0.007</v>
       </c>
       <c r="H16" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>0.35</v>
+        <v>3.81</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>92</v>
+        <v>801</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
         <v>62</v>
@@ -1443,31 +1467,31 @@
         <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="E17" t="s">
         <v>64</v>
       </c>
       <c r="F17" t="n">
-        <v>320</v>
+        <v>805</v>
       </c>
       <c r="G17" t="n">
-        <v>0.002</v>
+        <v>0.078</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="J17" t="n">
-        <v>1.56</v>
+        <v>2.16</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>321</v>
+        <v>831</v>
       </c>
     </row>
     <row r="18">
@@ -1481,36 +1505,36 @@
         <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="E18" t="s">
         <v>67</v>
       </c>
       <c r="F18" t="n">
-        <v>140</v>
+        <v>954</v>
       </c>
       <c r="G18" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.21</v>
+        <v>6.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6</v>
+        <v>3.36</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>141</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
         <v>68</v>
@@ -1519,13 +1543,13 @@
         <v>69</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E19" t="s">
         <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="G19" t="n">
         <v>0.006</v>
@@ -1543,12 +1567,12 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>217</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
         <v>71</v>
@@ -1557,107 +1581,107 @@
         <v>72</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="E20" t="s">
         <v>73</v>
       </c>
       <c r="F20" t="n">
-        <v>190</v>
+        <v>1098</v>
       </c>
       <c r="G20" t="n">
-        <v>0.015</v>
+        <v>0.001</v>
       </c>
       <c r="H20" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>0.55</v>
+        <v>3.82</v>
       </c>
       <c r="J20" t="n">
-        <v>1.44</v>
+        <v>1.92</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>191</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
         <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>76</v>
       </c>
       <c r="D21" t="n">
         <v>0.5</v>
       </c>
       <c r="E21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F21" t="n">
-        <v>131</v>
+        <v>581</v>
       </c>
       <c r="G21" t="n">
-        <v>0.122</v>
+        <v>0.098</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
       </c>
       <c r="I21" t="n">
-        <v>0.41</v>
+        <v>0.16</v>
       </c>
       <c r="J21" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>132</v>
+        <v>580</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" t="s">
         <v>78</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E22" t="s">
         <v>79</v>
       </c>
-      <c r="D22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E22" t="s">
-        <v>80</v>
-      </c>
       <c r="F22" t="n">
-        <v>196</v>
+        <v>1253</v>
       </c>
       <c r="G22" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="J22" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>197</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="23">
@@ -1665,303 +1689,303 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
         <v>81</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E23" t="s">
         <v>82</v>
       </c>
-      <c r="D23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E23" t="s">
-        <v>83</v>
-      </c>
       <c r="F23" t="n">
-        <v>55</v>
+        <v>743</v>
       </c>
       <c r="G23" t="n">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.03</v>
+        <v>0.75</v>
       </c>
       <c r="J23" t="n">
-        <v>0.36</v>
+        <v>1.2</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>56</v>
+        <v>740</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" t="s">
         <v>84</v>
-      </c>
-      <c r="C24" t="s">
-        <v>85</v>
       </c>
       <c r="D24" t="n">
         <v>0.5</v>
       </c>
       <c r="E24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F24" t="n">
-        <v>321</v>
+        <v>131</v>
       </c>
       <c r="G24" t="n">
-        <v>0.005</v>
+        <v>0.122</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>3.37</v>
+        <v>0.41</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>1.44</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>322</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" t="s">
         <v>87</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E25" t="s">
         <v>88</v>
       </c>
-      <c r="D25" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E25" t="s">
-        <v>89</v>
-      </c>
       <c r="F25" t="n">
-        <v>140</v>
+        <v>352</v>
       </c>
       <c r="G25" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
       </c>
       <c r="I25" t="n">
-        <v>0.21</v>
+        <v>4.99</v>
       </c>
       <c r="J25" t="n">
-        <v>0.84</v>
+        <v>5.76</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>141</v>
+        <v>353</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" t="s">
         <v>90</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E26" t="s">
         <v>91</v>
       </c>
-      <c r="D26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E26" t="s">
-        <v>92</v>
-      </c>
       <c r="F26" t="n">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="G26" t="n">
-        <v>0.07</v>
+        <v>0.008</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>0.92</v>
+        <v>0.3</v>
       </c>
       <c r="J26" t="n">
-        <v>2.04</v>
+        <v>2.52</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>166</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" t="s">
         <v>93</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E27" t="s">
         <v>94</v>
       </c>
-      <c r="D27" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E27" t="s">
-        <v>95</v>
-      </c>
       <c r="F27" t="n">
-        <v>467</v>
+        <v>231</v>
       </c>
       <c r="G27" t="n">
-        <v>0.29</v>
+        <v>0.018</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
       </c>
       <c r="I27" t="n">
-        <v>1.26</v>
+        <v>0.03</v>
       </c>
       <c r="J27" t="n">
-        <v>8.4</v>
+        <v>0.24</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>468</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" t="s">
         <v>96</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
         <v>97</v>
       </c>
-      <c r="D28" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="E28" t="s">
-        <v>98</v>
-      </c>
       <c r="F28" t="n">
-        <v>473</v>
+        <v>658</v>
       </c>
       <c r="G28" t="n">
-        <v>0.034</v>
+        <v>0.244</v>
       </c>
       <c r="H28" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>3.14</v>
+        <v>1.03</v>
       </c>
       <c r="J28" t="n">
-        <v>7.44</v>
+        <v>1.2</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>474</v>
+        <v>657</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" t="s">
         <v>99</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E29" t="s">
         <v>100</v>
       </c>
-      <c r="D29" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E29" t="s">
-        <v>101</v>
-      </c>
       <c r="F29" t="n">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="G29" t="n">
-        <v>0.195</v>
+        <v>0.004</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
       </c>
       <c r="I29" t="n">
-        <v>5.2</v>
+        <v>6.77</v>
       </c>
       <c r="J29" t="n">
-        <v>8.16</v>
+        <v>4.92</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>648</v>
+        <v>642</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B30" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" t="s">
         <v>102</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E30" t="s">
         <v>103</v>
       </c>
-      <c r="D30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E30" t="s">
-        <v>104</v>
-      </c>
       <c r="F30" t="n">
-        <v>455</v>
+        <v>55</v>
       </c>
       <c r="G30" t="n">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="H30" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>0.26</v>
+        <v>0.03</v>
       </c>
       <c r="J30" t="n">
-        <v>1.32</v>
+        <v>0.36</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>456</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31">
@@ -1969,37 +1993,37 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" t="s">
         <v>105</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E31" t="s">
         <v>106</v>
       </c>
-      <c r="D31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E31" t="s">
-        <v>107</v>
-      </c>
       <c r="F31" t="n">
-        <v>114</v>
+        <v>1030</v>
       </c>
       <c r="G31" t="n">
-        <v>0.024</v>
+        <v>0.001</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>0.52</v>
+        <v>3.37</v>
       </c>
       <c r="J31" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>115</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="32">
@@ -2007,303 +2031,417 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" t="s">
         <v>108</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E32" t="s">
         <v>109</v>
       </c>
-      <c r="D32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E32" t="s">
-        <v>110</v>
-      </c>
       <c r="F32" t="n">
-        <v>12</v>
+        <v>362</v>
       </c>
       <c r="G32" t="n">
-        <v>0.161</v>
+        <v>0.258</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>3.47</v>
+        <v>0.13</v>
       </c>
       <c r="J32" t="n">
-        <v>6.6</v>
+        <v>0.84</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>13</v>
+        <v>363</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" t="s">
         <v>111</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E33" t="s">
         <v>112</v>
       </c>
-      <c r="D33" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E33" t="s">
-        <v>113</v>
-      </c>
       <c r="F33" t="n">
-        <v>323</v>
+        <v>647</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003</v>
+        <v>0.195</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
       </c>
       <c r="I33" t="n">
-        <v>0.19</v>
+        <v>5.2</v>
       </c>
       <c r="J33" t="n">
-        <v>2.16</v>
+        <v>8.16</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>324</v>
+        <v>648</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" t="s">
         <v>114</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E34" t="s">
         <v>115</v>
       </c>
-      <c r="D34" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E34" t="s">
-        <v>116</v>
-      </c>
       <c r="F34" t="n">
-        <v>461</v>
+        <v>846</v>
       </c>
       <c r="G34" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
       </c>
       <c r="I34" t="n">
-        <v>3.21</v>
+        <v>0.11</v>
       </c>
       <c r="J34" t="n">
-        <v>3.36</v>
+        <v>0.48</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>462</v>
+        <v>845</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" t="s">
         <v>117</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E35" t="s">
         <v>118</v>
       </c>
-      <c r="D35" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E35" t="s">
-        <v>119</v>
-      </c>
       <c r="F35" t="n">
-        <v>319</v>
+        <v>265</v>
       </c>
       <c r="G35" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
       </c>
       <c r="I35" t="n">
-        <v>0.56</v>
+        <v>0.71</v>
       </c>
       <c r="J35" t="n">
-        <v>2.28</v>
+        <v>0.96</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>320</v>
+        <v>266</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" t="s">
         <v>120</v>
-      </c>
-      <c r="C36" t="s">
-        <v>121</v>
       </c>
       <c r="D36" t="n">
         <v>0.5</v>
       </c>
       <c r="E36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F36" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="G36" t="n">
-        <v>0.016</v>
+        <v>0.082</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>0.56</v>
+        <v>0.52</v>
       </c>
       <c r="J36" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" t="s">
         <v>123</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E37" t="s">
         <v>124</v>
       </c>
-      <c r="D37" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E37" t="s">
-        <v>125</v>
-      </c>
       <c r="F37" t="n">
-        <v>27</v>
+        <v>839</v>
       </c>
       <c r="G37" t="n">
-        <v>0.148</v>
+        <v>0.012</v>
       </c>
       <c r="H37" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="I37" t="n">
-        <v>2.14</v>
+        <v>1.26</v>
       </c>
       <c r="J37" t="n">
-        <v>3.72</v>
+        <v>1.92</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>28</v>
+        <v>840</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" t="s">
         <v>126</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E38" t="s">
         <v>127</v>
       </c>
-      <c r="D38" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E38" t="s">
-        <v>128</v>
-      </c>
       <c r="F38" t="n">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="G38" t="n">
-        <v>0.033</v>
+        <v>0.028</v>
       </c>
       <c r="H38" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="I38" t="n">
-        <v>1.07</v>
+        <v>0.11</v>
       </c>
       <c r="J38" t="n">
-        <v>3.72</v>
+        <v>0.6</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>279</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" t="s">
         <v>129</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E39" t="s">
         <v>130</v>
       </c>
-      <c r="D39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="F39" t="n">
+        <v>323</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H39" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
         <v>131</v>
       </c>
-      <c r="F39" t="n">
-        <v>699</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="H39" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="J39" t="n">
+      <c r="C40" t="s">
+        <v>132</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E40" t="s">
+        <v>133</v>
+      </c>
+      <c r="F40" t="n">
+        <v>461</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H40" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
+        <v>134</v>
+      </c>
+      <c r="C41" t="s">
+        <v>135</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
+        <v>136</v>
+      </c>
+      <c r="F41" t="n">
+        <v>495</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="H41" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J41" t="n">
         <v>3.72</v>
       </c>
-      <c r="K39" t="b">
-        <v>1</v>
-      </c>
-      <c r="L39" t="n">
-        <v>700</v>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" t="s">
+        <v>138</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E42" t="s">
+        <v>139</v>
+      </c>
+      <c r="F42" t="n">
+        <v>602</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>601</v>
       </c>
     </row>
   </sheetData>
@@ -2334,36 +2472,36 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E1" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2377,10 +2515,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
         <v>0.6</v>
@@ -2400,22 +2538,22 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="D4" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -2473,314 +2611,314 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="C2" t="n">
-        <v>278</v>
+        <v>374.5</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.033</v>
+        <v>0.019</v>
       </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="H2" t="n">
-        <v>3.72</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="C3" t="n">
-        <v>473</v>
+        <v>412</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1</v>
+        <v>4.3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.034</v>
+        <v>0.02</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>3.14</v>
+        <v>1.91</v>
       </c>
       <c r="H3" t="n">
-        <v>7.44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="C4" t="n">
-        <v>45.5</v>
+        <v>839</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.541</v>
+        <v>0.012</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>0.35</v>
+        <v>1.26</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>41</v>
+        <v>837</v>
       </c>
       <c r="D5" t="n">
-        <v>5.5</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.331</v>
+        <v>0.003</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.34</v>
+        <v>13.24</v>
       </c>
       <c r="H5" t="n">
-        <v>1.44</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>455</v>
+        <v>630</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="E6" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="F6" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>0.26</v>
+        <v>0.77</v>
       </c>
       <c r="H6" t="n">
-        <v>1.32</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="C7" t="n">
-        <v>190</v>
+        <v>485</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="E7" t="n">
-        <v>0.015</v>
+        <v>0.068</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>0.55</v>
+        <v>0.85</v>
       </c>
       <c r="H7" t="n">
-        <v>1.44</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>485</v>
+        <v>800</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.068</v>
+        <v>0.007</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>0.85</v>
+        <v>3.81</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>699</v>
+        <v>805</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.011</v>
+        <v>0.078</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>2.55</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
-        <v>3.72</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="C10" t="n">
-        <v>644</v>
+        <v>954</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>3.77</v>
+        <v>6.8</v>
       </c>
       <c r="H10" t="n">
-        <v>7.08</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C11" t="n">
-        <v>467</v>
+        <v>658</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.29</v>
+        <v>0.244</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="H11" t="n">
-        <v>8.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C12" t="n">
-        <v>461</v>
+        <v>495</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004</v>
+        <v>0.055</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>3.21</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
-        <v>3.36</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>461</v>
       </c>
       <c r="D13" t="n">
         <v>0.9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.148</v>
+        <v>0.004</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
       </c>
       <c r="G13" t="n">
-        <v>2.14</v>
+        <v>3.21</v>
       </c>
       <c r="H13" t="n">
-        <v>3.72</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="14">
@@ -2788,25 +2926,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>248.5</v>
+        <v>617.5</v>
       </c>
       <c r="D14" t="n">
         <v>0.8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.019</v>
+        <v>0.007</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>2.63</v>
+        <v>3.77</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="15">
@@ -2814,51 +2952,51 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C15" t="n">
-        <v>216</v>
+        <v>1253</v>
       </c>
       <c r="D15" t="n">
         <v>0.8</v>
       </c>
       <c r="E15" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>0.44</v>
+        <v>0.55</v>
       </c>
       <c r="H15" t="n">
-        <v>0.96</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C16" t="n">
-        <v>647</v>
+        <v>362</v>
       </c>
       <c r="D16" t="n">
         <v>0.8</v>
       </c>
       <c r="E16" t="n">
-        <v>0.195</v>
+        <v>0.258</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>5.2</v>
+        <v>0.13</v>
       </c>
       <c r="H16" t="n">
-        <v>8.16</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="17">
@@ -2866,25 +3004,25 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="C17" t="n">
-        <v>125</v>
+        <v>647</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E17" t="n">
-        <v>0.032</v>
+        <v>0.195</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.25</v>
+        <v>5.2</v>
       </c>
       <c r="H17" t="n">
-        <v>2.52</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="18">
@@ -2892,88 +3030,88 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="C18" t="n">
-        <v>117.5</v>
+        <v>846</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02</v>
+        <v>0.002</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>2.29</v>
+        <v>0.11</v>
       </c>
       <c r="H18" t="n">
-        <v>2.04</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="C19" t="n">
-        <v>114</v>
+        <v>602</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E19" t="n">
-        <v>0.024</v>
+        <v>0.002</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>0.52</v>
+        <v>0.69</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C20" t="n">
-        <v>323</v>
+        <v>740.5</v>
       </c>
       <c r="D20" t="n">
         <v>0.7</v>
       </c>
       <c r="E20" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>0.19</v>
+        <v>7.27</v>
       </c>
       <c r="H20" t="n">
-        <v>2.16</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="C21" t="n">
-        <v>319</v>
+        <v>188</v>
       </c>
       <c r="D21" t="n">
         <v>0.7</v>
@@ -2985,10 +3123,10 @@
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>0.56</v>
+        <v>0.44</v>
       </c>
       <c r="H21" t="n">
-        <v>2.28</v>
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -912,7 +912,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>13.24</v>
+        <v>25.88</v>
       </c>
       <c r="J2" t="n">
         <v>19.44</v>
@@ -2707,7 +2707,7 @@
         <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>13.24</v>
+        <v>25.88</v>
       </c>
       <c r="H5" t="n">
         <v>19.44</v>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -912,7 +912,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>25.88</v>
+        <v>38.52</v>
       </c>
       <c r="J2" t="n">
         <v>19.44</v>
@@ -2707,7 +2707,7 @@
         <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>25.88</v>
+        <v>38.52</v>
       </c>
       <c r="H5" t="n">
         <v>19.44</v>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -912,7 +912,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>38.52</v>
+        <v>89.12</v>
       </c>
       <c r="J2" t="n">
         <v>19.44</v>
@@ -2707,7 +2707,7 @@
         <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>38.52</v>
+        <v>89.12</v>
       </c>
       <c r="H5" t="n">
         <v>19.44</v>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -55,6 +55,18 @@
     <t xml:space="preserve">Königsallee_Springorum</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/05/04 16:10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/05 06:50:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/04 20:17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/04/18 15:25:30</t>
   </si>
   <si>
@@ -62,9 +74,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026/04/19 00:35:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
   </si>
   <si>
     <t xml:space="preserve">2026/04/13 15:34:00</t>
@@ -499,8 +508,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L42" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L43" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L43"/>
   <tableColumns count="12">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -897,13 +906,13 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>837</v>
+        <v>880</v>
       </c>
       <c r="G2" t="n">
         <v>0.003</v>
@@ -912,16 +921,16 @@
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>89.12</v>
+        <v>2.25</v>
       </c>
       <c r="J2" t="n">
-        <v>19.44</v>
+        <v>1.68</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1675</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="3">
@@ -935,13 +944,13 @@
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>940</v>
+        <v>837</v>
       </c>
       <c r="G3" t="n">
         <v>0.003</v>
@@ -950,16 +959,16 @@
         <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5</v>
+        <v>89.12</v>
       </c>
       <c r="J3" t="n">
-        <v>0.36</v>
+        <v>19.44</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1881</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="4">
@@ -973,74 +982,74 @@
         <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>617.5</v>
+        <v>940</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>3.77</v>
+        <v>1.5</v>
       </c>
       <c r="J4" t="n">
-        <v>7.08</v>
+        <v>0.36</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>1236</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
       <c r="F5" t="n">
-        <v>630</v>
+        <v>617.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.014</v>
+        <v>0.007</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>0.77</v>
+        <v>3.77</v>
       </c>
       <c r="J5" t="n">
-        <v>0.96</v>
+        <v>7.08</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1261</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
@@ -1049,31 +1058,31 @@
         <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="E6" t="s">
         <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>740.5</v>
+        <v>630</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>7.27</v>
+        <v>0.77</v>
       </c>
       <c r="J6" t="n">
-        <v>4.8</v>
+        <v>0.96</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1482</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="7">
@@ -1087,31 +1096,31 @@
         <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E7" t="s">
         <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>707</v>
+        <v>740.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.015</v>
+        <v>0.004</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>2.19</v>
+        <v>7.27</v>
       </c>
       <c r="J7" t="n">
-        <v>3.36</v>
+        <v>4.8</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1415</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="8">
@@ -1131,25 +1140,25 @@
         <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>126</v>
+        <v>707</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.75</v>
+        <v>2.19</v>
       </c>
       <c r="J8" t="n">
-        <v>2.16</v>
+        <v>3.36</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>253</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="9">
@@ -1169,25 +1178,25 @@
         <v>38</v>
       </c>
       <c r="F9" t="n">
-        <v>41.5</v>
+        <v>126</v>
       </c>
       <c r="G9" t="n">
-        <v>0.048</v>
+        <v>0.01</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.34</v>
+        <v>0.75</v>
       </c>
       <c r="J9" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>84</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -1201,36 +1210,36 @@
         <v>40</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="E10" t="s">
         <v>41</v>
       </c>
       <c r="F10" t="n">
-        <v>485</v>
+        <v>41.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.068</v>
+        <v>0.048</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.85</v>
+        <v>0.34</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6</v>
+        <v>1.44</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>971</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
         <v>42</v>
@@ -1239,74 +1248,74 @@
         <v>43</v>
       </c>
       <c r="D11" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>374.5</v>
+        <v>485</v>
       </c>
       <c r="G11" t="n">
-        <v>0.019</v>
+        <v>0.068</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
       <c r="J11" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>750</v>
+        <v>971</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
         <v>46</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E12" t="s">
         <v>47</v>
       </c>
-      <c r="C12" t="s">
+      <c r="F12" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="H12" t="s">
         <v>48</v>
       </c>
-      <c r="D12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" t="n">
-        <v>320</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="H12" t="s">
-        <v>16</v>
-      </c>
       <c r="I12" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="J12" t="n">
-        <v>1.56</v>
+        <v>4.8</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>321</v>
+        <v>750</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s">
         <v>50</v>
@@ -1315,22 +1324,22 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E13" t="s">
         <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>521</v>
+        <v>320</v>
       </c>
       <c r="G13" t="n">
-        <v>0.194</v>
+        <v>0.002</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>2.82</v>
+        <v>1.71</v>
       </c>
       <c r="J13" t="n">
         <v>1.56</v>
@@ -1339,7 +1348,7 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>522</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14">
@@ -1353,36 +1362,36 @@
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E14" t="s">
         <v>55</v>
       </c>
       <c r="F14" t="n">
-        <v>214</v>
+        <v>521</v>
       </c>
       <c r="G14" t="n">
-        <v>0.017</v>
+        <v>0.194</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1</v>
+        <v>2.82</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6</v>
+        <v>1.56</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>215</v>
+        <v>522</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
         <v>56</v>
@@ -1391,36 +1400,36 @@
         <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="E15" t="s">
         <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>412</v>
+        <v>214</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="H15" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>1.91</v>
+        <v>0.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>413</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
         <v>59</v>
@@ -1429,22 +1438,22 @@
         <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="E16" t="s">
         <v>61</v>
       </c>
       <c r="F16" t="n">
-        <v>800</v>
+        <v>412</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007</v>
+        <v>0.02</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>3.81</v>
+        <v>1.91</v>
       </c>
       <c r="J16" t="n">
         <v>3</v>
@@ -1453,12 +1462,12 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>801</v>
+        <v>413</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
         <v>62</v>
@@ -1473,30 +1482,30 @@
         <v>64</v>
       </c>
       <c r="F17" t="n">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="G17" t="n">
-        <v>0.078</v>
+        <v>0.007</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>2.02</v>
+        <v>3.81</v>
       </c>
       <c r="J17" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>831</v>
+        <v>801</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
         <v>65</v>
@@ -1511,30 +1520,30 @@
         <v>67</v>
       </c>
       <c r="F18" t="n">
-        <v>954</v>
+        <v>805</v>
       </c>
       <c r="G18" t="n">
-        <v>0.005</v>
+        <v>0.078</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>6.8</v>
+        <v>2.02</v>
       </c>
       <c r="J18" t="n">
-        <v>3.36</v>
+        <v>2.16</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1906</v>
+        <v>831</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
         <v>68</v>
@@ -1543,36 +1552,36 @@
         <v>69</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="E19" t="s">
         <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>188</v>
+        <v>954</v>
       </c>
       <c r="G19" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.44</v>
+        <v>6.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.96</v>
+        <v>3.36</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>189</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
         <v>71</v>
@@ -1587,25 +1596,25 @@
         <v>73</v>
       </c>
       <c r="F20" t="n">
-        <v>1098</v>
+        <v>188</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>3.82</v>
+        <v>0.44</v>
       </c>
       <c r="J20" t="n">
-        <v>1.92</v>
+        <v>0.96</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1093</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21">
@@ -1619,31 +1628,31 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E21" t="s">
         <v>76</v>
       </c>
       <c r="F21" t="n">
-        <v>581</v>
+        <v>1098</v>
       </c>
       <c r="G21" t="n">
-        <v>0.098</v>
+        <v>0.001</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
       </c>
       <c r="I21" t="n">
-        <v>0.16</v>
+        <v>3.82</v>
       </c>
       <c r="J21" t="n">
-        <v>1.32</v>
+        <v>1.92</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>580</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="22">
@@ -1657,31 +1666,31 @@
         <v>78</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E22" t="s">
         <v>79</v>
       </c>
       <c r="F22" t="n">
-        <v>1253</v>
+        <v>581</v>
       </c>
       <c r="G22" t="n">
-        <v>0.001</v>
+        <v>0.098</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>0.55</v>
+        <v>0.16</v>
       </c>
       <c r="J22" t="n">
-        <v>2.4</v>
+        <v>1.32</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1248</v>
+        <v>580</v>
       </c>
     </row>
     <row r="23">
@@ -1695,31 +1704,31 @@
         <v>81</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E23" t="s">
         <v>82</v>
       </c>
       <c r="F23" t="n">
-        <v>743</v>
+        <v>1253</v>
       </c>
       <c r="G23" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>740</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="24">
@@ -1733,31 +1742,31 @@
         <v>84</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E24" t="s">
         <v>85</v>
       </c>
       <c r="F24" t="n">
-        <v>131</v>
+        <v>743</v>
       </c>
       <c r="G24" t="n">
-        <v>0.122</v>
+        <v>0.005</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.41</v>
+        <v>0.75</v>
       </c>
       <c r="J24" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>132</v>
+        <v>740</v>
       </c>
     </row>
     <row r="25">
@@ -1777,25 +1786,25 @@
         <v>88</v>
       </c>
       <c r="F25" t="n">
-        <v>352</v>
+        <v>131</v>
       </c>
       <c r="G25" t="n">
-        <v>0.015</v>
+        <v>0.122</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
       </c>
       <c r="I25" t="n">
-        <v>4.99</v>
+        <v>0.41</v>
       </c>
       <c r="J25" t="n">
-        <v>5.76</v>
+        <v>1.44</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>353</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26">
@@ -1809,31 +1818,31 @@
         <v>90</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E26" t="s">
         <v>91</v>
       </c>
       <c r="F26" t="n">
-        <v>199</v>
+        <v>352</v>
       </c>
       <c r="G26" t="n">
-        <v>0.008</v>
+        <v>0.015</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3</v>
+        <v>4.99</v>
       </c>
       <c r="J26" t="n">
-        <v>2.52</v>
+        <v>5.76</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>200</v>
+        <v>353</v>
       </c>
     </row>
     <row r="27">
@@ -1853,25 +1862,25 @@
         <v>94</v>
       </c>
       <c r="F27" t="n">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="G27" t="n">
-        <v>0.018</v>
+        <v>0.008</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="J27" t="n">
-        <v>0.24</v>
+        <v>2.52</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>232</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28">
@@ -1885,31 +1894,31 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E28" t="s">
         <v>97</v>
       </c>
       <c r="F28" t="n">
-        <v>658</v>
+        <v>231</v>
       </c>
       <c r="G28" t="n">
-        <v>0.244</v>
+        <v>0.018</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>1.03</v>
+        <v>0.03</v>
       </c>
       <c r="J28" t="n">
-        <v>1.2</v>
+        <v>0.24</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>657</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29">
@@ -1923,36 +1932,36 @@
         <v>99</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>643</v>
+        <v>658</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004</v>
+        <v>0.244</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
       </c>
       <c r="I29" t="n">
-        <v>6.77</v>
+        <v>1.03</v>
       </c>
       <c r="J29" t="n">
-        <v>4.92</v>
+        <v>1.2</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>642</v>
+        <v>657</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
         <v>101</v>
@@ -1961,36 +1970,36 @@
         <v>102</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E30" t="s">
         <v>103</v>
       </c>
       <c r="F30" t="n">
-        <v>55</v>
+        <v>643</v>
       </c>
       <c r="G30" t="n">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>0.03</v>
+        <v>6.77</v>
       </c>
       <c r="J30" t="n">
-        <v>0.36</v>
+        <v>4.92</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>56</v>
+        <v>642</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="B31" t="s">
         <v>104</v>
@@ -1999,31 +2008,31 @@
         <v>105</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E31" t="s">
         <v>106</v>
       </c>
       <c r="F31" t="n">
-        <v>1030</v>
+        <v>55</v>
       </c>
       <c r="G31" t="n">
-        <v>0.001</v>
+        <v>0.013</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>3.37</v>
+        <v>0.03</v>
       </c>
       <c r="J31" t="n">
-        <v>3.6</v>
+        <v>0.36</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1029</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32">
@@ -2037,31 +2046,31 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E32" t="s">
         <v>109</v>
       </c>
       <c r="F32" t="n">
-        <v>362</v>
+        <v>1030</v>
       </c>
       <c r="G32" t="n">
-        <v>0.258</v>
+        <v>0.001</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>0.13</v>
+        <v>3.37</v>
       </c>
       <c r="J32" t="n">
-        <v>0.84</v>
+        <v>3.6</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>363</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="33">
@@ -2081,25 +2090,25 @@
         <v>112</v>
       </c>
       <c r="F33" t="n">
-        <v>647</v>
+        <v>362</v>
       </c>
       <c r="G33" t="n">
-        <v>0.195</v>
+        <v>0.258</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
       </c>
       <c r="I33" t="n">
-        <v>5.2</v>
+        <v>0.13</v>
       </c>
       <c r="J33" t="n">
-        <v>8.16</v>
+        <v>0.84</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>648</v>
+        <v>363</v>
       </c>
     </row>
     <row r="34">
@@ -2119,25 +2128,25 @@
         <v>115</v>
       </c>
       <c r="F34" t="n">
-        <v>846</v>
+        <v>647</v>
       </c>
       <c r="G34" t="n">
-        <v>0.002</v>
+        <v>0.195</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
       </c>
       <c r="I34" t="n">
-        <v>0.11</v>
+        <v>5.2</v>
       </c>
       <c r="J34" t="n">
-        <v>0.48</v>
+        <v>8.16</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>845</v>
+        <v>648</v>
       </c>
     </row>
     <row r="35">
@@ -2151,36 +2160,36 @@
         <v>117</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E35" t="s">
         <v>118</v>
       </c>
       <c r="F35" t="n">
-        <v>265</v>
+        <v>846</v>
       </c>
       <c r="G35" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
       </c>
       <c r="I35" t="n">
-        <v>0.71</v>
+        <v>0.11</v>
       </c>
       <c r="J35" t="n">
-        <v>0.96</v>
+        <v>0.48</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>266</v>
+        <v>845</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
         <v>119</v>
@@ -2189,36 +2198,36 @@
         <v>120</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E36" t="s">
         <v>121</v>
       </c>
       <c r="F36" t="n">
-        <v>22</v>
+        <v>265</v>
       </c>
       <c r="G36" t="n">
-        <v>0.082</v>
+        <v>0.004</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>0.52</v>
+        <v>0.71</v>
       </c>
       <c r="J36" t="n">
-        <v>2.4</v>
+        <v>0.96</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>23</v>
+        <v>266</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="B37" t="s">
         <v>122</v>
@@ -2227,31 +2236,31 @@
         <v>123</v>
       </c>
       <c r="D37" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="E37" t="s">
         <v>124</v>
       </c>
       <c r="F37" t="n">
-        <v>839</v>
+        <v>22</v>
       </c>
       <c r="G37" t="n">
-        <v>0.012</v>
+        <v>0.082</v>
       </c>
       <c r="H37" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="I37" t="n">
-        <v>1.26</v>
+        <v>0.52</v>
       </c>
       <c r="J37" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>840</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38">
@@ -2265,31 +2274,31 @@
         <v>126</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="E38" t="s">
         <v>127</v>
       </c>
       <c r="F38" t="n">
-        <v>21</v>
+        <v>839</v>
       </c>
       <c r="G38" t="n">
-        <v>0.028</v>
+        <v>0.012</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I38" t="n">
-        <v>0.11</v>
+        <v>1.26</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6</v>
+        <v>1.92</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>20</v>
+        <v>840</v>
       </c>
     </row>
     <row r="39">
@@ -2303,31 +2312,31 @@
         <v>129</v>
       </c>
       <c r="D39" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E39" t="s">
         <v>130</v>
       </c>
       <c r="F39" t="n">
-        <v>323</v>
+        <v>21</v>
       </c>
       <c r="G39" t="n">
-        <v>0.003</v>
+        <v>0.028</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="J39" t="n">
-        <v>2.16</v>
+        <v>0.6</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>324</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -2341,31 +2350,31 @@
         <v>132</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E40" t="s">
         <v>133</v>
       </c>
       <c r="F40" t="n">
-        <v>461</v>
+        <v>323</v>
       </c>
       <c r="G40" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
       </c>
       <c r="I40" t="n">
-        <v>3.21</v>
+        <v>0.19</v>
       </c>
       <c r="J40" t="n">
-        <v>3.36</v>
+        <v>2.16</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>462</v>
+        <v>324</v>
       </c>
     </row>
     <row r="41">
@@ -2379,36 +2388,36 @@
         <v>135</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E41" t="s">
         <v>136</v>
       </c>
       <c r="F41" t="n">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="G41" t="n">
-        <v>0.055</v>
+        <v>0.004</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>3.21</v>
       </c>
       <c r="J41" t="n">
-        <v>3.72</v>
+        <v>3.36</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>496</v>
+        <v>462</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
         <v>137</v>
@@ -2417,30 +2426,68 @@
         <v>138</v>
       </c>
       <c r="D42" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E42" t="s">
         <v>139</v>
       </c>
       <c r="F42" t="n">
+        <v>495</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="H42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" t="s">
+        <v>140</v>
+      </c>
+      <c r="C43" t="s">
+        <v>141</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E43" t="s">
+        <v>142</v>
+      </c>
+      <c r="F43" t="n">
         <v>602</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G43" t="n">
         <v>0.002</v>
       </c>
-      <c r="H42" t="s">
-        <v>16</v>
-      </c>
-      <c r="I42" t="n">
+      <c r="H43" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" t="n">
         <v>0.69</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J43" t="n">
         <v>3.24</v>
       </c>
-      <c r="K42" t="b">
-        <v>1</v>
-      </c>
-      <c r="L42" t="n">
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
         <v>601</v>
       </c>
     </row>
@@ -2472,22 +2519,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2">
@@ -2495,7 +2542,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
         <v>0.8</v>
@@ -2515,7 +2562,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B3" t="n">
         <v>5</v>
@@ -2538,7 +2585,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B4" t="n">
         <v>4</v>
@@ -2611,10 +2658,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
         <v>374.5</v>
@@ -2626,7 +2673,7 @@
         <v>0.019</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G2" t="n">
         <v>1.01</v>
@@ -2637,10 +2684,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
         <v>412</v>
@@ -2652,7 +2699,7 @@
         <v>0.02</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G3" t="n">
         <v>1.91</v>
@@ -2666,7 +2713,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C4" t="n">
         <v>839</v>
@@ -2678,7 +2725,7 @@
         <v>0.012</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G4" t="n">
         <v>1.26</v>
@@ -2692,7 +2739,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
         <v>837</v>
@@ -2715,10 +2762,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
         <v>630</v>
@@ -2744,7 +2791,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C7" t="n">
         <v>485</v>
@@ -2770,7 +2817,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
         <v>800</v>
@@ -2793,10 +2840,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
         <v>805</v>
@@ -2822,7 +2869,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C10" t="n">
         <v>954</v>
@@ -2848,7 +2895,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C11" t="n">
         <v>658</v>
@@ -2874,7 +2921,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C12" t="n">
         <v>495</v>
@@ -2900,7 +2947,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C13" t="n">
         <v>461</v>
@@ -2926,25 +2973,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>617.5</v>
+        <v>880</v>
       </c>
       <c r="D14" t="n">
         <v>0.8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>3.77</v>
+        <v>2.25</v>
       </c>
       <c r="H14" t="n">
-        <v>7.08</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="15">
@@ -2952,25 +2999,25 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>1253</v>
+        <v>617.5</v>
       </c>
       <c r="D15" t="n">
         <v>0.8</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>0.55</v>
+        <v>3.77</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="16">
@@ -2978,25 +3025,25 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="C16" t="n">
-        <v>362</v>
+        <v>1253</v>
       </c>
       <c r="D16" t="n">
         <v>0.8</v>
       </c>
       <c r="E16" t="n">
-        <v>0.258</v>
+        <v>0.001</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.13</v>
+        <v>0.55</v>
       </c>
       <c r="H16" t="n">
-        <v>0.84</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -3007,22 +3054,22 @@
         <v>110</v>
       </c>
       <c r="C17" t="n">
-        <v>647</v>
+        <v>362</v>
       </c>
       <c r="D17" t="n">
         <v>0.8</v>
       </c>
       <c r="E17" t="n">
-        <v>0.195</v>
+        <v>0.258</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>5.2</v>
+        <v>0.13</v>
       </c>
       <c r="H17" t="n">
-        <v>8.16</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="18">
@@ -3033,33 +3080,33 @@
         <v>113</v>
       </c>
       <c r="C18" t="n">
-        <v>846</v>
+        <v>647</v>
       </c>
       <c r="D18" t="n">
         <v>0.8</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002</v>
+        <v>0.195</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>0.11</v>
+        <v>5.2</v>
       </c>
       <c r="H18" t="n">
-        <v>0.48</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="C19" t="n">
-        <v>602</v>
+        <v>846</v>
       </c>
       <c r="D19" t="n">
         <v>0.8</v>
@@ -3071,62 +3118,62 @@
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>0.69</v>
+        <v>0.11</v>
       </c>
       <c r="H19" t="n">
-        <v>3.24</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>140</v>
       </c>
       <c r="C20" t="n">
-        <v>740.5</v>
+        <v>602</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E20" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>7.27</v>
+        <v>0.69</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C21" t="n">
-        <v>188</v>
+        <v>740.5</v>
       </c>
       <c r="D21" t="n">
         <v>0.7</v>
       </c>
       <c r="E21" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>0.44</v>
+        <v>7.27</v>
       </c>
       <c r="H21" t="n">
-        <v>0.96</v>
+        <v>4.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -52,6 +52,21 @@
     <t xml:space="preserve">points_count</t>
   </si>
   <si>
+    <t xml:space="preserve">An_der_Kost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/06 00:06:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/06 00:34:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/06 00:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wasserstraße_Springorum</t>
   </si>
   <si>
@@ -64,9 +79,6 @@
     <t xml:space="preserve">2026/03/29 12:47:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026/03/11 05:51:30</t>
   </si>
   <si>
@@ -77,9 +89,6 @@
   </si>
   <si>
     <t xml:space="preserve">Regenereignis / Natürlich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An_der_Kost</t>
   </si>
   <si>
     <t xml:space="preserve">2026/02/23 22:16:00</t>
@@ -274,8 +283,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L17" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L18" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L18"/>
   <tableColumns count="12">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -311,8 +320,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:H17" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:H18" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H18"/>
   <tableColumns count="8">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -672,107 +681,107 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>630</v>
+        <v>28.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="J2" t="n">
-        <v>0.96</v>
+        <v>1.44</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1261</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>374.5</v>
+        <v>630</v>
       </c>
       <c r="G3" t="n">
-        <v>0.019</v>
+        <v>0.014</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>1.01</v>
+        <v>0.77</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8</v>
+        <v>0.96</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>750</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="H4" t="s">
         <v>24</v>
       </c>
-      <c r="F4" t="n">
-        <v>320</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="H4" t="s">
-        <v>16</v>
-      </c>
       <c r="I4" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="J4" t="n">
-        <v>1.56</v>
+        <v>4.8</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>321</v>
+        <v>750</v>
       </c>
     </row>
     <row r="5">
@@ -786,36 +795,36 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>412</v>
+        <v>320</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02</v>
+        <v>0.002</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>413</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
@@ -824,74 +833,74 @@
         <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>805</v>
+        <v>412</v>
       </c>
       <c r="G6" t="n">
-        <v>0.078</v>
+        <v>0.02</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I6" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="J6" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>831</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
         <v>31</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E7" t="s">
         <v>33</v>
       </c>
-      <c r="D7" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="E7" t="s">
-        <v>34</v>
-      </c>
       <c r="F7" t="n">
-        <v>1298</v>
+        <v>805</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05</v>
+        <v>0.078</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="J7" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>2601</v>
+        <v>831</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
         <v>35</v>
@@ -900,36 +909,36 @@
         <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>39.8</v>
       </c>
       <c r="E8" t="s">
         <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>864</v>
+        <v>1298</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002</v>
+        <v>0.05</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I8" t="n">
-        <v>0.61</v>
+        <v>2.18</v>
       </c>
       <c r="J8" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>1732</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
         <v>38</v>
@@ -938,36 +947,36 @@
         <v>39</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="s">
         <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>1.29</v>
+        <v>0.61</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8</v>
+        <v>0.96</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1729</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
         <v>41</v>
@@ -976,13 +985,13 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E10" t="s">
         <v>43</v>
       </c>
       <c r="F10" t="n">
-        <v>462</v>
+        <v>862</v>
       </c>
       <c r="G10" t="n">
         <v>0.005</v>
@@ -991,21 +1000,21 @@
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.11</v>
+        <v>1.29</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>929</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
         <v>44</v>
@@ -1014,36 +1023,36 @@
         <v>45</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E11" t="s">
         <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>83</v>
+        <v>462</v>
       </c>
       <c r="G11" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="J11" t="n">
-        <v>0.84</v>
+        <v>0.6</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>168</v>
+        <v>929</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
         <v>47</v>
@@ -1052,36 +1061,36 @@
         <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E12" t="s">
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>188</v>
+        <v>83</v>
       </c>
       <c r="G12" t="n">
-        <v>0.006</v>
+        <v>0.014</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="J12" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>189</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>50</v>
@@ -1090,36 +1099,36 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E13" t="s">
         <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>69</v>
+        <v>188</v>
       </c>
       <c r="G13" t="n">
-        <v>0.025</v>
+        <v>0.006</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>0.03</v>
+        <v>0.44</v>
       </c>
       <c r="J13" t="n">
-        <v>0.24</v>
+        <v>0.96</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>70</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
         <v>53</v>
@@ -1128,16 +1137,16 @@
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E14" t="s">
         <v>55</v>
       </c>
       <c r="F14" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="G14" t="n">
-        <v>0.013</v>
+        <v>0.025</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
@@ -1146,18 +1155,18 @@
         <v>0.03</v>
       </c>
       <c r="J14" t="n">
-        <v>0.36</v>
+        <v>0.24</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
         <v>56</v>
@@ -1172,30 +1181,30 @@
         <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
-        <v>0.082</v>
+        <v>0.013</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>0.52</v>
+        <v>0.03</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4</v>
+        <v>0.36</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
         <v>59</v>
@@ -1210,30 +1219,30 @@
         <v>61</v>
       </c>
       <c r="F16" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05</v>
+        <v>0.082</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>1.79</v>
+        <v>0.52</v>
       </c>
       <c r="J16" t="n">
-        <v>3.36</v>
+        <v>2.4</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
         <v>62</v>
@@ -1242,30 +1251,68 @@
         <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E17" t="s">
         <v>64</v>
       </c>
       <c r="F17" t="n">
-        <v>602</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>0.002</v>
+        <v>0.05</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>0.69</v>
+        <v>1.79</v>
       </c>
       <c r="J17" t="n">
-        <v>3.24</v>
+        <v>3.36</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" t="n">
+        <v>602</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
         <v>601</v>
       </c>
     </row>
@@ -1297,27 +1344,27 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B2" t="n">
         <v>7</v>
@@ -1340,10 +1387,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
         <v>0.6</v>
@@ -1363,7 +1410,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B4" t="n">
         <v>4</v>
@@ -1436,10 +1483,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
         <v>1298</v>
@@ -1451,7 +1498,7 @@
         <v>0.05</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
         <v>2.18</v>
@@ -1462,10 +1509,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
         <v>374.5</v>
@@ -1477,7 +1524,7 @@
         <v>0.019</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G3" t="n">
         <v>1.01</v>
@@ -1488,10 +1535,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
         <v>412</v>
@@ -1503,7 +1550,7 @@
         <v>0.02</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
         <v>1.91</v>
@@ -1514,10 +1561,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
         <v>630</v>
@@ -1540,10 +1587,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C6" t="n">
         <v>805</v>
@@ -1566,10 +1613,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C7" t="n">
         <v>862</v>
@@ -1592,10 +1639,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C8" t="n">
         <v>864</v>
@@ -1618,10 +1665,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
         <v>83</v>
@@ -1644,10 +1691,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C10" t="n">
         <v>602</v>
@@ -1670,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
         <v>188</v>
@@ -1696,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C12" t="n">
         <v>462</v>
@@ -1722,131 +1769,157 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>320</v>
+        <v>28.5</v>
       </c>
       <c r="D13" t="n">
         <v>0.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002</v>
+        <v>0.02</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
       </c>
       <c r="G13" t="n">
-        <v>1.71</v>
+        <v>0.78</v>
       </c>
       <c r="H13" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>320</v>
       </c>
       <c r="D14" t="n">
         <v>0.5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.013</v>
+        <v>0.002</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.03</v>
+        <v>1.71</v>
       </c>
       <c r="H14" t="n">
-        <v>0.36</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
         <v>56</v>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.082</v>
+        <v>0.013</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>0.52</v>
+        <v>0.03</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
         <v>59</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
         <v>0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05</v>
+        <v>0.082</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>1.79</v>
+        <v>0.52</v>
       </c>
       <c r="H16" t="n">
-        <v>3.36</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C17" t="n">
+        <v>41</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="n">
         <v>69</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D18" t="n">
         <v>0.4</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E18" t="n">
         <v>0.025</v>
       </c>
-      <c r="F17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.03</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H18" t="n">
         <v>0.24</v>
       </c>
     </row>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -696,7 +696,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>0.78</v>
+        <v>3.9</v>
       </c>
       <c r="J2" t="n">
         <v>1.44</v>
@@ -1787,7 +1787,7 @@
         <v>16</v>
       </c>
       <c r="G13" t="n">
-        <v>0.78</v>
+        <v>3.9</v>
       </c>
       <c r="H13" t="n">
         <v>1.44</v>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -55,10 +55,10 @@
     <t xml:space="preserve">An_der_Kost</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/05/06 00:06:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/05/06 00:34:30</t>
+    <t xml:space="preserve">2026/05/05 21:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/06 03:44:00</t>
   </si>
   <si>
     <t xml:space="preserve">2026/05/06 00:31:00</t>
@@ -67,6 +67,42 @@
     <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/04/19 00:35:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/19 02:05:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/19 00:45:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 19:15:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 20:16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 19:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/30 01:37:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/30 03:07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/30 02:15:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 22:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 23:24:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 22:44:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wasserstraße_Springorum</t>
   </si>
   <si>
@@ -79,6 +115,42 @@
     <t xml:space="preserve">2026/03/29 12:47:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/03/14 08:47:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/14 09:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/14 08:54:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/13 17:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/13 21:44:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/13 17:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/13 10:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/13 16:06:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/13 13:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 13:17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 14:50:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 14:14:30</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/03/11 05:51:30</t>
   </si>
   <si>
@@ -91,15 +163,42 @@
     <t xml:space="preserve">Regenereignis / Natürlich</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/02/23 22:16:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/02/24 03:36:00</t>
+    <t xml:space="preserve">2026/02/23 21:56:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/24 04:06:00</t>
   </si>
   <si>
     <t xml:space="preserve">2026/02/24 03:24:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/02/22 17:17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 19:24:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 17:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 09:59:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 15:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 11:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 09:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 11:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 11:08:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/02/19 04:48:00</t>
   </si>
   <si>
@@ -118,6 +217,15 @@
     <t xml:space="preserve">2026/02/18 13:41:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/02/16 13:26:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/16 16:12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/16 14:46:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Königsallee_Springorum</t>
   </si>
   <si>
@@ -127,7 +235,7 @@
     <t xml:space="preserve">2026/02/03 14:37:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/02/03 06:21:00</t>
+    <t xml:space="preserve">2026/02/03 11:44:00</t>
   </si>
   <si>
     <t xml:space="preserve">2026/02/01 19:25:00</t>
@@ -166,15 +274,24 @@
     <t xml:space="preserve">2026/01/24 03:44:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/01/14 04:27:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/01/14 07:35:00</t>
+    <t xml:space="preserve">2026/01/14 04:18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/14 07:54:00</t>
   </si>
   <si>
     <t xml:space="preserve">2026/01/14 06:29:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/01/09 11:41:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/09 17:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/09 11:44:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/01/09 10:41:00</t>
   </si>
   <si>
@@ -184,24 +301,123 @@
     <t xml:space="preserve">2026/01/09 10:57:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2025/11/24 17:27:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/11/24 18:22:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/11/24 18:05:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/10/23 17:14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/10/23 17:36:00</t>
+    <t xml:space="preserve">2026/01/07 17:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/07 18:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/07 17:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/08 18:37:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/09 01:55:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/08 19:50:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/07 16:36:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/07 22:12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/07 19:57:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/02 06:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/02 09:47:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/02 07:10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/20 04:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/20 08:41:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/20 04:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/19 19:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/20 01:14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/19 20:52:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/17 13:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/17 15:05:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/17 13:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/15 00:51:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/15 01:17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/15 00:55:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/01 13:12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/01 14:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/01 13:38:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/28 06:47:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/28 10:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/28 08:36:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 16:56:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 17:42:00</t>
   </si>
   <si>
     <t xml:space="preserve">2025/10/23 17:20:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2025/10/23 03:37:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 03:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 03:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 05:41:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 11:18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 06:23:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025/10/04 00:17:00</t>
   </si>
   <si>
@@ -211,13 +427,112 @@
     <t xml:space="preserve">2025/10/04 00:27:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2025/09/15 04:22:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/09/15 14:24:00</t>
+    <t xml:space="preserve">2025/10/03 22:55:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 00:16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/03 23:53:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/26 20:36:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/26 22:50:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/26 21:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/22 08:02:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/22 20:02:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/22 10:17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 17:09:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/22 06:02:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 18:55:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/15 04:14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/15 16:29:00</t>
   </si>
   <si>
     <t xml:space="preserve">2025/09/15 10:02:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/13 06:56:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/14 01:16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/13 10:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/09 13:35:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/09 21:53:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/09 14:25:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/09 02:54:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/09 07:11:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/09 05:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/05 08:50:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/05 16:28:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/05 08:55:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/04 07:12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/04 22:35:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/04 09:22:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/02 08:38:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/03 01:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/02 11:06:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/01 14:09:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/01 19:53:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/01 16:31:00</t>
   </si>
   <si>
     <t xml:space="preserve">Ereignisse</t>
@@ -283,8 +598,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L18" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L53" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L53"/>
   <tableColumns count="12">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -320,8 +635,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:H18" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:H21" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H21"/>
   <tableColumns count="8">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -687,101 +1002,101 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>28.5</v>
+        <v>361</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02</v>
+        <v>0.003</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9</v>
+        <v>42.9</v>
       </c>
       <c r="J2" t="n">
-        <v>1.44</v>
+        <v>9.48</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>58</v>
+        <v>723</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
       <c r="F3" t="n">
-        <v>630</v>
+        <v>90.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.014</v>
+        <v>0.04</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>0.77</v>
+        <v>44.02</v>
       </c>
       <c r="J3" t="n">
-        <v>0.96</v>
+        <v>20.16</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1261</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="D4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
       <c r="F4" t="n">
-        <v>374.5</v>
+        <v>60.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.019</v>
+        <v>0.054</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>1.01</v>
+        <v>2.91</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>750</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5">
@@ -789,247 +1104,247 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
       <c r="F5" t="n">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>1.71</v>
+        <v>1.09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.56</v>
+        <v>2.04</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>321</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
       <c r="F6" t="n">
-        <v>412</v>
+        <v>50.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.04</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>413</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
-      </c>
       <c r="F7" t="n">
-        <v>805</v>
+        <v>630</v>
       </c>
       <c r="G7" t="n">
-        <v>0.078</v>
+        <v>0.014</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>2.02</v>
+        <v>0.77</v>
       </c>
       <c r="J7" t="n">
-        <v>2.16</v>
+        <v>0.96</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>831</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E8" t="s">
         <v>35</v>
       </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="E8" t="s">
-        <v>37</v>
-      </c>
       <c r="F8" t="n">
-        <v>1298</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05</v>
+        <v>0.039</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>2.18</v>
+        <v>0.08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.04</v>
+        <v>0.96</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>2601</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E9" t="s">
         <v>38</v>
       </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E9" t="s">
-        <v>40</v>
-      </c>
       <c r="F9" t="n">
-        <v>864</v>
+        <v>276.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002</v>
+        <v>0.013</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.61</v>
+        <v>8.81</v>
       </c>
       <c r="J9" t="n">
-        <v>0.96</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1732</v>
+        <v>554</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E10" t="s">
         <v>41</v>
       </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>43</v>
-      </c>
       <c r="F10" t="n">
-        <v>862</v>
+        <v>326.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8</v>
+        <v>3.12</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1729</v>
+        <v>654</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E11" t="s">
         <v>44</v>
       </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E11" t="s">
-        <v>46</v>
-      </c>
       <c r="F11" t="n">
-        <v>462</v>
+        <v>93</v>
       </c>
       <c r="G11" t="n">
         <v>0.005</v>
@@ -1038,54 +1353,54 @@
         <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>0.11</v>
+        <v>2.91</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6</v>
+        <v>2.52</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>929</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E12" t="s">
         <v>47</v>
       </c>
-      <c r="C12" t="s">
+      <c r="F12" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="H12" t="s">
         <v>48</v>
       </c>
-      <c r="D12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" t="n">
-        <v>83</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="H12" t="s">
-        <v>16</v>
-      </c>
       <c r="I12" t="n">
-        <v>0.46</v>
+        <v>1.01</v>
       </c>
       <c r="J12" t="n">
-        <v>0.84</v>
+        <v>4.8</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>168</v>
+        <v>750</v>
       </c>
     </row>
     <row r="13">
@@ -1093,75 +1408,75 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
         <v>50</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="s">
         <v>51</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E13" t="s">
-        <v>52</v>
-      </c>
       <c r="F13" t="n">
-        <v>188</v>
+        <v>370</v>
       </c>
       <c r="G13" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>0.44</v>
+        <v>1.99</v>
       </c>
       <c r="J13" t="n">
-        <v>0.96</v>
+        <v>1.56</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>189</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s">
         <v>53</v>
-      </c>
-      <c r="C14" t="s">
-        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>0.4</v>
       </c>
       <c r="E14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F14" t="n">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="G14" t="n">
-        <v>0.025</v>
+        <v>0.129</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03</v>
+        <v>4.49</v>
       </c>
       <c r="J14" t="n">
-        <v>0.24</v>
+        <v>4.68</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>70</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15">
@@ -1169,37 +1484,37 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
         <v>56</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E15" t="s">
         <v>57</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>58</v>
-      </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>322</v>
       </c>
       <c r="G15" t="n">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03</v>
+        <v>0.43</v>
       </c>
       <c r="J15" t="n">
-        <v>0.36</v>
+        <v>2.52</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>56</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16">
@@ -1207,113 +1522,1443 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" t="s">
         <v>59</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E16" t="s">
         <v>60</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E16" t="s">
-        <v>61</v>
-      </c>
       <c r="F16" t="n">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="G16" t="n">
-        <v>0.082</v>
+        <v>0.005</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>0.52</v>
+        <v>0.18</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>23</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" t="s">
         <v>62</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E17" t="s">
         <v>63</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E17" t="s">
-        <v>64</v>
-      </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>412</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="J17" t="n">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>42</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
         <v>65</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E18" t="s">
         <v>66</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
+        <v>805</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="H18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" t="n">
+        <v>166</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" t="n">
         <v>0.8</v>
       </c>
-      <c r="E18" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18" t="n">
-        <v>602</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="E20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1298</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2601</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" t="n">
+        <v>864</v>
+      </c>
+      <c r="G21" t="n">
         <v>0.002</v>
       </c>
-      <c r="H18" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E22" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" t="n">
+        <v>862</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E23" t="s">
+        <v>82</v>
+      </c>
+      <c r="F23" t="n">
+        <v>462</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H23" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" t="n">
+        <v>83</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E25" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" t="n">
+        <v>216</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E26" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" t="n">
+        <v>349</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E27" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" t="n">
+        <v>69</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E28" t="s">
+        <v>97</v>
+      </c>
+      <c r="F28" t="n">
+        <v>101</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" t="s">
+        <v>99</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E29" t="s">
+        <v>100</v>
+      </c>
+      <c r="F29" t="n">
+        <v>438</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H29" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E30" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30" t="n">
+        <v>336</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H30" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" t="s">
+        <v>105</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E31" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" t="n">
+        <v>193</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E32" t="s">
+        <v>109</v>
+      </c>
+      <c r="F32" t="n">
+        <v>281</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" t="s">
+        <v>111</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E33" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33" t="n">
+        <v>332</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E34" t="s">
+        <v>115</v>
+      </c>
+      <c r="F34" t="n">
+        <v>96</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="H34" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J34" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E35" t="s">
+        <v>118</v>
+      </c>
+      <c r="F35" t="n">
+        <v>26</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E36" t="s">
+        <v>121</v>
+      </c>
+      <c r="F36" t="n">
+        <v>77</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H36" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E37" t="s">
+        <v>124</v>
+      </c>
+      <c r="F37" t="n">
+        <v>214</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" t="s">
+        <v>126</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E38" t="s">
+        <v>127</v>
+      </c>
+      <c r="F38" t="n">
+        <v>46</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="H38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" t="s">
+        <v>129</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E39" t="s">
+        <v>130</v>
+      </c>
+      <c r="F39" t="n">
+        <v>7</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="H39" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="J39" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" t="s">
+        <v>132</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E40" t="s">
+        <v>133</v>
+      </c>
+      <c r="F40" t="n">
+        <v>337</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H40" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="J40" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" t="s">
+        <v>134</v>
+      </c>
+      <c r="C41" t="s">
+        <v>135</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E41" t="s">
+        <v>136</v>
+      </c>
+      <c r="F41" t="n">
+        <v>41</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H41" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" t="s">
+        <v>138</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E42" t="s">
+        <v>139</v>
+      </c>
+      <c r="F42" t="n">
+        <v>81</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" t="s">
+        <v>140</v>
+      </c>
+      <c r="C43" t="s">
+        <v>141</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E43" t="s">
+        <v>142</v>
+      </c>
+      <c r="F43" t="n">
+        <v>134</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H43" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" t="s">
+        <v>143</v>
+      </c>
+      <c r="C44" t="s">
+        <v>144</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E44" t="s">
+        <v>145</v>
+      </c>
+      <c r="F44" t="n">
+        <v>720</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H44" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="J44" t="n">
+        <v>8.04</v>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" t="s">
+        <v>146</v>
+      </c>
+      <c r="C45" t="s">
+        <v>147</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E45" t="s">
+        <v>148</v>
+      </c>
+      <c r="F45" t="n">
+        <v>773</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H45" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" t="s">
+        <v>149</v>
+      </c>
+      <c r="C46" t="s">
+        <v>150</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E46" t="s">
+        <v>151</v>
+      </c>
+      <c r="F46" t="n">
+        <v>735</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H46" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" t="n">
         <v>0.69</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J46" t="n">
         <v>3.24</v>
       </c>
-      <c r="K18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>601</v>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" t="s">
+        <v>152</v>
+      </c>
+      <c r="C47" t="s">
+        <v>153</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E47" t="s">
+        <v>154</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H47" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="J47" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K47" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" t="s">
+        <v>155</v>
+      </c>
+      <c r="C48" t="s">
+        <v>156</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E48" t="s">
+        <v>157</v>
+      </c>
+      <c r="F48" t="n">
+        <v>498</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H48" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J48" t="n">
+        <v>3</v>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C49" t="s">
+        <v>159</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E49" t="s">
+        <v>160</v>
+      </c>
+      <c r="F49" t="n">
+        <v>257</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H49" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="J49" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="K49" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" t="s">
+        <v>161</v>
+      </c>
+      <c r="C50" t="s">
+        <v>162</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E50" t="s">
+        <v>163</v>
+      </c>
+      <c r="F50" t="n">
+        <v>458</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="H50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="J50" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
+        <v>164</v>
+      </c>
+      <c r="C51" t="s">
+        <v>165</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E51" t="s">
+        <v>166</v>
+      </c>
+      <c r="F51" t="n">
+        <v>923</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H51" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" t="s">
+        <v>167</v>
+      </c>
+      <c r="C52" t="s">
+        <v>168</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E52" t="s">
+        <v>169</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1012</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H52" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" t="s">
+        <v>170</v>
+      </c>
+      <c r="C53" t="s">
+        <v>171</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E53" t="s">
+        <v>172</v>
+      </c>
+      <c r="F53" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H53" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>688</v>
       </c>
     </row>
   </sheetData>
@@ -1344,42 +2989,42 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
+        <v>173</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>174</v>
       </c>
       <c r="D1" t="s">
-        <v>70</v>
+        <v>175</v>
       </c>
       <c r="E1" t="s">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="F1" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
-        <v>6.3</v>
+        <v>0.4</v>
       </c>
       <c r="D2" t="n">
-        <v>39.8</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1387,16 +3032,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1410,7 +3055,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B4" t="n">
         <v>4</v>
@@ -1483,88 +3128,88 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>1298</v>
+        <v>374.5</v>
       </c>
       <c r="D2" t="n">
-        <v>39.8</v>
+        <v>6.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05</v>
+        <v>0.019</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G2" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="H2" t="n">
-        <v>2.04</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="C3" t="n">
-        <v>374.5</v>
+        <v>412</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G3" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="C4" t="n">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02</v>
+        <v>0.082</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C5" t="n">
         <v>630</v>
@@ -1587,10 +3232,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C6" t="n">
         <v>805</v>
@@ -1613,10 +3258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="C7" t="n">
         <v>862</v>
@@ -1639,80 +3284,80 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>864</v>
+        <v>1298</v>
       </c>
       <c r="D8" t="n">
         <v>0.8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>0.61</v>
+        <v>2.18</v>
       </c>
       <c r="H8" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>83</v>
+        <v>864</v>
       </c>
       <c r="D9" t="n">
         <v>0.8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="H9" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C10" t="n">
-        <v>602</v>
+        <v>83</v>
       </c>
       <c r="D10" t="n">
         <v>0.8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.69</v>
+        <v>0.46</v>
       </c>
       <c r="H10" t="n">
-        <v>3.24</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="11">
@@ -1720,39 +3365,39 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>735</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.44</v>
+        <v>0.69</v>
       </c>
       <c r="H11" t="n">
-        <v>0.96</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="C12" t="n">
-        <v>462</v>
+        <v>216</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E12" t="n">
         <v>0.005</v>
@@ -1761,36 +3406,36 @@
         <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="C13" t="n">
-        <v>28.5</v>
+        <v>462</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
       </c>
       <c r="G13" t="n">
-        <v>3.9</v>
+        <v>0.11</v>
       </c>
       <c r="H13" t="n">
-        <v>1.44</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14">
@@ -1798,25 +3443,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="C14" t="n">
-        <v>320</v>
+        <v>438</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>1.71</v>
+        <v>0.12</v>
       </c>
       <c r="H14" t="n">
-        <v>1.56</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="15">
@@ -1824,25 +3469,25 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>361</v>
       </c>
       <c r="D15" t="n">
         <v>0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>0.03</v>
+        <v>42.9</v>
       </c>
       <c r="H15" t="n">
-        <v>0.36</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="16">
@@ -1850,77 +3495,155 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>326.5</v>
       </c>
       <c r="D16" t="n">
         <v>0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>0.082</v>
+        <v>0.003</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.52</v>
+        <v>1.05</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>370</v>
       </c>
       <c r="D17" t="n">
         <v>0.5</v>
       </c>
       <c r="E17" t="n">
-        <v>0.05</v>
+        <v>0.002</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="H17" t="n">
-        <v>3.36</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C18" t="n">
-        <v>69</v>
+        <v>166</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E18" t="n">
-        <v>0.025</v>
+        <v>0.006</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03</v>
+        <v>0.49</v>
       </c>
       <c r="H18" t="n">
-        <v>0.24</v>
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" t="n">
+        <v>26</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" t="n">
+        <v>214</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" t="n">
+        <v>46</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="F21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -52,9 +52,33 @@
     <t xml:space="preserve">points_count</t>
   </si>
   <si>
+    <t xml:space="preserve">Wasserstraße_Springorum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/11 12:42:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/12 08:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/11 21:05:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
     <t xml:space="preserve">An_der_Kost</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/05/11 06:13:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/11 08:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/11 06:30:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/05/05 21:43:00</t>
   </si>
   <si>
@@ -64,9 +88,6 @@
     <t xml:space="preserve">2026/05/06 00:31:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026/04/19 00:35:00</t>
   </si>
   <si>
@@ -101,9 +122,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026/03/29 22:44:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wasserstraße_Springorum</t>
   </si>
   <si>
     <t xml:space="preserve">2026/03/29 11:16:00</t>
@@ -598,8 +616,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L53" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L53"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L55" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L55"/>
   <tableColumns count="12">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -996,188 +1014,188 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>361</v>
+        <v>1157.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>42.9</v>
+        <v>2.36</v>
       </c>
       <c r="J2" t="n">
-        <v>9.48</v>
+        <v>3.24</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>723</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>90.5</v>
+        <v>139</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04</v>
+        <v>0.018</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>44.02</v>
+        <v>5.95</v>
       </c>
       <c r="J3" t="n">
-        <v>20.16</v>
+        <v>5.16</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>182</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n">
-        <v>60.5</v>
+        <v>361</v>
       </c>
       <c r="G4" t="n">
-        <v>0.054</v>
+        <v>0.003</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>2.91</v>
+        <v>42.9</v>
       </c>
       <c r="J4" t="n">
-        <v>7.8</v>
+        <v>9.48</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>122</v>
+        <v>723</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
         <v>0.4</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>1.09</v>
+        <v>44.02</v>
       </c>
       <c r="J5" t="n">
-        <v>2.04</v>
+        <v>20.16</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
         <v>0.3</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>50.5</v>
+        <v>60.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03</v>
+        <v>0.054</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>1.89</v>
+        <v>2.91</v>
       </c>
       <c r="J6" t="n">
-        <v>2.04</v>
+        <v>7.8</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>102</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
@@ -1186,36 +1204,36 @@
         <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="s">
         <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>630</v>
+        <v>90</v>
       </c>
       <c r="G7" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.77</v>
+        <v>1.09</v>
       </c>
       <c r="J7" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1261</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
@@ -1230,25 +1248,25 @@
         <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>50.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08</v>
+        <v>1.89</v>
       </c>
       <c r="J8" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9">
@@ -1262,36 +1280,36 @@
         <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
       </c>
       <c r="F9" t="n">
-        <v>276.5</v>
+        <v>630</v>
       </c>
       <c r="G9" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>8.81</v>
+        <v>0.77</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>0.96</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>554</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>39</v>
@@ -1300,36 +1318,36 @@
         <v>40</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E10" t="s">
         <v>41</v>
       </c>
       <c r="F10" t="n">
-        <v>326.5</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003</v>
+        <v>0.039</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>1.05</v>
+        <v>0.08</v>
       </c>
       <c r="J10" t="n">
-        <v>3.12</v>
+        <v>0.96</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>654</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
         <v>42</v>
@@ -1344,30 +1362,30 @@
         <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>93</v>
+        <v>276.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>2.91</v>
+        <v>8.81</v>
       </c>
       <c r="J11" t="n">
-        <v>2.52</v>
+        <v>4.2</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>187</v>
+        <v>554</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>45</v>
@@ -1376,69 +1394,69 @@
         <v>46</v>
       </c>
       <c r="D12" t="n">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
       <c r="E12" t="s">
         <v>47</v>
       </c>
       <c r="F12" t="n">
-        <v>374.5</v>
+        <v>326.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.019</v>
+        <v>0.003</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="J12" t="n">
-        <v>4.8</v>
+        <v>3.12</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>750</v>
+        <v>654</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
         <v>49</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E13" t="s">
         <v>50</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E13" t="s">
-        <v>51</v>
-      </c>
       <c r="F13" t="n">
-        <v>370</v>
+        <v>93</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>1.99</v>
+        <v>2.91</v>
       </c>
       <c r="J13" t="n">
-        <v>1.56</v>
+        <v>2.52</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>371</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14">
@@ -1446,42 +1464,42 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
         <v>52</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E14" t="s">
         <v>53</v>
       </c>
-      <c r="D14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="F14" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="H14" t="s">
         <v>54</v>
       </c>
-      <c r="F14" t="n">
-        <v>127</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="H14" t="s">
-        <v>16</v>
-      </c>
       <c r="I14" t="n">
-        <v>4.49</v>
+        <v>1.01</v>
       </c>
       <c r="J14" t="n">
-        <v>4.68</v>
+        <v>4.8</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>128</v>
+        <v>750</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
         <v>55</v>
@@ -1490,36 +1508,36 @@
         <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E15" t="s">
         <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>322</v>
+        <v>370</v>
       </c>
       <c r="G15" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>0.43</v>
+        <v>1.99</v>
       </c>
       <c r="J15" t="n">
-        <v>2.52</v>
+        <v>1.56</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>323</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
         <v>58</v>
@@ -1534,30 +1552,30 @@
         <v>60</v>
       </c>
       <c r="F16" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="G16" t="n">
-        <v>0.005</v>
+        <v>0.129</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>0.18</v>
+        <v>4.49</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>4.68</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>113</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
         <v>61</v>
@@ -1566,36 +1584,36 @@
         <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
       <c r="E17" t="s">
         <v>63</v>
       </c>
       <c r="F17" t="n">
-        <v>412</v>
+        <v>322</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
       <c r="H17" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>1.91</v>
+        <v>0.43</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>413</v>
+        <v>323</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>64</v>
@@ -1604,31 +1622,31 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="E18" t="s">
         <v>66</v>
       </c>
       <c r="F18" t="n">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="G18" t="n">
-        <v>0.078</v>
+        <v>0.005</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>2.02</v>
+        <v>0.18</v>
       </c>
       <c r="J18" t="n">
-        <v>2.16</v>
+        <v>0.6</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>831</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19">
@@ -1642,112 +1660,112 @@
         <v>68</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="E19" t="s">
         <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>166</v>
+        <v>412</v>
       </c>
       <c r="G19" t="n">
-        <v>0.006</v>
+        <v>0.02</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="I19" t="n">
-        <v>0.49</v>
+        <v>1.91</v>
       </c>
       <c r="J19" t="n">
-        <v>0.72</v>
+        <v>3</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>332</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
         <v>70</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>71</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E20" t="s">
         <v>72</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E20" t="s">
-        <v>73</v>
-      </c>
       <c r="F20" t="n">
-        <v>1298</v>
+        <v>805</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001</v>
+        <v>0.078</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="J20" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>2601</v>
+        <v>831</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" t="s">
         <v>74</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E21" t="s">
         <v>75</v>
       </c>
-      <c r="D21" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E21" t="s">
-        <v>76</v>
-      </c>
       <c r="F21" t="n">
-        <v>864</v>
+        <v>166</v>
       </c>
       <c r="G21" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
       </c>
       <c r="I21" t="n">
-        <v>0.61</v>
+        <v>0.49</v>
       </c>
       <c r="J21" t="n">
-        <v>0.96</v>
+        <v>0.72</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1732</v>
+        <v>332</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
         <v>77</v>
@@ -1756,36 +1774,36 @@
         <v>78</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E22" t="s">
         <v>79</v>
       </c>
       <c r="F22" t="n">
-        <v>862</v>
+        <v>1298</v>
       </c>
       <c r="G22" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>1.29</v>
+        <v>2.18</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1729</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B23" t="s">
         <v>80</v>
@@ -1794,36 +1812,36 @@
         <v>81</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E23" t="s">
         <v>82</v>
       </c>
       <c r="F23" t="n">
-        <v>462</v>
+        <v>864</v>
       </c>
       <c r="G23" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.11</v>
+        <v>0.61</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>929</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s">
         <v>83</v>
@@ -1832,36 +1850,36 @@
         <v>84</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E24" t="s">
         <v>85</v>
       </c>
       <c r="F24" t="n">
-        <v>83</v>
+        <v>862</v>
       </c>
       <c r="G24" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.46</v>
+        <v>1.29</v>
       </c>
       <c r="J24" t="n">
-        <v>0.84</v>
+        <v>1.8</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>168</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
         <v>86</v>
@@ -1870,13 +1888,13 @@
         <v>87</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E25" t="s">
         <v>88</v>
       </c>
       <c r="F25" t="n">
-        <v>216</v>
+        <v>462</v>
       </c>
       <c r="G25" t="n">
         <v>0.005</v>
@@ -1885,21 +1903,21 @@
         <v>16</v>
       </c>
       <c r="I25" t="n">
-        <v>0.44</v>
+        <v>0.11</v>
       </c>
       <c r="J25" t="n">
-        <v>0.96</v>
+        <v>0.6</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>217</v>
+        <v>929</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
         <v>89</v>
@@ -1908,36 +1926,36 @@
         <v>90</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E26" t="s">
         <v>91</v>
       </c>
       <c r="F26" t="n">
-        <v>349</v>
+        <v>83</v>
       </c>
       <c r="G26" t="n">
-        <v>0.129</v>
+        <v>0.014</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>0.76</v>
+        <v>0.46</v>
       </c>
       <c r="J26" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>346</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
         <v>92</v>
@@ -1946,36 +1964,36 @@
         <v>93</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E27" t="s">
         <v>94</v>
       </c>
       <c r="F27" t="n">
-        <v>69</v>
+        <v>216</v>
       </c>
       <c r="G27" t="n">
-        <v>0.025</v>
+        <v>0.005</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.03</v>
+        <v>0.44</v>
       </c>
       <c r="J27" t="n">
-        <v>0.24</v>
+        <v>0.96</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>70</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
         <v>95</v>
@@ -1984,36 +2002,36 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E28" t="s">
         <v>97</v>
       </c>
       <c r="F28" t="n">
-        <v>101</v>
+        <v>349</v>
       </c>
       <c r="G28" t="n">
-        <v>0.012</v>
+        <v>0.129</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="J28" t="n">
-        <v>2.4</v>
+        <v>1.08</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>102</v>
+        <v>346</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="B29" t="s">
         <v>98</v>
@@ -2022,36 +2040,36 @@
         <v>99</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>438</v>
+        <v>69</v>
       </c>
       <c r="G29" t="n">
-        <v>0.008</v>
+        <v>0.025</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
       </c>
       <c r="I29" t="n">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="J29" t="n">
-        <v>0.36</v>
+        <v>0.24</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>435</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
         <v>101</v>
@@ -2060,36 +2078,36 @@
         <v>102</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E30" t="s">
         <v>103</v>
       </c>
       <c r="F30" t="n">
-        <v>336</v>
+        <v>101</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002</v>
+        <v>0.012</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>9.49</v>
+        <v>0.75</v>
       </c>
       <c r="J30" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>337</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
         <v>104</v>
@@ -2098,13 +2116,13 @@
         <v>105</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="E31" t="s">
         <v>106</v>
       </c>
       <c r="F31" t="n">
-        <v>193</v>
+        <v>438</v>
       </c>
       <c r="G31" t="n">
         <v>0.008</v>
@@ -2113,21 +2131,21 @@
         <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>5.68</v>
+        <v>0.12</v>
       </c>
       <c r="J31" t="n">
-        <v>3.96</v>
+        <v>0.36</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>192</v>
+        <v>435</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
         <v>107</v>
@@ -2136,36 +2154,36 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E32" t="s">
         <v>109</v>
       </c>
       <c r="F32" t="n">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="G32" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>0.68</v>
+        <v>9.49</v>
       </c>
       <c r="J32" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>282</v>
+        <v>337</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
         <v>110</v>
@@ -2174,36 +2192,36 @@
         <v>111</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E33" t="s">
         <v>112</v>
       </c>
       <c r="F33" t="n">
-        <v>332</v>
+        <v>193</v>
       </c>
       <c r="G33" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
       </c>
       <c r="I33" t="n">
-        <v>2.38</v>
+        <v>5.68</v>
       </c>
       <c r="J33" t="n">
-        <v>3.36</v>
+        <v>3.96</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>331</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
         <v>113</v>
@@ -2212,36 +2230,36 @@
         <v>114</v>
       </c>
       <c r="D34" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="E34" t="s">
         <v>115</v>
       </c>
       <c r="F34" t="n">
-        <v>96</v>
+        <v>281</v>
       </c>
       <c r="G34" t="n">
-        <v>0.082</v>
+        <v>0.007</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
       </c>
       <c r="I34" t="n">
-        <v>2.04</v>
+        <v>0.68</v>
       </c>
       <c r="J34" t="n">
-        <v>8.76</v>
+        <v>1.2</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>95</v>
+        <v>282</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
         <v>116</v>
@@ -2250,22 +2268,22 @@
         <v>117</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E35" t="s">
         <v>118</v>
       </c>
       <c r="F35" t="n">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="G35" t="n">
-        <v>0.122</v>
+        <v>0.006</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
       </c>
       <c r="I35" t="n">
-        <v>1.72</v>
+        <v>2.38</v>
       </c>
       <c r="J35" t="n">
         <v>3.36</v>
@@ -2274,12 +2292,12 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>27</v>
+        <v>331</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
         <v>119</v>
@@ -2288,36 +2306,36 @@
         <v>120</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="E36" t="s">
         <v>121</v>
       </c>
       <c r="F36" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="G36" t="n">
-        <v>0.015</v>
+        <v>0.082</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>0.93</v>
+        <v>2.04</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>8.76</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
         <v>122</v>
@@ -2332,30 +2350,30 @@
         <v>124</v>
       </c>
       <c r="F37" t="n">
-        <v>214</v>
+        <v>26</v>
       </c>
       <c r="G37" t="n">
-        <v>0.005</v>
+        <v>0.122</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
       </c>
       <c r="I37" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="J37" t="n">
-        <v>1.2</v>
+        <v>3.36</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>213</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
         <v>125</v>
@@ -2364,36 +2382,36 @@
         <v>126</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E38" t="s">
         <v>127</v>
       </c>
       <c r="F38" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="G38" t="n">
-        <v>0.021</v>
+        <v>0.015</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.52</v>
+        <v>0.93</v>
       </c>
       <c r="J38" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
         <v>128</v>
@@ -2402,36 +2420,36 @@
         <v>129</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E39" t="s">
         <v>130</v>
       </c>
       <c r="F39" t="n">
-        <v>7</v>
+        <v>214</v>
       </c>
       <c r="G39" t="n">
-        <v>0.097</v>
+        <v>0.005</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>3.46</v>
+        <v>0.47</v>
       </c>
       <c r="J39" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>8</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
         <v>131</v>
@@ -2440,36 +2458,36 @@
         <v>132</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E40" t="s">
         <v>133</v>
       </c>
       <c r="F40" t="n">
-        <v>337</v>
+        <v>46</v>
       </c>
       <c r="G40" t="n">
-        <v>0.01</v>
+        <v>0.021</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
       </c>
       <c r="I40" t="n">
-        <v>6.39</v>
+        <v>0.52</v>
       </c>
       <c r="J40" t="n">
-        <v>10.92</v>
+        <v>2.4</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>336</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
         <v>134</v>
@@ -2478,36 +2496,36 @@
         <v>135</v>
       </c>
       <c r="D41" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E41" t="s">
         <v>136</v>
       </c>
       <c r="F41" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G41" t="n">
-        <v>0.05</v>
+        <v>0.097</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
       </c>
       <c r="I41" t="n">
-        <v>1.79</v>
+        <v>3.46</v>
       </c>
       <c r="J41" t="n">
-        <v>3.36</v>
+        <v>6.6</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
         <v>137</v>
@@ -2516,36 +2534,36 @@
         <v>138</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E42" t="s">
         <v>139</v>
       </c>
       <c r="F42" t="n">
-        <v>81</v>
+        <v>337</v>
       </c>
       <c r="G42" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>1.34</v>
+        <v>6.39</v>
       </c>
       <c r="J42" t="n">
-        <v>1.2</v>
+        <v>10.92</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>82</v>
+        <v>336</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="B43" t="s">
         <v>140</v>
@@ -2554,36 +2572,36 @@
         <v>141</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E43" t="s">
         <v>142</v>
       </c>
       <c r="F43" t="n">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="G43" t="n">
-        <v>0.004</v>
+        <v>0.05</v>
       </c>
       <c r="H43" t="s">
         <v>16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.03</v>
+        <v>1.79</v>
       </c>
       <c r="J43" t="n">
-        <v>0.36</v>
+        <v>3.36</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>135</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
         <v>143</v>
@@ -2598,30 +2616,30 @@
         <v>145</v>
       </c>
       <c r="F44" t="n">
-        <v>720</v>
+        <v>81</v>
       </c>
       <c r="G44" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H44" t="s">
         <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>4.71</v>
+        <v>1.34</v>
       </c>
       <c r="J44" t="n">
-        <v>8.04</v>
+        <v>1.2</v>
       </c>
       <c r="K44" t="b">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>717</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
         <v>146</v>
@@ -2636,30 +2654,30 @@
         <v>148</v>
       </c>
       <c r="F45" t="n">
-        <v>773</v>
+        <v>134</v>
       </c>
       <c r="G45" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
       </c>
       <c r="I45" t="n">
-        <v>0.37</v>
+        <v>0.03</v>
       </c>
       <c r="J45" t="n">
-        <v>1.56</v>
+        <v>0.36</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>774</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
         <v>149</v>
@@ -2668,13 +2686,13 @@
         <v>150</v>
       </c>
       <c r="D46" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E46" t="s">
         <v>151</v>
       </c>
       <c r="F46" t="n">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="G46" t="n">
         <v>0.002</v>
@@ -2683,21 +2701,21 @@
         <v>16</v>
       </c>
       <c r="I46" t="n">
-        <v>0.69</v>
+        <v>4.71</v>
       </c>
       <c r="J46" t="n">
-        <v>3.24</v>
+        <v>8.04</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>734</v>
+        <v>717</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
         <v>152</v>
@@ -2706,36 +2724,36 @@
         <v>153</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E47" t="s">
         <v>154</v>
       </c>
       <c r="F47" t="n">
-        <v>1100</v>
+        <v>773</v>
       </c>
       <c r="G47" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
       </c>
       <c r="I47" t="n">
-        <v>6.45</v>
+        <v>0.37</v>
       </c>
       <c r="J47" t="n">
-        <v>14.4</v>
+        <v>1.56</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1097</v>
+        <v>774</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
         <v>155</v>
@@ -2744,36 +2762,36 @@
         <v>156</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E48" t="s">
         <v>157</v>
       </c>
       <c r="F48" t="n">
-        <v>498</v>
+        <v>735</v>
       </c>
       <c r="G48" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
       </c>
       <c r="I48" t="n">
-        <v>1.38</v>
+        <v>0.69</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="K48" t="b">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>495</v>
+        <v>734</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
         <v>158</v>
@@ -2788,30 +2806,30 @@
         <v>160</v>
       </c>
       <c r="F49" t="n">
-        <v>257</v>
+        <v>1100</v>
       </c>
       <c r="G49" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
       </c>
       <c r="I49" t="n">
-        <v>6.15</v>
+        <v>6.45</v>
       </c>
       <c r="J49" t="n">
-        <v>9.48</v>
+        <v>14.4</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>258</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
         <v>161</v>
@@ -2826,30 +2844,30 @@
         <v>163</v>
       </c>
       <c r="F50" t="n">
-        <v>458</v>
+        <v>498</v>
       </c>
       <c r="G50" t="n">
-        <v>0.059</v>
+        <v>0.006</v>
       </c>
       <c r="H50" t="s">
         <v>16</v>
       </c>
       <c r="I50" t="n">
-        <v>2.47</v>
+        <v>1.38</v>
       </c>
       <c r="J50" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>453</v>
+        <v>495</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
         <v>164</v>
@@ -2858,36 +2876,36 @@
         <v>165</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E51" t="s">
         <v>166</v>
       </c>
       <c r="F51" t="n">
-        <v>923</v>
+        <v>257</v>
       </c>
       <c r="G51" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H51" t="s">
         <v>16</v>
       </c>
       <c r="I51" t="n">
-        <v>3.76</v>
+        <v>6.15</v>
       </c>
       <c r="J51" t="n">
-        <v>5.4</v>
+        <v>9.48</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>918</v>
+        <v>258</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
         <v>167</v>
@@ -2896,36 +2914,36 @@
         <v>168</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E52" t="s">
         <v>169</v>
       </c>
       <c r="F52" t="n">
-        <v>1012</v>
+        <v>458</v>
       </c>
       <c r="G52" t="n">
-        <v>0.003</v>
+        <v>0.059</v>
       </c>
       <c r="H52" t="s">
         <v>16</v>
       </c>
       <c r="I52" t="n">
-        <v>0.08</v>
+        <v>2.47</v>
       </c>
       <c r="J52" t="n">
-        <v>0.72</v>
+        <v>7.2</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>1211</v>
+        <v>453</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
         <v>170</v>
@@ -2940,7 +2958,7 @@
         <v>172</v>
       </c>
       <c r="F53" t="n">
-        <v>344.5</v>
+        <v>923</v>
       </c>
       <c r="G53" t="n">
         <v>0.002</v>
@@ -2949,15 +2967,91 @@
         <v>16</v>
       </c>
       <c r="I53" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J53" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54" t="s">
+        <v>173</v>
+      </c>
+      <c r="C54" t="s">
+        <v>174</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E54" t="s">
+        <v>175</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1012</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H54" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>17</v>
+      </c>
+      <c r="B55" t="s">
+        <v>176</v>
+      </c>
+      <c r="C55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E55" t="s">
+        <v>178</v>
+      </c>
+      <c r="F55" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H55" t="s">
+        <v>16</v>
+      </c>
+      <c r="I55" t="n">
         <v>0.32</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J55" t="n">
         <v>2.04</v>
       </c>
-      <c r="K53" t="b">
-        <v>1</v>
-      </c>
-      <c r="L53" t="n">
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
         <v>688</v>
       </c>
     </row>
@@ -2989,30 +3083,30 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="F1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" t="n">
         <v>0.4</v>
@@ -3032,7 +3126,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B3" t="n">
         <v>7</v>
@@ -3055,13 +3149,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="D4" t="n">
         <v>6.5</v>
@@ -3128,10 +3222,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C2" t="n">
         <v>374.5</v>
@@ -3143,7 +3237,7 @@
         <v>0.019</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G2" t="n">
         <v>1.01</v>
@@ -3154,10 +3248,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C3" t="n">
         <v>412</v>
@@ -3169,7 +3263,7 @@
         <v>0.02</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
         <v>1.91</v>
@@ -3180,10 +3274,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C4" t="n">
         <v>96</v>
@@ -3206,10 +3300,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
         <v>630</v>
@@ -3232,10 +3326,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C6" t="n">
         <v>805</v>
@@ -3258,172 +3352,172 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>862</v>
+        <v>1157.5</v>
       </c>
       <c r="D7" t="n">
         <v>0.9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>1.29</v>
+        <v>2.36</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>1298</v>
+        <v>862</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18</v>
+        <v>1.29</v>
       </c>
       <c r="H8" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>864</v>
+        <v>1298</v>
       </c>
       <c r="D9" t="n">
         <v>0.8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.61</v>
+        <v>2.18</v>
       </c>
       <c r="H9" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C10" t="n">
-        <v>83</v>
+        <v>864</v>
       </c>
       <c r="D10" t="n">
         <v>0.8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="H10" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="C11" t="n">
-        <v>735</v>
+        <v>83</v>
       </c>
       <c r="D11" t="n">
         <v>0.8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.69</v>
+        <v>0.46</v>
       </c>
       <c r="H11" t="n">
-        <v>3.24</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="C12" t="n">
-        <v>216</v>
+        <v>735</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.44</v>
+        <v>0.69</v>
       </c>
       <c r="H12" t="n">
-        <v>0.96</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C13" t="n">
-        <v>462</v>
+        <v>216</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E13" t="n">
         <v>0.005</v>
@@ -3432,73 +3526,73 @@
         <v>16</v>
       </c>
       <c r="G13" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C14" t="n">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="D14" t="n">
         <v>0.6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="H14" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>361</v>
+        <v>438</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>42.9</v>
+        <v>0.12</v>
       </c>
       <c r="H15" t="n">
-        <v>9.48</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
-        <v>326.5</v>
+        <v>361</v>
       </c>
       <c r="D16" t="n">
         <v>0.5</v>
@@ -3510,140 +3604,140 @@
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>1.05</v>
+        <v>42.9</v>
       </c>
       <c r="H16" t="n">
-        <v>3.12</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C17" t="n">
-        <v>370</v>
+        <v>326.5</v>
       </c>
       <c r="D17" t="n">
         <v>0.5</v>
       </c>
       <c r="E17" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>1.99</v>
+        <v>1.05</v>
       </c>
       <c r="H17" t="n">
-        <v>1.56</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C18" t="n">
-        <v>166</v>
+        <v>370</v>
       </c>
       <c r="D18" t="n">
         <v>0.5</v>
       </c>
       <c r="E18" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>0.49</v>
+        <v>1.99</v>
       </c>
       <c r="H18" t="n">
-        <v>0.72</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>166</v>
       </c>
       <c r="D19" t="n">
         <v>0.5</v>
       </c>
       <c r="E19" t="n">
-        <v>0.122</v>
+        <v>0.006</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>1.72</v>
+        <v>0.49</v>
       </c>
       <c r="H19" t="n">
-        <v>3.36</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
         <v>122</v>
       </c>
       <c r="C20" t="n">
-        <v>214</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
         <v>0.5</v>
       </c>
       <c r="E20" t="n">
-        <v>0.005</v>
+        <v>0.122</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C21" t="n">
-        <v>46</v>
+        <v>214</v>
       </c>
       <c r="D21" t="n">
         <v>0.5</v>
       </c>
       <c r="E21" t="n">
-        <v>0.021</v>
+        <v>0.005</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -52,76 +52,67 @@
     <t xml:space="preserve">points_count</t>
   </si>
   <si>
+    <t xml:space="preserve">An_der_Kost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/11 06:13:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/11 08:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/11 06:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/05 21:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/06 03:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/06 00:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/19 00:35:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/19 02:05:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/19 00:45:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 19:15:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 20:16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 19:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/30 01:37:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/30 03:07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/30 02:15:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 22:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 23:24:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 22:44:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wasserstraße_Springorum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/05/11 12:42:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/05/12 08:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/05/11 21:05:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An_der_Kost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/05/11 06:13:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/05/11 08:32:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/05/11 06:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/05/05 21:43:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/05/06 03:44:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/05/06 00:31:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/19 00:35:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/19 02:05:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/19 00:45:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/11 19:15:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/11 20:16:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04/11 19:21:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/30 01:37:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/30 03:07:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/30 02:15:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/29 22:34:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/29 23:24:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/29 22:44:00</t>
   </si>
   <si>
     <t xml:space="preserve">2026/03/29 11:16:00</t>
@@ -616,8 +607,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L55" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L55"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L54" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L54"/>
   <tableColumns count="12">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -1014,212 +1005,212 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1157.5</v>
+        <v>139</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002</v>
+        <v>0.018</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>2.36</v>
+        <v>11.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.24</v>
+        <v>5.16</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>2316</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
       <c r="F3" t="n">
-        <v>139</v>
+        <v>361</v>
       </c>
       <c r="G3" t="n">
-        <v>0.018</v>
+        <v>0.003</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>5.95</v>
+        <v>42.9</v>
       </c>
       <c r="J3" t="n">
-        <v>5.16</v>
+        <v>9.48</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>279</v>
+        <v>723</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
       <c r="F4" t="n">
-        <v>361</v>
+        <v>90.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003</v>
+        <v>0.04</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>42.9</v>
+        <v>44.02</v>
       </c>
       <c r="J4" t="n">
-        <v>9.48</v>
+        <v>20.16</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>723</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
       <c r="F5" t="n">
-        <v>90.5</v>
+        <v>60.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04</v>
+        <v>0.054</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>44.02</v>
+        <v>2.91</v>
       </c>
       <c r="J5" t="n">
-        <v>20.16</v>
+        <v>7.8</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>182</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E6" t="s">
-        <v>29</v>
-      </c>
       <c r="F6" t="n">
-        <v>60.5</v>
+        <v>90</v>
       </c>
       <c r="G6" t="n">
-        <v>0.054</v>
+        <v>0.01</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>2.91</v>
+        <v>1.09</v>
       </c>
       <c r="J6" t="n">
-        <v>7.8</v>
+        <v>2.04</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>122</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" t="s">
         <v>31</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
-      </c>
       <c r="F7" t="n">
-        <v>90</v>
+        <v>50.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>1.09</v>
+        <v>1.89</v>
       </c>
       <c r="J7" t="n">
         <v>2.04</v>
@@ -1228,12 +1219,12 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>181</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
@@ -1242,31 +1233,31 @@
         <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="E8" t="s">
         <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>50.5</v>
+        <v>630</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03</v>
+        <v>0.014</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>1.89</v>
+        <v>0.77</v>
       </c>
       <c r="J8" t="n">
-        <v>2.04</v>
+        <v>0.96</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>102</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="9">
@@ -1280,22 +1271,22 @@
         <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
       </c>
       <c r="F9" t="n">
-        <v>630</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>0.014</v>
+        <v>0.039</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.77</v>
+        <v>0.08</v>
       </c>
       <c r="J9" t="n">
         <v>0.96</v>
@@ -1304,12 +1295,12 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1261</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>39</v>
@@ -1324,30 +1315,30 @@
         <v>41</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>276.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.039</v>
+        <v>0.013</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08</v>
+        <v>8.81</v>
       </c>
       <c r="J10" t="n">
-        <v>0.96</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>81</v>
+        <v>554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
         <v>42</v>
@@ -1356,36 +1347,36 @@
         <v>43</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>276.5</v>
+        <v>326.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>8.81</v>
+        <v>1.05</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>554</v>
+        <v>654</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
         <v>45</v>
@@ -1394,36 +1385,36 @@
         <v>46</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E12" t="s">
         <v>47</v>
       </c>
       <c r="F12" t="n">
-        <v>326.5</v>
+        <v>93</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>1.05</v>
+        <v>2.91</v>
       </c>
       <c r="J12" t="n">
-        <v>3.12</v>
+        <v>2.52</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>654</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
         <v>48</v>
@@ -1432,31 +1423,31 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3</v>
+        <v>6.5</v>
       </c>
       <c r="E13" t="s">
         <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>93</v>
+        <v>374.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.005</v>
+        <v>0.019</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="I13" t="n">
-        <v>2.91</v>
+        <v>1.01</v>
       </c>
       <c r="J13" t="n">
-        <v>2.52</v>
+        <v>4.8</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>187</v>
+        <v>750</v>
       </c>
     </row>
     <row r="14">
@@ -1464,42 +1455,42 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F14" t="n">
-        <v>374.5</v>
+        <v>370</v>
       </c>
       <c r="G14" t="n">
-        <v>0.019</v>
+        <v>0.002</v>
       </c>
       <c r="H14" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="J14" t="n">
-        <v>4.8</v>
+        <v>1.56</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>750</v>
+        <v>371</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
         <v>55</v>
@@ -1508,36 +1499,36 @@
         <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E15" t="s">
         <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>370</v>
+        <v>127</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002</v>
+        <v>0.129</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>1.99</v>
+        <v>4.49</v>
       </c>
       <c r="J15" t="n">
-        <v>1.56</v>
+        <v>4.68</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>371</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
         <v>58</v>
@@ -1552,30 +1543,30 @@
         <v>60</v>
       </c>
       <c r="F16" t="n">
-        <v>127</v>
+        <v>322</v>
       </c>
       <c r="G16" t="n">
-        <v>0.129</v>
+        <v>0.004</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>4.49</v>
+        <v>0.43</v>
       </c>
       <c r="J16" t="n">
-        <v>4.68</v>
+        <v>2.52</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>128</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
         <v>61</v>
@@ -1590,30 +1581,30 @@
         <v>63</v>
       </c>
       <c r="F17" t="n">
-        <v>322</v>
+        <v>112</v>
       </c>
       <c r="G17" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>0.43</v>
+        <v>0.18</v>
       </c>
       <c r="J17" t="n">
-        <v>2.52</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>323</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
         <v>64</v>
@@ -1622,36 +1613,36 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>4.3</v>
       </c>
       <c r="E18" t="s">
         <v>66</v>
       </c>
       <c r="F18" t="n">
-        <v>112</v>
+        <v>412</v>
       </c>
       <c r="G18" t="n">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="I18" t="n">
-        <v>0.18</v>
+        <v>1.91</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>113</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
         <v>67</v>
@@ -1660,31 +1651,31 @@
         <v>68</v>
       </c>
       <c r="D19" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="E19" t="s">
         <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>412</v>
+        <v>805</v>
       </c>
       <c r="G19" t="n">
-        <v>0.02</v>
+        <v>0.078</v>
       </c>
       <c r="H19" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="I19" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>413</v>
+        <v>831</v>
       </c>
     </row>
     <row r="20">
@@ -1698,74 +1689,74 @@
         <v>71</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="E20" t="s">
         <v>72</v>
       </c>
       <c r="F20" t="n">
-        <v>805</v>
+        <v>166</v>
       </c>
       <c r="G20" t="n">
-        <v>0.078</v>
+        <v>0.006</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>2.02</v>
+        <v>0.49</v>
       </c>
       <c r="J20" t="n">
-        <v>2.16</v>
+        <v>0.72</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>831</v>
+        <v>332</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F21" t="n">
-        <v>166</v>
+        <v>1298</v>
       </c>
       <c r="G21" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
       </c>
       <c r="I21" t="n">
-        <v>0.49</v>
+        <v>2.18</v>
       </c>
       <c r="J21" t="n">
-        <v>0.72</v>
+        <v>2.04</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>332</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s">
         <v>77</v>
@@ -1780,30 +1771,30 @@
         <v>79</v>
       </c>
       <c r="F22" t="n">
-        <v>1298</v>
+        <v>864</v>
       </c>
       <c r="G22" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>2.18</v>
+        <v>0.61</v>
       </c>
       <c r="J22" t="n">
-        <v>2.04</v>
+        <v>0.96</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>2601</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
         <v>80</v>
@@ -1812,36 +1803,36 @@
         <v>81</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E23" t="s">
         <v>82</v>
       </c>
       <c r="F23" t="n">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="G23" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.61</v>
+        <v>1.29</v>
       </c>
       <c r="J23" t="n">
-        <v>0.96</v>
+        <v>1.8</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1732</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
         <v>83</v>
@@ -1850,13 +1841,13 @@
         <v>84</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E24" t="s">
         <v>85</v>
       </c>
       <c r="F24" t="n">
-        <v>862</v>
+        <v>462</v>
       </c>
       <c r="G24" t="n">
         <v>0.005</v>
@@ -1865,21 +1856,21 @@
         <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>1.29</v>
+        <v>0.11</v>
       </c>
       <c r="J24" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1729</v>
+        <v>929</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
         <v>86</v>
@@ -1888,36 +1879,36 @@
         <v>87</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E25" t="s">
         <v>88</v>
       </c>
       <c r="F25" t="n">
-        <v>462</v>
+        <v>83</v>
       </c>
       <c r="G25" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
       </c>
       <c r="I25" t="n">
-        <v>0.11</v>
+        <v>0.46</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6</v>
+        <v>0.84</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>929</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
         <v>89</v>
@@ -1926,36 +1917,36 @@
         <v>90</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E26" t="s">
         <v>91</v>
       </c>
       <c r="F26" t="n">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="G26" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="J26" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>168</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
         <v>92</v>
@@ -1964,36 +1955,36 @@
         <v>93</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E27" t="s">
         <v>94</v>
       </c>
       <c r="F27" t="n">
-        <v>216</v>
+        <v>349</v>
       </c>
       <c r="G27" t="n">
-        <v>0.005</v>
+        <v>0.129</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.44</v>
+        <v>0.76</v>
       </c>
       <c r="J27" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>217</v>
+        <v>346</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="B28" t="s">
         <v>95</v>
@@ -2008,30 +1999,30 @@
         <v>97</v>
       </c>
       <c r="F28" t="n">
-        <v>349</v>
+        <v>69</v>
       </c>
       <c r="G28" t="n">
-        <v>0.129</v>
+        <v>0.025</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>0.76</v>
+        <v>0.03</v>
       </c>
       <c r="J28" t="n">
-        <v>1.08</v>
+        <v>0.24</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>346</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
         <v>98</v>
@@ -2040,36 +2031,36 @@
         <v>99</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="G29" t="n">
-        <v>0.025</v>
+        <v>0.012</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
       </c>
       <c r="I29" t="n">
-        <v>0.03</v>
+        <v>0.75</v>
       </c>
       <c r="J29" t="n">
-        <v>0.24</v>
+        <v>2.4</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>70</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
         <v>101</v>
@@ -2078,36 +2069,36 @@
         <v>102</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="E30" t="s">
         <v>103</v>
       </c>
       <c r="F30" t="n">
-        <v>101</v>
+        <v>438</v>
       </c>
       <c r="G30" t="n">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>0.75</v>
+        <v>0.12</v>
       </c>
       <c r="J30" t="n">
-        <v>2.4</v>
+        <v>0.36</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>102</v>
+        <v>435</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
         <v>104</v>
@@ -2116,36 +2107,36 @@
         <v>105</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E31" t="s">
         <v>106</v>
       </c>
       <c r="F31" t="n">
-        <v>438</v>
+        <v>336</v>
       </c>
       <c r="G31" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>0.12</v>
+        <v>9.49</v>
       </c>
       <c r="J31" t="n">
-        <v>0.36</v>
+        <v>5.4</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>435</v>
+        <v>337</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
         <v>107</v>
@@ -2154,36 +2145,36 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E32" t="s">
         <v>109</v>
       </c>
       <c r="F32" t="n">
-        <v>336</v>
+        <v>193</v>
       </c>
       <c r="G32" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>9.49</v>
+        <v>5.68</v>
       </c>
       <c r="J32" t="n">
-        <v>5.4</v>
+        <v>3.96</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>337</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
         <v>110</v>
@@ -2198,30 +2189,30 @@
         <v>112</v>
       </c>
       <c r="F33" t="n">
-        <v>193</v>
+        <v>281</v>
       </c>
       <c r="G33" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
       </c>
       <c r="I33" t="n">
-        <v>5.68</v>
+        <v>0.68</v>
       </c>
       <c r="J33" t="n">
-        <v>3.96</v>
+        <v>1.2</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>192</v>
+        <v>282</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
         <v>113</v>
@@ -2230,36 +2221,36 @@
         <v>114</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E34" t="s">
         <v>115</v>
       </c>
       <c r="F34" t="n">
-        <v>281</v>
+        <v>332</v>
       </c>
       <c r="G34" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
       </c>
       <c r="I34" t="n">
-        <v>0.68</v>
+        <v>2.38</v>
       </c>
       <c r="J34" t="n">
-        <v>1.2</v>
+        <v>3.36</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>282</v>
+        <v>331</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
         <v>116</v>
@@ -2268,36 +2259,36 @@
         <v>117</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="E35" t="s">
         <v>118</v>
       </c>
       <c r="F35" t="n">
-        <v>332</v>
+        <v>96</v>
       </c>
       <c r="G35" t="n">
-        <v>0.006</v>
+        <v>0.082</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
       </c>
       <c r="I35" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="J35" t="n">
-        <v>3.36</v>
+        <v>8.76</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>331</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
         <v>119</v>
@@ -2306,36 +2297,36 @@
         <v>120</v>
       </c>
       <c r="D36" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="E36" t="s">
         <v>121</v>
       </c>
       <c r="F36" t="n">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="G36" t="n">
-        <v>0.082</v>
+        <v>0.122</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="J36" t="n">
-        <v>8.76</v>
+        <v>3.36</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>95</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
         <v>122</v>
@@ -2344,36 +2335,36 @@
         <v>123</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E37" t="s">
         <v>124</v>
       </c>
       <c r="F37" t="n">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="G37" t="n">
-        <v>0.122</v>
+        <v>0.015</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
       </c>
       <c r="I37" t="n">
-        <v>1.72</v>
+        <v>0.93</v>
       </c>
       <c r="J37" t="n">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>27</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
         <v>125</v>
@@ -2382,36 +2373,36 @@
         <v>126</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E38" t="s">
         <v>127</v>
       </c>
       <c r="F38" t="n">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="G38" t="n">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.93</v>
+        <v>0.47</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>78</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
         <v>128</v>
@@ -2426,30 +2417,30 @@
         <v>130</v>
       </c>
       <c r="F39" t="n">
-        <v>214</v>
+        <v>46</v>
       </c>
       <c r="G39" t="n">
-        <v>0.005</v>
+        <v>0.021</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="J39" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>213</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
         <v>131</v>
@@ -2458,36 +2449,36 @@
         <v>132</v>
       </c>
       <c r="D40" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E40" t="s">
         <v>133</v>
       </c>
       <c r="F40" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="G40" t="n">
-        <v>0.021</v>
+        <v>0.097</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
       </c>
       <c r="I40" t="n">
-        <v>0.52</v>
+        <v>3.46</v>
       </c>
       <c r="J40" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
         <v>134</v>
@@ -2496,36 +2487,36 @@
         <v>135</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E41" t="s">
         <v>136</v>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>337</v>
       </c>
       <c r="G41" t="n">
-        <v>0.097</v>
+        <v>0.01</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
       </c>
       <c r="I41" t="n">
-        <v>3.46</v>
+        <v>6.39</v>
       </c>
       <c r="J41" t="n">
-        <v>6.6</v>
+        <v>10.92</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>8</v>
+        <v>336</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="B42" t="s">
         <v>137</v>
@@ -2534,36 +2525,36 @@
         <v>138</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E42" t="s">
         <v>139</v>
       </c>
       <c r="F42" t="n">
-        <v>337</v>
+        <v>41</v>
       </c>
       <c r="G42" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>6.39</v>
+        <v>1.79</v>
       </c>
       <c r="J42" t="n">
-        <v>10.92</v>
+        <v>3.36</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>336</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
         <v>140</v>
@@ -2572,36 +2563,36 @@
         <v>141</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E43" t="s">
         <v>142</v>
       </c>
       <c r="F43" t="n">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="G43" t="n">
-        <v>0.05</v>
+        <v>0.005</v>
       </c>
       <c r="H43" t="s">
         <v>16</v>
       </c>
       <c r="I43" t="n">
-        <v>1.79</v>
+        <v>1.34</v>
       </c>
       <c r="J43" t="n">
-        <v>3.36</v>
+        <v>1.2</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
         <v>143</v>
@@ -2616,30 +2607,30 @@
         <v>145</v>
       </c>
       <c r="F44" t="n">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="G44" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="H44" t="s">
         <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>1.34</v>
+        <v>0.03</v>
       </c>
       <c r="J44" t="n">
-        <v>1.2</v>
+        <v>0.36</v>
       </c>
       <c r="K44" t="b">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>82</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
         <v>146</v>
@@ -2654,30 +2645,30 @@
         <v>148</v>
       </c>
       <c r="F45" t="n">
-        <v>134</v>
+        <v>720</v>
       </c>
       <c r="G45" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
       </c>
       <c r="I45" t="n">
-        <v>0.03</v>
+        <v>4.71</v>
       </c>
       <c r="J45" t="n">
-        <v>0.36</v>
+        <v>8.04</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>135</v>
+        <v>717</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
         <v>149</v>
@@ -2692,30 +2683,30 @@
         <v>151</v>
       </c>
       <c r="F46" t="n">
-        <v>720</v>
+        <v>773</v>
       </c>
       <c r="G46" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
       </c>
       <c r="I46" t="n">
-        <v>4.71</v>
+        <v>0.37</v>
       </c>
       <c r="J46" t="n">
-        <v>8.04</v>
+        <v>1.56</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>717</v>
+        <v>774</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
         <v>152</v>
@@ -2724,36 +2715,36 @@
         <v>153</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E47" t="s">
         <v>154</v>
       </c>
       <c r="F47" t="n">
-        <v>773</v>
+        <v>735</v>
       </c>
       <c r="G47" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
       </c>
       <c r="I47" t="n">
-        <v>0.37</v>
+        <v>0.69</v>
       </c>
       <c r="J47" t="n">
-        <v>1.56</v>
+        <v>3.24</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>774</v>
+        <v>734</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
         <v>155</v>
@@ -2762,13 +2753,13 @@
         <v>156</v>
       </c>
       <c r="D48" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="E48" t="s">
         <v>157</v>
       </c>
       <c r="F48" t="n">
-        <v>735</v>
+        <v>1100</v>
       </c>
       <c r="G48" t="n">
         <v>0.002</v>
@@ -2777,21 +2768,21 @@
         <v>16</v>
       </c>
       <c r="I48" t="n">
-        <v>0.69</v>
+        <v>6.45</v>
       </c>
       <c r="J48" t="n">
-        <v>3.24</v>
+        <v>14.4</v>
       </c>
       <c r="K48" t="b">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>734</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
         <v>158</v>
@@ -2800,36 +2791,36 @@
         <v>159</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E49" t="s">
         <v>160</v>
       </c>
       <c r="F49" t="n">
-        <v>1100</v>
+        <v>498</v>
       </c>
       <c r="G49" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
       </c>
       <c r="I49" t="n">
-        <v>6.45</v>
+        <v>1.38</v>
       </c>
       <c r="J49" t="n">
-        <v>14.4</v>
+        <v>3</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>1097</v>
+        <v>495</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
         <v>161</v>
@@ -2838,36 +2829,36 @@
         <v>162</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E50" t="s">
         <v>163</v>
       </c>
       <c r="F50" t="n">
-        <v>498</v>
+        <v>257</v>
       </c>
       <c r="G50" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="H50" t="s">
         <v>16</v>
       </c>
       <c r="I50" t="n">
-        <v>1.38</v>
+        <v>6.15</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>9.48</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>495</v>
+        <v>258</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
         <v>164</v>
@@ -2876,36 +2867,36 @@
         <v>165</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E51" t="s">
         <v>166</v>
       </c>
       <c r="F51" t="n">
-        <v>257</v>
+        <v>458</v>
       </c>
       <c r="G51" t="n">
-        <v>0.003</v>
+        <v>0.059</v>
       </c>
       <c r="H51" t="s">
         <v>16</v>
       </c>
       <c r="I51" t="n">
-        <v>6.15</v>
+        <v>2.47</v>
       </c>
       <c r="J51" t="n">
-        <v>9.48</v>
+        <v>7.2</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>258</v>
+        <v>453</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
         <v>167</v>
@@ -2920,30 +2911,30 @@
         <v>169</v>
       </c>
       <c r="F52" t="n">
-        <v>458</v>
+        <v>923</v>
       </c>
       <c r="G52" t="n">
-        <v>0.059</v>
+        <v>0.002</v>
       </c>
       <c r="H52" t="s">
         <v>16</v>
       </c>
       <c r="I52" t="n">
-        <v>2.47</v>
+        <v>3.76</v>
       </c>
       <c r="J52" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>453</v>
+        <v>918</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
         <v>170</v>
@@ -2952,36 +2943,36 @@
         <v>171</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E53" t="s">
         <v>172</v>
       </c>
       <c r="F53" t="n">
-        <v>923</v>
+        <v>1012</v>
       </c>
       <c r="G53" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H53" t="s">
         <v>16</v>
       </c>
       <c r="I53" t="n">
-        <v>3.76</v>
+        <v>0.08</v>
       </c>
       <c r="J53" t="n">
-        <v>5.4</v>
+        <v>0.72</v>
       </c>
       <c r="K53" t="b">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>918</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
         <v>173</v>
@@ -2990,68 +2981,30 @@
         <v>174</v>
       </c>
       <c r="D54" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E54" t="s">
         <v>175</v>
       </c>
       <c r="F54" t="n">
-        <v>1012</v>
+        <v>344.5</v>
       </c>
       <c r="G54" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H54" t="s">
         <v>16</v>
       </c>
       <c r="I54" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="J54" t="n">
-        <v>0.72</v>
+        <v>2.04</v>
       </c>
       <c r="K54" t="b">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>17</v>
-      </c>
-      <c r="B55" t="s">
-        <v>176</v>
-      </c>
-      <c r="C55" t="s">
-        <v>177</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E55" t="s">
-        <v>178</v>
-      </c>
-      <c r="F55" t="n">
-        <v>344.5</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="H55" t="s">
-        <v>16</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="K55" t="b">
-        <v>1</v>
-      </c>
-      <c r="L55" t="n">
         <v>688</v>
       </c>
     </row>
@@ -3083,27 +3036,27 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" t="s">
         <v>179</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>180</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>181</v>
-      </c>
-      <c r="E1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G1" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B2" t="n">
         <v>42</v>
@@ -3126,7 +3079,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B3" t="n">
         <v>7</v>
@@ -3149,13 +3102,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="D4" t="n">
         <v>6.5</v>
@@ -3222,10 +3175,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C2" t="n">
         <v>374.5</v>
@@ -3237,7 +3190,7 @@
         <v>0.019</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G2" t="n">
         <v>1.01</v>
@@ -3248,10 +3201,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C3" t="n">
         <v>412</v>
@@ -3263,7 +3216,7 @@
         <v>0.02</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
         <v>1.91</v>
@@ -3274,10 +3227,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C4" t="n">
         <v>96</v>
@@ -3300,10 +3253,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C5" t="n">
         <v>630</v>
@@ -3326,10 +3279,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C6" t="n">
         <v>805</v>
@@ -3352,172 +3305,172 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="C7" t="n">
-        <v>1157.5</v>
+        <v>862</v>
       </c>
       <c r="D7" t="n">
         <v>0.9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36</v>
+        <v>1.29</v>
       </c>
       <c r="H7" t="n">
-        <v>3.24</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>862</v>
+        <v>1298</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>1.29</v>
+        <v>2.18</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
         <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>1298</v>
+        <v>864</v>
       </c>
       <c r="D9" t="n">
         <v>0.8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>2.18</v>
+        <v>0.61</v>
       </c>
       <c r="H9" t="n">
-        <v>2.04</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C10" t="n">
-        <v>864</v>
+        <v>83</v>
       </c>
       <c r="D10" t="n">
         <v>0.8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
       <c r="H10" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>152</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>735</v>
       </c>
       <c r="D11" t="n">
         <v>0.8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.46</v>
+        <v>0.69</v>
       </c>
       <c r="H11" t="n">
-        <v>0.84</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="C12" t="n">
-        <v>735</v>
+        <v>216</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.69</v>
+        <v>0.44</v>
       </c>
       <c r="H12" t="n">
-        <v>3.24</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C13" t="n">
-        <v>216</v>
+        <v>462</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E13" t="n">
         <v>0.005</v>
@@ -3526,73 +3479,73 @@
         <v>16</v>
       </c>
       <c r="G13" t="n">
-        <v>0.44</v>
+        <v>0.11</v>
       </c>
       <c r="H13" t="n">
-        <v>0.96</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C14" t="n">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="D14" t="n">
         <v>0.6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="B15" t="s">
-        <v>104</v>
-      </c>
       <c r="C15" t="n">
-        <v>438</v>
+        <v>361</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>0.12</v>
+        <v>42.9</v>
       </c>
       <c r="H15" t="n">
-        <v>0.36</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C16" t="n">
-        <v>361</v>
+        <v>326.5</v>
       </c>
       <c r="D16" t="n">
         <v>0.5</v>
@@ -3604,140 +3557,140 @@
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>42.9</v>
+        <v>1.05</v>
       </c>
       <c r="H16" t="n">
-        <v>9.48</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C17" t="n">
-        <v>326.5</v>
+        <v>370</v>
       </c>
       <c r="D17" t="n">
         <v>0.5</v>
       </c>
       <c r="E17" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>1.05</v>
+        <v>1.99</v>
       </c>
       <c r="H17" t="n">
-        <v>3.12</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C18" t="n">
-        <v>370</v>
+        <v>166</v>
       </c>
       <c r="D18" t="n">
         <v>0.5</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>1.99</v>
+        <v>0.49</v>
       </c>
       <c r="H18" t="n">
-        <v>1.56</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="C19" t="n">
-        <v>166</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
         <v>0.5</v>
       </c>
       <c r="E19" t="n">
-        <v>0.006</v>
+        <v>0.122</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>0.49</v>
+        <v>1.72</v>
       </c>
       <c r="H19" t="n">
-        <v>0.72</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>214</v>
       </c>
       <c r="D20" t="n">
         <v>0.5</v>
       </c>
       <c r="E20" t="n">
-        <v>0.122</v>
+        <v>0.005</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>1.72</v>
+        <v>0.47</v>
       </c>
       <c r="H20" t="n">
-        <v>3.36</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
         <v>128</v>
       </c>
       <c r="C21" t="n">
-        <v>214</v>
+        <v>46</v>
       </c>
       <c r="D21" t="n">
         <v>0.5</v>
       </c>
       <c r="E21" t="n">
-        <v>0.005</v>
+        <v>0.021</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -1020,7 +1020,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>11.9</v>
+        <v>29.75</v>
       </c>
       <c r="J2" t="n">
         <v>5.16</v>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -55,6 +55,30 @@
     <t xml:space="preserve">An_der_Kost</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/05/13 13:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/13 13:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/13 13:13:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wasserstraße_Springorum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/13 08:08:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/13 11:51:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/13 08:40:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/05/11 06:13:00</t>
   </si>
   <si>
@@ -64,9 +88,6 @@
     <t xml:space="preserve">2026/05/11 06:30:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026/05/05 21:43:00</t>
   </si>
   <si>
@@ -110,9 +131,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026/03/29 22:44:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wasserstraße_Springorum</t>
   </si>
   <si>
     <t xml:space="preserve">2026/03/29 11:16:00</t>
@@ -607,8 +625,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L54" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L56" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L56"/>
   <tableColumns count="12">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -1005,69 +1023,69 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>0.018</v>
+        <v>0.071</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>29.75</v>
+        <v>0.23</v>
       </c>
       <c r="J2" t="n">
-        <v>5.16</v>
+        <v>0.84</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>279</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>361</v>
+        <v>222.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003</v>
+        <v>0.028</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>42.9</v>
+        <v>0.3</v>
       </c>
       <c r="J3" t="n">
-        <v>9.48</v>
+        <v>0.72</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>723</v>
+        <v>446</v>
       </c>
     </row>
     <row r="4">
@@ -1075,37 +1093,37 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n">
-        <v>90.5</v>
+        <v>139</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04</v>
+        <v>0.018</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>44.02</v>
+        <v>29.75</v>
       </c>
       <c r="J4" t="n">
-        <v>20.16</v>
+        <v>5.16</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>182</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5">
@@ -1113,37 +1131,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>60.5</v>
+        <v>361</v>
       </c>
       <c r="G5" t="n">
-        <v>0.054</v>
+        <v>0.003</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>2.91</v>
+        <v>42.9</v>
       </c>
       <c r="J5" t="n">
-        <v>7.8</v>
+        <v>9.48</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>122</v>
+        <v>723</v>
       </c>
     </row>
     <row r="6">
@@ -1151,37 +1169,37 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
         <v>0.4</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>1.09</v>
+        <v>44.02</v>
       </c>
       <c r="J6" t="n">
-        <v>2.04</v>
+        <v>20.16</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7">
@@ -1189,42 +1207,42 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" t="n">
         <v>0.3</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>50.5</v>
+        <v>60.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03</v>
+        <v>0.054</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>1.89</v>
+        <v>2.91</v>
       </c>
       <c r="J7" t="n">
-        <v>2.04</v>
+        <v>7.8</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>102</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
@@ -1233,31 +1251,31 @@
         <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="E8" t="s">
         <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>630</v>
+        <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.77</v>
+        <v>1.09</v>
       </c>
       <c r="J8" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>1261</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9">
@@ -1277,30 +1295,30 @@
         <v>38</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>50.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08</v>
+        <v>1.89</v>
       </c>
       <c r="J9" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>39</v>
@@ -1309,31 +1327,31 @@
         <v>40</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="E10" t="s">
         <v>41</v>
       </c>
       <c r="F10" t="n">
-        <v>276.5</v>
+        <v>630</v>
       </c>
       <c r="G10" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>8.81</v>
+        <v>0.77</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>0.96</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>554</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="11">
@@ -1347,31 +1365,31 @@
         <v>43</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>326.5</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>0.003</v>
+        <v>0.039</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>1.05</v>
+        <v>0.08</v>
       </c>
       <c r="J11" t="n">
-        <v>3.12</v>
+        <v>0.96</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>654</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
@@ -1391,30 +1409,30 @@
         <v>47</v>
       </c>
       <c r="F12" t="n">
-        <v>93</v>
+        <v>276.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>2.91</v>
+        <v>8.81</v>
       </c>
       <c r="J12" t="n">
-        <v>2.52</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>187</v>
+        <v>554</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>48</v>
@@ -1423,31 +1441,31 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
       <c r="E13" t="s">
         <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>374.5</v>
+        <v>326.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.019</v>
+        <v>0.003</v>
       </c>
       <c r="H13" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="J13" t="n">
-        <v>4.8</v>
+        <v>3.12</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>750</v>
+        <v>654</v>
       </c>
     </row>
     <row r="14">
@@ -1455,75 +1473,75 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
         <v>52</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E14" t="s">
         <v>53</v>
       </c>
-      <c r="D14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E14" t="s">
-        <v>54</v>
-      </c>
       <c r="F14" t="n">
-        <v>370</v>
+        <v>93</v>
       </c>
       <c r="G14" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>1.99</v>
+        <v>2.91</v>
       </c>
       <c r="J14" t="n">
-        <v>1.56</v>
+        <v>2.52</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>371</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
         <v>55</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E15" t="s">
         <v>56</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="H15" t="s">
         <v>57</v>
       </c>
-      <c r="F15" t="n">
-        <v>127</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="H15" t="s">
-        <v>16</v>
-      </c>
       <c r="I15" t="n">
-        <v>4.49</v>
+        <v>1.01</v>
       </c>
       <c r="J15" t="n">
-        <v>4.68</v>
+        <v>4.8</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>128</v>
+        <v>750</v>
       </c>
     </row>
     <row r="16">
@@ -1537,31 +1555,31 @@
         <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E16" t="s">
         <v>60</v>
       </c>
       <c r="F16" t="n">
-        <v>322</v>
+        <v>370</v>
       </c>
       <c r="G16" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>0.43</v>
+        <v>1.99</v>
       </c>
       <c r="J16" t="n">
-        <v>2.52</v>
+        <v>1.56</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>323</v>
+        <v>371</v>
       </c>
     </row>
     <row r="17">
@@ -1581,30 +1599,30 @@
         <v>63</v>
       </c>
       <c r="F17" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="G17" t="n">
-        <v>0.005</v>
+        <v>0.129</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>0.18</v>
+        <v>4.49</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>4.68</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>113</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
         <v>64</v>
@@ -1613,36 +1631,36 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
       <c r="E18" t="s">
         <v>66</v>
       </c>
       <c r="F18" t="n">
-        <v>412</v>
+        <v>322</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
       <c r="H18" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>1.91</v>
+        <v>0.43</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>413</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
         <v>67</v>
@@ -1651,36 +1669,36 @@
         <v>68</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="E19" t="s">
         <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="G19" t="n">
-        <v>0.078</v>
+        <v>0.005</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
       </c>
       <c r="I19" t="n">
-        <v>2.02</v>
+        <v>0.18</v>
       </c>
       <c r="J19" t="n">
-        <v>2.16</v>
+        <v>0.6</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>831</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
         <v>70</v>
@@ -1689,112 +1707,112 @@
         <v>71</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="E20" t="s">
         <v>72</v>
       </c>
       <c r="F20" t="n">
-        <v>166</v>
+        <v>412</v>
       </c>
       <c r="G20" t="n">
-        <v>0.006</v>
+        <v>0.02</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="I20" t="n">
-        <v>0.49</v>
+        <v>1.91</v>
       </c>
       <c r="J20" t="n">
-        <v>0.72</v>
+        <v>3</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>332</v>
+        <v>413</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
         <v>73</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>74</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E21" t="s">
         <v>75</v>
       </c>
-      <c r="D21" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E21" t="s">
-        <v>76</v>
-      </c>
       <c r="F21" t="n">
-        <v>1298</v>
+        <v>805</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001</v>
+        <v>0.078</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
       </c>
       <c r="I21" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="J21" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>2601</v>
+        <v>831</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
         <v>77</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E22" t="s">
         <v>78</v>
       </c>
-      <c r="D22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E22" t="s">
-        <v>79</v>
-      </c>
       <c r="F22" t="n">
-        <v>864</v>
+        <v>166</v>
       </c>
       <c r="G22" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>0.61</v>
+        <v>0.49</v>
       </c>
       <c r="J22" t="n">
-        <v>0.96</v>
+        <v>0.72</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1732</v>
+        <v>332</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
         <v>80</v>
@@ -1803,36 +1821,36 @@
         <v>81</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E23" t="s">
         <v>82</v>
       </c>
       <c r="F23" t="n">
-        <v>862</v>
+        <v>1298</v>
       </c>
       <c r="G23" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>1.29</v>
+        <v>2.18</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1729</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B24" t="s">
         <v>83</v>
@@ -1841,36 +1859,36 @@
         <v>84</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E24" t="s">
         <v>85</v>
       </c>
       <c r="F24" t="n">
-        <v>462</v>
+        <v>864</v>
       </c>
       <c r="G24" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.11</v>
+        <v>0.61</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>929</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B25" t="s">
         <v>86</v>
@@ -1879,36 +1897,36 @@
         <v>87</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E25" t="s">
         <v>88</v>
       </c>
       <c r="F25" t="n">
-        <v>83</v>
+        <v>862</v>
       </c>
       <c r="G25" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
       </c>
       <c r="I25" t="n">
-        <v>0.46</v>
+        <v>1.29</v>
       </c>
       <c r="J25" t="n">
-        <v>0.84</v>
+        <v>1.8</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>168</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="B26" t="s">
         <v>89</v>
@@ -1917,13 +1935,13 @@
         <v>90</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E26" t="s">
         <v>91</v>
       </c>
       <c r="F26" t="n">
-        <v>216</v>
+        <v>462</v>
       </c>
       <c r="G26" t="n">
         <v>0.005</v>
@@ -1932,21 +1950,21 @@
         <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>0.44</v>
+        <v>0.11</v>
       </c>
       <c r="J26" t="n">
-        <v>0.96</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>217</v>
+        <v>929</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
         <v>92</v>
@@ -1955,36 +1973,36 @@
         <v>93</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E27" t="s">
         <v>94</v>
       </c>
       <c r="F27" t="n">
-        <v>349</v>
+        <v>83</v>
       </c>
       <c r="G27" t="n">
-        <v>0.129</v>
+        <v>0.014</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.76</v>
+        <v>0.46</v>
       </c>
       <c r="J27" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>346</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
         <v>95</v>
@@ -1993,31 +2011,31 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E28" t="s">
         <v>97</v>
       </c>
       <c r="F28" t="n">
-        <v>69</v>
+        <v>216</v>
       </c>
       <c r="G28" t="n">
-        <v>0.025</v>
+        <v>0.005</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>0.03</v>
+        <v>0.44</v>
       </c>
       <c r="J28" t="n">
-        <v>0.24</v>
+        <v>0.96</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>70</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29">
@@ -2031,36 +2049,36 @@
         <v>99</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>101</v>
+        <v>349</v>
       </c>
       <c r="G29" t="n">
-        <v>0.012</v>
+        <v>0.129</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
       </c>
       <c r="I29" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="J29" t="n">
-        <v>2.4</v>
+        <v>1.08</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>102</v>
+        <v>346</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="B30" t="s">
         <v>101</v>
@@ -2069,31 +2087,31 @@
         <v>102</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E30" t="s">
         <v>103</v>
       </c>
       <c r="F30" t="n">
-        <v>438</v>
+        <v>69</v>
       </c>
       <c r="G30" t="n">
-        <v>0.008</v>
+        <v>0.025</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="J30" t="n">
-        <v>0.36</v>
+        <v>0.24</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>435</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31">
@@ -2107,31 +2125,31 @@
         <v>105</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E31" t="s">
         <v>106</v>
       </c>
       <c r="F31" t="n">
-        <v>336</v>
+        <v>101</v>
       </c>
       <c r="G31" t="n">
-        <v>0.002</v>
+        <v>0.012</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>9.49</v>
+        <v>0.75</v>
       </c>
       <c r="J31" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>337</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32">
@@ -2145,13 +2163,13 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="E32" t="s">
         <v>109</v>
       </c>
       <c r="F32" t="n">
-        <v>193</v>
+        <v>438</v>
       </c>
       <c r="G32" t="n">
         <v>0.008</v>
@@ -2160,16 +2178,16 @@
         <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>5.68</v>
+        <v>0.12</v>
       </c>
       <c r="J32" t="n">
-        <v>3.96</v>
+        <v>0.36</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>192</v>
+        <v>435</v>
       </c>
     </row>
     <row r="33">
@@ -2183,31 +2201,31 @@
         <v>111</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E33" t="s">
         <v>112</v>
       </c>
       <c r="F33" t="n">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="G33" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
       </c>
       <c r="I33" t="n">
-        <v>0.68</v>
+        <v>9.49</v>
       </c>
       <c r="J33" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>282</v>
+        <v>337</v>
       </c>
     </row>
     <row r="34">
@@ -2221,31 +2239,31 @@
         <v>114</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E34" t="s">
         <v>115</v>
       </c>
       <c r="F34" t="n">
-        <v>332</v>
+        <v>193</v>
       </c>
       <c r="G34" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
       </c>
       <c r="I34" t="n">
-        <v>2.38</v>
+        <v>5.68</v>
       </c>
       <c r="J34" t="n">
-        <v>3.36</v>
+        <v>3.96</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>331</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35">
@@ -2259,31 +2277,31 @@
         <v>117</v>
       </c>
       <c r="D35" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="E35" t="s">
         <v>118</v>
       </c>
       <c r="F35" t="n">
-        <v>96</v>
+        <v>281</v>
       </c>
       <c r="G35" t="n">
-        <v>0.082</v>
+        <v>0.007</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
       </c>
       <c r="I35" t="n">
-        <v>2.04</v>
+        <v>0.68</v>
       </c>
       <c r="J35" t="n">
-        <v>8.76</v>
+        <v>1.2</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>95</v>
+        <v>282</v>
       </c>
     </row>
     <row r="36">
@@ -2297,22 +2315,22 @@
         <v>120</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E36" t="s">
         <v>121</v>
       </c>
       <c r="F36" t="n">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="G36" t="n">
-        <v>0.122</v>
+        <v>0.006</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>1.72</v>
+        <v>2.38</v>
       </c>
       <c r="J36" t="n">
         <v>3.36</v>
@@ -2321,7 +2339,7 @@
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>27</v>
+        <v>331</v>
       </c>
     </row>
     <row r="37">
@@ -2335,31 +2353,31 @@
         <v>123</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="E37" t="s">
         <v>124</v>
       </c>
       <c r="F37" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="G37" t="n">
-        <v>0.015</v>
+        <v>0.082</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
       </c>
       <c r="I37" t="n">
-        <v>0.93</v>
+        <v>2.04</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>8.76</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38">
@@ -2379,25 +2397,25 @@
         <v>127</v>
       </c>
       <c r="F38" t="n">
-        <v>214</v>
+        <v>26</v>
       </c>
       <c r="G38" t="n">
-        <v>0.005</v>
+        <v>0.122</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="J38" t="n">
-        <v>1.2</v>
+        <v>3.36</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>213</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39">
@@ -2411,31 +2429,31 @@
         <v>129</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E39" t="s">
         <v>130</v>
       </c>
       <c r="F39" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="G39" t="n">
-        <v>0.021</v>
+        <v>0.015</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>0.52</v>
+        <v>0.93</v>
       </c>
       <c r="J39" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40">
@@ -2449,31 +2467,31 @@
         <v>132</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E40" t="s">
         <v>133</v>
       </c>
       <c r="F40" t="n">
-        <v>7</v>
+        <v>214</v>
       </c>
       <c r="G40" t="n">
-        <v>0.097</v>
+        <v>0.005</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
       </c>
       <c r="I40" t="n">
-        <v>3.46</v>
+        <v>0.47</v>
       </c>
       <c r="J40" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>8</v>
+        <v>213</v>
       </c>
     </row>
     <row r="41">
@@ -2487,36 +2505,36 @@
         <v>135</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E41" t="s">
         <v>136</v>
       </c>
       <c r="F41" t="n">
-        <v>337</v>
+        <v>46</v>
       </c>
       <c r="G41" t="n">
-        <v>0.01</v>
+        <v>0.021</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
       </c>
       <c r="I41" t="n">
-        <v>6.39</v>
+        <v>0.52</v>
       </c>
       <c r="J41" t="n">
-        <v>10.92</v>
+        <v>2.4</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>336</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
         <v>137</v>
@@ -2525,31 +2543,31 @@
         <v>138</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E42" t="s">
         <v>139</v>
       </c>
       <c r="F42" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G42" t="n">
-        <v>0.05</v>
+        <v>0.097</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>1.79</v>
+        <v>3.46</v>
       </c>
       <c r="J42" t="n">
-        <v>3.36</v>
+        <v>6.6</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -2563,36 +2581,36 @@
         <v>141</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E43" t="s">
         <v>142</v>
       </c>
       <c r="F43" t="n">
-        <v>81</v>
+        <v>337</v>
       </c>
       <c r="G43" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="H43" t="s">
         <v>16</v>
       </c>
       <c r="I43" t="n">
-        <v>1.34</v>
+        <v>6.39</v>
       </c>
       <c r="J43" t="n">
-        <v>1.2</v>
+        <v>10.92</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>82</v>
+        <v>336</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="B44" t="s">
         <v>143</v>
@@ -2601,31 +2619,31 @@
         <v>144</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E44" t="s">
         <v>145</v>
       </c>
       <c r="F44" t="n">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="G44" t="n">
-        <v>0.004</v>
+        <v>0.05</v>
       </c>
       <c r="H44" t="s">
         <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>0.03</v>
+        <v>1.79</v>
       </c>
       <c r="J44" t="n">
-        <v>0.36</v>
+        <v>3.36</v>
       </c>
       <c r="K44" t="b">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>135</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45">
@@ -2645,25 +2663,25 @@
         <v>148</v>
       </c>
       <c r="F45" t="n">
-        <v>720</v>
+        <v>81</v>
       </c>
       <c r="G45" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
       </c>
       <c r="I45" t="n">
-        <v>4.71</v>
+        <v>1.34</v>
       </c>
       <c r="J45" t="n">
-        <v>8.04</v>
+        <v>1.2</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>717</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46">
@@ -2683,25 +2701,25 @@
         <v>151</v>
       </c>
       <c r="F46" t="n">
-        <v>773</v>
+        <v>134</v>
       </c>
       <c r="G46" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
       </c>
       <c r="I46" t="n">
-        <v>0.37</v>
+        <v>0.03</v>
       </c>
       <c r="J46" t="n">
-        <v>1.56</v>
+        <v>0.36</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>774</v>
+        <v>135</v>
       </c>
     </row>
     <row r="47">
@@ -2715,13 +2733,13 @@
         <v>153</v>
       </c>
       <c r="D47" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E47" t="s">
         <v>154</v>
       </c>
       <c r="F47" t="n">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="G47" t="n">
         <v>0.002</v>
@@ -2730,16 +2748,16 @@
         <v>16</v>
       </c>
       <c r="I47" t="n">
-        <v>0.69</v>
+        <v>4.71</v>
       </c>
       <c r="J47" t="n">
-        <v>3.24</v>
+        <v>8.04</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>734</v>
+        <v>717</v>
       </c>
     </row>
     <row r="48">
@@ -2753,31 +2771,31 @@
         <v>156</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E48" t="s">
         <v>157</v>
       </c>
       <c r="F48" t="n">
-        <v>1100</v>
+        <v>773</v>
       </c>
       <c r="G48" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
       </c>
       <c r="I48" t="n">
-        <v>6.45</v>
+        <v>0.37</v>
       </c>
       <c r="J48" t="n">
-        <v>14.4</v>
+        <v>1.56</v>
       </c>
       <c r="K48" t="b">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>1097</v>
+        <v>774</v>
       </c>
     </row>
     <row r="49">
@@ -2791,31 +2809,31 @@
         <v>159</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E49" t="s">
         <v>160</v>
       </c>
       <c r="F49" t="n">
-        <v>498</v>
+        <v>735</v>
       </c>
       <c r="G49" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
       </c>
       <c r="I49" t="n">
-        <v>1.38</v>
+        <v>0.69</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>495</v>
+        <v>734</v>
       </c>
     </row>
     <row r="50">
@@ -2835,25 +2853,25 @@
         <v>163</v>
       </c>
       <c r="F50" t="n">
-        <v>257</v>
+        <v>1100</v>
       </c>
       <c r="G50" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H50" t="s">
         <v>16</v>
       </c>
       <c r="I50" t="n">
-        <v>6.15</v>
+        <v>6.45</v>
       </c>
       <c r="J50" t="n">
-        <v>9.48</v>
+        <v>14.4</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>258</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="51">
@@ -2873,25 +2891,25 @@
         <v>166</v>
       </c>
       <c r="F51" t="n">
-        <v>458</v>
+        <v>498</v>
       </c>
       <c r="G51" t="n">
-        <v>0.059</v>
+        <v>0.006</v>
       </c>
       <c r="H51" t="s">
         <v>16</v>
       </c>
       <c r="I51" t="n">
-        <v>2.47</v>
+        <v>1.38</v>
       </c>
       <c r="J51" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>453</v>
+        <v>495</v>
       </c>
     </row>
     <row r="52">
@@ -2905,31 +2923,31 @@
         <v>168</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E52" t="s">
         <v>169</v>
       </c>
       <c r="F52" t="n">
-        <v>923</v>
+        <v>257</v>
       </c>
       <c r="G52" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H52" t="s">
         <v>16</v>
       </c>
       <c r="I52" t="n">
-        <v>3.76</v>
+        <v>6.15</v>
       </c>
       <c r="J52" t="n">
-        <v>5.4</v>
+        <v>9.48</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>918</v>
+        <v>258</v>
       </c>
     </row>
     <row r="53">
@@ -2943,31 +2961,31 @@
         <v>171</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E53" t="s">
         <v>172</v>
       </c>
       <c r="F53" t="n">
-        <v>1012</v>
+        <v>458</v>
       </c>
       <c r="G53" t="n">
-        <v>0.003</v>
+        <v>0.059</v>
       </c>
       <c r="H53" t="s">
         <v>16</v>
       </c>
       <c r="I53" t="n">
-        <v>0.08</v>
+        <v>2.47</v>
       </c>
       <c r="J53" t="n">
-        <v>0.72</v>
+        <v>7.2</v>
       </c>
       <c r="K53" t="b">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>1211</v>
+        <v>453</v>
       </c>
     </row>
     <row r="54">
@@ -2987,7 +3005,7 @@
         <v>175</v>
       </c>
       <c r="F54" t="n">
-        <v>344.5</v>
+        <v>923</v>
       </c>
       <c r="G54" t="n">
         <v>0.002</v>
@@ -2996,15 +3014,91 @@
         <v>16</v>
       </c>
       <c r="I54" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" t="s">
+        <v>176</v>
+      </c>
+      <c r="C55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E55" t="s">
+        <v>178</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1012</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H55" t="s">
+        <v>16</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>179</v>
+      </c>
+      <c r="C56" t="s">
+        <v>180</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E56" t="s">
+        <v>181</v>
+      </c>
+      <c r="F56" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H56" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" t="n">
         <v>0.32</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J56" t="n">
         <v>2.04</v>
       </c>
-      <c r="K54" t="b">
-        <v>1</v>
-      </c>
-      <c r="L54" t="n">
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
         <v>688</v>
       </c>
     </row>
@@ -3036,22 +3130,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="F1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="G1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2">
@@ -3059,7 +3153,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="n">
         <v>0.4</v>
@@ -3079,7 +3173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B3" t="n">
         <v>7</v>
@@ -3102,13 +3196,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="D4" t="n">
         <v>6.5</v>
@@ -3175,10 +3269,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C2" t="n">
         <v>374.5</v>
@@ -3190,7 +3284,7 @@
         <v>0.019</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G2" t="n">
         <v>1.01</v>
@@ -3201,10 +3295,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C3" t="n">
         <v>412</v>
@@ -3216,7 +3310,7 @@
         <v>0.02</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G3" t="n">
         <v>1.91</v>
@@ -3230,7 +3324,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C4" t="n">
         <v>96</v>
@@ -3253,10 +3347,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C5" t="n">
         <v>630</v>
@@ -3279,10 +3373,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C6" t="n">
         <v>805</v>
@@ -3305,132 +3399,132 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>862</v>
+        <v>222.5</v>
       </c>
       <c r="D7" t="n">
         <v>0.9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005</v>
+        <v>0.028</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>1.29</v>
+        <v>0.3</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C8" t="n">
-        <v>1298</v>
+        <v>862</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18</v>
+        <v>1.29</v>
       </c>
       <c r="H8" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
-        <v>864</v>
+        <v>1298</v>
       </c>
       <c r="D9" t="n">
         <v>0.8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.61</v>
+        <v>2.18</v>
       </c>
       <c r="H9" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C10" t="n">
-        <v>83</v>
+        <v>864</v>
       </c>
       <c r="D10" t="n">
         <v>0.8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="H10" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="C11" t="n">
-        <v>735</v>
+        <v>83</v>
       </c>
       <c r="D11" t="n">
         <v>0.8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.69</v>
+        <v>0.46</v>
       </c>
       <c r="H11" t="n">
-        <v>3.24</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="12">
@@ -3438,39 +3532,39 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="C12" t="n">
-        <v>216</v>
+        <v>735</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.44</v>
+        <v>0.69</v>
       </c>
       <c r="H12" t="n">
-        <v>0.96</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C13" t="n">
-        <v>462</v>
+        <v>216</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E13" t="n">
         <v>0.005</v>
@@ -3479,36 +3573,36 @@
         <v>16</v>
       </c>
       <c r="G13" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C14" t="n">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="D14" t="n">
         <v>0.6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="H14" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15">
@@ -3516,25 +3610,25 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="C15" t="n">
-        <v>361</v>
+        <v>438</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>42.9</v>
+        <v>0.12</v>
       </c>
       <c r="H15" t="n">
-        <v>9.48</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="16">
@@ -3542,10 +3636,10 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
-        <v>326.5</v>
+        <v>361</v>
       </c>
       <c r="D16" t="n">
         <v>0.5</v>
@@ -3557,10 +3651,10 @@
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>1.05</v>
+        <v>42.9</v>
       </c>
       <c r="H16" t="n">
-        <v>3.12</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="17">
@@ -3568,25 +3662,25 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C17" t="n">
-        <v>370</v>
+        <v>326.5</v>
       </c>
       <c r="D17" t="n">
         <v>0.5</v>
       </c>
       <c r="E17" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>1.99</v>
+        <v>1.05</v>
       </c>
       <c r="H17" t="n">
-        <v>1.56</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="18">
@@ -3594,25 +3688,25 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C18" t="n">
-        <v>166</v>
+        <v>370</v>
       </c>
       <c r="D18" t="n">
         <v>0.5</v>
       </c>
       <c r="E18" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>0.49</v>
+        <v>1.99</v>
       </c>
       <c r="H18" t="n">
-        <v>0.72</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="19">
@@ -3620,25 +3714,25 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>166</v>
       </c>
       <c r="D19" t="n">
         <v>0.5</v>
       </c>
       <c r="E19" t="n">
-        <v>0.122</v>
+        <v>0.006</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>1.72</v>
+        <v>0.49</v>
       </c>
       <c r="H19" t="n">
-        <v>3.36</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="20">
@@ -3649,22 +3743,22 @@
         <v>125</v>
       </c>
       <c r="C20" t="n">
-        <v>214</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
         <v>0.5</v>
       </c>
       <c r="E20" t="n">
-        <v>0.005</v>
+        <v>0.122</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="21">
@@ -3672,25 +3766,25 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C21" t="n">
-        <v>46</v>
+        <v>214</v>
       </c>
       <c r="D21" t="n">
         <v>0.5</v>
       </c>
       <c r="E21" t="n">
-        <v>0.021</v>
+        <v>0.005</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -1038,7 +1038,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>0.23</v>
+        <v>1.15</v>
       </c>
       <c r="J2" t="n">
         <v>0.84</v>
@@ -1076,7 +1076,7 @@
         <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J3" t="n">
         <v>0.72</v>
@@ -3417,7 +3417,7 @@
         <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="H7" t="n">
         <v>0.72</v>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -52,6 +52,21 @@
     <t xml:space="preserve">points_count</t>
   </si>
   <si>
+    <t xml:space="preserve">Wasserstraße_Springorum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/30 05:52:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/31 04:40:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/30 09:54:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
     <t xml:space="preserve">An_der_Kost</t>
   </si>
   <si>
@@ -62,12 +77,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026/05/13 13:13:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wasserstraße_Springorum</t>
   </si>
   <si>
     <t xml:space="preserve">2026/05/13 08:08:30</t>
@@ -625,8 +634,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L56" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L56"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L57" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L57"/>
   <tableColumns count="12">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -1023,31 +1032,31 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>1368.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.071</v>
+        <v>0.005</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="J2" t="n">
-        <v>0.84</v>
+        <v>1.44</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>101</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="3">
@@ -1061,31 +1070,31 @@
         <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>222.5</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>0.028</v>
+        <v>0.071</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="J3" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>446</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4">
@@ -1099,36 +1108,36 @@
         <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="E4" t="s">
         <v>23</v>
       </c>
       <c r="F4" t="n">
-        <v>139</v>
+        <v>222.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.018</v>
+        <v>0.028</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>29.75</v>
+        <v>1.5</v>
       </c>
       <c r="J4" t="n">
-        <v>5.16</v>
+        <v>0.72</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>279</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1137,36 +1146,36 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E5" t="s">
         <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>361</v>
+        <v>139</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003</v>
+        <v>0.018</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>42.9</v>
+        <v>29.75</v>
       </c>
       <c r="J5" t="n">
-        <v>9.48</v>
+        <v>5.16</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>723</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
@@ -1175,36 +1184,36 @@
         <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="s">
         <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>90.5</v>
+        <v>361</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04</v>
+        <v>0.003</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>44.02</v>
+        <v>42.9</v>
       </c>
       <c r="J6" t="n">
-        <v>20.16</v>
+        <v>9.48</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>182</v>
+        <v>723</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
@@ -1213,36 +1222,36 @@
         <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="s">
         <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>60.5</v>
+        <v>90.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.054</v>
+        <v>0.04</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>2.91</v>
+        <v>44.02</v>
       </c>
       <c r="J7" t="n">
-        <v>7.8</v>
+        <v>20.16</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>122</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
@@ -1251,36 +1260,36 @@
         <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E8" t="s">
         <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>90</v>
+        <v>60.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01</v>
+        <v>0.054</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>1.09</v>
+        <v>2.91</v>
       </c>
       <c r="J8" t="n">
-        <v>2.04</v>
+        <v>7.8</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
         <v>36</v>
@@ -1289,22 +1298,22 @@
         <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
       </c>
       <c r="F9" t="n">
-        <v>50.5</v>
+        <v>90</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>1.89</v>
+        <v>1.09</v>
       </c>
       <c r="J9" t="n">
         <v>2.04</v>
@@ -1313,7 +1322,7 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>102</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -1327,31 +1336,31 @@
         <v>40</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="E10" t="s">
         <v>41</v>
       </c>
       <c r="F10" t="n">
-        <v>630</v>
+        <v>50.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.014</v>
+        <v>0.03</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.77</v>
+        <v>1.89</v>
       </c>
       <c r="J10" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1261</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
@@ -1365,22 +1374,22 @@
         <v>43</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>630</v>
       </c>
       <c r="G11" t="n">
-        <v>0.039</v>
+        <v>0.014</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08</v>
+        <v>0.77</v>
       </c>
       <c r="J11" t="n">
         <v>0.96</v>
@@ -1389,12 +1398,12 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>81</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>45</v>
@@ -1409,30 +1418,30 @@
         <v>47</v>
       </c>
       <c r="F12" t="n">
-        <v>276.5</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>0.013</v>
+        <v>0.039</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>8.81</v>
+        <v>0.08</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>0.96</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>554</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
         <v>48</v>
@@ -1441,36 +1450,36 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E13" t="s">
         <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>326.5</v>
+        <v>276.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.003</v>
+        <v>0.013</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>1.05</v>
+        <v>8.81</v>
       </c>
       <c r="J13" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>654</v>
+        <v>554</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>51</v>
@@ -1479,31 +1488,31 @@
         <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E14" t="s">
         <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>93</v>
+        <v>326.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>2.91</v>
+        <v>1.05</v>
       </c>
       <c r="J14" t="n">
-        <v>2.52</v>
+        <v>3.12</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>187</v>
+        <v>654</v>
       </c>
     </row>
     <row r="15">
@@ -1517,31 +1526,31 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>6.5</v>
+        <v>0.3</v>
       </c>
       <c r="E15" t="s">
         <v>56</v>
       </c>
       <c r="F15" t="n">
-        <v>374.5</v>
+        <v>93</v>
       </c>
       <c r="G15" t="n">
-        <v>0.019</v>
+        <v>0.005</v>
       </c>
       <c r="H15" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>1.01</v>
+        <v>2.91</v>
       </c>
       <c r="J15" t="n">
-        <v>4.8</v>
+        <v>2.52</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>750</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16">
@@ -1549,42 +1558,42 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
         <v>58</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E16" t="s">
         <v>59</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="H16" t="s">
         <v>60</v>
       </c>
-      <c r="F16" t="n">
-        <v>370</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="H16" t="s">
-        <v>16</v>
-      </c>
       <c r="I16" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="J16" t="n">
-        <v>1.56</v>
+        <v>4.8</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>371</v>
+        <v>750</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
         <v>61</v>
@@ -1593,36 +1602,36 @@
         <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E17" t="s">
         <v>63</v>
       </c>
       <c r="F17" t="n">
-        <v>127</v>
+        <v>370</v>
       </c>
       <c r="G17" t="n">
-        <v>0.129</v>
+        <v>0.002</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>4.49</v>
+        <v>1.99</v>
       </c>
       <c r="J17" t="n">
-        <v>4.68</v>
+        <v>1.56</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>128</v>
+        <v>371</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>64</v>
@@ -1637,30 +1646,30 @@
         <v>66</v>
       </c>
       <c r="F18" t="n">
-        <v>322</v>
+        <v>127</v>
       </c>
       <c r="G18" t="n">
-        <v>0.004</v>
+        <v>0.129</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.43</v>
+        <v>4.49</v>
       </c>
       <c r="J18" t="n">
-        <v>2.52</v>
+        <v>4.68</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>323</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>67</v>
@@ -1675,25 +1684,25 @@
         <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>112</v>
+        <v>322</v>
       </c>
       <c r="G19" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.18</v>
+        <v>0.43</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>2.52</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>113</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20">
@@ -1707,36 +1716,36 @@
         <v>71</v>
       </c>
       <c r="D20" t="n">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
       <c r="E20" t="s">
         <v>72</v>
       </c>
       <c r="F20" t="n">
-        <v>412</v>
+        <v>112</v>
       </c>
       <c r="G20" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="H20" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>1.91</v>
+        <v>0.18</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>413</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
         <v>73</v>
@@ -1745,31 +1754,31 @@
         <v>74</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="E21" t="s">
         <v>75</v>
       </c>
       <c r="F21" t="n">
-        <v>805</v>
+        <v>412</v>
       </c>
       <c r="G21" t="n">
-        <v>0.078</v>
+        <v>0.02</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="I21" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="J21" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>831</v>
+        <v>413</v>
       </c>
     </row>
     <row r="22">
@@ -1783,74 +1792,74 @@
         <v>77</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="E22" t="s">
         <v>78</v>
       </c>
       <c r="F22" t="n">
-        <v>166</v>
+        <v>805</v>
       </c>
       <c r="G22" t="n">
-        <v>0.006</v>
+        <v>0.078</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>0.49</v>
+        <v>2.02</v>
       </c>
       <c r="J22" t="n">
-        <v>0.72</v>
+        <v>2.16</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>332</v>
+        <v>831</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
         <v>79</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>80</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E23" t="s">
         <v>81</v>
       </c>
-      <c r="D23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E23" t="s">
-        <v>82</v>
-      </c>
       <c r="F23" t="n">
-        <v>1298</v>
+        <v>166</v>
       </c>
       <c r="G23" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>2.18</v>
+        <v>0.49</v>
       </c>
       <c r="J23" t="n">
-        <v>2.04</v>
+        <v>0.72</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>2601</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s">
         <v>83</v>
@@ -1865,30 +1874,30 @@
         <v>85</v>
       </c>
       <c r="F24" t="n">
-        <v>864</v>
+        <v>1298</v>
       </c>
       <c r="G24" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.61</v>
+        <v>2.18</v>
       </c>
       <c r="J24" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1732</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B25" t="s">
         <v>86</v>
@@ -1897,36 +1906,36 @@
         <v>87</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E25" t="s">
         <v>88</v>
       </c>
       <c r="F25" t="n">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G25" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
       </c>
       <c r="I25" t="n">
-        <v>1.29</v>
+        <v>0.61</v>
       </c>
       <c r="J25" t="n">
-        <v>1.8</v>
+        <v>0.96</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1729</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s">
         <v>89</v>
@@ -1935,13 +1944,13 @@
         <v>90</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E26" t="s">
         <v>91</v>
       </c>
       <c r="F26" t="n">
-        <v>462</v>
+        <v>862</v>
       </c>
       <c r="G26" t="n">
         <v>0.005</v>
@@ -1950,21 +1959,21 @@
         <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>0.11</v>
+        <v>1.29</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>929</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B27" t="s">
         <v>92</v>
@@ -1973,36 +1982,36 @@
         <v>93</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E27" t="s">
         <v>94</v>
       </c>
       <c r="F27" t="n">
-        <v>83</v>
+        <v>462</v>
       </c>
       <c r="G27" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="J27" t="n">
-        <v>0.84</v>
+        <v>0.6</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>168</v>
+        <v>929</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s">
         <v>95</v>
@@ -2011,36 +2020,36 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E28" t="s">
         <v>97</v>
       </c>
       <c r="F28" t="n">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="G28" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="J28" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>217</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
         <v>98</v>
@@ -2049,36 +2058,36 @@
         <v>99</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>349</v>
+        <v>216</v>
       </c>
       <c r="G29" t="n">
-        <v>0.129</v>
+        <v>0.005</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
       </c>
       <c r="I29" t="n">
-        <v>0.76</v>
+        <v>0.44</v>
       </c>
       <c r="J29" t="n">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>346</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
         <v>101</v>
@@ -2093,30 +2102,30 @@
         <v>103</v>
       </c>
       <c r="F30" t="n">
-        <v>69</v>
+        <v>349</v>
       </c>
       <c r="G30" t="n">
-        <v>0.025</v>
+        <v>0.129</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>0.03</v>
+        <v>0.76</v>
       </c>
       <c r="J30" t="n">
-        <v>0.24</v>
+        <v>1.08</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>70</v>
+        <v>346</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="B31" t="s">
         <v>104</v>
@@ -2125,36 +2134,36 @@
         <v>105</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E31" t="s">
         <v>106</v>
       </c>
       <c r="F31" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="G31" t="n">
-        <v>0.012</v>
+        <v>0.025</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>0.75</v>
+        <v>0.03</v>
       </c>
       <c r="J31" t="n">
-        <v>2.4</v>
+        <v>0.24</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
         <v>107</v>
@@ -2163,36 +2172,36 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E32" t="s">
         <v>109</v>
       </c>
       <c r="F32" t="n">
-        <v>438</v>
+        <v>101</v>
       </c>
       <c r="G32" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>0.12</v>
+        <v>0.75</v>
       </c>
       <c r="J32" t="n">
-        <v>0.36</v>
+        <v>2.4</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>435</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
         <v>110</v>
@@ -2201,36 +2210,36 @@
         <v>111</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E33" t="s">
         <v>112</v>
       </c>
       <c r="F33" t="n">
-        <v>336</v>
+        <v>438</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
       </c>
       <c r="I33" t="n">
-        <v>9.49</v>
+        <v>0.12</v>
       </c>
       <c r="J33" t="n">
-        <v>5.4</v>
+        <v>0.36</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>337</v>
+        <v>435</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
         <v>113</v>
@@ -2239,36 +2248,36 @@
         <v>114</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E34" t="s">
         <v>115</v>
       </c>
       <c r="F34" t="n">
-        <v>193</v>
+        <v>336</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
       </c>
       <c r="I34" t="n">
-        <v>5.68</v>
+        <v>9.49</v>
       </c>
       <c r="J34" t="n">
-        <v>3.96</v>
+        <v>5.4</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>192</v>
+        <v>337</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
         <v>116</v>
@@ -2283,30 +2292,30 @@
         <v>118</v>
       </c>
       <c r="F35" t="n">
-        <v>281</v>
+        <v>193</v>
       </c>
       <c r="G35" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
       </c>
       <c r="I35" t="n">
-        <v>0.68</v>
+        <v>5.68</v>
       </c>
       <c r="J35" t="n">
-        <v>1.2</v>
+        <v>3.96</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>282</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
         <v>119</v>
@@ -2315,36 +2324,36 @@
         <v>120</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E36" t="s">
         <v>121</v>
       </c>
       <c r="F36" t="n">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="G36" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>2.38</v>
+        <v>0.68</v>
       </c>
       <c r="J36" t="n">
-        <v>3.36</v>
+        <v>1.2</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>331</v>
+        <v>282</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
         <v>122</v>
@@ -2353,36 +2362,36 @@
         <v>123</v>
       </c>
       <c r="D37" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="E37" t="s">
         <v>124</v>
       </c>
       <c r="F37" t="n">
-        <v>96</v>
+        <v>332</v>
       </c>
       <c r="G37" t="n">
-        <v>0.082</v>
+        <v>0.006</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
       </c>
       <c r="I37" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="J37" t="n">
-        <v>8.76</v>
+        <v>3.36</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>95</v>
+        <v>331</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
         <v>125</v>
@@ -2391,36 +2400,36 @@
         <v>126</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="E38" t="s">
         <v>127</v>
       </c>
       <c r="F38" t="n">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="G38" t="n">
-        <v>0.122</v>
+        <v>0.082</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
       </c>
       <c r="I38" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="J38" t="n">
-        <v>3.36</v>
+        <v>8.76</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>27</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
         <v>128</v>
@@ -2429,36 +2438,36 @@
         <v>129</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E39" t="s">
         <v>130</v>
       </c>
       <c r="F39" t="n">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="G39" t="n">
-        <v>0.015</v>
+        <v>0.122</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>0.93</v>
+        <v>1.72</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>78</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
         <v>131</v>
@@ -2467,36 +2476,36 @@
         <v>132</v>
       </c>
       <c r="D40" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E40" t="s">
         <v>133</v>
       </c>
       <c r="F40" t="n">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="G40" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
       </c>
       <c r="I40" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="J40" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>213</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
         <v>134</v>
@@ -2511,30 +2520,30 @@
         <v>136</v>
       </c>
       <c r="F41" t="n">
-        <v>46</v>
+        <v>214</v>
       </c>
       <c r="G41" t="n">
-        <v>0.021</v>
+        <v>0.005</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
       </c>
       <c r="I41" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="J41" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>47</v>
+        <v>213</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
         <v>137</v>
@@ -2543,36 +2552,36 @@
         <v>138</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E42" t="s">
         <v>139</v>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="G42" t="n">
-        <v>0.097</v>
+        <v>0.021</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>3.46</v>
+        <v>0.52</v>
       </c>
       <c r="J42" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
         <v>140</v>
@@ -2581,36 +2590,36 @@
         <v>141</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E43" t="s">
         <v>142</v>
       </c>
       <c r="F43" t="n">
-        <v>337</v>
+        <v>7</v>
       </c>
       <c r="G43" t="n">
-        <v>0.01</v>
+        <v>0.097</v>
       </c>
       <c r="H43" t="s">
         <v>16</v>
       </c>
       <c r="I43" t="n">
-        <v>6.39</v>
+        <v>3.46</v>
       </c>
       <c r="J43" t="n">
-        <v>10.92</v>
+        <v>6.6</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>336</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
         <v>143</v>
@@ -2619,36 +2628,36 @@
         <v>144</v>
       </c>
       <c r="D44" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E44" t="s">
         <v>145</v>
       </c>
       <c r="F44" t="n">
-        <v>41</v>
+        <v>337</v>
       </c>
       <c r="G44" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H44" t="s">
         <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>1.79</v>
+        <v>6.39</v>
       </c>
       <c r="J44" t="n">
-        <v>3.36</v>
+        <v>10.92</v>
       </c>
       <c r="K44" t="b">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>42</v>
+        <v>336</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="B45" t="s">
         <v>146</v>
@@ -2657,36 +2666,36 @@
         <v>147</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E45" t="s">
         <v>148</v>
       </c>
       <c r="F45" t="n">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="G45" t="n">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
       </c>
       <c r="I45" t="n">
-        <v>1.34</v>
+        <v>1.79</v>
       </c>
       <c r="J45" t="n">
-        <v>1.2</v>
+        <v>3.36</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
         <v>149</v>
@@ -2701,30 +2710,30 @@
         <v>151</v>
       </c>
       <c r="F46" t="n">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="G46" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
       </c>
       <c r="I46" t="n">
-        <v>0.03</v>
+        <v>1.34</v>
       </c>
       <c r="J46" t="n">
-        <v>0.36</v>
+        <v>1.2</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>135</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
         <v>152</v>
@@ -2739,30 +2748,30 @@
         <v>154</v>
       </c>
       <c r="F47" t="n">
-        <v>720</v>
+        <v>134</v>
       </c>
       <c r="G47" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
       </c>
       <c r="I47" t="n">
-        <v>4.71</v>
+        <v>0.03</v>
       </c>
       <c r="J47" t="n">
-        <v>8.04</v>
+        <v>0.36</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>717</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
         <v>155</v>
@@ -2777,30 +2786,30 @@
         <v>157</v>
       </c>
       <c r="F48" t="n">
-        <v>773</v>
+        <v>720</v>
       </c>
       <c r="G48" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
       </c>
       <c r="I48" t="n">
-        <v>0.37</v>
+        <v>4.71</v>
       </c>
       <c r="J48" t="n">
-        <v>1.56</v>
+        <v>8.04</v>
       </c>
       <c r="K48" t="b">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>774</v>
+        <v>717</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
         <v>158</v>
@@ -2809,36 +2818,36 @@
         <v>159</v>
       </c>
       <c r="D49" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E49" t="s">
         <v>160</v>
       </c>
       <c r="F49" t="n">
-        <v>735</v>
+        <v>773</v>
       </c>
       <c r="G49" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
       </c>
       <c r="I49" t="n">
-        <v>0.69</v>
+        <v>0.37</v>
       </c>
       <c r="J49" t="n">
-        <v>3.24</v>
+        <v>1.56</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>734</v>
+        <v>774</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
         <v>161</v>
@@ -2847,13 +2856,13 @@
         <v>162</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E50" t="s">
         <v>163</v>
       </c>
       <c r="F50" t="n">
-        <v>1100</v>
+        <v>735</v>
       </c>
       <c r="G50" t="n">
         <v>0.002</v>
@@ -2862,21 +2871,21 @@
         <v>16</v>
       </c>
       <c r="I50" t="n">
-        <v>6.45</v>
+        <v>0.69</v>
       </c>
       <c r="J50" t="n">
-        <v>14.4</v>
+        <v>3.24</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>1097</v>
+        <v>734</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
         <v>164</v>
@@ -2885,36 +2894,36 @@
         <v>165</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E51" t="s">
         <v>166</v>
       </c>
       <c r="F51" t="n">
-        <v>498</v>
+        <v>1100</v>
       </c>
       <c r="G51" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="H51" t="s">
         <v>16</v>
       </c>
       <c r="I51" t="n">
-        <v>1.38</v>
+        <v>6.45</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>14.4</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>495</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
         <v>167</v>
@@ -2923,36 +2932,36 @@
         <v>168</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E52" t="s">
         <v>169</v>
       </c>
       <c r="F52" t="n">
-        <v>257</v>
+        <v>498</v>
       </c>
       <c r="G52" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="H52" t="s">
         <v>16</v>
       </c>
       <c r="I52" t="n">
-        <v>6.15</v>
+        <v>1.38</v>
       </c>
       <c r="J52" t="n">
-        <v>9.48</v>
+        <v>3</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>258</v>
+        <v>495</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
         <v>170</v>
@@ -2961,36 +2970,36 @@
         <v>171</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E53" t="s">
         <v>172</v>
       </c>
       <c r="F53" t="n">
-        <v>458</v>
+        <v>257</v>
       </c>
       <c r="G53" t="n">
-        <v>0.059</v>
+        <v>0.003</v>
       </c>
       <c r="H53" t="s">
         <v>16</v>
       </c>
       <c r="I53" t="n">
-        <v>2.47</v>
+        <v>6.15</v>
       </c>
       <c r="J53" t="n">
-        <v>7.2</v>
+        <v>9.48</v>
       </c>
       <c r="K53" t="b">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>453</v>
+        <v>258</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
         <v>173</v>
@@ -3005,30 +3014,30 @@
         <v>175</v>
       </c>
       <c r="F54" t="n">
-        <v>923</v>
+        <v>458</v>
       </c>
       <c r="G54" t="n">
-        <v>0.002</v>
+        <v>0.059</v>
       </c>
       <c r="H54" t="s">
         <v>16</v>
       </c>
       <c r="I54" t="n">
-        <v>3.76</v>
+        <v>2.47</v>
       </c>
       <c r="J54" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="K54" t="b">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>918</v>
+        <v>453</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
         <v>176</v>
@@ -3037,36 +3046,36 @@
         <v>177</v>
       </c>
       <c r="D55" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E55" t="s">
         <v>178</v>
       </c>
       <c r="F55" t="n">
-        <v>1012</v>
+        <v>923</v>
       </c>
       <c r="G55" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H55" t="s">
         <v>16</v>
       </c>
       <c r="I55" t="n">
-        <v>0.08</v>
+        <v>3.76</v>
       </c>
       <c r="J55" t="n">
-        <v>0.72</v>
+        <v>5.4</v>
       </c>
       <c r="K55" t="b">
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>1211</v>
+        <v>918</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
         <v>179</v>
@@ -3075,30 +3084,68 @@
         <v>180</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E56" t="s">
         <v>181</v>
       </c>
       <c r="F56" t="n">
+        <v>1012</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H56" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" t="s">
+        <v>182</v>
+      </c>
+      <c r="C57" t="s">
+        <v>183</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E57" t="s">
+        <v>184</v>
+      </c>
+      <c r="F57" t="n">
         <v>344.5</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G57" t="n">
         <v>0.002</v>
       </c>
-      <c r="H56" t="s">
-        <v>16</v>
-      </c>
-      <c r="I56" t="n">
+      <c r="H57" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" t="n">
         <v>0.32</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J57" t="n">
         <v>2.04</v>
       </c>
-      <c r="K56" t="b">
-        <v>1</v>
-      </c>
-      <c r="L56" t="n">
+      <c r="K57" t="b">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
         <v>688</v>
       </c>
     </row>
@@ -3130,27 +3177,27 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B2" t="n">
         <v>43</v>
@@ -3173,7 +3220,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B3" t="n">
         <v>7</v>
@@ -3196,13 +3243,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="D4" t="n">
         <v>6.5</v>
@@ -3269,10 +3316,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C2" t="n">
         <v>374.5</v>
@@ -3284,7 +3331,7 @@
         <v>0.019</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
         <v>1.01</v>
@@ -3295,10 +3342,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C3" t="n">
         <v>412</v>
@@ -3310,7 +3357,7 @@
         <v>0.02</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>1.91</v>
@@ -3321,10 +3368,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C4" t="n">
         <v>96</v>
@@ -3347,10 +3394,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C5" t="n">
         <v>630</v>
@@ -3373,224 +3420,224 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>805</v>
+        <v>1368.5</v>
       </c>
       <c r="D6" t="n">
         <v>1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.078</v>
+        <v>0.005</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="C7" t="n">
-        <v>222.5</v>
+        <v>805</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.028</v>
+        <v>0.078</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="H7" t="n">
-        <v>0.72</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>862</v>
+        <v>222.5</v>
       </c>
       <c r="D8" t="n">
         <v>0.9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005</v>
+        <v>0.028</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>1298</v>
+        <v>862</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>2.18</v>
+        <v>1.29</v>
       </c>
       <c r="H9" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
         <v>83</v>
       </c>
       <c r="C10" t="n">
-        <v>864</v>
+        <v>1298</v>
       </c>
       <c r="D10" t="n">
         <v>0.8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.61</v>
+        <v>2.18</v>
       </c>
       <c r="H10" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>864</v>
       </c>
       <c r="D11" t="n">
         <v>0.8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="H11" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="C12" t="n">
-        <v>735</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
         <v>0.8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.69</v>
+        <v>0.46</v>
       </c>
       <c r="H12" t="n">
-        <v>3.24</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="C13" t="n">
-        <v>216</v>
+        <v>735</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
       </c>
       <c r="G13" t="n">
-        <v>0.44</v>
+        <v>0.69</v>
       </c>
       <c r="H13" t="n">
-        <v>0.96</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C14" t="n">
-        <v>462</v>
+        <v>216</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E14" t="n">
         <v>0.005</v>
@@ -3599,73 +3646,73 @@
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="C15" t="n">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="D15" t="n">
         <v>0.6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="H15" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="C16" t="n">
-        <v>361</v>
+        <v>438</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>42.9</v>
+        <v>0.12</v>
       </c>
       <c r="H16" t="n">
-        <v>9.48</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C17" t="n">
-        <v>326.5</v>
+        <v>361</v>
       </c>
       <c r="D17" t="n">
         <v>0.5</v>
@@ -3677,114 +3724,114 @@
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>1.05</v>
+        <v>42.9</v>
       </c>
       <c r="H17" t="n">
-        <v>3.12</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C18" t="n">
-        <v>370</v>
+        <v>326.5</v>
       </c>
       <c r="D18" t="n">
         <v>0.5</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>1.99</v>
+        <v>1.05</v>
       </c>
       <c r="H18" t="n">
-        <v>1.56</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C19" t="n">
-        <v>166</v>
+        <v>370</v>
       </c>
       <c r="D19" t="n">
         <v>0.5</v>
       </c>
       <c r="E19" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>0.49</v>
+        <v>1.99</v>
       </c>
       <c r="H19" t="n">
-        <v>0.72</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>166</v>
       </c>
       <c r="D20" t="n">
         <v>0.5</v>
       </c>
       <c r="E20" t="n">
-        <v>0.122</v>
+        <v>0.006</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>1.72</v>
+        <v>0.49</v>
       </c>
       <c r="H20" t="n">
-        <v>3.36</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C21" t="n">
-        <v>214</v>
+        <v>26</v>
       </c>
       <c r="D21" t="n">
         <v>0.5</v>
       </c>
       <c r="E21" t="n">
-        <v>0.005</v>
+        <v>0.122</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2</v>
+        <v>3.36</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -52,6 +52,21 @@
     <t xml:space="preserve">points_count</t>
   </si>
   <si>
+    <t xml:space="preserve">An_der_Kost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/31 03:42:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/31 05:28:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/31 04:49:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wasserstraße_Springorum</t>
   </si>
   <si>
@@ -62,12 +77,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026/05/30 09:54:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An_der_Kost</t>
   </si>
   <si>
     <t xml:space="preserve">2026/05/13 13:08:00</t>
@@ -634,8 +643,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L57" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L58" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L58"/>
   <tableColumns count="12">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -1032,31 +1041,31 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1368.5</v>
+        <v>105.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>1.08</v>
+        <v>3.72</v>
       </c>
       <c r="J2" t="n">
-        <v>1.44</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>2738</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3">
@@ -1070,31 +1079,31 @@
         <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>1368.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.071</v>
+        <v>0.005</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>1.15</v>
+        <v>7.08</v>
       </c>
       <c r="J3" t="n">
-        <v>0.84</v>
+        <v>1.44</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>101</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="4">
@@ -1108,31 +1117,31 @@
         <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="s">
         <v>23</v>
       </c>
       <c r="F4" t="n">
-        <v>222.5</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>0.028</v>
+        <v>0.071</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="J4" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>446</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5">
@@ -1146,36 +1155,36 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="E5" t="s">
         <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>139</v>
+        <v>222.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.018</v>
+        <v>0.028</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>29.75</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>5.16</v>
+        <v>0.72</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>279</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
@@ -1184,36 +1193,36 @@
         <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E6" t="s">
         <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>361</v>
+        <v>139</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003</v>
+        <v>0.018</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>42.9</v>
+        <v>29.75</v>
       </c>
       <c r="J6" t="n">
-        <v>9.48</v>
+        <v>5.16</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>723</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
@@ -1222,36 +1231,36 @@
         <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="s">
         <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>90.5</v>
+        <v>361</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04</v>
+        <v>0.003</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>44.02</v>
+        <v>42.9</v>
       </c>
       <c r="J7" t="n">
-        <v>20.16</v>
+        <v>9.48</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>182</v>
+        <v>723</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
@@ -1260,36 +1269,36 @@
         <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E8" t="s">
         <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>60.5</v>
+        <v>90.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.054</v>
+        <v>0.04</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>2.91</v>
+        <v>44.02</v>
       </c>
       <c r="J8" t="n">
-        <v>7.8</v>
+        <v>20.16</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>122</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>36</v>
@@ -1298,36 +1307,36 @@
         <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
       </c>
       <c r="F9" t="n">
-        <v>90</v>
+        <v>60.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01</v>
+        <v>0.054</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>1.09</v>
+        <v>2.91</v>
       </c>
       <c r="J9" t="n">
-        <v>2.04</v>
+        <v>7.8</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>39</v>
@@ -1336,22 +1345,22 @@
         <v>40</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E10" t="s">
         <v>41</v>
       </c>
       <c r="F10" t="n">
-        <v>50.5</v>
+        <v>90</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>1.89</v>
+        <v>1.09</v>
       </c>
       <c r="J10" t="n">
         <v>2.04</v>
@@ -1360,7 +1369,7 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>102</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -1374,31 +1383,31 @@
         <v>43</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>630</v>
+        <v>50.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.014</v>
+        <v>0.03</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>0.77</v>
+        <v>1.89</v>
       </c>
       <c r="J11" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1261</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -1412,22 +1421,22 @@
         <v>46</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="E12" t="s">
         <v>47</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>630</v>
       </c>
       <c r="G12" t="n">
-        <v>0.039</v>
+        <v>0.014</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08</v>
+        <v>0.77</v>
       </c>
       <c r="J12" t="n">
         <v>0.96</v>
@@ -1436,12 +1445,12 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>81</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>48</v>
@@ -1456,30 +1465,30 @@
         <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>276.5</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>0.013</v>
+        <v>0.039</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>8.81</v>
+        <v>0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>0.96</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>554</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>51</v>
@@ -1488,36 +1497,36 @@
         <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E14" t="s">
         <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>326.5</v>
+        <v>276.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.003</v>
+        <v>0.013</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>1.05</v>
+        <v>8.81</v>
       </c>
       <c r="J14" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>654</v>
+        <v>554</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
         <v>54</v>
@@ -1526,31 +1535,31 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E15" t="s">
         <v>56</v>
       </c>
       <c r="F15" t="n">
-        <v>93</v>
+        <v>326.5</v>
       </c>
       <c r="G15" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>2.91</v>
+        <v>1.05</v>
       </c>
       <c r="J15" t="n">
-        <v>2.52</v>
+        <v>3.12</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>187</v>
+        <v>654</v>
       </c>
     </row>
     <row r="16">
@@ -1564,31 +1573,31 @@
         <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>6.5</v>
+        <v>0.3</v>
       </c>
       <c r="E16" t="s">
         <v>59</v>
       </c>
       <c r="F16" t="n">
-        <v>374.5</v>
+        <v>93</v>
       </c>
       <c r="G16" t="n">
-        <v>0.019</v>
+        <v>0.005</v>
       </c>
       <c r="H16" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>1.01</v>
+        <v>2.91</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8</v>
+        <v>2.52</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>750</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17">
@@ -1596,42 +1605,42 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
         <v>61</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E17" t="s">
         <v>62</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="F17" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="H17" t="s">
         <v>63</v>
       </c>
-      <c r="F17" t="n">
-        <v>370</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="H17" t="s">
-        <v>16</v>
-      </c>
       <c r="I17" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="J17" t="n">
-        <v>1.56</v>
+        <v>4.8</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>371</v>
+        <v>750</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
         <v>64</v>
@@ -1640,36 +1649,36 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E18" t="s">
         <v>66</v>
       </c>
       <c r="F18" t="n">
-        <v>127</v>
+        <v>370</v>
       </c>
       <c r="G18" t="n">
-        <v>0.129</v>
+        <v>0.002</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>4.49</v>
+        <v>1.99</v>
       </c>
       <c r="J18" t="n">
-        <v>4.68</v>
+        <v>1.56</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>128</v>
+        <v>371</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
         <v>67</v>
@@ -1684,30 +1693,30 @@
         <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>322</v>
+        <v>127</v>
       </c>
       <c r="G19" t="n">
-        <v>0.004</v>
+        <v>0.129</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.43</v>
+        <v>4.49</v>
       </c>
       <c r="J19" t="n">
-        <v>2.52</v>
+        <v>4.68</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>323</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
         <v>70</v>
@@ -1722,25 +1731,25 @@
         <v>72</v>
       </c>
       <c r="F20" t="n">
-        <v>112</v>
+        <v>322</v>
       </c>
       <c r="G20" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>0.18</v>
+        <v>0.43</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>2.52</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>113</v>
+        <v>323</v>
       </c>
     </row>
     <row r="21">
@@ -1754,36 +1763,36 @@
         <v>74</v>
       </c>
       <c r="D21" t="n">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
       <c r="E21" t="s">
         <v>75</v>
       </c>
       <c r="F21" t="n">
-        <v>412</v>
+        <v>112</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="H21" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="I21" t="n">
-        <v>1.91</v>
+        <v>0.18</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>413</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
         <v>76</v>
@@ -1792,31 +1801,31 @@
         <v>77</v>
       </c>
       <c r="D22" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="E22" t="s">
         <v>78</v>
       </c>
       <c r="F22" t="n">
-        <v>805</v>
+        <v>412</v>
       </c>
       <c r="G22" t="n">
-        <v>0.078</v>
+        <v>0.02</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="I22" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="J22" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>831</v>
+        <v>413</v>
       </c>
     </row>
     <row r="23">
@@ -1830,74 +1839,74 @@
         <v>80</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="E23" t="s">
         <v>81</v>
       </c>
       <c r="F23" t="n">
-        <v>166</v>
+        <v>805</v>
       </c>
       <c r="G23" t="n">
-        <v>0.006</v>
+        <v>0.078</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.49</v>
+        <v>2.02</v>
       </c>
       <c r="J23" t="n">
-        <v>0.72</v>
+        <v>2.16</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>332</v>
+        <v>831</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
         <v>82</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>83</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E24" t="s">
         <v>84</v>
       </c>
-      <c r="D24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E24" t="s">
-        <v>85</v>
-      </c>
       <c r="F24" t="n">
-        <v>1298</v>
+        <v>166</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>2.18</v>
+        <v>0.49</v>
       </c>
       <c r="J24" t="n">
-        <v>2.04</v>
+        <v>0.72</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>2601</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
         <v>86</v>
@@ -1912,30 +1921,30 @@
         <v>88</v>
       </c>
       <c r="F25" t="n">
-        <v>864</v>
+        <v>1298</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
       </c>
       <c r="I25" t="n">
-        <v>0.61</v>
+        <v>2.18</v>
       </c>
       <c r="J25" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1732</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B26" t="s">
         <v>89</v>
@@ -1944,36 +1953,36 @@
         <v>90</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E26" t="s">
         <v>91</v>
       </c>
       <c r="F26" t="n">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G26" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>1.29</v>
+        <v>0.61</v>
       </c>
       <c r="J26" t="n">
-        <v>1.8</v>
+        <v>0.96</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1729</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B27" t="s">
         <v>92</v>
@@ -1982,13 +1991,13 @@
         <v>93</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E27" t="s">
         <v>94</v>
       </c>
       <c r="F27" t="n">
-        <v>462</v>
+        <v>862</v>
       </c>
       <c r="G27" t="n">
         <v>0.005</v>
@@ -1997,21 +2006,21 @@
         <v>16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.11</v>
+        <v>1.29</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>929</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B28" t="s">
         <v>95</v>
@@ -2020,36 +2029,36 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E28" t="s">
         <v>97</v>
       </c>
       <c r="F28" t="n">
-        <v>83</v>
+        <v>462</v>
       </c>
       <c r="G28" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="J28" t="n">
-        <v>0.84</v>
+        <v>0.6</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>168</v>
+        <v>929</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="B29" t="s">
         <v>98</v>
@@ -2058,36 +2067,36 @@
         <v>99</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="G29" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
       </c>
       <c r="I29" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="J29" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>217</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
         <v>101</v>
@@ -2096,36 +2105,36 @@
         <v>102</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E30" t="s">
         <v>103</v>
       </c>
       <c r="F30" t="n">
-        <v>349</v>
+        <v>216</v>
       </c>
       <c r="G30" t="n">
-        <v>0.129</v>
+        <v>0.005</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>0.76</v>
+        <v>0.44</v>
       </c>
       <c r="J30" t="n">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>346</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
         <v>104</v>
@@ -2140,30 +2149,30 @@
         <v>106</v>
       </c>
       <c r="F31" t="n">
-        <v>69</v>
+        <v>349</v>
       </c>
       <c r="G31" t="n">
-        <v>0.025</v>
+        <v>0.129</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>0.03</v>
+        <v>0.76</v>
       </c>
       <c r="J31" t="n">
-        <v>0.24</v>
+        <v>1.08</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>70</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="B32" t="s">
         <v>107</v>
@@ -2172,36 +2181,36 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E32" t="s">
         <v>109</v>
       </c>
       <c r="F32" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="G32" t="n">
-        <v>0.012</v>
+        <v>0.025</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>0.75</v>
+        <v>0.03</v>
       </c>
       <c r="J32" t="n">
-        <v>2.4</v>
+        <v>0.24</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
         <v>110</v>
@@ -2210,36 +2219,36 @@
         <v>111</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E33" t="s">
         <v>112</v>
       </c>
       <c r="F33" t="n">
-        <v>438</v>
+        <v>101</v>
       </c>
       <c r="G33" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
       </c>
       <c r="I33" t="n">
-        <v>0.12</v>
+        <v>0.75</v>
       </c>
       <c r="J33" t="n">
-        <v>0.36</v>
+        <v>2.4</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>435</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
         <v>113</v>
@@ -2248,36 +2257,36 @@
         <v>114</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E34" t="s">
         <v>115</v>
       </c>
       <c r="F34" t="n">
-        <v>336</v>
+        <v>438</v>
       </c>
       <c r="G34" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
       </c>
       <c r="I34" t="n">
-        <v>9.49</v>
+        <v>0.12</v>
       </c>
       <c r="J34" t="n">
-        <v>5.4</v>
+        <v>0.36</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>337</v>
+        <v>435</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
         <v>116</v>
@@ -2286,36 +2295,36 @@
         <v>117</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E35" t="s">
         <v>118</v>
       </c>
       <c r="F35" t="n">
-        <v>193</v>
+        <v>336</v>
       </c>
       <c r="G35" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
       </c>
       <c r="I35" t="n">
-        <v>5.68</v>
+        <v>9.49</v>
       </c>
       <c r="J35" t="n">
-        <v>3.96</v>
+        <v>5.4</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>192</v>
+        <v>337</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
         <v>119</v>
@@ -2330,30 +2339,30 @@
         <v>121</v>
       </c>
       <c r="F36" t="n">
-        <v>281</v>
+        <v>193</v>
       </c>
       <c r="G36" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>0.68</v>
+        <v>5.68</v>
       </c>
       <c r="J36" t="n">
-        <v>1.2</v>
+        <v>3.96</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>282</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
         <v>122</v>
@@ -2362,36 +2371,36 @@
         <v>123</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E37" t="s">
         <v>124</v>
       </c>
       <c r="F37" t="n">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="G37" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
       </c>
       <c r="I37" t="n">
-        <v>2.38</v>
+        <v>0.68</v>
       </c>
       <c r="J37" t="n">
-        <v>3.36</v>
+        <v>1.2</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>331</v>
+        <v>282</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
         <v>125</v>
@@ -2400,36 +2409,36 @@
         <v>126</v>
       </c>
       <c r="D38" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="E38" t="s">
         <v>127</v>
       </c>
       <c r="F38" t="n">
-        <v>96</v>
+        <v>332</v>
       </c>
       <c r="G38" t="n">
-        <v>0.082</v>
+        <v>0.006</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
       </c>
       <c r="I38" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="J38" t="n">
-        <v>8.76</v>
+        <v>3.36</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>95</v>
+        <v>331</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
         <v>128</v>
@@ -2438,36 +2447,36 @@
         <v>129</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="E39" t="s">
         <v>130</v>
       </c>
       <c r="F39" t="n">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="G39" t="n">
-        <v>0.122</v>
+        <v>0.082</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="J39" t="n">
-        <v>3.36</v>
+        <v>8.76</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>27</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
         <v>131</v>
@@ -2476,36 +2485,36 @@
         <v>132</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E40" t="s">
         <v>133</v>
       </c>
       <c r="F40" t="n">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="G40" t="n">
-        <v>0.015</v>
+        <v>0.122</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
       </c>
       <c r="I40" t="n">
-        <v>0.93</v>
+        <v>1.72</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>78</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
         <v>134</v>
@@ -2514,36 +2523,36 @@
         <v>135</v>
       </c>
       <c r="D41" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E41" t="s">
         <v>136</v>
       </c>
       <c r="F41" t="n">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="G41" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
       </c>
       <c r="I41" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="J41" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>213</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
         <v>137</v>
@@ -2558,30 +2567,30 @@
         <v>139</v>
       </c>
       <c r="F42" t="n">
-        <v>46</v>
+        <v>214</v>
       </c>
       <c r="G42" t="n">
-        <v>0.021</v>
+        <v>0.005</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="J42" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>47</v>
+        <v>213</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
         <v>140</v>
@@ -2590,36 +2599,36 @@
         <v>141</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E43" t="s">
         <v>142</v>
       </c>
       <c r="F43" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="G43" t="n">
-        <v>0.097</v>
+        <v>0.021</v>
       </c>
       <c r="H43" t="s">
         <v>16</v>
       </c>
       <c r="I43" t="n">
-        <v>3.46</v>
+        <v>0.52</v>
       </c>
       <c r="J43" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
         <v>143</v>
@@ -2628,36 +2637,36 @@
         <v>144</v>
       </c>
       <c r="D44" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E44" t="s">
         <v>145</v>
       </c>
       <c r="F44" t="n">
-        <v>337</v>
+        <v>7</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01</v>
+        <v>0.097</v>
       </c>
       <c r="H44" t="s">
         <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>6.39</v>
+        <v>3.46</v>
       </c>
       <c r="J44" t="n">
-        <v>10.92</v>
+        <v>6.6</v>
       </c>
       <c r="K44" t="b">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>336</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
         <v>146</v>
@@ -2666,36 +2675,36 @@
         <v>147</v>
       </c>
       <c r="D45" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E45" t="s">
         <v>148</v>
       </c>
       <c r="F45" t="n">
-        <v>41</v>
+        <v>337</v>
       </c>
       <c r="G45" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
       </c>
       <c r="I45" t="n">
-        <v>1.79</v>
+        <v>6.39</v>
       </c>
       <c r="J45" t="n">
-        <v>3.36</v>
+        <v>10.92</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>42</v>
+        <v>336</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="B46" t="s">
         <v>149</v>
@@ -2704,36 +2713,36 @@
         <v>150</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E46" t="s">
         <v>151</v>
       </c>
       <c r="F46" t="n">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="G46" t="n">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
       </c>
       <c r="I46" t="n">
-        <v>1.34</v>
+        <v>1.79</v>
       </c>
       <c r="J46" t="n">
-        <v>1.2</v>
+        <v>3.36</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
         <v>152</v>
@@ -2748,30 +2757,30 @@
         <v>154</v>
       </c>
       <c r="F47" t="n">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="G47" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
       </c>
       <c r="I47" t="n">
-        <v>0.03</v>
+        <v>1.34</v>
       </c>
       <c r="J47" t="n">
-        <v>0.36</v>
+        <v>1.2</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>135</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
         <v>155</v>
@@ -2786,30 +2795,30 @@
         <v>157</v>
       </c>
       <c r="F48" t="n">
-        <v>720</v>
+        <v>134</v>
       </c>
       <c r="G48" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
       </c>
       <c r="I48" t="n">
-        <v>4.71</v>
+        <v>0.03</v>
       </c>
       <c r="J48" t="n">
-        <v>8.04</v>
+        <v>0.36</v>
       </c>
       <c r="K48" t="b">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>717</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
         <v>158</v>
@@ -2824,30 +2833,30 @@
         <v>160</v>
       </c>
       <c r="F49" t="n">
-        <v>773</v>
+        <v>720</v>
       </c>
       <c r="G49" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
       </c>
       <c r="I49" t="n">
-        <v>0.37</v>
+        <v>4.71</v>
       </c>
       <c r="J49" t="n">
-        <v>1.56</v>
+        <v>8.04</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>774</v>
+        <v>717</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
         <v>161</v>
@@ -2856,36 +2865,36 @@
         <v>162</v>
       </c>
       <c r="D50" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E50" t="s">
         <v>163</v>
       </c>
       <c r="F50" t="n">
-        <v>735</v>
+        <v>773</v>
       </c>
       <c r="G50" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H50" t="s">
         <v>16</v>
       </c>
       <c r="I50" t="n">
-        <v>0.69</v>
+        <v>0.37</v>
       </c>
       <c r="J50" t="n">
-        <v>3.24</v>
+        <v>1.56</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>734</v>
+        <v>774</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
         <v>164</v>
@@ -2894,13 +2903,13 @@
         <v>165</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E51" t="s">
         <v>166</v>
       </c>
       <c r="F51" t="n">
-        <v>1100</v>
+        <v>735</v>
       </c>
       <c r="G51" t="n">
         <v>0.002</v>
@@ -2909,21 +2918,21 @@
         <v>16</v>
       </c>
       <c r="I51" t="n">
-        <v>6.45</v>
+        <v>0.69</v>
       </c>
       <c r="J51" t="n">
-        <v>14.4</v>
+        <v>3.24</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>1097</v>
+        <v>734</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
         <v>167</v>
@@ -2932,36 +2941,36 @@
         <v>168</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E52" t="s">
         <v>169</v>
       </c>
       <c r="F52" t="n">
-        <v>498</v>
+        <v>1100</v>
       </c>
       <c r="G52" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="H52" t="s">
         <v>16</v>
       </c>
       <c r="I52" t="n">
-        <v>1.38</v>
+        <v>6.45</v>
       </c>
       <c r="J52" t="n">
-        <v>3</v>
+        <v>14.4</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>495</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
         <v>170</v>
@@ -2970,36 +2979,36 @@
         <v>171</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E53" t="s">
         <v>172</v>
       </c>
       <c r="F53" t="n">
-        <v>257</v>
+        <v>498</v>
       </c>
       <c r="G53" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="H53" t="s">
         <v>16</v>
       </c>
       <c r="I53" t="n">
-        <v>6.15</v>
+        <v>1.38</v>
       </c>
       <c r="J53" t="n">
-        <v>9.48</v>
+        <v>3</v>
       </c>
       <c r="K53" t="b">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>258</v>
+        <v>495</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
         <v>173</v>
@@ -3008,36 +3017,36 @@
         <v>174</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E54" t="s">
         <v>175</v>
       </c>
       <c r="F54" t="n">
-        <v>458</v>
+        <v>257</v>
       </c>
       <c r="G54" t="n">
-        <v>0.059</v>
+        <v>0.003</v>
       </c>
       <c r="H54" t="s">
         <v>16</v>
       </c>
       <c r="I54" t="n">
-        <v>2.47</v>
+        <v>6.15</v>
       </c>
       <c r="J54" t="n">
-        <v>7.2</v>
+        <v>9.48</v>
       </c>
       <c r="K54" t="b">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>453</v>
+        <v>258</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B55" t="s">
         <v>176</v>
@@ -3052,30 +3061,30 @@
         <v>178</v>
       </c>
       <c r="F55" t="n">
-        <v>923</v>
+        <v>458</v>
       </c>
       <c r="G55" t="n">
-        <v>0.002</v>
+        <v>0.059</v>
       </c>
       <c r="H55" t="s">
         <v>16</v>
       </c>
       <c r="I55" t="n">
-        <v>3.76</v>
+        <v>2.47</v>
       </c>
       <c r="J55" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="K55" t="b">
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>918</v>
+        <v>453</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B56" t="s">
         <v>179</v>
@@ -3084,36 +3093,36 @@
         <v>180</v>
       </c>
       <c r="D56" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E56" t="s">
         <v>181</v>
       </c>
       <c r="F56" t="n">
-        <v>1012</v>
+        <v>923</v>
       </c>
       <c r="G56" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H56" t="s">
         <v>16</v>
       </c>
       <c r="I56" t="n">
-        <v>0.08</v>
+        <v>3.76</v>
       </c>
       <c r="J56" t="n">
-        <v>0.72</v>
+        <v>5.4</v>
       </c>
       <c r="K56" t="b">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>1211</v>
+        <v>918</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
         <v>182</v>
@@ -3122,30 +3131,68 @@
         <v>183</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E57" t="s">
         <v>184</v>
       </c>
       <c r="F57" t="n">
+        <v>1012</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H57" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K57" t="b">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" t="s">
+        <v>185</v>
+      </c>
+      <c r="C58" t="s">
+        <v>186</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>187</v>
+      </c>
+      <c r="F58" t="n">
         <v>344.5</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G58" t="n">
         <v>0.002</v>
       </c>
-      <c r="H57" t="s">
-        <v>16</v>
-      </c>
-      <c r="I57" t="n">
+      <c r="H58" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" t="n">
         <v>0.32</v>
       </c>
-      <c r="J57" t="n">
+      <c r="J58" t="n">
         <v>2.04</v>
       </c>
-      <c r="K57" t="b">
-        <v>1</v>
-      </c>
-      <c r="L57" t="n">
+      <c r="K58" t="b">
+        <v>1</v>
+      </c>
+      <c r="L58" t="n">
         <v>688</v>
       </c>
     </row>
@@ -3177,30 +3224,30 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
         <v>0.4</v>
@@ -3220,7 +3267,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B3" t="n">
         <v>7</v>
@@ -3243,7 +3290,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B4" t="n">
         <v>6</v>
@@ -3316,10 +3363,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C2" t="n">
         <v>374.5</v>
@@ -3331,7 +3378,7 @@
         <v>0.019</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
         <v>1.01</v>
@@ -3342,10 +3389,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C3" t="n">
         <v>412</v>
@@ -3357,7 +3404,7 @@
         <v>0.02</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
         <v>1.91</v>
@@ -3368,10 +3415,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C4" t="n">
         <v>96</v>
@@ -3394,10 +3441,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C5" t="n">
         <v>630</v>
@@ -3420,10 +3467,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>1368.5</v>
@@ -3438,7 +3485,7 @@
         <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>1.08</v>
+        <v>7.08</v>
       </c>
       <c r="H6" t="n">
         <v>1.44</v>
@@ -3446,10 +3493,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C7" t="n">
         <v>805</v>
@@ -3472,10 +3519,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
         <v>222.5</v>
@@ -3498,10 +3545,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C9" t="n">
         <v>862</v>
@@ -3524,10 +3571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C10" t="n">
         <v>1298</v>
@@ -3550,10 +3597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C11" t="n">
         <v>864</v>
@@ -3576,10 +3623,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C12" t="n">
         <v>83</v>
@@ -3602,10 +3649,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C13" t="n">
         <v>735</v>
@@ -3628,42 +3675,42 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>216</v>
+        <v>105.5</v>
       </c>
       <c r="D14" t="n">
         <v>0.7</v>
       </c>
       <c r="E14" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.44</v>
+        <v>3.72</v>
       </c>
       <c r="H14" t="n">
-        <v>0.96</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C15" t="n">
-        <v>462</v>
+        <v>216</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E15" t="n">
         <v>0.005</v>
@@ -3672,73 +3719,73 @@
         <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C16" t="n">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="D16" t="n">
         <v>0.6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="H16" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C17" t="n">
-        <v>361</v>
+        <v>438</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>42.9</v>
+        <v>0.12</v>
       </c>
       <c r="H17" t="n">
-        <v>9.48</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C18" t="n">
-        <v>326.5</v>
+        <v>361</v>
       </c>
       <c r="D18" t="n">
         <v>0.5</v>
@@ -3750,88 +3797,88 @@
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>1.05</v>
+        <v>42.9</v>
       </c>
       <c r="H18" t="n">
-        <v>3.12</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C19" t="n">
-        <v>370</v>
+        <v>326.5</v>
       </c>
       <c r="D19" t="n">
         <v>0.5</v>
       </c>
       <c r="E19" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>1.99</v>
+        <v>1.05</v>
       </c>
       <c r="H19" t="n">
-        <v>1.56</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="C20" t="n">
-        <v>166</v>
+        <v>370</v>
       </c>
       <c r="D20" t="n">
         <v>0.5</v>
       </c>
       <c r="E20" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>0.49</v>
+        <v>1.99</v>
       </c>
       <c r="H20" t="n">
-        <v>0.72</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="C21" t="n">
-        <v>26</v>
+        <v>166</v>
       </c>
       <c r="D21" t="n">
         <v>0.5</v>
       </c>
       <c r="E21" t="n">
-        <v>0.122</v>
+        <v>0.006</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>1.72</v>
+        <v>0.49</v>
       </c>
       <c r="H21" t="n">
-        <v>3.36</v>
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="174">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -67,18 +67,6 @@
     <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
   </si>
   <si>
-    <t xml:space="preserve">Wasserstraße_Springorum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/05/30 05:52:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/05/31 04:40:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/05/30 09:54:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026/05/13 13:08:00</t>
   </si>
   <si>
@@ -88,15 +76,6 @@
     <t xml:space="preserve">2026/05/13 13:13:30</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/05/13 08:08:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/05/13 11:51:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/05/13 08:40:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026/05/11 06:13:00</t>
   </si>
   <si>
@@ -151,15 +130,6 @@
     <t xml:space="preserve">2026/03/29 22:44:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/03/29 11:16:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/29 21:46:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/29 12:47:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026/03/14 08:47:00</t>
   </si>
   <si>
@@ -196,18 +166,6 @@
     <t xml:space="preserve">2026/03/11 14:14:30</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/03/11 05:51:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/11 12:06:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03/11 11:31:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regenereignis / Natürlich</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026/02/23 21:56:00</t>
   </si>
   <si>
@@ -242,24 +200,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026/02/19 11:08:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/02/19 04:48:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/02/19 11:40:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/02/19 08:24:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/02/18 13:27:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/02/19 02:52:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/02/18 13:41:00</t>
   </si>
   <si>
     <t xml:space="preserve">2026/02/16 13:26:00</t>
@@ -643,8 +583,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L58" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L58"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L52" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L52"/>
   <tableColumns count="12">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -664,8 +604,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:G4" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:G4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:G3" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:G3"/>
   <tableColumns count="7">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="Ereignisse"/>
@@ -978,7 +918,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="23.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="19.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="19.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
@@ -1070,40 +1010,40 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
       <c r="F3" t="n">
-        <v>1368.5</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005</v>
+        <v>0.071</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>7.08</v>
+        <v>1.15</v>
       </c>
       <c r="J3" t="n">
-        <v>1.44</v>
+        <v>0.84</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>2738</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4">
@@ -1111,75 +1051,75 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="G4" t="n">
-        <v>0.071</v>
+        <v>0.018</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>1.15</v>
+        <v>29.75</v>
       </c>
       <c r="J4" t="n">
-        <v>0.84</v>
+        <v>5.16</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>101</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
       <c r="F5" t="n">
-        <v>222.5</v>
+        <v>361</v>
       </c>
       <c r="G5" t="n">
-        <v>0.028</v>
+        <v>0.003</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>42.9</v>
       </c>
       <c r="J5" t="n">
-        <v>0.72</v>
+        <v>9.48</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>446</v>
+        <v>723</v>
       </c>
     </row>
     <row r="6">
@@ -1187,37 +1127,37 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E6" t="s">
-        <v>29</v>
-      </c>
       <c r="F6" t="n">
-        <v>139</v>
+        <v>90.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.018</v>
+        <v>0.04</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>29.75</v>
+        <v>44.02</v>
       </c>
       <c r="J6" t="n">
-        <v>5.16</v>
+        <v>20.16</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>279</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7">
@@ -1225,37 +1165,37 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" t="s">
         <v>31</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
-      </c>
       <c r="F7" t="n">
-        <v>361</v>
+        <v>60.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003</v>
+        <v>0.054</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>42.9</v>
+        <v>2.91</v>
       </c>
       <c r="J7" t="n">
-        <v>9.48</v>
+        <v>7.8</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>723</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8">
@@ -1263,37 +1203,37 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
         <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
       </c>
       <c r="D8" t="n">
         <v>0.4</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F8" t="n">
-        <v>90.5</v>
+        <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>44.02</v>
+        <v>1.09</v>
       </c>
       <c r="J8" t="n">
-        <v>20.16</v>
+        <v>2.04</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9">
@@ -1301,37 +1241,37 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
         <v>36</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
       </c>
       <c r="D9" t="n">
         <v>0.3</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F9" t="n">
-        <v>60.5</v>
+        <v>50.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.054</v>
+        <v>0.03</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>2.91</v>
+        <v>1.89</v>
       </c>
       <c r="J9" t="n">
-        <v>7.8</v>
+        <v>2.04</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>122</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
@@ -1339,37 +1279,37 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E10" t="s">
         <v>40</v>
       </c>
-      <c r="D10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
       <c r="F10" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01</v>
+        <v>0.039</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>1.09</v>
+        <v>0.08</v>
       </c>
       <c r="J10" t="n">
-        <v>2.04</v>
+        <v>0.96</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>181</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11">
@@ -1377,75 +1317,75 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
         <v>42</v>
-      </c>
-      <c r="C11" t="s">
-        <v>43</v>
       </c>
       <c r="D11" t="n">
         <v>0.3</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
-        <v>50.5</v>
+        <v>276.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03</v>
+        <v>0.013</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>1.89</v>
+        <v>8.81</v>
       </c>
       <c r="J11" t="n">
-        <v>2.04</v>
+        <v>4.2</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>102</v>
+        <v>554</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s">
         <v>45</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="s">
         <v>46</v>
       </c>
-      <c r="D12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E12" t="s">
-        <v>47</v>
-      </c>
       <c r="F12" t="n">
-        <v>630</v>
+        <v>326.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.014</v>
+        <v>0.003</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>0.77</v>
+        <v>1.05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.96</v>
+        <v>3.12</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1261</v>
+        <v>654</v>
       </c>
     </row>
     <row r="13">
@@ -1453,37 +1393,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
         <v>48</v>
-      </c>
-      <c r="C13" t="s">
-        <v>49</v>
       </c>
       <c r="D13" t="n">
         <v>0.3</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="G13" t="n">
-        <v>0.039</v>
+        <v>0.005</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08</v>
+        <v>2.91</v>
       </c>
       <c r="J13" t="n">
-        <v>0.96</v>
+        <v>2.52</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>81</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14">
@@ -1491,37 +1431,37 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
         <v>51</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E14" t="s">
         <v>52</v>
       </c>
-      <c r="D14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E14" t="s">
-        <v>53</v>
-      </c>
       <c r="F14" t="n">
-        <v>276.5</v>
+        <v>370</v>
       </c>
       <c r="G14" t="n">
-        <v>0.013</v>
+        <v>0.002</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>8.81</v>
+        <v>1.99</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>1.56</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>554</v>
+        <v>371</v>
       </c>
     </row>
     <row r="15">
@@ -1529,37 +1469,37 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" t="s">
         <v>54</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E15" t="s">
         <v>55</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>56</v>
-      </c>
       <c r="F15" t="n">
-        <v>326.5</v>
+        <v>127</v>
       </c>
       <c r="G15" t="n">
-        <v>0.003</v>
+        <v>0.129</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>1.05</v>
+        <v>4.49</v>
       </c>
       <c r="J15" t="n">
-        <v>3.12</v>
+        <v>4.68</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>654</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16">
@@ -1567,28 +1507,28 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
         <v>57</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E16" t="s">
         <v>58</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E16" t="s">
-        <v>59</v>
-      </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>322</v>
       </c>
       <c r="G16" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>2.91</v>
+        <v>0.43</v>
       </c>
       <c r="J16" t="n">
         <v>2.52</v>
@@ -1597,45 +1537,45 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>187</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
         <v>60</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E17" t="s">
         <v>61</v>
       </c>
-      <c r="D17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E17" t="s">
-        <v>62</v>
-      </c>
       <c r="F17" t="n">
-        <v>374.5</v>
+        <v>112</v>
       </c>
       <c r="G17" t="n">
-        <v>0.019</v>
+        <v>0.005</v>
       </c>
       <c r="H17" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>1.01</v>
+        <v>0.18</v>
       </c>
       <c r="J17" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>750</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18">
@@ -1643,133 +1583,133 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D18" t="n">
         <v>0.5</v>
       </c>
       <c r="E18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F18" t="n">
-        <v>370</v>
+        <v>166</v>
       </c>
       <c r="G18" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>1.99</v>
+        <v>0.49</v>
       </c>
       <c r="J18" t="n">
-        <v>1.56</v>
+        <v>0.72</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>371</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
         <v>67</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E19" t="s">
         <v>68</v>
       </c>
-      <c r="D19" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E19" t="s">
-        <v>69</v>
-      </c>
       <c r="F19" t="n">
-        <v>127</v>
+        <v>1298</v>
       </c>
       <c r="G19" t="n">
-        <v>0.129</v>
+        <v>0.001</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
       </c>
       <c r="I19" t="n">
-        <v>4.49</v>
+        <v>2.18</v>
       </c>
       <c r="J19" t="n">
-        <v>4.68</v>
+        <v>2.04</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>128</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
         <v>70</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E20" t="s">
         <v>71</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E20" t="s">
-        <v>72</v>
-      </c>
       <c r="F20" t="n">
-        <v>322</v>
+        <v>864</v>
       </c>
       <c r="G20" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>0.43</v>
+        <v>0.61</v>
       </c>
       <c r="J20" t="n">
-        <v>2.52</v>
+        <v>0.96</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>323</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" t="s">
         <v>73</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E21" t="s">
         <v>74</v>
       </c>
-      <c r="D21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E21" t="s">
-        <v>75</v>
-      </c>
       <c r="F21" t="n">
-        <v>112</v>
+        <v>862</v>
       </c>
       <c r="G21" t="n">
         <v>0.005</v>
@@ -1778,92 +1718,92 @@
         <v>16</v>
       </c>
       <c r="I21" t="n">
-        <v>0.18</v>
+        <v>1.29</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>113</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" t="s">
         <v>76</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E22" t="s">
         <v>77</v>
       </c>
-      <c r="D22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E22" t="s">
-        <v>78</v>
-      </c>
       <c r="F22" t="n">
-        <v>412</v>
+        <v>462</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="H22" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>1.91</v>
+        <v>0.11</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>413</v>
+        <v>929</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" t="s">
         <v>79</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E23" t="s">
         <v>80</v>
       </c>
-      <c r="D23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E23" t="s">
-        <v>81</v>
-      </c>
       <c r="F23" t="n">
-        <v>805</v>
+        <v>83</v>
       </c>
       <c r="G23" t="n">
-        <v>0.078</v>
+        <v>0.014</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>2.02</v>
+        <v>0.46</v>
       </c>
       <c r="J23" t="n">
-        <v>2.16</v>
+        <v>0.84</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>831</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24">
@@ -1871,227 +1811,227 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" t="s">
         <v>82</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E24" t="s">
         <v>83</v>
       </c>
-      <c r="D24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E24" t="s">
-        <v>84</v>
-      </c>
       <c r="F24" t="n">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="G24" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="J24" t="n">
-        <v>0.72</v>
+        <v>0.96</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>332</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" t="s">
         <v>85</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E25" t="s">
         <v>86</v>
       </c>
-      <c r="C25" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E25" t="s">
-        <v>88</v>
-      </c>
       <c r="F25" t="n">
-        <v>1298</v>
+        <v>349</v>
       </c>
       <c r="G25" t="n">
-        <v>0.001</v>
+        <v>0.129</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
       </c>
       <c r="I25" t="n">
-        <v>2.18</v>
+        <v>0.76</v>
       </c>
       <c r="J25" t="n">
-        <v>2.04</v>
+        <v>1.08</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>2601</v>
+        <v>346</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E26" t="s">
         <v>89</v>
       </c>
-      <c r="C26" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E26" t="s">
-        <v>91</v>
-      </c>
       <c r="F26" t="n">
-        <v>864</v>
+        <v>69</v>
       </c>
       <c r="G26" t="n">
-        <v>0.002</v>
+        <v>0.025</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>0.61</v>
+        <v>0.03</v>
       </c>
       <c r="J26" t="n">
-        <v>0.96</v>
+        <v>0.24</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1732</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E27" t="s">
         <v>92</v>
       </c>
-      <c r="C27" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E27" t="s">
-        <v>94</v>
-      </c>
       <c r="F27" t="n">
-        <v>862</v>
+        <v>101</v>
       </c>
       <c r="G27" t="n">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
       </c>
       <c r="I27" t="n">
-        <v>1.29</v>
+        <v>0.75</v>
       </c>
       <c r="J27" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1729</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D28" t="n">
         <v>0.6</v>
       </c>
       <c r="E28" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F28" t="n">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="G28" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6</v>
+        <v>0.36</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>929</v>
+        <v>435</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E29" t="s">
         <v>98</v>
       </c>
-      <c r="C29" t="s">
-        <v>99</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E29" t="s">
-        <v>100</v>
-      </c>
       <c r="F29" t="n">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="G29" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
       </c>
       <c r="I29" t="n">
-        <v>0.46</v>
+        <v>9.49</v>
       </c>
       <c r="J29" t="n">
-        <v>0.84</v>
+        <v>5.4</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>168</v>
+        <v>337</v>
       </c>
     </row>
     <row r="30">
@@ -2099,37 +2039,37 @@
         <v>12</v>
       </c>
       <c r="B30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E30" t="s">
         <v>101</v>
       </c>
-      <c r="C30" t="s">
-        <v>102</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E30" t="s">
-        <v>103</v>
-      </c>
       <c r="F30" t="n">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="G30" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>0.44</v>
+        <v>5.68</v>
       </c>
       <c r="J30" t="n">
-        <v>0.96</v>
+        <v>3.96</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>217</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31">
@@ -2137,75 +2077,75 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E31" t="s">
         <v>104</v>
       </c>
-      <c r="C31" t="s">
-        <v>105</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E31" t="s">
-        <v>106</v>
-      </c>
       <c r="F31" t="n">
-        <v>349</v>
+        <v>281</v>
       </c>
       <c r="G31" t="n">
-        <v>0.129</v>
+        <v>0.007</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>0.76</v>
+        <v>0.68</v>
       </c>
       <c r="J31" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>346</v>
+        <v>282</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D32" t="n">
         <v>0.4</v>
       </c>
       <c r="E32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F32" t="n">
-        <v>69</v>
+        <v>332</v>
       </c>
       <c r="G32" t="n">
-        <v>0.025</v>
+        <v>0.006</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>0.03</v>
+        <v>2.38</v>
       </c>
       <c r="J32" t="n">
-        <v>0.24</v>
+        <v>3.36</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>70</v>
+        <v>331</v>
       </c>
     </row>
     <row r="33">
@@ -2213,37 +2153,37 @@
         <v>12</v>
       </c>
       <c r="B33" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E33" t="s">
         <v>110</v>
       </c>
-      <c r="C33" t="s">
-        <v>111</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E33" t="s">
-        <v>112</v>
-      </c>
       <c r="F33" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G33" t="n">
-        <v>0.012</v>
+        <v>0.082</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
       </c>
       <c r="I33" t="n">
-        <v>0.75</v>
+        <v>2.04</v>
       </c>
       <c r="J33" t="n">
-        <v>2.4</v>
+        <v>8.76</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34">
@@ -2251,37 +2191,37 @@
         <v>12</v>
       </c>
       <c r="B34" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" t="s">
+        <v>112</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E34" t="s">
         <v>113</v>
       </c>
-      <c r="C34" t="s">
-        <v>114</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E34" t="s">
-        <v>115</v>
-      </c>
       <c r="F34" t="n">
-        <v>438</v>
+        <v>26</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008</v>
+        <v>0.122</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
       </c>
       <c r="I34" t="n">
-        <v>0.12</v>
+        <v>1.72</v>
       </c>
       <c r="J34" t="n">
-        <v>0.36</v>
+        <v>3.36</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>435</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35">
@@ -2289,37 +2229,37 @@
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C35" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D35" t="n">
         <v>0.4</v>
       </c>
       <c r="E35" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F35" t="n">
-        <v>336</v>
+        <v>77</v>
       </c>
       <c r="G35" t="n">
-        <v>0.002</v>
+        <v>0.015</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
       </c>
       <c r="I35" t="n">
-        <v>9.49</v>
+        <v>0.93</v>
       </c>
       <c r="J35" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>337</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36">
@@ -2327,37 +2267,37 @@
         <v>12</v>
       </c>
       <c r="B36" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" t="s">
+        <v>118</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E36" t="s">
         <v>119</v>
       </c>
-      <c r="C36" t="s">
-        <v>120</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E36" t="s">
-        <v>121</v>
-      </c>
       <c r="F36" t="n">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="G36" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>5.68</v>
+        <v>0.47</v>
       </c>
       <c r="J36" t="n">
-        <v>3.96</v>
+        <v>1.2</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>192</v>
+        <v>213</v>
       </c>
     </row>
     <row r="37">
@@ -2365,37 +2305,37 @@
         <v>12</v>
       </c>
       <c r="B37" t="s">
+        <v>120</v>
+      </c>
+      <c r="C37" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E37" t="s">
         <v>122</v>
       </c>
-      <c r="C37" t="s">
-        <v>123</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E37" t="s">
-        <v>124</v>
-      </c>
       <c r="F37" t="n">
-        <v>281</v>
+        <v>46</v>
       </c>
       <c r="G37" t="n">
-        <v>0.007</v>
+        <v>0.021</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
       </c>
       <c r="I37" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="J37" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>282</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38">
@@ -2403,37 +2343,37 @@
         <v>12</v>
       </c>
       <c r="B38" t="s">
+        <v>123</v>
+      </c>
+      <c r="C38" t="s">
+        <v>124</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E38" t="s">
         <v>125</v>
       </c>
-      <c r="C38" t="s">
-        <v>126</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E38" t="s">
-        <v>127</v>
-      </c>
       <c r="F38" t="n">
-        <v>332</v>
+        <v>7</v>
       </c>
       <c r="G38" t="n">
-        <v>0.006</v>
+        <v>0.097</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
       </c>
       <c r="I38" t="n">
-        <v>2.38</v>
+        <v>3.46</v>
       </c>
       <c r="J38" t="n">
-        <v>3.36</v>
+        <v>6.6</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>331</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -2441,66 +2381,66 @@
         <v>12</v>
       </c>
       <c r="B39" t="s">
+        <v>126</v>
+      </c>
+      <c r="C39" t="s">
+        <v>127</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E39" t="s">
         <v>128</v>
       </c>
-      <c r="C39" t="s">
-        <v>129</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E39" t="s">
-        <v>130</v>
-      </c>
       <c r="F39" t="n">
-        <v>96</v>
+        <v>337</v>
       </c>
       <c r="G39" t="n">
-        <v>0.082</v>
+        <v>0.01</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>2.04</v>
+        <v>6.39</v>
       </c>
       <c r="J39" t="n">
-        <v>8.76</v>
+        <v>10.92</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>95</v>
+        <v>336</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="B40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D40" t="n">
         <v>0.5</v>
       </c>
       <c r="E40" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F40" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="G40" t="n">
-        <v>0.122</v>
+        <v>0.05</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
       </c>
       <c r="I40" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="J40" t="n">
         <v>3.36</v>
@@ -2509,7 +2449,7 @@
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41">
@@ -2517,37 +2457,37 @@
         <v>12</v>
       </c>
       <c r="B41" t="s">
+        <v>132</v>
+      </c>
+      <c r="C41" t="s">
+        <v>133</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E41" t="s">
         <v>134</v>
       </c>
-      <c r="C41" t="s">
-        <v>135</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E41" t="s">
-        <v>136</v>
-      </c>
       <c r="F41" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G41" t="n">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
       </c>
       <c r="I41" t="n">
-        <v>0.93</v>
+        <v>1.34</v>
       </c>
       <c r="J41" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42">
@@ -2555,37 +2495,37 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
+        <v>135</v>
+      </c>
+      <c r="C42" t="s">
+        <v>136</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E42" t="s">
         <v>137</v>
       </c>
-      <c r="C42" t="s">
-        <v>138</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E42" t="s">
-        <v>139</v>
-      </c>
       <c r="F42" t="n">
-        <v>214</v>
+        <v>134</v>
       </c>
       <c r="G42" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>0.47</v>
+        <v>0.03</v>
       </c>
       <c r="J42" t="n">
-        <v>1.2</v>
+        <v>0.36</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43">
@@ -2593,37 +2533,37 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
+        <v>138</v>
+      </c>
+      <c r="C43" t="s">
+        <v>139</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E43" t="s">
         <v>140</v>
       </c>
-      <c r="C43" t="s">
-        <v>141</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E43" t="s">
-        <v>142</v>
-      </c>
       <c r="F43" t="n">
-        <v>46</v>
+        <v>720</v>
       </c>
       <c r="G43" t="n">
-        <v>0.021</v>
+        <v>0.002</v>
       </c>
       <c r="H43" t="s">
         <v>16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.52</v>
+        <v>4.71</v>
       </c>
       <c r="J43" t="n">
-        <v>2.4</v>
+        <v>8.04</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>47</v>
+        <v>717</v>
       </c>
     </row>
     <row r="44">
@@ -2631,37 +2571,37 @@
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C44" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D44" t="n">
         <v>0.3</v>
       </c>
       <c r="E44" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F44" t="n">
-        <v>7</v>
+        <v>773</v>
       </c>
       <c r="G44" t="n">
-        <v>0.097</v>
+        <v>0.003</v>
       </c>
       <c r="H44" t="s">
         <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>3.46</v>
+        <v>0.37</v>
       </c>
       <c r="J44" t="n">
-        <v>6.6</v>
+        <v>1.56</v>
       </c>
       <c r="K44" t="b">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>8</v>
+        <v>774</v>
       </c>
     </row>
     <row r="45">
@@ -2669,75 +2609,75 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
+        <v>144</v>
+      </c>
+      <c r="C45" t="s">
+        <v>145</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E45" t="s">
         <v>146</v>
       </c>
-      <c r="C45" t="s">
-        <v>147</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E45" t="s">
-        <v>148</v>
-      </c>
       <c r="F45" t="n">
-        <v>337</v>
+        <v>735</v>
       </c>
       <c r="G45" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
       </c>
       <c r="I45" t="n">
-        <v>6.39</v>
+        <v>0.69</v>
       </c>
       <c r="J45" t="n">
-        <v>10.92</v>
+        <v>3.24</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>336</v>
+        <v>734</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
+        <v>147</v>
+      </c>
+      <c r="C46" t="s">
+        <v>148</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E46" t="s">
         <v>149</v>
       </c>
-      <c r="C46" t="s">
-        <v>150</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E46" t="s">
-        <v>151</v>
-      </c>
       <c r="F46" t="n">
-        <v>41</v>
+        <v>1100</v>
       </c>
       <c r="G46" t="n">
-        <v>0.05</v>
+        <v>0.002</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
       </c>
       <c r="I46" t="n">
-        <v>1.79</v>
+        <v>6.45</v>
       </c>
       <c r="J46" t="n">
-        <v>3.36</v>
+        <v>14.4</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>42</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="47">
@@ -2745,37 +2685,37 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C47" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D47" t="n">
         <v>0.3</v>
       </c>
       <c r="E47" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F47" t="n">
-        <v>81</v>
+        <v>498</v>
       </c>
       <c r="G47" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
       </c>
       <c r="I47" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="J47" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>82</v>
+        <v>495</v>
       </c>
     </row>
     <row r="48">
@@ -2783,37 +2723,37 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" t="s">
+        <v>154</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E48" t="s">
         <v>155</v>
       </c>
-      <c r="C48" t="s">
-        <v>156</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E48" t="s">
-        <v>157</v>
-      </c>
       <c r="F48" t="n">
-        <v>134</v>
+        <v>257</v>
       </c>
       <c r="G48" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
       </c>
       <c r="I48" t="n">
-        <v>0.03</v>
+        <v>6.15</v>
       </c>
       <c r="J48" t="n">
-        <v>0.36</v>
+        <v>9.48</v>
       </c>
       <c r="K48" t="b">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>135</v>
+        <v>258</v>
       </c>
     </row>
     <row r="49">
@@ -2821,37 +2761,37 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C49" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D49" t="n">
         <v>0.3</v>
       </c>
       <c r="E49" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F49" t="n">
-        <v>720</v>
+        <v>458</v>
       </c>
       <c r="G49" t="n">
-        <v>0.002</v>
+        <v>0.059</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
       </c>
       <c r="I49" t="n">
-        <v>4.71</v>
+        <v>2.47</v>
       </c>
       <c r="J49" t="n">
-        <v>8.04</v>
+        <v>7.2</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>717</v>
+        <v>453</v>
       </c>
     </row>
     <row r="50">
@@ -2859,37 +2799,37 @@
         <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C50" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D50" t="n">
         <v>0.3</v>
       </c>
       <c r="E50" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F50" t="n">
-        <v>773</v>
+        <v>923</v>
       </c>
       <c r="G50" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H50" t="s">
         <v>16</v>
       </c>
       <c r="I50" t="n">
-        <v>0.37</v>
+        <v>3.76</v>
       </c>
       <c r="J50" t="n">
-        <v>1.56</v>
+        <v>5.4</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>774</v>
+        <v>918</v>
       </c>
     </row>
     <row r="51">
@@ -2897,37 +2837,37 @@
         <v>12</v>
       </c>
       <c r="B51" t="s">
+        <v>162</v>
+      </c>
+      <c r="C51" t="s">
+        <v>163</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E51" t="s">
         <v>164</v>
       </c>
-      <c r="C51" t="s">
-        <v>165</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E51" t="s">
-        <v>166</v>
-      </c>
       <c r="F51" t="n">
-        <v>735</v>
+        <v>1012</v>
       </c>
       <c r="G51" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H51" t="s">
         <v>16</v>
       </c>
       <c r="I51" t="n">
-        <v>0.69</v>
+        <v>0.08</v>
       </c>
       <c r="J51" t="n">
-        <v>3.24</v>
+        <v>0.72</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>734</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="52">
@@ -2935,19 +2875,19 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
+        <v>165</v>
+      </c>
+      <c r="C52" t="s">
+        <v>166</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E52" t="s">
         <v>167</v>
       </c>
-      <c r="C52" t="s">
-        <v>168</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E52" t="s">
-        <v>169</v>
-      </c>
       <c r="F52" t="n">
-        <v>1100</v>
+        <v>344.5</v>
       </c>
       <c r="G52" t="n">
         <v>0.002</v>
@@ -2956,243 +2896,15 @@
         <v>16</v>
       </c>
       <c r="I52" t="n">
-        <v>6.45</v>
+        <v>0.32</v>
       </c>
       <c r="J52" t="n">
-        <v>14.4</v>
+        <v>2.04</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>12</v>
-      </c>
-      <c r="B53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C53" t="s">
-        <v>171</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E53" t="s">
-        <v>172</v>
-      </c>
-      <c r="F53" t="n">
-        <v>498</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="H53" t="s">
-        <v>16</v>
-      </c>
-      <c r="I53" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="J53" t="n">
-        <v>3</v>
-      </c>
-      <c r="K53" t="b">
-        <v>1</v>
-      </c>
-      <c r="L53" t="n">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>12</v>
-      </c>
-      <c r="B54" t="s">
-        <v>173</v>
-      </c>
-      <c r="C54" t="s">
-        <v>174</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E54" t="s">
-        <v>175</v>
-      </c>
-      <c r="F54" t="n">
-        <v>257</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="H54" t="s">
-        <v>16</v>
-      </c>
-      <c r="I54" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="J54" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="K54" t="b">
-        <v>1</v>
-      </c>
-      <c r="L54" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>12</v>
-      </c>
-      <c r="B55" t="s">
-        <v>176</v>
-      </c>
-      <c r="C55" t="s">
-        <v>177</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E55" t="s">
-        <v>178</v>
-      </c>
-      <c r="F55" t="n">
-        <v>458</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="H55" t="s">
-        <v>16</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J55" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K55" t="b">
-        <v>1</v>
-      </c>
-      <c r="L55" t="n">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>12</v>
-      </c>
-      <c r="B56" t="s">
-        <v>179</v>
-      </c>
-      <c r="C56" t="s">
-        <v>180</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E56" t="s">
-        <v>181</v>
-      </c>
-      <c r="F56" t="n">
-        <v>923</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="H56" t="s">
-        <v>16</v>
-      </c>
-      <c r="I56" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="J56" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K56" t="b">
-        <v>1</v>
-      </c>
-      <c r="L56" t="n">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>12</v>
-      </c>
-      <c r="B57" t="s">
-        <v>182</v>
-      </c>
-      <c r="C57" t="s">
-        <v>183</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E57" t="s">
-        <v>184</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1012</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="H57" t="s">
-        <v>16</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="K57" t="b">
-        <v>1</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>12</v>
-      </c>
-      <c r="B58" t="s">
-        <v>185</v>
-      </c>
-      <c r="C58" t="s">
-        <v>186</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E58" t="s">
-        <v>187</v>
-      </c>
-      <c r="F58" t="n">
-        <v>344.5</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="H58" t="s">
-        <v>16</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="K58" t="b">
-        <v>1</v>
-      </c>
-      <c r="L58" t="n">
         <v>688</v>
       </c>
     </row>
@@ -3210,7 +2922,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="23.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
@@ -3224,22 +2936,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="C1" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D1" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="E1" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="F1" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="G1" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2">
@@ -3267,7 +2979,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B3" t="n">
         <v>7</v>
@@ -3285,29 +2997,6 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3325,7 +3014,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="23.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="19.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
@@ -3363,103 +3052,103 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="C2" t="n">
-        <v>374.5</v>
+        <v>96</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="n">
-        <v>0.019</v>
+        <v>0.082</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>412</v>
+        <v>862</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="C4" t="n">
-        <v>96</v>
+        <v>1298</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.082</v>
+        <v>0.001</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H4" t="n">
         <v>2.04</v>
-      </c>
-      <c r="H4" t="n">
-        <v>8.76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C5" t="n">
-        <v>630</v>
+        <v>864</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.77</v>
+        <v>0.61</v>
       </c>
       <c r="H5" t="n">
         <v>0.96</v>
@@ -3467,94 +3156,94 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="C6" t="n">
-        <v>1368.5</v>
+        <v>83</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>7.08</v>
+        <v>0.46</v>
       </c>
       <c r="H6" t="n">
-        <v>1.44</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>805</v>
+        <v>735</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.078</v>
+        <v>0.002</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>2.02</v>
+        <v>0.69</v>
       </c>
       <c r="H7" t="n">
-        <v>2.16</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>222.5</v>
+        <v>105.5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.028</v>
+        <v>0.01</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>3.72</v>
       </c>
       <c r="H8" t="n">
-        <v>0.72</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C9" t="n">
-        <v>862</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E9" t="n">
         <v>0.005</v>
@@ -3563,88 +3252,88 @@
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>1.29</v>
+        <v>0.44</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C10" t="n">
-        <v>1298</v>
+        <v>462</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>2.18</v>
+        <v>0.11</v>
       </c>
       <c r="H10" t="n">
-        <v>2.04</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C11" t="n">
-        <v>864</v>
+        <v>438</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.61</v>
+        <v>0.12</v>
       </c>
       <c r="H11" t="n">
-        <v>0.96</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>361</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.014</v>
+        <v>0.003</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.46</v>
+        <v>42.9</v>
       </c>
       <c r="H12" t="n">
-        <v>0.84</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="13">
@@ -3652,25 +3341,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="C13" t="n">
-        <v>735</v>
+        <v>326.5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
       </c>
       <c r="G13" t="n">
-        <v>0.69</v>
+        <v>1.05</v>
       </c>
       <c r="H13" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="14">
@@ -3678,25 +3367,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C14" t="n">
-        <v>105.5</v>
+        <v>370</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>3.72</v>
+        <v>1.99</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="15">
@@ -3704,51 +3393,51 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="C15" t="n">
-        <v>216</v>
+        <v>166</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="H15" t="n">
-        <v>0.96</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C16" t="n">
-        <v>462</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>0.005</v>
+        <v>0.122</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.11</v>
+        <v>1.72</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="17">
@@ -3756,25 +3445,25 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C17" t="n">
-        <v>438</v>
+        <v>214</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E17" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.12</v>
+        <v>0.47</v>
       </c>
       <c r="H17" t="n">
-        <v>0.36</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="18">
@@ -3782,51 +3471,51 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="C18" t="n">
-        <v>361</v>
+        <v>46</v>
       </c>
       <c r="D18" t="n">
         <v>0.5</v>
       </c>
       <c r="E18" t="n">
-        <v>0.003</v>
+        <v>0.021</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>42.9</v>
+        <v>0.52</v>
       </c>
       <c r="H18" t="n">
-        <v>9.48</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>129</v>
       </c>
       <c r="C19" t="n">
-        <v>326.5</v>
+        <v>41</v>
       </c>
       <c r="D19" t="n">
         <v>0.5</v>
       </c>
       <c r="E19" t="n">
-        <v>0.003</v>
+        <v>0.05</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>1.05</v>
+        <v>1.79</v>
       </c>
       <c r="H19" t="n">
-        <v>3.12</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="20">
@@ -3834,25 +3523,25 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="C20" t="n">
-        <v>370</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002</v>
+        <v>0.071</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>1.99</v>
+        <v>1.15</v>
       </c>
       <c r="H20" t="n">
-        <v>1.56</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="21">
@@ -3860,25 +3549,25 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="C21" t="n">
-        <v>166</v>
+        <v>90.5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E21" t="n">
-        <v>0.006</v>
+        <v>0.04</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>0.49</v>
+        <v>44.02</v>
       </c>
       <c r="H21" t="n">
-        <v>0.72</v>
+        <v>20.16</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -50,6 +50,21 @@
   </si>
   <si>
     <t xml:space="preserve">points_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wasserstraße_Springorum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/06 18:56:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/06 23:48:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/06 18:59:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sturzflut-Ereignis</t>
   </si>
   <si>
     <t xml:space="preserve">An_der_Kost</t>
@@ -583,8 +598,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L52" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L52"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L53" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L53"/>
   <tableColumns count="12">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -604,8 +619,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:G3" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:G3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:G4" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:G4"/>
   <tableColumns count="7">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="Ereignisse"/>
@@ -918,7 +933,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="23.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="19.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="19.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
@@ -981,288 +996,288 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>105.5</v>
+        <v>292.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01</v>
+        <v>1.694</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>3.72</v>
+        <v>0.01</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>0.12</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>212</v>
+        <v>586</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>105.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.071</v>
+        <v>0.01</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I3" t="n">
-        <v>1.15</v>
+        <v>3.72</v>
       </c>
       <c r="J3" t="n">
-        <v>0.84</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>101</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>0.018</v>
+        <v>0.071</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I4" t="n">
-        <v>29.75</v>
+        <v>1.15</v>
       </c>
       <c r="J4" t="n">
-        <v>5.16</v>
+        <v>0.84</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>279</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>361</v>
+        <v>139</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003</v>
+        <v>0.018</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I5" t="n">
-        <v>42.9</v>
+        <v>29.75</v>
       </c>
       <c r="J5" t="n">
-        <v>9.48</v>
+        <v>5.16</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>723</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>90.5</v>
+        <v>361</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04</v>
+        <v>0.003</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I6" t="n">
-        <v>44.02</v>
+        <v>42.9</v>
       </c>
       <c r="J6" t="n">
-        <v>20.16</v>
+        <v>9.48</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>182</v>
+        <v>723</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>60.5</v>
+        <v>90.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.054</v>
+        <v>0.04</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I7" t="n">
-        <v>2.91</v>
+        <v>44.02</v>
       </c>
       <c r="J7" t="n">
-        <v>7.8</v>
+        <v>20.16</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>122</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8" t="n">
-        <v>90</v>
+        <v>60.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01</v>
+        <v>0.054</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I8" t="n">
-        <v>1.09</v>
+        <v>2.91</v>
       </c>
       <c r="J8" t="n">
-        <v>2.04</v>
+        <v>7.8</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F9" t="n">
-        <v>50.5</v>
+        <v>90</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H9" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I9" t="n">
-        <v>1.89</v>
+        <v>1.09</v>
       </c>
       <c r="J9" t="n">
         <v>2.04</v>
@@ -1271,1640 +1286,1678 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>102</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D10" t="n">
         <v>0.3</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>50.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08</v>
+        <v>1.89</v>
       </c>
       <c r="J10" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" t="n">
         <v>0.3</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>276.5</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>0.013</v>
+        <v>0.039</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I11" t="n">
-        <v>8.81</v>
+        <v>0.08</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2</v>
+        <v>0.96</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>554</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>326.5</v>
+        <v>276.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003</v>
+        <v>0.013</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I12" t="n">
-        <v>1.05</v>
+        <v>8.81</v>
       </c>
       <c r="J12" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>654</v>
+        <v>554</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F13" t="n">
-        <v>93</v>
+        <v>326.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I13" t="n">
-        <v>2.91</v>
+        <v>1.05</v>
       </c>
       <c r="J13" t="n">
-        <v>2.52</v>
+        <v>3.12</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>187</v>
+        <v>654</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F14" t="n">
-        <v>370</v>
+        <v>93</v>
       </c>
       <c r="G14" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I14" t="n">
-        <v>1.99</v>
+        <v>2.91</v>
       </c>
       <c r="J14" t="n">
-        <v>1.56</v>
+        <v>2.52</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>371</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>127</v>
+        <v>370</v>
       </c>
       <c r="G15" t="n">
-        <v>0.129</v>
+        <v>0.002</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I15" t="n">
-        <v>4.49</v>
+        <v>1.99</v>
       </c>
       <c r="J15" t="n">
-        <v>4.68</v>
+        <v>1.56</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>128</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
         <v>0.4</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F16" t="n">
-        <v>322</v>
+        <v>127</v>
       </c>
       <c r="G16" t="n">
-        <v>0.004</v>
+        <v>0.129</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I16" t="n">
-        <v>0.43</v>
+        <v>4.49</v>
       </c>
       <c r="J16" t="n">
-        <v>2.52</v>
+        <v>4.68</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>323</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>0.4</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F17" t="n">
-        <v>112</v>
+        <v>322</v>
       </c>
       <c r="G17" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I17" t="n">
-        <v>0.18</v>
+        <v>0.43</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>2.52</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>113</v>
+        <v>323</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F18" t="n">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="G18" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I18" t="n">
-        <v>0.49</v>
+        <v>0.18</v>
       </c>
       <c r="J18" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>332</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>1298</v>
+        <v>166</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I19" t="n">
-        <v>2.18</v>
+        <v>0.49</v>
       </c>
       <c r="J19" t="n">
-        <v>2.04</v>
+        <v>0.72</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>2601</v>
+        <v>332</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D20" t="n">
         <v>0.8</v>
       </c>
       <c r="E20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F20" t="n">
-        <v>864</v>
+        <v>1298</v>
       </c>
       <c r="G20" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I20" t="n">
-        <v>0.61</v>
+        <v>2.18</v>
       </c>
       <c r="J20" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1732</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F21" t="n">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G21" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I21" t="n">
-        <v>1.29</v>
+        <v>0.61</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8</v>
+        <v>0.96</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1729</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F22" t="n">
-        <v>462</v>
+        <v>862</v>
       </c>
       <c r="G22" t="n">
         <v>0.005</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I22" t="n">
-        <v>0.11</v>
+        <v>1.29</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>929</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F23" t="n">
-        <v>83</v>
+        <v>462</v>
       </c>
       <c r="G23" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I23" t="n">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="J23" t="n">
-        <v>0.84</v>
+        <v>0.6</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>168</v>
+        <v>929</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" t="n">
         <v>83</v>
       </c>
-      <c r="F24" t="n">
-        <v>216</v>
-      </c>
       <c r="G24" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I24" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="J24" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>217</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F25" t="n">
-        <v>349</v>
+        <v>216</v>
       </c>
       <c r="G25" t="n">
-        <v>0.129</v>
+        <v>0.005</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I25" t="n">
-        <v>0.76</v>
+        <v>0.44</v>
       </c>
       <c r="J25" t="n">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>346</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D26" t="n">
         <v>0.4</v>
       </c>
       <c r="E26" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F26" t="n">
-        <v>69</v>
+        <v>349</v>
       </c>
       <c r="G26" t="n">
-        <v>0.025</v>
+        <v>0.129</v>
       </c>
       <c r="H26" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I26" t="n">
-        <v>0.03</v>
+        <v>0.76</v>
       </c>
       <c r="J26" t="n">
-        <v>0.24</v>
+        <v>1.08</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>70</v>
+        <v>346</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F27" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="G27" t="n">
-        <v>0.012</v>
+        <v>0.025</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I27" t="n">
-        <v>0.75</v>
+        <v>0.03</v>
       </c>
       <c r="J27" t="n">
-        <v>2.4</v>
+        <v>0.24</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E28" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F28" t="n">
-        <v>438</v>
+        <v>101</v>
       </c>
       <c r="G28" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I28" t="n">
-        <v>0.12</v>
+        <v>0.75</v>
       </c>
       <c r="J28" t="n">
-        <v>0.36</v>
+        <v>2.4</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>435</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>336</v>
+        <v>438</v>
       </c>
       <c r="G29" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="H29" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I29" t="n">
-        <v>9.49</v>
+        <v>0.12</v>
       </c>
       <c r="J29" t="n">
-        <v>5.4</v>
+        <v>0.36</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>337</v>
+        <v>435</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E30" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F30" t="n">
-        <v>193</v>
+        <v>336</v>
       </c>
       <c r="G30" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I30" t="n">
-        <v>5.68</v>
+        <v>9.49</v>
       </c>
       <c r="J30" t="n">
-        <v>3.96</v>
+        <v>5.4</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>192</v>
+        <v>337</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D31" t="n">
         <v>0.3</v>
       </c>
       <c r="E31" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F31" t="n">
-        <v>281</v>
+        <v>193</v>
       </c>
       <c r="G31" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="H31" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I31" t="n">
-        <v>0.68</v>
+        <v>5.68</v>
       </c>
       <c r="J31" t="n">
-        <v>1.2</v>
+        <v>3.96</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>282</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E32" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F32" t="n">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="G32" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I32" t="n">
-        <v>2.38</v>
+        <v>0.68</v>
       </c>
       <c r="J32" t="n">
-        <v>3.36</v>
+        <v>1.2</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>331</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D33" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="E33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F33" t="n">
-        <v>96</v>
+        <v>332</v>
       </c>
       <c r="G33" t="n">
-        <v>0.082</v>
+        <v>0.006</v>
       </c>
       <c r="H33" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I33" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="J33" t="n">
-        <v>8.76</v>
+        <v>3.36</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>95</v>
+        <v>331</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="E34" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F34" t="n">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="G34" t="n">
-        <v>0.122</v>
+        <v>0.082</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I34" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="J34" t="n">
-        <v>3.36</v>
+        <v>8.76</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>27</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E35" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F35" t="n">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="G35" t="n">
-        <v>0.015</v>
+        <v>0.122</v>
       </c>
       <c r="H35" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I35" t="n">
-        <v>0.93</v>
+        <v>1.72</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>78</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C36" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E36" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F36" t="n">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="G36" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="H36" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I36" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="J36" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>213</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D37" t="n">
         <v>0.5</v>
       </c>
       <c r="E37" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F37" t="n">
-        <v>46</v>
+        <v>214</v>
       </c>
       <c r="G37" t="n">
-        <v>0.021</v>
+        <v>0.005</v>
       </c>
       <c r="H37" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I37" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="J37" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>47</v>
+        <v>213</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C38" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E38" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F38" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="G38" t="n">
-        <v>0.097</v>
+        <v>0.021</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I38" t="n">
-        <v>3.46</v>
+        <v>0.52</v>
       </c>
       <c r="J38" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C39" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E39" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F39" t="n">
-        <v>337</v>
+        <v>7</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01</v>
+        <v>0.097</v>
       </c>
       <c r="H39" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I39" t="n">
-        <v>6.39</v>
+        <v>3.46</v>
       </c>
       <c r="J39" t="n">
-        <v>10.92</v>
+        <v>6.6</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>336</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C40" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D40" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E40" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F40" t="n">
-        <v>41</v>
+        <v>337</v>
       </c>
       <c r="G40" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H40" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I40" t="n">
-        <v>1.79</v>
+        <v>6.39</v>
       </c>
       <c r="J40" t="n">
-        <v>3.36</v>
+        <v>10.92</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>42</v>
+        <v>336</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E41" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F41" t="n">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="G41" t="n">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I41" t="n">
-        <v>1.34</v>
+        <v>1.79</v>
       </c>
       <c r="J41" t="n">
-        <v>1.2</v>
+        <v>3.36</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C42" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D42" t="n">
         <v>0.3</v>
       </c>
       <c r="E42" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F42" t="n">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="G42" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H42" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I42" t="n">
-        <v>0.03</v>
+        <v>1.34</v>
       </c>
       <c r="J42" t="n">
-        <v>0.36</v>
+        <v>1.2</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>135</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C43" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D43" t="n">
         <v>0.3</v>
       </c>
       <c r="E43" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F43" t="n">
-        <v>720</v>
+        <v>134</v>
       </c>
       <c r="G43" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H43" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I43" t="n">
-        <v>4.71</v>
+        <v>0.03</v>
       </c>
       <c r="J43" t="n">
-        <v>8.04</v>
+        <v>0.36</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>717</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C44" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D44" t="n">
         <v>0.3</v>
       </c>
       <c r="E44" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F44" t="n">
-        <v>773</v>
+        <v>720</v>
       </c>
       <c r="G44" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H44" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I44" t="n">
-        <v>0.37</v>
+        <v>4.71</v>
       </c>
       <c r="J44" t="n">
-        <v>1.56</v>
+        <v>8.04</v>
       </c>
       <c r="K44" t="b">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>774</v>
+        <v>717</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C45" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F45" t="n">
-        <v>735</v>
+        <v>773</v>
       </c>
       <c r="G45" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H45" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I45" t="n">
-        <v>0.69</v>
+        <v>0.37</v>
       </c>
       <c r="J45" t="n">
-        <v>3.24</v>
+        <v>1.56</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>734</v>
+        <v>774</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C46" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E46" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F46" t="n">
-        <v>1100</v>
+        <v>735</v>
       </c>
       <c r="G46" t="n">
         <v>0.002</v>
       </c>
       <c r="H46" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I46" t="n">
-        <v>6.45</v>
+        <v>0.69</v>
       </c>
       <c r="J46" t="n">
-        <v>14.4</v>
+        <v>3.24</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1097</v>
+        <v>734</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C47" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E47" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F47" t="n">
-        <v>498</v>
+        <v>1100</v>
       </c>
       <c r="G47" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="H47" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I47" t="n">
-        <v>1.38</v>
+        <v>6.45</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>14.4</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>495</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C48" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E48" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F48" t="n">
-        <v>257</v>
+        <v>498</v>
       </c>
       <c r="G48" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="H48" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I48" t="n">
-        <v>6.15</v>
+        <v>1.38</v>
       </c>
       <c r="J48" t="n">
-        <v>9.48</v>
+        <v>3</v>
       </c>
       <c r="K48" t="b">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>258</v>
+        <v>495</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C49" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E49" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F49" t="n">
-        <v>458</v>
+        <v>257</v>
       </c>
       <c r="G49" t="n">
-        <v>0.059</v>
+        <v>0.003</v>
       </c>
       <c r="H49" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I49" t="n">
-        <v>2.47</v>
+        <v>6.15</v>
       </c>
       <c r="J49" t="n">
-        <v>7.2</v>
+        <v>9.48</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>453</v>
+        <v>258</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C50" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D50" t="n">
         <v>0.3</v>
       </c>
       <c r="E50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F50" t="n">
-        <v>923</v>
+        <v>458</v>
       </c>
       <c r="G50" t="n">
-        <v>0.002</v>
+        <v>0.059</v>
       </c>
       <c r="H50" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I50" t="n">
-        <v>3.76</v>
+        <v>2.47</v>
       </c>
       <c r="J50" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>918</v>
+        <v>453</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C51" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E51" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F51" t="n">
-        <v>1012</v>
+        <v>923</v>
       </c>
       <c r="G51" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H51" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I51" t="n">
-        <v>0.08</v>
+        <v>3.76</v>
       </c>
       <c r="J51" t="n">
-        <v>0.72</v>
+        <v>5.4</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>1211</v>
+        <v>918</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C52" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E52" t="s">
+        <v>169</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1012</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H52" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53" t="s">
+        <v>170</v>
+      </c>
+      <c r="C53" t="s">
+        <v>171</v>
+      </c>
+      <c r="D53" t="n">
         <v>0.3</v>
       </c>
-      <c r="E52" t="s">
-        <v>167</v>
-      </c>
-      <c r="F52" t="n">
+      <c r="E53" t="s">
+        <v>172</v>
+      </c>
+      <c r="F53" t="n">
         <v>344.5</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G53" t="n">
         <v>0.002</v>
       </c>
-      <c r="H52" t="s">
-        <v>16</v>
-      </c>
-      <c r="I52" t="n">
+      <c r="H53" t="s">
+        <v>21</v>
+      </c>
+      <c r="I53" t="n">
         <v>0.32</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J53" t="n">
         <v>2.04</v>
       </c>
-      <c r="K52" t="b">
-        <v>1</v>
-      </c>
-      <c r="L52" t="n">
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
         <v>688</v>
       </c>
     </row>
@@ -2922,7 +2975,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="23.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
@@ -2936,27 +2989,27 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="G1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B2" t="n">
         <v>44</v>
@@ -2979,7 +3032,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B3" t="n">
         <v>7</v>
@@ -2997,6 +3050,29 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3014,7 +3090,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="23.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="19.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
@@ -3055,296 +3131,296 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>96</v>
+        <v>292.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4</v>
+        <v>6.1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.082</v>
+        <v>1.694</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>2.04</v>
+        <v>0.01</v>
       </c>
       <c r="H2" t="n">
-        <v>8.76</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="C3" t="n">
-        <v>862</v>
+        <v>96</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005</v>
+        <v>0.082</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
-        <v>1.29</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C4" t="n">
-        <v>1298</v>
+        <v>862</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>2.18</v>
+        <v>1.29</v>
       </c>
       <c r="H4" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C5" t="n">
-        <v>864</v>
+        <v>1298</v>
       </c>
       <c r="D5" t="n">
         <v>0.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G5" t="n">
-        <v>0.61</v>
+        <v>2.18</v>
       </c>
       <c r="H5" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C6" t="n">
-        <v>83</v>
+        <v>864</v>
       </c>
       <c r="D6" t="n">
         <v>0.8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="H6" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="C7" t="n">
-        <v>735</v>
+        <v>83</v>
       </c>
       <c r="D7" t="n">
         <v>0.8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>0.69</v>
+        <v>0.46</v>
       </c>
       <c r="H7" t="n">
-        <v>3.24</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>149</v>
       </c>
       <c r="C8" t="n">
-        <v>105.5</v>
+        <v>735</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>3.72</v>
+        <v>0.69</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>216</v>
+        <v>105.5</v>
       </c>
       <c r="D9" t="n">
         <v>0.7</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
-        <v>0.44</v>
+        <v>3.72</v>
       </c>
       <c r="H9" t="n">
-        <v>0.96</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C10" t="n">
-        <v>462</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E10" t="n">
         <v>0.005</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G10" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C11" t="n">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="D11" t="n">
         <v>0.6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="H11" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="C12" t="n">
-        <v>361</v>
+        <v>438</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
-        <v>42.9</v>
+        <v>0.12</v>
       </c>
       <c r="H12" t="n">
-        <v>9.48</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>326.5</v>
+        <v>361</v>
       </c>
       <c r="D13" t="n">
         <v>0.5</v>
@@ -3353,221 +3429,221 @@
         <v>0.003</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>1.05</v>
+        <v>42.9</v>
       </c>
       <c r="H13" t="n">
-        <v>3.12</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" t="n">
-        <v>370</v>
+        <v>326.5</v>
       </c>
       <c r="D14" t="n">
         <v>0.5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G14" t="n">
-        <v>1.99</v>
+        <v>1.05</v>
       </c>
       <c r="H14" t="n">
-        <v>1.56</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C15" t="n">
-        <v>166</v>
+        <v>370</v>
       </c>
       <c r="D15" t="n">
         <v>0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G15" t="n">
-        <v>0.49</v>
+        <v>1.99</v>
       </c>
       <c r="H15" t="n">
-        <v>0.72</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>166</v>
       </c>
       <c r="D16" t="n">
         <v>0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>0.122</v>
+        <v>0.006</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G16" t="n">
-        <v>1.72</v>
+        <v>0.49</v>
       </c>
       <c r="H16" t="n">
-        <v>3.36</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C17" t="n">
-        <v>214</v>
+        <v>26</v>
       </c>
       <c r="D17" t="n">
         <v>0.5</v>
       </c>
       <c r="E17" t="n">
-        <v>0.005</v>
+        <v>0.122</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C18" t="n">
-        <v>46</v>
+        <v>214</v>
       </c>
       <c r="D18" t="n">
         <v>0.5</v>
       </c>
       <c r="E18" t="n">
-        <v>0.021</v>
+        <v>0.005</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G18" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C19" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D19" t="n">
         <v>0.5</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05</v>
+        <v>0.021</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>1.79</v>
+        <v>0.52</v>
       </c>
       <c r="H19" t="n">
-        <v>3.36</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="C20" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E20" t="n">
-        <v>0.071</v>
+        <v>0.05</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>1.15</v>
+        <v>1.79</v>
       </c>
       <c r="H20" t="n">
-        <v>0.84</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C21" t="n">
-        <v>90.5</v>
+        <v>50</v>
       </c>
       <c r="D21" t="n">
         <v>0.4</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04</v>
+        <v>0.071</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G21" t="n">
-        <v>44.02</v>
+        <v>1.15</v>
       </c>
       <c r="H21" t="n">
-        <v>20.16</v>
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -1011,7 +1011,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="J2" t="n">
         <v>0.12</v>
@@ -3146,7 +3146,7 @@
         <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="H2" t="n">
         <v>0.12</v>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -52,6 +52,21 @@
     <t xml:space="preserve">points_count</t>
   </si>
   <si>
+    <t xml:space="preserve">An_der_Kost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/21 01:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/21 02:16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/21 01:51:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wasserstraße_Springorum</t>
   </si>
   <si>
@@ -67,9 +82,6 @@
     <t xml:space="preserve">Sturzflut-Ereignis</t>
   </si>
   <si>
-    <t xml:space="preserve">An_der_Kost</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026/05/31 03:42:30</t>
   </si>
   <si>
@@ -77,9 +89,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026/05/31 04:49:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
   </si>
   <si>
     <t xml:space="preserve">2026/05/13 13:08:00</t>
@@ -598,8 +607,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L53" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L53"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L54" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L54"/>
   <tableColumns count="12">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -996,31 +1005,31 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1</v>
+        <v>0.3</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>292.5</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>1.694</v>
+        <v>0.035</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.12</v>
+        <v>1.2</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>586</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -1034,36 +1043,36 @@
         <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>105.5</v>
+        <v>292.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01</v>
+        <v>1.694</v>
       </c>
       <c r="H3" t="s">
         <v>21</v>
       </c>
       <c r="I3" t="n">
-        <v>3.72</v>
+        <v>0.04</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>0.12</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>212</v>
+        <v>586</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -1072,36 +1081,36 @@
         <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>105.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.071</v>
+        <v>0.01</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>1.15</v>
+        <v>3.72</v>
       </c>
       <c r="J4" t="n">
-        <v>0.84</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>101</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1110,36 +1119,36 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>0.018</v>
+        <v>0.071</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>29.75</v>
+        <v>1.15</v>
       </c>
       <c r="J5" t="n">
-        <v>5.16</v>
+        <v>0.84</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>279</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
@@ -1148,36 +1157,36 @@
         <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>361</v>
+        <v>139</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003</v>
+        <v>0.018</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>42.9</v>
+        <v>29.75</v>
       </c>
       <c r="J6" t="n">
-        <v>9.48</v>
+        <v>5.16</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>723</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
@@ -1186,36 +1195,36 @@
         <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="s">
         <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>90.5</v>
+        <v>361</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04</v>
+        <v>0.003</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>44.02</v>
+        <v>42.9</v>
       </c>
       <c r="J7" t="n">
-        <v>20.16</v>
+        <v>9.48</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>182</v>
+        <v>723</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
@@ -1224,36 +1233,36 @@
         <v>35</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E8" t="s">
         <v>36</v>
       </c>
       <c r="F8" t="n">
-        <v>60.5</v>
+        <v>90.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.054</v>
+        <v>0.04</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>2.91</v>
+        <v>44.02</v>
       </c>
       <c r="J8" t="n">
-        <v>7.8</v>
+        <v>20.16</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>122</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
@@ -1262,36 +1271,36 @@
         <v>38</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E9" t="s">
         <v>39</v>
       </c>
       <c r="F9" t="n">
-        <v>90</v>
+        <v>60.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01</v>
+        <v>0.054</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>1.09</v>
+        <v>2.91</v>
       </c>
       <c r="J9" t="n">
-        <v>2.04</v>
+        <v>7.8</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>40</v>
@@ -1300,22 +1309,22 @@
         <v>41</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E10" t="s">
         <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>50.5</v>
+        <v>90</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>1.89</v>
+        <v>1.09</v>
       </c>
       <c r="J10" t="n">
         <v>2.04</v>
@@ -1324,12 +1333,12 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>102</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
         <v>43</v>
@@ -1344,30 +1353,30 @@
         <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>50.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08</v>
+        <v>1.89</v>
       </c>
       <c r="J11" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
         <v>46</v>
@@ -1382,30 +1391,30 @@
         <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>276.5</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>0.013</v>
+        <v>0.039</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>8.81</v>
+        <v>0.08</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>0.96</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>554</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>49</v>
@@ -1414,36 +1423,36 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E13" t="s">
         <v>51</v>
       </c>
       <c r="F13" t="n">
-        <v>326.5</v>
+        <v>276.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.003</v>
+        <v>0.013</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>1.05</v>
+        <v>8.81</v>
       </c>
       <c r="J13" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>654</v>
+        <v>554</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>52</v>
@@ -1452,36 +1461,36 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E14" t="s">
         <v>54</v>
       </c>
       <c r="F14" t="n">
-        <v>93</v>
+        <v>326.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>2.91</v>
+        <v>1.05</v>
       </c>
       <c r="J14" t="n">
-        <v>2.52</v>
+        <v>3.12</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>187</v>
+        <v>654</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
         <v>55</v>
@@ -1490,36 +1499,36 @@
         <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E15" t="s">
         <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>370</v>
+        <v>93</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>1.99</v>
+        <v>2.91</v>
       </c>
       <c r="J15" t="n">
-        <v>1.56</v>
+        <v>2.52</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>371</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
         <v>58</v>
@@ -1528,36 +1537,36 @@
         <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E16" t="s">
         <v>60</v>
       </c>
       <c r="F16" t="n">
-        <v>127</v>
+        <v>370</v>
       </c>
       <c r="G16" t="n">
-        <v>0.129</v>
+        <v>0.002</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>4.49</v>
+        <v>1.99</v>
       </c>
       <c r="J16" t="n">
-        <v>4.68</v>
+        <v>1.56</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>128</v>
+        <v>371</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
         <v>61</v>
@@ -1572,30 +1581,30 @@
         <v>63</v>
       </c>
       <c r="F17" t="n">
-        <v>322</v>
+        <v>127</v>
       </c>
       <c r="G17" t="n">
-        <v>0.004</v>
+        <v>0.129</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>0.43</v>
+        <v>4.49</v>
       </c>
       <c r="J17" t="n">
-        <v>2.52</v>
+        <v>4.68</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>323</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
         <v>64</v>
@@ -1610,30 +1619,30 @@
         <v>66</v>
       </c>
       <c r="F18" t="n">
-        <v>112</v>
+        <v>322</v>
       </c>
       <c r="G18" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.18</v>
+        <v>0.43</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6</v>
+        <v>2.52</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>113</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
         <v>67</v>
@@ -1642,74 +1651,74 @@
         <v>68</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E19" t="s">
         <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="G19" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.49</v>
+        <v>0.18</v>
       </c>
       <c r="J19" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>332</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
         <v>70</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>71</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E20" t="s">
         <v>72</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E20" t="s">
-        <v>73</v>
-      </c>
       <c r="F20" t="n">
-        <v>1298</v>
+        <v>166</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H20" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>2.18</v>
+        <v>0.49</v>
       </c>
       <c r="J20" t="n">
-        <v>2.04</v>
+        <v>0.72</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>2601</v>
+        <v>332</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
         <v>74</v>
@@ -1724,30 +1733,30 @@
         <v>76</v>
       </c>
       <c r="F21" t="n">
-        <v>864</v>
+        <v>1298</v>
       </c>
       <c r="G21" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I21" t="n">
-        <v>0.61</v>
+        <v>2.18</v>
       </c>
       <c r="J21" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1732</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s">
         <v>77</v>
@@ -1756,36 +1765,36 @@
         <v>78</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E22" t="s">
         <v>79</v>
       </c>
       <c r="F22" t="n">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G22" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="H22" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>1.29</v>
+        <v>0.61</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8</v>
+        <v>0.96</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1729</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
         <v>80</v>
@@ -1794,36 +1803,36 @@
         <v>81</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E23" t="s">
         <v>82</v>
       </c>
       <c r="F23" t="n">
-        <v>462</v>
+        <v>862</v>
       </c>
       <c r="G23" t="n">
         <v>0.005</v>
       </c>
       <c r="H23" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.11</v>
+        <v>1.29</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>929</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
         <v>83</v>
@@ -1832,36 +1841,36 @@
         <v>84</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E24" t="s">
         <v>85</v>
       </c>
       <c r="F24" t="n">
-        <v>83</v>
+        <v>462</v>
       </c>
       <c r="G24" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="J24" t="n">
-        <v>0.84</v>
+        <v>0.6</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>168</v>
+        <v>929</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
         <v>86</v>
@@ -1870,36 +1879,36 @@
         <v>87</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E25" t="s">
         <v>88</v>
       </c>
       <c r="F25" t="n">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="G25" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="H25" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I25" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="J25" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>217</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
         <v>89</v>
@@ -1908,36 +1917,36 @@
         <v>90</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E26" t="s">
         <v>91</v>
       </c>
       <c r="F26" t="n">
-        <v>349</v>
+        <v>216</v>
       </c>
       <c r="G26" t="n">
-        <v>0.129</v>
+        <v>0.005</v>
       </c>
       <c r="H26" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>0.76</v>
+        <v>0.44</v>
       </c>
       <c r="J26" t="n">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>346</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
         <v>92</v>
@@ -1952,30 +1961,30 @@
         <v>94</v>
       </c>
       <c r="F27" t="n">
-        <v>69</v>
+        <v>349</v>
       </c>
       <c r="G27" t="n">
-        <v>0.025</v>
+        <v>0.129</v>
       </c>
       <c r="H27" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.03</v>
+        <v>0.76</v>
       </c>
       <c r="J27" t="n">
-        <v>0.24</v>
+        <v>1.08</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>70</v>
+        <v>346</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="B28" t="s">
         <v>95</v>
@@ -1984,36 +1993,36 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E28" t="s">
         <v>97</v>
       </c>
       <c r="F28" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="G28" t="n">
-        <v>0.012</v>
+        <v>0.025</v>
       </c>
       <c r="H28" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>0.75</v>
+        <v>0.03</v>
       </c>
       <c r="J28" t="n">
-        <v>2.4</v>
+        <v>0.24</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
         <v>98</v>
@@ -2022,36 +2031,36 @@
         <v>99</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>438</v>
+        <v>101</v>
       </c>
       <c r="G29" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="H29" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I29" t="n">
-        <v>0.12</v>
+        <v>0.75</v>
       </c>
       <c r="J29" t="n">
-        <v>0.36</v>
+        <v>2.4</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>435</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
         <v>101</v>
@@ -2060,36 +2069,36 @@
         <v>102</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E30" t="s">
         <v>103</v>
       </c>
       <c r="F30" t="n">
-        <v>336</v>
+        <v>438</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="H30" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>9.49</v>
+        <v>0.12</v>
       </c>
       <c r="J30" t="n">
-        <v>5.4</v>
+        <v>0.36</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>337</v>
+        <v>435</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
         <v>104</v>
@@ -2098,36 +2107,36 @@
         <v>105</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E31" t="s">
         <v>106</v>
       </c>
       <c r="F31" t="n">
-        <v>193</v>
+        <v>336</v>
       </c>
       <c r="G31" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="H31" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>5.68</v>
+        <v>9.49</v>
       </c>
       <c r="J31" t="n">
-        <v>3.96</v>
+        <v>5.4</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>192</v>
+        <v>337</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
         <v>107</v>
@@ -2142,30 +2151,30 @@
         <v>109</v>
       </c>
       <c r="F32" t="n">
-        <v>281</v>
+        <v>193</v>
       </c>
       <c r="G32" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="H32" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>0.68</v>
+        <v>5.68</v>
       </c>
       <c r="J32" t="n">
-        <v>1.2</v>
+        <v>3.96</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>282</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
         <v>110</v>
@@ -2174,36 +2183,36 @@
         <v>111</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E33" t="s">
         <v>112</v>
       </c>
       <c r="F33" t="n">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="G33" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="H33" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I33" t="n">
-        <v>2.38</v>
+        <v>0.68</v>
       </c>
       <c r="J33" t="n">
-        <v>3.36</v>
+        <v>1.2</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>331</v>
+        <v>282</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
         <v>113</v>
@@ -2212,36 +2221,36 @@
         <v>114</v>
       </c>
       <c r="D34" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="E34" t="s">
         <v>115</v>
       </c>
       <c r="F34" t="n">
-        <v>96</v>
+        <v>332</v>
       </c>
       <c r="G34" t="n">
-        <v>0.082</v>
+        <v>0.006</v>
       </c>
       <c r="H34" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I34" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="J34" t="n">
-        <v>8.76</v>
+        <v>3.36</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>95</v>
+        <v>331</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
         <v>116</v>
@@ -2250,36 +2259,36 @@
         <v>117</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="E35" t="s">
         <v>118</v>
       </c>
       <c r="F35" t="n">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="G35" t="n">
-        <v>0.122</v>
+        <v>0.082</v>
       </c>
       <c r="H35" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I35" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="J35" t="n">
-        <v>3.36</v>
+        <v>8.76</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>27</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
         <v>119</v>
@@ -2288,36 +2297,36 @@
         <v>120</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E36" t="s">
         <v>121</v>
       </c>
       <c r="F36" t="n">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="G36" t="n">
-        <v>0.015</v>
+        <v>0.122</v>
       </c>
       <c r="H36" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>0.93</v>
+        <v>1.72</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>78</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
         <v>122</v>
@@ -2326,36 +2335,36 @@
         <v>123</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E37" t="s">
         <v>124</v>
       </c>
       <c r="F37" t="n">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="G37" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="H37" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I37" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="J37" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>213</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
         <v>125</v>
@@ -2370,30 +2379,30 @@
         <v>127</v>
       </c>
       <c r="F38" t="n">
-        <v>46</v>
+        <v>214</v>
       </c>
       <c r="G38" t="n">
-        <v>0.021</v>
+        <v>0.005</v>
       </c>
       <c r="H38" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="J38" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>47</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
         <v>128</v>
@@ -2402,36 +2411,36 @@
         <v>129</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E39" t="s">
         <v>130</v>
       </c>
       <c r="F39" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="G39" t="n">
-        <v>0.097</v>
+        <v>0.021</v>
       </c>
       <c r="H39" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>3.46</v>
+        <v>0.52</v>
       </c>
       <c r="J39" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
         <v>131</v>
@@ -2440,36 +2449,36 @@
         <v>132</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E40" t="s">
         <v>133</v>
       </c>
       <c r="F40" t="n">
-        <v>337</v>
+        <v>7</v>
       </c>
       <c r="G40" t="n">
-        <v>0.01</v>
+        <v>0.097</v>
       </c>
       <c r="H40" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I40" t="n">
-        <v>6.39</v>
+        <v>3.46</v>
       </c>
       <c r="J40" t="n">
-        <v>10.92</v>
+        <v>6.6</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>336</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
         <v>134</v>
@@ -2478,36 +2487,36 @@
         <v>135</v>
       </c>
       <c r="D41" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E41" t="s">
         <v>136</v>
       </c>
       <c r="F41" t="n">
-        <v>41</v>
+        <v>337</v>
       </c>
       <c r="G41" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H41" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I41" t="n">
-        <v>1.79</v>
+        <v>6.39</v>
       </c>
       <c r="J41" t="n">
-        <v>3.36</v>
+        <v>10.92</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>42</v>
+        <v>336</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="B42" t="s">
         <v>137</v>
@@ -2516,36 +2525,36 @@
         <v>138</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E42" t="s">
         <v>139</v>
       </c>
       <c r="F42" t="n">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="G42" t="n">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="H42" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>1.34</v>
+        <v>1.79</v>
       </c>
       <c r="J42" t="n">
-        <v>1.2</v>
+        <v>3.36</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
         <v>140</v>
@@ -2560,30 +2569,30 @@
         <v>142</v>
       </c>
       <c r="F43" t="n">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="G43" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H43" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.03</v>
+        <v>1.34</v>
       </c>
       <c r="J43" t="n">
-        <v>0.36</v>
+        <v>1.2</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>135</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
         <v>143</v>
@@ -2598,30 +2607,30 @@
         <v>145</v>
       </c>
       <c r="F44" t="n">
-        <v>720</v>
+        <v>134</v>
       </c>
       <c r="G44" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H44" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>4.71</v>
+        <v>0.03</v>
       </c>
       <c r="J44" t="n">
-        <v>8.04</v>
+        <v>0.36</v>
       </c>
       <c r="K44" t="b">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>717</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
         <v>146</v>
@@ -2636,30 +2645,30 @@
         <v>148</v>
       </c>
       <c r="F45" t="n">
-        <v>773</v>
+        <v>720</v>
       </c>
       <c r="G45" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H45" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I45" t="n">
-        <v>0.37</v>
+        <v>4.71</v>
       </c>
       <c r="J45" t="n">
-        <v>1.56</v>
+        <v>8.04</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>774</v>
+        <v>717</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
         <v>149</v>
@@ -2668,36 +2677,36 @@
         <v>150</v>
       </c>
       <c r="D46" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E46" t="s">
         <v>151</v>
       </c>
       <c r="F46" t="n">
-        <v>735</v>
+        <v>773</v>
       </c>
       <c r="G46" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H46" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I46" t="n">
-        <v>0.69</v>
+        <v>0.37</v>
       </c>
       <c r="J46" t="n">
-        <v>3.24</v>
+        <v>1.56</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>734</v>
+        <v>774</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
         <v>152</v>
@@ -2706,36 +2715,36 @@
         <v>153</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E47" t="s">
         <v>154</v>
       </c>
       <c r="F47" t="n">
-        <v>1100</v>
+        <v>735</v>
       </c>
       <c r="G47" t="n">
         <v>0.002</v>
       </c>
       <c r="H47" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I47" t="n">
-        <v>6.45</v>
+        <v>0.69</v>
       </c>
       <c r="J47" t="n">
-        <v>14.4</v>
+        <v>3.24</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1097</v>
+        <v>734</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
         <v>155</v>
@@ -2744,36 +2753,36 @@
         <v>156</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E48" t="s">
         <v>157</v>
       </c>
       <c r="F48" t="n">
-        <v>498</v>
+        <v>1100</v>
       </c>
       <c r="G48" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="H48" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I48" t="n">
-        <v>1.38</v>
+        <v>6.45</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>14.4</v>
       </c>
       <c r="K48" t="b">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>495</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
         <v>158</v>
@@ -2782,36 +2791,36 @@
         <v>159</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E49" t="s">
         <v>160</v>
       </c>
       <c r="F49" t="n">
-        <v>257</v>
+        <v>498</v>
       </c>
       <c r="G49" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="H49" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I49" t="n">
-        <v>6.15</v>
+        <v>1.38</v>
       </c>
       <c r="J49" t="n">
-        <v>9.48</v>
+        <v>3</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>258</v>
+        <v>495</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
         <v>161</v>
@@ -2820,36 +2829,36 @@
         <v>162</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E50" t="s">
         <v>163</v>
       </c>
       <c r="F50" t="n">
-        <v>458</v>
+        <v>257</v>
       </c>
       <c r="G50" t="n">
-        <v>0.059</v>
+        <v>0.003</v>
       </c>
       <c r="H50" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I50" t="n">
-        <v>2.47</v>
+        <v>6.15</v>
       </c>
       <c r="J50" t="n">
-        <v>7.2</v>
+        <v>9.48</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>453</v>
+        <v>258</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
         <v>164</v>
@@ -2864,30 +2873,30 @@
         <v>166</v>
       </c>
       <c r="F51" t="n">
-        <v>923</v>
+        <v>458</v>
       </c>
       <c r="G51" t="n">
-        <v>0.002</v>
+        <v>0.059</v>
       </c>
       <c r="H51" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I51" t="n">
-        <v>3.76</v>
+        <v>2.47</v>
       </c>
       <c r="J51" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>918</v>
+        <v>453</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
         <v>167</v>
@@ -2896,36 +2905,36 @@
         <v>168</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E52" t="s">
         <v>169</v>
       </c>
       <c r="F52" t="n">
-        <v>1012</v>
+        <v>923</v>
       </c>
       <c r="G52" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H52" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I52" t="n">
-        <v>0.08</v>
+        <v>3.76</v>
       </c>
       <c r="J52" t="n">
-        <v>0.72</v>
+        <v>5.4</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>1211</v>
+        <v>918</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
         <v>170</v>
@@ -2934,30 +2943,68 @@
         <v>171</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E53" t="s">
         <v>172</v>
       </c>
       <c r="F53" t="n">
+        <v>1012</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H53" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" t="s">
+        <v>173</v>
+      </c>
+      <c r="C54" t="s">
+        <v>174</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E54" t="s">
+        <v>175</v>
+      </c>
+      <c r="F54" t="n">
         <v>344.5</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G54" t="n">
         <v>0.002</v>
       </c>
-      <c r="H53" t="s">
-        <v>21</v>
-      </c>
-      <c r="I53" t="n">
+      <c r="H54" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" t="n">
         <v>0.32</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J54" t="n">
         <v>2.04</v>
       </c>
-      <c r="K53" t="b">
-        <v>1</v>
-      </c>
-      <c r="L53" t="n">
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
         <v>688</v>
       </c>
     </row>
@@ -2989,30 +3036,30 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
         <v>0.4</v>
@@ -3032,7 +3079,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B3" t="n">
         <v>7</v>
@@ -3055,7 +3102,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -3128,10 +3175,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
         <v>292.5</v>
@@ -3143,7 +3190,7 @@
         <v>1.694</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
         <v>0.04</v>
@@ -3154,10 +3201,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C3" t="n">
         <v>96</v>
@@ -3169,7 +3216,7 @@
         <v>0.082</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
         <v>2.04</v>
@@ -3180,10 +3227,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C4" t="n">
         <v>862</v>
@@ -3195,7 +3242,7 @@
         <v>0.005</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
         <v>1.29</v>
@@ -3206,10 +3253,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C5" t="n">
         <v>1298</v>
@@ -3221,7 +3268,7 @@
         <v>0.001</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
         <v>2.18</v>
@@ -3232,10 +3279,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C6" t="n">
         <v>864</v>
@@ -3247,7 +3294,7 @@
         <v>0.002</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
         <v>0.61</v>
@@ -3258,10 +3305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
         <v>83</v>
@@ -3273,7 +3320,7 @@
         <v>0.014</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
         <v>0.46</v>
@@ -3284,10 +3331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C8" t="n">
         <v>735</v>
@@ -3299,7 +3346,7 @@
         <v>0.002</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G8" t="n">
         <v>0.69</v>
@@ -3310,10 +3357,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
         <v>105.5</v>
@@ -3325,7 +3372,7 @@
         <v>0.01</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
         <v>3.72</v>
@@ -3336,10 +3383,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C10" t="n">
         <v>216</v>
@@ -3351,7 +3398,7 @@
         <v>0.005</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G10" t="n">
         <v>0.44</v>
@@ -3362,10 +3409,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C11" t="n">
         <v>462</v>
@@ -3377,7 +3424,7 @@
         <v>0.005</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G11" t="n">
         <v>0.11</v>
@@ -3388,10 +3435,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C12" t="n">
         <v>438</v>
@@ -3403,7 +3450,7 @@
         <v>0.008</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
         <v>0.12</v>
@@ -3414,10 +3461,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C13" t="n">
         <v>361</v>
@@ -3429,7 +3476,7 @@
         <v>0.003</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G13" t="n">
         <v>42.9</v>
@@ -3440,10 +3487,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C14" t="n">
         <v>326.5</v>
@@ -3455,7 +3502,7 @@
         <v>0.003</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G14" t="n">
         <v>1.05</v>
@@ -3466,10 +3513,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C15" t="n">
         <v>370</v>
@@ -3481,7 +3528,7 @@
         <v>0.002</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G15" t="n">
         <v>1.99</v>
@@ -3492,10 +3539,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C16" t="n">
         <v>166</v>
@@ -3507,7 +3554,7 @@
         <v>0.006</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G16" t="n">
         <v>0.49</v>
@@ -3518,10 +3565,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C17" t="n">
         <v>26</v>
@@ -3533,7 +3580,7 @@
         <v>0.122</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
         <v>1.72</v>
@@ -3544,10 +3591,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C18" t="n">
         <v>214</v>
@@ -3559,7 +3606,7 @@
         <v>0.005</v>
       </c>
       <c r="F18" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G18" t="n">
         <v>0.47</v>
@@ -3570,10 +3617,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C19" t="n">
         <v>46</v>
@@ -3585,7 +3632,7 @@
         <v>0.021</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G19" t="n">
         <v>0.52</v>
@@ -3596,10 +3643,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C20" t="n">
         <v>41</v>
@@ -3611,7 +3658,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G20" t="n">
         <v>1.79</v>
@@ -3622,10 +3669,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C21" t="n">
         <v>50</v>
@@ -3637,7 +3684,7 @@
         <v>0.071</v>
       </c>
       <c r="F21" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
         <v>1.15</v>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t xml:space="preserve">radolan_verified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level_reliable</t>
   </si>
   <si>
     <t xml:space="preserve">points_count</t>
@@ -607,9 +610,9 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:L54" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L54"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M54" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M54"/>
+  <tableColumns count="13">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
     <tableColumn id="3" name="end_time"/>
@@ -621,7 +624,8 @@
     <tableColumn id="9" name="total_precip_mm"/>
     <tableColumn id="10" name="max_intensity_mm_h"/>
     <tableColumn id="11" name="radolan_verified"/>
-    <tableColumn id="12" name="points_count"/>
+    <tableColumn id="12" name="level_reliable"/>
+    <tableColumn id="13" name="points_count"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -953,7 +957,8 @@
     <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="18.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="16.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="12.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="14.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="12.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,22 +998,25 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
         <v>0.3</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" t="n">
         <v>33</v>
@@ -1017,10 +1025,10 @@
         <v>0.035</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J2" t="n">
         <v>1.2</v>
@@ -1028,25 +1036,28 @@
       <c r="K2" t="b">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
         <v>67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
         <v>6.1</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
         <v>292.5</v>
@@ -1055,7 +1066,7 @@
         <v>1.694</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="n">
         <v>0.04</v>
@@ -1066,25 +1077,28 @@
       <c r="K3" t="b">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
         <v>586</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
         <v>0.7</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
         <v>105.5</v>
@@ -1093,7 +1107,7 @@
         <v>0.01</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
         <v>3.72</v>
@@ -1104,25 +1118,28 @@
       <c r="K4" t="b">
         <v>1</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
         <v>212</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
         <v>0.4</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" t="n">
         <v>50</v>
@@ -1131,7 +1148,7 @@
         <v>0.071</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" t="n">
         <v>1.15</v>
@@ -1142,25 +1159,28 @@
       <c r="K5" t="b">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
         <v>101</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
         <v>0.3</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" t="n">
         <v>139</v>
@@ -1169,7 +1189,7 @@
         <v>0.018</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
         <v>29.75</v>
@@ -1180,25 +1200,28 @@
       <c r="K6" t="b">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
         <v>279</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="n">
         <v>0.5</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="n">
         <v>361</v>
@@ -1207,7 +1230,7 @@
         <v>0.003</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" t="n">
         <v>42.9</v>
@@ -1218,25 +1241,28 @@
       <c r="K7" t="b">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
         <v>723</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
         <v>0.4</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F8" t="n">
         <v>90.5</v>
@@ -1245,7 +1271,7 @@
         <v>0.04</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" t="n">
         <v>44.02</v>
@@ -1256,25 +1282,28 @@
       <c r="K8" t="b">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
         <v>182</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="n">
         <v>0.3</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
         <v>60.5</v>
@@ -1283,7 +1312,7 @@
         <v>0.054</v>
       </c>
       <c r="H9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I9" t="n">
         <v>2.91</v>
@@ -1294,25 +1323,28 @@
       <c r="K9" t="b">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
         <v>122</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="n">
         <v>0.4</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
         <v>90</v>
@@ -1321,7 +1353,7 @@
         <v>0.01</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
         <v>1.09</v>
@@ -1332,25 +1364,28 @@
       <c r="K10" t="b">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
         <v>181</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" t="n">
         <v>0.3</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
         <v>50.5</v>
@@ -1359,7 +1394,7 @@
         <v>0.03</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
         <v>1.89</v>
@@ -1370,25 +1405,28 @@
       <c r="K11" t="b">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
         <v>102</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
         <v>0.3</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
         <v>40</v>
@@ -1397,7 +1435,7 @@
         <v>0.039</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I12" t="n">
         <v>0.08</v>
@@ -1408,25 +1446,28 @@
       <c r="K12" t="b">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
         <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>0.3</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F13" t="n">
         <v>276.5</v>
@@ -1435,7 +1476,7 @@
         <v>0.013</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I13" t="n">
         <v>8.81</v>
@@ -1446,25 +1487,28 @@
       <c r="K13" t="b">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
         <v>554</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>0.5</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F14" t="n">
         <v>326.5</v>
@@ -1473,7 +1517,7 @@
         <v>0.003</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I14" t="n">
         <v>1.05</v>
@@ -1484,25 +1528,28 @@
       <c r="K14" t="b">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
         <v>654</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>0.3</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F15" t="n">
         <v>93</v>
@@ -1511,7 +1558,7 @@
         <v>0.005</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I15" t="n">
         <v>2.91</v>
@@ -1522,25 +1569,28 @@
       <c r="K15" t="b">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
         <v>187</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
         <v>0.5</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F16" t="n">
         <v>370</v>
@@ -1549,7 +1599,7 @@
         <v>0.002</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I16" t="n">
         <v>1.99</v>
@@ -1560,25 +1610,28 @@
       <c r="K16" t="b">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
         <v>371</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>0.4</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F17" t="n">
         <v>127</v>
@@ -1587,7 +1640,7 @@
         <v>0.129</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I17" t="n">
         <v>4.49</v>
@@ -1598,25 +1651,28 @@
       <c r="K17" t="b">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
         <v>128</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>0.4</v>
       </c>
       <c r="E18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F18" t="n">
         <v>322</v>
@@ -1625,7 +1681,7 @@
         <v>0.004</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I18" t="n">
         <v>0.43</v>
@@ -1636,25 +1692,28 @@
       <c r="K18" t="b">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
         <v>323</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D19" t="n">
         <v>0.4</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
         <v>112</v>
@@ -1663,7 +1722,7 @@
         <v>0.005</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I19" t="n">
         <v>0.18</v>
@@ -1674,25 +1733,28 @@
       <c r="K19" t="b">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
         <v>113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D20" t="n">
         <v>0.5</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F20" t="n">
         <v>166</v>
@@ -1701,7 +1763,7 @@
         <v>0.006</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" t="n">
         <v>0.49</v>
@@ -1712,25 +1774,28 @@
       <c r="K20" t="b">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
         <v>332</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
         <v>0.8</v>
       </c>
       <c r="E21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F21" t="n">
         <v>1298</v>
@@ -1739,7 +1804,7 @@
         <v>0.001</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I21" t="n">
         <v>2.18</v>
@@ -1750,25 +1815,28 @@
       <c r="K21" t="b">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
         <v>2601</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D22" t="n">
         <v>0.8</v>
       </c>
       <c r="E22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F22" t="n">
         <v>864</v>
@@ -1777,7 +1845,7 @@
         <v>0.002</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I22" t="n">
         <v>0.61</v>
@@ -1788,25 +1856,28 @@
       <c r="K22" t="b">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
         <v>1732</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D23" t="n">
         <v>0.9</v>
       </c>
       <c r="E23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F23" t="n">
         <v>862</v>
@@ -1815,7 +1886,7 @@
         <v>0.005</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I23" t="n">
         <v>1.29</v>
@@ -1826,25 +1897,28 @@
       <c r="K23" t="b">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
         <v>1729</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D24" t="n">
         <v>0.6</v>
       </c>
       <c r="E24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F24" t="n">
         <v>462</v>
@@ -1853,7 +1927,7 @@
         <v>0.005</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I24" t="n">
         <v>0.11</v>
@@ -1864,25 +1938,28 @@
       <c r="K24" t="b">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
         <v>929</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D25" t="n">
         <v>0.8</v>
       </c>
       <c r="E25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F25" t="n">
         <v>83</v>
@@ -1891,7 +1968,7 @@
         <v>0.014</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25" t="n">
         <v>0.46</v>
@@ -1902,25 +1979,28 @@
       <c r="K25" t="b">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
         <v>168</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D26" t="n">
         <v>0.7</v>
       </c>
       <c r="E26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F26" t="n">
         <v>216</v>
@@ -1929,7 +2009,7 @@
         <v>0.005</v>
       </c>
       <c r="H26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I26" t="n">
         <v>0.44</v>
@@ -1940,25 +2020,28 @@
       <c r="K26" t="b">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
         <v>217</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D27" t="n">
         <v>0.4</v>
       </c>
       <c r="E27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F27" t="n">
         <v>349</v>
@@ -1967,7 +2050,7 @@
         <v>0.129</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I27" t="n">
         <v>0.76</v>
@@ -1978,25 +2061,28 @@
       <c r="K27" t="b">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
         <v>346</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D28" t="n">
         <v>0.4</v>
       </c>
       <c r="E28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F28" t="n">
         <v>69</v>
@@ -2005,7 +2091,7 @@
         <v>0.025</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I28" t="n">
         <v>0.03</v>
@@ -2016,25 +2102,28 @@
       <c r="K28" t="b">
         <v>1</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D29" t="n">
         <v>0.3</v>
       </c>
       <c r="E29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F29" t="n">
         <v>101</v>
@@ -2043,7 +2132,7 @@
         <v>0.012</v>
       </c>
       <c r="H29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I29" t="n">
         <v>0.75</v>
@@ -2054,25 +2143,28 @@
       <c r="K29" t="b">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
         <v>102</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D30" t="n">
         <v>0.6</v>
       </c>
       <c r="E30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F30" t="n">
         <v>438</v>
@@ -2081,7 +2173,7 @@
         <v>0.008</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I30" t="n">
         <v>0.12</v>
@@ -2092,25 +2184,28 @@
       <c r="K30" t="b">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
         <v>435</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D31" t="n">
         <v>0.4</v>
       </c>
       <c r="E31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F31" t="n">
         <v>336</v>
@@ -2119,7 +2214,7 @@
         <v>0.002</v>
       </c>
       <c r="H31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I31" t="n">
         <v>9.49</v>
@@ -2130,25 +2225,28 @@
       <c r="K31" t="b">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
         <v>337</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D32" t="n">
         <v>0.3</v>
       </c>
       <c r="E32" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F32" t="n">
         <v>193</v>
@@ -2157,7 +2255,7 @@
         <v>0.008</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I32" t="n">
         <v>5.68</v>
@@ -2168,25 +2266,28 @@
       <c r="K32" t="b">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
         <v>192</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D33" t="n">
         <v>0.3</v>
       </c>
       <c r="E33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F33" t="n">
         <v>281</v>
@@ -2195,7 +2296,7 @@
         <v>0.007</v>
       </c>
       <c r="H33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I33" t="n">
         <v>0.68</v>
@@ -2206,25 +2307,28 @@
       <c r="K33" t="b">
         <v>1</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
         <v>282</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D34" t="n">
         <v>0.4</v>
       </c>
       <c r="E34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F34" t="n">
         <v>332</v>
@@ -2233,7 +2337,7 @@
         <v>0.006</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I34" t="n">
         <v>2.38</v>
@@ -2244,25 +2348,28 @@
       <c r="K34" t="b">
         <v>1</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
         <v>331</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D35" t="n">
         <v>1.4</v>
       </c>
       <c r="E35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F35" t="n">
         <v>96</v>
@@ -2271,7 +2378,7 @@
         <v>0.082</v>
       </c>
       <c r="H35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I35" t="n">
         <v>2.04</v>
@@ -2282,25 +2389,28 @@
       <c r="K35" t="b">
         <v>1</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
         <v>95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C36" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D36" t="n">
         <v>0.5</v>
       </c>
       <c r="E36" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F36" t="n">
         <v>26</v>
@@ -2309,7 +2419,7 @@
         <v>0.122</v>
       </c>
       <c r="H36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I36" t="n">
         <v>1.72</v>
@@ -2320,25 +2430,28 @@
       <c r="K36" t="b">
         <v>1</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C37" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D37" t="n">
         <v>0.4</v>
       </c>
       <c r="E37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F37" t="n">
         <v>77</v>
@@ -2347,7 +2460,7 @@
         <v>0.015</v>
       </c>
       <c r="H37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I37" t="n">
         <v>0.93</v>
@@ -2358,25 +2471,28 @@
       <c r="K37" t="b">
         <v>1</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L37" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
         <v>78</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C38" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D38" t="n">
         <v>0.5</v>
       </c>
       <c r="E38" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F38" t="n">
         <v>214</v>
@@ -2385,7 +2501,7 @@
         <v>0.005</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I38" t="n">
         <v>0.47</v>
@@ -2396,25 +2512,28 @@
       <c r="K38" t="b">
         <v>1</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L38" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
         <v>213</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D39" t="n">
         <v>0.5</v>
       </c>
       <c r="E39" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F39" t="n">
         <v>46</v>
@@ -2423,7 +2542,7 @@
         <v>0.021</v>
       </c>
       <c r="H39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I39" t="n">
         <v>0.52</v>
@@ -2434,25 +2553,28 @@
       <c r="K39" t="b">
         <v>1</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L39" t="b">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
         <v>47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C40" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D40" t="n">
         <v>0.3</v>
       </c>
       <c r="E40" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F40" t="n">
         <v>7</v>
@@ -2461,7 +2583,7 @@
         <v>0.097</v>
       </c>
       <c r="H40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I40" t="n">
         <v>3.46</v>
@@ -2472,25 +2594,28 @@
       <c r="K40" t="b">
         <v>1</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L40" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C41" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D41" t="n">
         <v>0.4</v>
       </c>
       <c r="E41" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F41" t="n">
         <v>337</v>
@@ -2499,7 +2624,7 @@
         <v>0.01</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I41" t="n">
         <v>6.39</v>
@@ -2510,25 +2635,28 @@
       <c r="K41" t="b">
         <v>1</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L41" t="b">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
         <v>336</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B42" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D42" t="n">
         <v>0.5</v>
       </c>
       <c r="E42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F42" t="n">
         <v>41</v>
@@ -2537,7 +2665,7 @@
         <v>0.05</v>
       </c>
       <c r="H42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I42" t="n">
         <v>1.79</v>
@@ -2548,25 +2676,28 @@
       <c r="K42" t="b">
         <v>1</v>
       </c>
-      <c r="L42" t="n">
+      <c r="L42" t="b">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D43" t="n">
         <v>0.3</v>
       </c>
       <c r="E43" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F43" t="n">
         <v>81</v>
@@ -2575,7 +2706,7 @@
         <v>0.005</v>
       </c>
       <c r="H43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I43" t="n">
         <v>1.34</v>
@@ -2586,25 +2717,28 @@
       <c r="K43" t="b">
         <v>1</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L43" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
         <v>82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B44" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C44" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D44" t="n">
         <v>0.3</v>
       </c>
       <c r="E44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F44" t="n">
         <v>134</v>
@@ -2613,7 +2747,7 @@
         <v>0.004</v>
       </c>
       <c r="H44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I44" t="n">
         <v>0.03</v>
@@ -2624,25 +2758,28 @@
       <c r="K44" t="b">
         <v>1</v>
       </c>
-      <c r="L44" t="n">
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
         <v>135</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B45" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C45" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D45" t="n">
         <v>0.3</v>
       </c>
       <c r="E45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F45" t="n">
         <v>720</v>
@@ -2651,7 +2788,7 @@
         <v>0.002</v>
       </c>
       <c r="H45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I45" t="n">
         <v>4.71</v>
@@ -2662,25 +2799,28 @@
       <c r="K45" t="b">
         <v>1</v>
       </c>
-      <c r="L45" t="n">
+      <c r="L45" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
         <v>717</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B46" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C46" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D46" t="n">
         <v>0.3</v>
       </c>
       <c r="E46" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F46" t="n">
         <v>773</v>
@@ -2689,7 +2829,7 @@
         <v>0.003</v>
       </c>
       <c r="H46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I46" t="n">
         <v>0.37</v>
@@ -2700,25 +2840,28 @@
       <c r="K46" t="b">
         <v>1</v>
       </c>
-      <c r="L46" t="n">
+      <c r="L46" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
         <v>774</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D47" t="n">
         <v>0.8</v>
       </c>
       <c r="E47" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F47" t="n">
         <v>735</v>
@@ -2727,7 +2870,7 @@
         <v>0.002</v>
       </c>
       <c r="H47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I47" t="n">
         <v>0.69</v>
@@ -2738,25 +2881,28 @@
       <c r="K47" t="b">
         <v>1</v>
       </c>
-      <c r="L47" t="n">
+      <c r="L47" t="b">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
         <v>734</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B48" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C48" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D48" t="n">
         <v>0.4</v>
       </c>
       <c r="E48" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F48" t="n">
         <v>1100</v>
@@ -2765,7 +2911,7 @@
         <v>0.002</v>
       </c>
       <c r="H48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I48" t="n">
         <v>6.45</v>
@@ -2776,25 +2922,28 @@
       <c r="K48" t="b">
         <v>1</v>
       </c>
-      <c r="L48" t="n">
+      <c r="L48" t="b">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
         <v>1097</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B49" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C49" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D49" t="n">
         <v>0.3</v>
       </c>
       <c r="E49" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F49" t="n">
         <v>498</v>
@@ -2803,7 +2952,7 @@
         <v>0.006</v>
       </c>
       <c r="H49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I49" t="n">
         <v>1.38</v>
@@ -2814,25 +2963,28 @@
       <c r="K49" t="b">
         <v>1</v>
       </c>
-      <c r="L49" t="n">
+      <c r="L49" t="b">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
         <v>495</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D50" t="n">
         <v>0.4</v>
       </c>
       <c r="E50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F50" t="n">
         <v>257</v>
@@ -2841,7 +2993,7 @@
         <v>0.003</v>
       </c>
       <c r="H50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I50" t="n">
         <v>6.15</v>
@@ -2852,25 +3004,28 @@
       <c r="K50" t="b">
         <v>1</v>
       </c>
-      <c r="L50" t="n">
+      <c r="L50" t="b">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
         <v>258</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B51" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C51" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D51" t="n">
         <v>0.3</v>
       </c>
       <c r="E51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F51" t="n">
         <v>458</v>
@@ -2879,7 +3034,7 @@
         <v>0.059</v>
       </c>
       <c r="H51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I51" t="n">
         <v>2.47</v>
@@ -2890,25 +3045,28 @@
       <c r="K51" t="b">
         <v>1</v>
       </c>
-      <c r="L51" t="n">
+      <c r="L51" t="b">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
         <v>453</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B52" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C52" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D52" t="n">
         <v>0.3</v>
       </c>
       <c r="E52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F52" t="n">
         <v>923</v>
@@ -2917,7 +3075,7 @@
         <v>0.002</v>
       </c>
       <c r="H52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I52" t="n">
         <v>3.76</v>
@@ -2928,25 +3086,28 @@
       <c r="K52" t="b">
         <v>1</v>
       </c>
-      <c r="L52" t="n">
+      <c r="L52" t="b">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
         <v>918</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D53" t="n">
         <v>0.4</v>
       </c>
       <c r="E53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F53" t="n">
         <v>1012</v>
@@ -2955,7 +3116,7 @@
         <v>0.003</v>
       </c>
       <c r="H53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I53" t="n">
         <v>0.08</v>
@@ -2966,25 +3127,28 @@
       <c r="K53" t="b">
         <v>1</v>
       </c>
-      <c r="L53" t="n">
+      <c r="L53" t="b">
+        <v>1</v>
+      </c>
+      <c r="M53" t="n">
         <v>1211</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B54" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C54" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D54" t="n">
         <v>0.3</v>
       </c>
       <c r="E54" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F54" t="n">
         <v>344.5</v>
@@ -2993,7 +3157,7 @@
         <v>0.002</v>
       </c>
       <c r="H54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I54" t="n">
         <v>0.32</v>
@@ -3004,7 +3168,10 @@
       <c r="K54" t="b">
         <v>1</v>
       </c>
-      <c r="L54" t="n">
+      <c r="L54" t="b">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
         <v>688</v>
       </c>
     </row>
@@ -3036,27 +3203,27 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="n">
         <v>45</v>
@@ -3079,7 +3246,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B3" t="n">
         <v>7</v>
@@ -3102,7 +3269,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -3175,10 +3342,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
         <v>292.5</v>
@@ -3190,7 +3357,7 @@
         <v>1.694</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
         <v>0.04</v>
@@ -3201,10 +3368,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C3" t="n">
         <v>96</v>
@@ -3216,7 +3383,7 @@
         <v>0.082</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
         <v>2.04</v>
@@ -3227,10 +3394,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" t="n">
         <v>862</v>
@@ -3242,7 +3409,7 @@
         <v>0.005</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
         <v>1.29</v>
@@ -3253,10 +3420,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" t="n">
         <v>1298</v>
@@ -3268,7 +3435,7 @@
         <v>0.001</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
         <v>2.18</v>
@@ -3279,10 +3446,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" t="n">
         <v>864</v>
@@ -3294,7 +3461,7 @@
         <v>0.002</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
         <v>0.61</v>
@@ -3305,10 +3472,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="n">
         <v>83</v>
@@ -3320,7 +3487,7 @@
         <v>0.014</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" t="n">
         <v>0.46</v>
@@ -3331,10 +3498,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C8" t="n">
         <v>735</v>
@@ -3346,7 +3513,7 @@
         <v>0.002</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
         <v>0.69</v>
@@ -3357,10 +3524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
         <v>105.5</v>
@@ -3372,7 +3539,7 @@
         <v>0.01</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
         <v>3.72</v>
@@ -3383,10 +3550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" t="n">
         <v>216</v>
@@ -3398,7 +3565,7 @@
         <v>0.005</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" t="n">
         <v>0.44</v>
@@ -3409,10 +3576,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C11" t="n">
         <v>462</v>
@@ -3424,7 +3591,7 @@
         <v>0.005</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11" t="n">
         <v>0.11</v>
@@ -3435,10 +3602,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C12" t="n">
         <v>438</v>
@@ -3450,7 +3617,7 @@
         <v>0.008</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12" t="n">
         <v>0.12</v>
@@ -3461,10 +3628,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" t="n">
         <v>361</v>
@@ -3476,7 +3643,7 @@
         <v>0.003</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G13" t="n">
         <v>42.9</v>
@@ -3487,10 +3654,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" t="n">
         <v>326.5</v>
@@ -3502,7 +3669,7 @@
         <v>0.003</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G14" t="n">
         <v>1.05</v>
@@ -3513,10 +3680,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" t="n">
         <v>370</v>
@@ -3528,7 +3695,7 @@
         <v>0.002</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
         <v>1.99</v>
@@ -3539,10 +3706,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" t="n">
         <v>166</v>
@@ -3554,7 +3721,7 @@
         <v>0.006</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G16" t="n">
         <v>0.49</v>
@@ -3565,10 +3732,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C17" t="n">
         <v>26</v>
@@ -3580,7 +3747,7 @@
         <v>0.122</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
         <v>1.72</v>
@@ -3591,10 +3758,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C18" t="n">
         <v>214</v>
@@ -3606,7 +3773,7 @@
         <v>0.005</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18" t="n">
         <v>0.47</v>
@@ -3617,10 +3784,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C19" t="n">
         <v>46</v>
@@ -3632,7 +3799,7 @@
         <v>0.021</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" t="n">
         <v>0.52</v>
@@ -3643,10 +3810,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C20" t="n">
         <v>41</v>
@@ -3658,7 +3825,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G20" t="n">
         <v>1.79</v>
@@ -3669,10 +3836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C21" t="n">
         <v>50</v>
@@ -3684,7 +3851,7 @@
         <v>0.071</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G21" t="n">
         <v>1.15</v>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -563,6 +563,9 @@
   </si>
   <si>
     <t xml:space="preserve">Verdächtig_Anzahl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pegel_unzuverl</t>
   </si>
 </sst>
 </file>
@@ -632,9 +635,9 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:G4" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:G4"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:H4" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H4"/>
+  <tableColumns count="8">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="Ereignisse"/>
     <tableColumn id="3" name="Ø_Peak_cm"/>
@@ -642,6 +645,7 @@
     <tableColumn id="5" name="Sturzflut_Anzahl"/>
     <tableColumn id="6" name="Regen_Anzahl"/>
     <tableColumn id="7" name="Verdächtig_Anzahl"/>
+    <tableColumn id="8" name="Pegel_unzuverl"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3196,6 +3200,7 @@
     <col min="5" max="5" width="16.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="12.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="18.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="14.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3220,6 +3225,9 @@
       <c r="G1" t="s">
         <v>182</v>
       </c>
+      <c r="H1" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -3241,6 +3249,9 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3266,6 +3277,9 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -3287,6 +3301,9 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -1032,7 +1032,7 @@
         <v>17</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J2" t="n">
         <v>1.2</v>
@@ -1073,7 +1073,7 @@
         <v>22</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="J3" t="n">
         <v>0.12</v>
@@ -1114,7 +1114,7 @@
         <v>17</v>
       </c>
       <c r="I4" t="n">
-        <v>3.72</v>
+        <v>0.93</v>
       </c>
       <c r="J4" t="n">
         <v>3.6</v>
@@ -1155,7 +1155,7 @@
         <v>17</v>
       </c>
       <c r="I5" t="n">
-        <v>1.15</v>
+        <v>0.23</v>
       </c>
       <c r="J5" t="n">
         <v>0.84</v>
@@ -1196,7 +1196,7 @@
         <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>29.75</v>
+        <v>5.95</v>
       </c>
       <c r="J6" t="n">
         <v>5.16</v>
@@ -1237,7 +1237,7 @@
         <v>17</v>
       </c>
       <c r="I7" t="n">
-        <v>42.9</v>
+        <v>8.58</v>
       </c>
       <c r="J7" t="n">
         <v>9.48</v>
@@ -1278,7 +1278,7 @@
         <v>17</v>
       </c>
       <c r="I8" t="n">
-        <v>44.02</v>
+        <v>6.36</v>
       </c>
       <c r="J8" t="n">
         <v>20.16</v>
@@ -3377,7 +3377,7 @@
         <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H2" t="n">
         <v>0.12</v>
@@ -3559,7 +3559,7 @@
         <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>3.72</v>
+        <v>0.93</v>
       </c>
       <c r="H9" t="n">
         <v>3.6</v>
@@ -3663,7 +3663,7 @@
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>42.9</v>
+        <v>8.58</v>
       </c>
       <c r="H13" t="n">
         <v>9.48</v>
@@ -3871,7 +3871,7 @@
         <v>17</v>
       </c>
       <c r="G21" t="n">
-        <v>1.15</v>
+        <v>0.23</v>
       </c>
       <c r="H21" t="n">
         <v>0.84</v>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -55,6 +55,21 @@
     <t xml:space="preserve">points_count</t>
   </si>
   <si>
+    <t xml:space="preserve">Wasserstraße_Springorum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/26 05:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/27 01:04:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/26 15:46:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
     <t xml:space="preserve">An_der_Kost</t>
   </si>
   <si>
@@ -65,12 +80,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026/06/21 01:51:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wasserstraße_Springorum</t>
   </si>
   <si>
     <t xml:space="preserve">2026/06/06 18:56:00</t>
@@ -613,8 +622,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M54" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M55" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M55"/>
   <tableColumns count="13">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -1017,25 +1026,25 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>1160.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.035</v>
+        <v>0.002</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1</v>
+        <v>9.3</v>
       </c>
       <c r="J2" t="n">
-        <v>1.2</v>
+        <v>62.52</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
@@ -1044,7 +1053,7 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>67</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1067,25 @@
         <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1</v>
+        <v>0.3</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>292.5</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>1.694</v>
+        <v>0.035</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.12</v>
+        <v>1.2</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
@@ -1085,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>586</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4">
@@ -1093,31 +1102,31 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.694</v>
+      </c>
+      <c r="H4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="n">
-        <v>105.5</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>0.01</v>
       </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.93</v>
-      </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>0.12</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -1126,12 +1135,12 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>212</v>
+        <v>586</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -1140,25 +1149,25 @@
         <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>105.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.071</v>
+        <v>0.01</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
       </c>
       <c r="I5" t="n">
-        <v>0.23</v>
+        <v>0.93</v>
       </c>
       <c r="J5" t="n">
-        <v>0.84</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -1167,12 +1176,12 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>101</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -1181,25 +1190,25 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
       </c>
       <c r="F6" t="n">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>0.018</v>
+        <v>0.071</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>5.95</v>
+        <v>0.23</v>
       </c>
       <c r="J6" t="n">
-        <v>5.16</v>
+        <v>0.84</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -1208,12 +1217,12 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>279</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
         <v>32</v>
@@ -1222,25 +1231,25 @@
         <v>33</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E7" t="s">
         <v>34</v>
       </c>
       <c r="F7" t="n">
-        <v>361</v>
+        <v>139</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003</v>
+        <v>0.018</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
       </c>
       <c r="I7" t="n">
-        <v>8.58</v>
+        <v>5.95</v>
       </c>
       <c r="J7" t="n">
-        <v>9.48</v>
+        <v>5.16</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -1249,12 +1258,12 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>723</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
         <v>35</v>
@@ -1263,25 +1272,25 @@
         <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E8" t="s">
         <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>90.5</v>
+        <v>361</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04</v>
+        <v>0.003</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
       </c>
       <c r="I8" t="n">
-        <v>6.36</v>
+        <v>8.58</v>
       </c>
       <c r="J8" t="n">
-        <v>20.16</v>
+        <v>9.48</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -1290,12 +1299,12 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>182</v>
+        <v>723</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
         <v>38</v>
@@ -1304,25 +1313,25 @@
         <v>39</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E9" t="s">
         <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>60.5</v>
+        <v>90.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.054</v>
+        <v>0.04</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
       </c>
       <c r="I9" t="n">
-        <v>2.91</v>
+        <v>6.36</v>
       </c>
       <c r="J9" t="n">
-        <v>7.8</v>
+        <v>20.16</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
@@ -1331,12 +1340,12 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>122</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
         <v>41</v>
@@ -1345,25 +1354,25 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E10" t="s">
         <v>43</v>
       </c>
       <c r="F10" t="n">
-        <v>90</v>
+        <v>60.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01</v>
+        <v>0.054</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
       </c>
       <c r="I10" t="n">
-        <v>1.09</v>
+        <v>2.91</v>
       </c>
       <c r="J10" t="n">
-        <v>2.04</v>
+        <v>7.8</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
@@ -1372,12 +1381,12 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
         <v>44</v>
@@ -1386,22 +1395,22 @@
         <v>45</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E11" t="s">
         <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>50.5</v>
+        <v>90</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>1.89</v>
+        <v>1.09</v>
       </c>
       <c r="J11" t="n">
         <v>2.04</v>
@@ -1413,12 +1422,12 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>102</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
         <v>47</v>
@@ -1433,19 +1442,19 @@
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>50.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08</v>
+        <v>1.89</v>
       </c>
       <c r="J12" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -1454,12 +1463,12 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
         <v>50</v>
@@ -1474,19 +1483,19 @@
         <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>276.5</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>0.013</v>
+        <v>0.039</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
       </c>
       <c r="I13" t="n">
-        <v>8.81</v>
+        <v>0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>0.96</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -1495,12 +1504,12 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>554</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
         <v>53</v>
@@ -1509,25 +1518,25 @@
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E14" t="s">
         <v>55</v>
       </c>
       <c r="F14" t="n">
-        <v>326.5</v>
+        <v>276.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.003</v>
+        <v>0.013</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
       </c>
       <c r="I14" t="n">
-        <v>1.05</v>
+        <v>8.81</v>
       </c>
       <c r="J14" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
@@ -1536,12 +1545,12 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>654</v>
+        <v>554</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
         <v>56</v>
@@ -1550,25 +1559,25 @@
         <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E15" t="s">
         <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>93</v>
+        <v>326.5</v>
       </c>
       <c r="G15" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
       </c>
       <c r="I15" t="n">
-        <v>2.91</v>
+        <v>1.05</v>
       </c>
       <c r="J15" t="n">
-        <v>2.52</v>
+        <v>3.12</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
@@ -1577,12 +1586,12 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>187</v>
+        <v>654</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
         <v>59</v>
@@ -1591,25 +1600,25 @@
         <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E16" t="s">
         <v>61</v>
       </c>
       <c r="F16" t="n">
-        <v>370</v>
+        <v>93</v>
       </c>
       <c r="G16" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
       </c>
       <c r="I16" t="n">
-        <v>1.99</v>
+        <v>2.91</v>
       </c>
       <c r="J16" t="n">
-        <v>1.56</v>
+        <v>2.52</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -1618,12 +1627,12 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>371</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
         <v>62</v>
@@ -1632,25 +1641,25 @@
         <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E17" t="s">
         <v>64</v>
       </c>
       <c r="F17" t="n">
-        <v>127</v>
+        <v>370</v>
       </c>
       <c r="G17" t="n">
-        <v>0.129</v>
+        <v>0.002</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
       </c>
       <c r="I17" t="n">
-        <v>4.49</v>
+        <v>1.99</v>
       </c>
       <c r="J17" t="n">
-        <v>4.68</v>
+        <v>1.56</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -1659,12 +1668,12 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>128</v>
+        <v>371</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
         <v>65</v>
@@ -1679,19 +1688,19 @@
         <v>67</v>
       </c>
       <c r="F18" t="n">
-        <v>322</v>
+        <v>127</v>
       </c>
       <c r="G18" t="n">
-        <v>0.004</v>
+        <v>0.129</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
       </c>
       <c r="I18" t="n">
-        <v>0.43</v>
+        <v>4.49</v>
       </c>
       <c r="J18" t="n">
-        <v>2.52</v>
+        <v>4.68</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
@@ -1700,12 +1709,12 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>323</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>68</v>
@@ -1720,19 +1729,19 @@
         <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>112</v>
+        <v>322</v>
       </c>
       <c r="G19" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
       </c>
       <c r="I19" t="n">
-        <v>0.18</v>
+        <v>0.43</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>2.52</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
@@ -1741,12 +1750,12 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>113</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>71</v>
@@ -1755,25 +1764,25 @@
         <v>72</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E20" t="s">
         <v>73</v>
       </c>
       <c r="F20" t="n">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="G20" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
       </c>
       <c r="I20" t="n">
-        <v>0.49</v>
+        <v>0.18</v>
       </c>
       <c r="J20" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
@@ -1782,39 +1791,39 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>332</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
         <v>74</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>75</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E21" t="s">
         <v>76</v>
       </c>
-      <c r="D21" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E21" t="s">
-        <v>77</v>
-      </c>
       <c r="F21" t="n">
-        <v>1298</v>
+        <v>166</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>2.18</v>
+        <v>0.49</v>
       </c>
       <c r="J21" t="n">
-        <v>2.04</v>
+        <v>0.72</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
@@ -1823,12 +1832,12 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>2601</v>
+        <v>332</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B22" t="s">
         <v>78</v>
@@ -1843,19 +1852,19 @@
         <v>80</v>
       </c>
       <c r="F22" t="n">
-        <v>864</v>
+        <v>1298</v>
       </c>
       <c r="G22" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
       </c>
       <c r="I22" t="n">
-        <v>0.61</v>
+        <v>2.18</v>
       </c>
       <c r="J22" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
@@ -1864,12 +1873,12 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>1732</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B23" t="s">
         <v>81</v>
@@ -1878,25 +1887,25 @@
         <v>82</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E23" t="s">
         <v>83</v>
       </c>
       <c r="F23" t="n">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G23" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
       </c>
       <c r="I23" t="n">
-        <v>1.29</v>
+        <v>0.61</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8</v>
+        <v>0.96</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
@@ -1905,12 +1914,12 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>1729</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B24" t="s">
         <v>84</v>
@@ -1919,13 +1928,13 @@
         <v>85</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E24" t="s">
         <v>86</v>
       </c>
       <c r="F24" t="n">
-        <v>462</v>
+        <v>862</v>
       </c>
       <c r="G24" t="n">
         <v>0.005</v>
@@ -1934,10 +1943,10 @@
         <v>17</v>
       </c>
       <c r="I24" t="n">
-        <v>0.11</v>
+        <v>1.29</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
@@ -1946,12 +1955,12 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>929</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s">
         <v>87</v>
@@ -1960,25 +1969,25 @@
         <v>88</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E25" t="s">
         <v>89</v>
       </c>
       <c r="F25" t="n">
-        <v>83</v>
+        <v>462</v>
       </c>
       <c r="G25" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
       </c>
       <c r="I25" t="n">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="J25" t="n">
-        <v>0.84</v>
+        <v>0.6</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
@@ -1987,12 +1996,12 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>168</v>
+        <v>929</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s">
         <v>90</v>
@@ -2001,25 +2010,25 @@
         <v>91</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E26" t="s">
         <v>92</v>
       </c>
       <c r="F26" t="n">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="G26" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
       </c>
       <c r="I26" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="J26" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
@@ -2028,12 +2037,12 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>217</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
         <v>93</v>
@@ -2042,25 +2051,25 @@
         <v>94</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E27" t="s">
         <v>95</v>
       </c>
       <c r="F27" t="n">
-        <v>349</v>
+        <v>216</v>
       </c>
       <c r="G27" t="n">
-        <v>0.129</v>
+        <v>0.005</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
       </c>
       <c r="I27" t="n">
-        <v>0.76</v>
+        <v>0.44</v>
       </c>
       <c r="J27" t="n">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
@@ -2069,12 +2078,12 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>346</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
         <v>96</v>
@@ -2089,19 +2098,19 @@
         <v>98</v>
       </c>
       <c r="F28" t="n">
-        <v>69</v>
+        <v>349</v>
       </c>
       <c r="G28" t="n">
-        <v>0.025</v>
+        <v>0.129</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
       </c>
       <c r="I28" t="n">
-        <v>0.03</v>
+        <v>0.76</v>
       </c>
       <c r="J28" t="n">
-        <v>0.24</v>
+        <v>1.08</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
@@ -2110,12 +2119,12 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>70</v>
+        <v>346</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="B29" t="s">
         <v>99</v>
@@ -2124,25 +2133,25 @@
         <v>100</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E29" t="s">
         <v>101</v>
       </c>
       <c r="F29" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="G29" t="n">
-        <v>0.012</v>
+        <v>0.025</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.75</v>
+        <v>0.03</v>
       </c>
       <c r="J29" t="n">
-        <v>2.4</v>
+        <v>0.24</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
@@ -2151,12 +2160,12 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B30" t="s">
         <v>102</v>
@@ -2165,25 +2174,25 @@
         <v>103</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E30" t="s">
         <v>104</v>
       </c>
       <c r="F30" t="n">
-        <v>438</v>
+        <v>101</v>
       </c>
       <c r="G30" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
       </c>
       <c r="I30" t="n">
-        <v>0.12</v>
+        <v>0.75</v>
       </c>
       <c r="J30" t="n">
-        <v>0.36</v>
+        <v>2.4</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
@@ -2192,12 +2201,12 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>435</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B31" t="s">
         <v>105</v>
@@ -2206,25 +2215,25 @@
         <v>106</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E31" t="s">
         <v>107</v>
       </c>
       <c r="F31" t="n">
-        <v>336</v>
+        <v>438</v>
       </c>
       <c r="G31" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
       </c>
       <c r="I31" t="n">
-        <v>9.49</v>
+        <v>0.12</v>
       </c>
       <c r="J31" t="n">
-        <v>5.4</v>
+        <v>0.36</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
@@ -2233,12 +2242,12 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>337</v>
+        <v>435</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
         <v>108</v>
@@ -2247,25 +2256,25 @@
         <v>109</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E32" t="s">
         <v>110</v>
       </c>
       <c r="F32" t="n">
-        <v>193</v>
+        <v>336</v>
       </c>
       <c r="G32" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
       </c>
       <c r="I32" t="n">
-        <v>5.68</v>
+        <v>9.49</v>
       </c>
       <c r="J32" t="n">
-        <v>3.96</v>
+        <v>5.4</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
@@ -2274,12 +2283,12 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>192</v>
+        <v>337</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B33" t="s">
         <v>111</v>
@@ -2294,19 +2303,19 @@
         <v>113</v>
       </c>
       <c r="F33" t="n">
-        <v>281</v>
+        <v>193</v>
       </c>
       <c r="G33" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.68</v>
+        <v>5.68</v>
       </c>
       <c r="J33" t="n">
-        <v>1.2</v>
+        <v>3.96</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
@@ -2315,12 +2324,12 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>282</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B34" t="s">
         <v>114</v>
@@ -2329,25 +2338,25 @@
         <v>115</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E34" t="s">
         <v>116</v>
       </c>
       <c r="F34" t="n">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="G34" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
       </c>
       <c r="I34" t="n">
-        <v>2.38</v>
+        <v>0.68</v>
       </c>
       <c r="J34" t="n">
-        <v>3.36</v>
+        <v>1.2</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
@@ -2356,12 +2365,12 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>331</v>
+        <v>282</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B35" t="s">
         <v>117</v>
@@ -2370,25 +2379,25 @@
         <v>118</v>
       </c>
       <c r="D35" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="E35" t="s">
         <v>119</v>
       </c>
       <c r="F35" t="n">
-        <v>96</v>
+        <v>332</v>
       </c>
       <c r="G35" t="n">
-        <v>0.082</v>
+        <v>0.006</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
       </c>
       <c r="I35" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="J35" t="n">
-        <v>8.76</v>
+        <v>3.36</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
@@ -2397,12 +2406,12 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>95</v>
+        <v>331</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B36" t="s">
         <v>120</v>
@@ -2411,25 +2420,25 @@
         <v>121</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="E36" t="s">
         <v>122</v>
       </c>
       <c r="F36" t="n">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="G36" t="n">
-        <v>0.122</v>
+        <v>0.082</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
       </c>
       <c r="I36" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="J36" t="n">
-        <v>3.36</v>
+        <v>8.76</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
@@ -2438,12 +2447,12 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>27</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B37" t="s">
         <v>123</v>
@@ -2452,25 +2461,25 @@
         <v>124</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E37" t="s">
         <v>125</v>
       </c>
       <c r="F37" t="n">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="G37" t="n">
-        <v>0.015</v>
+        <v>0.122</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
       </c>
       <c r="I37" t="n">
-        <v>0.93</v>
+        <v>1.72</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
@@ -2479,12 +2488,12 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>78</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B38" t="s">
         <v>126</v>
@@ -2493,25 +2502,25 @@
         <v>127</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E38" t="s">
         <v>128</v>
       </c>
       <c r="F38" t="n">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="G38" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
       </c>
       <c r="I38" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="J38" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
@@ -2520,12 +2529,12 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>213</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B39" t="s">
         <v>129</v>
@@ -2540,19 +2549,19 @@
         <v>131</v>
       </c>
       <c r="F39" t="n">
-        <v>46</v>
+        <v>214</v>
       </c>
       <c r="G39" t="n">
-        <v>0.021</v>
+        <v>0.005</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="J39" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
@@ -2561,12 +2570,12 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>47</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B40" t="s">
         <v>132</v>
@@ -2575,25 +2584,25 @@
         <v>133</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E40" t="s">
         <v>134</v>
       </c>
       <c r="F40" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="G40" t="n">
-        <v>0.097</v>
+        <v>0.021</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
       </c>
       <c r="I40" t="n">
-        <v>3.46</v>
+        <v>0.52</v>
       </c>
       <c r="J40" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
@@ -2602,12 +2611,12 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B41" t="s">
         <v>135</v>
@@ -2616,25 +2625,25 @@
         <v>136</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E41" t="s">
         <v>137</v>
       </c>
       <c r="F41" t="n">
-        <v>337</v>
+        <v>7</v>
       </c>
       <c r="G41" t="n">
-        <v>0.01</v>
+        <v>0.097</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
       </c>
       <c r="I41" t="n">
-        <v>6.39</v>
+        <v>3.46</v>
       </c>
       <c r="J41" t="n">
-        <v>10.92</v>
+        <v>6.6</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
@@ -2643,12 +2652,12 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>336</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="B42" t="s">
         <v>138</v>
@@ -2657,25 +2666,25 @@
         <v>139</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E42" t="s">
         <v>140</v>
       </c>
       <c r="F42" t="n">
-        <v>41</v>
+        <v>337</v>
       </c>
       <c r="G42" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
       </c>
       <c r="I42" t="n">
-        <v>1.79</v>
+        <v>6.39</v>
       </c>
       <c r="J42" t="n">
-        <v>3.36</v>
+        <v>10.92</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
@@ -2684,12 +2693,12 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>42</v>
+        <v>336</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="B43" t="s">
         <v>141</v>
@@ -2698,25 +2707,25 @@
         <v>142</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E43" t="s">
         <v>143</v>
       </c>
       <c r="F43" t="n">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="G43" t="n">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
       </c>
       <c r="I43" t="n">
-        <v>1.34</v>
+        <v>1.79</v>
       </c>
       <c r="J43" t="n">
-        <v>1.2</v>
+        <v>3.36</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
@@ -2725,12 +2734,12 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B44" t="s">
         <v>144</v>
@@ -2745,19 +2754,19 @@
         <v>146</v>
       </c>
       <c r="F44" t="n">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="G44" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
       </c>
       <c r="I44" t="n">
-        <v>0.03</v>
+        <v>1.34</v>
       </c>
       <c r="J44" t="n">
-        <v>0.36</v>
+        <v>1.2</v>
       </c>
       <c r="K44" t="b">
         <v>1</v>
@@ -2766,12 +2775,12 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>135</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B45" t="s">
         <v>147</v>
@@ -2786,19 +2795,19 @@
         <v>149</v>
       </c>
       <c r="F45" t="n">
-        <v>720</v>
+        <v>134</v>
       </c>
       <c r="G45" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H45" t="s">
         <v>17</v>
       </c>
       <c r="I45" t="n">
-        <v>4.71</v>
+        <v>0.03</v>
       </c>
       <c r="J45" t="n">
-        <v>8.04</v>
+        <v>0.36</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
@@ -2807,12 +2816,12 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>717</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B46" t="s">
         <v>150</v>
@@ -2827,19 +2836,19 @@
         <v>152</v>
       </c>
       <c r="F46" t="n">
-        <v>773</v>
+        <v>720</v>
       </c>
       <c r="G46" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
       </c>
       <c r="I46" t="n">
-        <v>0.37</v>
+        <v>4.71</v>
       </c>
       <c r="J46" t="n">
-        <v>1.56</v>
+        <v>8.04</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
@@ -2848,12 +2857,12 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>774</v>
+        <v>717</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B47" t="s">
         <v>153</v>
@@ -2862,25 +2871,25 @@
         <v>154</v>
       </c>
       <c r="D47" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E47" t="s">
         <v>155</v>
       </c>
       <c r="F47" t="n">
-        <v>735</v>
+        <v>773</v>
       </c>
       <c r="G47" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
       </c>
       <c r="I47" t="n">
-        <v>0.69</v>
+        <v>0.37</v>
       </c>
       <c r="J47" t="n">
-        <v>3.24</v>
+        <v>1.56</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
@@ -2889,12 +2898,12 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>734</v>
+        <v>774</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B48" t="s">
         <v>156</v>
@@ -2903,13 +2912,13 @@
         <v>157</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E48" t="s">
         <v>158</v>
       </c>
       <c r="F48" t="n">
-        <v>1100</v>
+        <v>735</v>
       </c>
       <c r="G48" t="n">
         <v>0.002</v>
@@ -2918,10 +2927,10 @@
         <v>17</v>
       </c>
       <c r="I48" t="n">
-        <v>6.45</v>
+        <v>0.69</v>
       </c>
       <c r="J48" t="n">
-        <v>14.4</v>
+        <v>3.24</v>
       </c>
       <c r="K48" t="b">
         <v>1</v>
@@ -2930,12 +2939,12 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>1097</v>
+        <v>734</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B49" t="s">
         <v>159</v>
@@ -2944,25 +2953,25 @@
         <v>160</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E49" t="s">
         <v>161</v>
       </c>
       <c r="F49" t="n">
-        <v>498</v>
+        <v>1100</v>
       </c>
       <c r="G49" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
       </c>
       <c r="I49" t="n">
-        <v>1.38</v>
+        <v>6.45</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>14.4</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
@@ -2971,12 +2980,12 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>495</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B50" t="s">
         <v>162</v>
@@ -2985,25 +2994,25 @@
         <v>163</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E50" t="s">
         <v>164</v>
       </c>
       <c r="F50" t="n">
-        <v>257</v>
+        <v>498</v>
       </c>
       <c r="G50" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="H50" t="s">
         <v>17</v>
       </c>
       <c r="I50" t="n">
-        <v>6.15</v>
+        <v>1.38</v>
       </c>
       <c r="J50" t="n">
-        <v>9.48</v>
+        <v>3</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
@@ -3012,12 +3021,12 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>258</v>
+        <v>495</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B51" t="s">
         <v>165</v>
@@ -3026,25 +3035,25 @@
         <v>166</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E51" t="s">
         <v>167</v>
       </c>
       <c r="F51" t="n">
-        <v>458</v>
+        <v>257</v>
       </c>
       <c r="G51" t="n">
-        <v>0.059</v>
+        <v>0.003</v>
       </c>
       <c r="H51" t="s">
         <v>17</v>
       </c>
       <c r="I51" t="n">
-        <v>2.47</v>
+        <v>6.15</v>
       </c>
       <c r="J51" t="n">
-        <v>7.2</v>
+        <v>9.48</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
@@ -3053,12 +3062,12 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>453</v>
+        <v>258</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B52" t="s">
         <v>168</v>
@@ -3073,19 +3082,19 @@
         <v>170</v>
       </c>
       <c r="F52" t="n">
-        <v>923</v>
+        <v>458</v>
       </c>
       <c r="G52" t="n">
-        <v>0.002</v>
+        <v>0.059</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
       </c>
       <c r="I52" t="n">
-        <v>3.76</v>
+        <v>2.47</v>
       </c>
       <c r="J52" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
@@ -3094,12 +3103,12 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>918</v>
+        <v>453</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B53" t="s">
         <v>171</v>
@@ -3108,25 +3117,25 @@
         <v>172</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E53" t="s">
         <v>173</v>
       </c>
       <c r="F53" t="n">
-        <v>1012</v>
+        <v>923</v>
       </c>
       <c r="G53" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
       </c>
       <c r="I53" t="n">
-        <v>0.08</v>
+        <v>3.76</v>
       </c>
       <c r="J53" t="n">
-        <v>0.72</v>
+        <v>5.4</v>
       </c>
       <c r="K53" t="b">
         <v>1</v>
@@ -3135,12 +3144,12 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>1211</v>
+        <v>918</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B54" t="s">
         <v>174</v>
@@ -3149,33 +3158,74 @@
         <v>175</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E54" t="s">
         <v>176</v>
       </c>
       <c r="F54" t="n">
+        <v>1012</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H54" t="s">
+        <v>17</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
+      <c r="L54" t="b">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>18</v>
+      </c>
+      <c r="B55" t="s">
+        <v>177</v>
+      </c>
+      <c r="C55" t="s">
+        <v>178</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E55" t="s">
+        <v>179</v>
+      </c>
+      <c r="F55" t="n">
         <v>344.5</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G55" t="n">
         <v>0.002</v>
       </c>
-      <c r="H54" t="s">
-        <v>17</v>
-      </c>
-      <c r="I54" t="n">
+      <c r="H55" t="s">
+        <v>17</v>
+      </c>
+      <c r="I55" t="n">
         <v>0.32</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J55" t="n">
         <v>2.04</v>
       </c>
-      <c r="K54" t="b">
-        <v>1</v>
-      </c>
-      <c r="L54" t="b">
-        <v>1</v>
-      </c>
-      <c r="M54" t="n">
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" t="b">
+        <v>1</v>
+      </c>
+      <c r="M55" t="n">
         <v>688</v>
       </c>
     </row>
@@ -3208,30 +3258,30 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B2" t="n">
         <v>45</v>
@@ -3257,7 +3307,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B3" t="n">
         <v>7</v>
@@ -3283,13 +3333,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>6.1</v>
+        <v>3.6</v>
       </c>
       <c r="D4" t="n">
         <v>6.1</v>
@@ -3359,10 +3409,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
         <v>292.5</v>
@@ -3374,7 +3424,7 @@
         <v>1.694</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
         <v>0.01</v>
@@ -3385,10 +3435,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C3" t="n">
         <v>96</v>
@@ -3411,198 +3461,198 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>862</v>
+        <v>1160.5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>1.29</v>
+        <v>9.3</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8</v>
+        <v>62.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C5" t="n">
-        <v>1298</v>
+        <v>862</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>2.18</v>
+        <v>1.29</v>
       </c>
       <c r="H5" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="n">
-        <v>864</v>
+        <v>1298</v>
       </c>
       <c r="D6" t="n">
         <v>0.8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>0.61</v>
+        <v>2.18</v>
       </c>
       <c r="H6" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C7" t="n">
-        <v>83</v>
+        <v>864</v>
       </c>
       <c r="D7" t="n">
         <v>0.8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="H7" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>735</v>
+        <v>83</v>
       </c>
       <c r="D8" t="n">
         <v>0.8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>0.69</v>
+        <v>0.46</v>
       </c>
       <c r="H8" t="n">
-        <v>3.24</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>156</v>
       </c>
       <c r="C9" t="n">
-        <v>105.5</v>
+        <v>735</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>0.93</v>
+        <v>0.69</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>105.5</v>
       </c>
       <c r="D10" t="n">
         <v>0.7</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="n">
-        <v>0.44</v>
+        <v>0.93</v>
       </c>
       <c r="H10" t="n">
-        <v>0.96</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C11" t="n">
-        <v>462</v>
+        <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E11" t="n">
         <v>0.005</v>
@@ -3611,73 +3661,73 @@
         <v>17</v>
       </c>
       <c r="G11" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C12" t="n">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="D12" t="n">
         <v>0.6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="H12" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="C13" t="n">
-        <v>361</v>
+        <v>438</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="F13" t="s">
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>8.58</v>
+        <v>0.12</v>
       </c>
       <c r="H13" t="n">
-        <v>9.48</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C14" t="n">
-        <v>326.5</v>
+        <v>361</v>
       </c>
       <c r="D14" t="n">
         <v>0.5</v>
@@ -3689,192 +3739,192 @@
         <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>1.05</v>
+        <v>8.58</v>
       </c>
       <c r="H14" t="n">
-        <v>3.12</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C15" t="n">
-        <v>370</v>
+        <v>326.5</v>
       </c>
       <c r="D15" t="n">
         <v>0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="F15" t="s">
         <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>1.99</v>
+        <v>1.05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.56</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C16" t="n">
-        <v>166</v>
+        <v>370</v>
       </c>
       <c r="D16" t="n">
         <v>0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>0.49</v>
+        <v>1.99</v>
       </c>
       <c r="H16" t="n">
-        <v>0.72</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>166</v>
       </c>
       <c r="D17" t="n">
         <v>0.5</v>
       </c>
       <c r="E17" t="n">
-        <v>0.122</v>
+        <v>0.006</v>
       </c>
       <c r="F17" t="s">
         <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>1.72</v>
+        <v>0.49</v>
       </c>
       <c r="H17" t="n">
-        <v>3.36</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C18" t="n">
-        <v>214</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>0.5</v>
       </c>
       <c r="E18" t="n">
-        <v>0.005</v>
+        <v>0.122</v>
       </c>
       <c r="F18" t="s">
         <v>17</v>
       </c>
       <c r="G18" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>129</v>
       </c>
       <c r="C19" t="n">
-        <v>46</v>
+        <v>214</v>
       </c>
       <c r="D19" t="n">
         <v>0.5</v>
       </c>
       <c r="E19" t="n">
-        <v>0.021</v>
+        <v>0.005</v>
       </c>
       <c r="F19" t="s">
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C20" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
         <v>0.5</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05</v>
+        <v>0.021</v>
       </c>
       <c r="F20" t="s">
         <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>1.79</v>
+        <v>0.52</v>
       </c>
       <c r="H20" t="n">
-        <v>3.36</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>141</v>
       </c>
       <c r="C21" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E21" t="n">
-        <v>0.071</v>
+        <v>0.05</v>
       </c>
       <c r="F21" t="s">
         <v>17</v>
       </c>
       <c r="G21" t="n">
-        <v>0.23</v>
+        <v>1.79</v>
       </c>
       <c r="H21" t="n">
-        <v>0.84</v>
+        <v>3.36</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="263">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -55,6 +55,21 @@
     <t xml:space="preserve">points_count</t>
   </si>
   <si>
+    <t xml:space="preserve">An_der_Kost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/07/16 12:09:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/07/16 17:57:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/07/16 12:54:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wasserstraße_Springorum</t>
   </si>
   <si>
@@ -67,12 +82,6 @@
     <t xml:space="preserve">2026/06/26 15:46:30</t>
   </si>
   <si>
-    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An_der_Kost</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026/06/21 01:43:00</t>
   </si>
   <si>
@@ -82,6 +91,15 @@
     <t xml:space="preserve">2026/06/21 01:51:30</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/06/10 23:22:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/11 17:48:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/11 08:03:30</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/06/06 18:56:00</t>
   </si>
   <si>
@@ -94,6 +112,54 @@
     <t xml:space="preserve">Sturzflut-Ereignis</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/06/06 07:16:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/06 16:50:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/06 13:46:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/04 22:11:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/05 15:28:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/05 14:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regenereignis / Natürlich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/04 14:24:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/04 20:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/04 14:35:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/04 09:45:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/04 14:27:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/04 12:05:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/03 06:12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/03 22:38:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/03 16:16:30</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/05/31 03:42:30</t>
   </si>
   <si>
@@ -103,6 +169,15 @@
     <t xml:space="preserve">2026/05/31 04:49:30</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/05/30 05:52:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/31 04:40:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/30 09:54:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/05/13 13:08:00</t>
   </si>
   <si>
@@ -112,6 +187,15 @@
     <t xml:space="preserve">2026/05/13 13:13:30</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/05/13 08:08:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/13 11:51:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/13 08:40:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/05/11 06:13:00</t>
   </si>
   <si>
@@ -130,6 +214,15 @@
     <t xml:space="preserve">2026/05/06 00:31:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/05/03 12:00:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/03 17:26:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/03 12:11:30</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/04/19 00:35:00</t>
   </si>
   <si>
@@ -166,6 +259,15 @@
     <t xml:space="preserve">2026/03/29 22:44:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/03/29 11:16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 21:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 12:47:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/03/14 08:47:00</t>
   </si>
   <si>
@@ -202,6 +304,15 @@
     <t xml:space="preserve">2026/03/11 14:14:30</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/03/11 05:51:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 12:06:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 11:31:30</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/02/23 21:56:00</t>
   </si>
   <si>
@@ -238,6 +349,24 @@
     <t xml:space="preserve">2026/02/19 11:08:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/02/19 04:48:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 11:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 08:24:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/18 13:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 02:52:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/18 13:41:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/02/16 13:26:00</t>
   </si>
   <si>
@@ -331,6 +460,15 @@
     <t xml:space="preserve">2026/01/07 17:27:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2025/12/09 17:19:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/10 09:41:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/10 07:27:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025/12/08 18:37:00</t>
   </si>
   <si>
@@ -349,6 +487,33 @@
     <t xml:space="preserve">2025/12/07 19:57:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2025/12/05 14:15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/06 04:09:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/06 04:06:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/04 11:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/05 05:10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/04 21:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/02 23:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/03 08:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/03 03:23:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025/12/02 06:34:00</t>
   </si>
   <si>
@@ -394,6 +559,24 @@
     <t xml:space="preserve">2025/11/15 00:55:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2025/11/10 02:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/10 21:25:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/10 12:38:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/02 09:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/03 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/02 18:13:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025/11/01 13:12:00</t>
   </si>
   <si>
@@ -403,6 +586,15 @@
     <t xml:space="preserve">2025/11/01 13:38:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2025/10/29 14:15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/29 21:33:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/29 21:00:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025/10/28 06:47:00</t>
   </si>
   <si>
@@ -421,6 +613,15 @@
     <t xml:space="preserve">2025/10/23 17:20:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2025/10/23 07:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 13:59:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 11:28:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025/10/23 03:37:00</t>
   </si>
   <si>
@@ -430,6 +631,24 @@
     <t xml:space="preserve">2025/10/23 03:40:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2025/10/05 07:28:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/05 11:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/05 09:10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 12:17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/05 01:02:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 20:47:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025/10/04 05:41:00</t>
   </si>
   <si>
@@ -464,6 +683,15 @@
   </si>
   <si>
     <t xml:space="preserve">2025/09/26 21:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/25 09:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/25 14:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/25 14:10:00</t>
   </si>
   <si>
     <t xml:space="preserve">2025/09/22 08:02:00</t>
@@ -622,8 +850,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M55" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M55"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M80" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M80"/>
   <tableColumns count="13">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -1026,25 +1254,25 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="n">
-        <v>1160.5</v>
+        <v>348</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
       </c>
       <c r="I2" t="n">
-        <v>9.3</v>
+        <v>1.17</v>
       </c>
       <c r="J2" t="n">
-        <v>62.52</v>
+        <v>5.04</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
@@ -1053,7 +1281,7 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>2322</v>
+        <v>694</v>
       </c>
     </row>
     <row r="3">
@@ -1067,25 +1295,25 @@
         <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>1160.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.035</v>
+        <v>0.002</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1</v>
+        <v>9.3</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2</v>
+        <v>62.52</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
@@ -1094,7 +1322,7 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>67</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="4">
@@ -1108,25 +1336,25 @@
         <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1</v>
+        <v>0.3</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>292.5</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.694</v>
+        <v>0.035</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.12</v>
+        <v>1.2</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -1135,7 +1363,7 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>586</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5">
@@ -1143,31 +1371,31 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
         <v>26</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E5" t="s">
         <v>27</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
       <c r="F5" t="n">
-        <v>105.5</v>
+        <v>1106</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
       </c>
       <c r="I5" t="n">
-        <v>0.93</v>
+        <v>0.94</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>2.04</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -1176,7 +1404,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>212</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="6">
@@ -1184,31 +1412,31 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E6" t="s">
         <v>30</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.694</v>
+      </c>
+      <c r="H6" t="s">
         <v>31</v>
       </c>
-      <c r="F6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.071</v>
-      </c>
-      <c r="H6" t="s">
-        <v>17</v>
-      </c>
       <c r="I6" t="n">
-        <v>0.23</v>
+        <v>0.01</v>
       </c>
       <c r="J6" t="n">
-        <v>0.84</v>
+        <v>0.12</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -1217,7 +1445,7 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>101</v>
+        <v>586</v>
       </c>
     </row>
     <row r="7">
@@ -1231,25 +1459,25 @@
         <v>33</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="s">
         <v>34</v>
       </c>
       <c r="F7" t="n">
-        <v>139</v>
+        <v>573.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.018</v>
+        <v>0.003</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
       </c>
       <c r="I7" t="n">
-        <v>5.95</v>
+        <v>0.46</v>
       </c>
       <c r="J7" t="n">
-        <v>5.16</v>
+        <v>2.16</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -1258,7 +1486,7 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>279</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="8">
@@ -1272,25 +1500,25 @@
         <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="E8" t="s">
         <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>361</v>
+        <v>1037.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I8" t="n">
-        <v>8.58</v>
+        <v>6.03</v>
       </c>
       <c r="J8" t="n">
-        <v>9.48</v>
+        <v>21</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -1299,39 +1527,39 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>723</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" t="n">
-        <v>90.5</v>
+        <v>336</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04</v>
+        <v>0.069</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
       </c>
       <c r="I9" t="n">
-        <v>6.36</v>
+        <v>4.47</v>
       </c>
       <c r="J9" t="n">
-        <v>20.16</v>
+        <v>32.64</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
@@ -1340,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>182</v>
+        <v>673</v>
       </c>
     </row>
     <row r="10">
@@ -1348,31 +1576,31 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F10" t="n">
-        <v>60.5</v>
+        <v>282.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.054</v>
+        <v>0.006</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
       </c>
       <c r="I10" t="n">
-        <v>2.91</v>
+        <v>1.95</v>
       </c>
       <c r="J10" t="n">
-        <v>7.8</v>
+        <v>9.36</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
@@ -1381,7 +1609,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>122</v>
+        <v>566</v>
       </c>
     </row>
     <row r="11">
@@ -1389,31 +1617,31 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F11" t="n">
-        <v>90</v>
+        <v>986</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>2.04</v>
+        <v>5.76</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -1422,39 +1650,39 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>181</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>50.5</v>
+        <v>105.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
       </c>
       <c r="I12" t="n">
-        <v>1.89</v>
+        <v>0.93</v>
       </c>
       <c r="J12" t="n">
-        <v>2.04</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -1463,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>102</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13">
@@ -1471,31 +1699,31 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>1368.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.039</v>
+        <v>0.005</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.96</v>
+        <v>1.44</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -1504,39 +1732,39 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>81</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F14" t="n">
-        <v>276.5</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
-        <v>0.013</v>
+        <v>0.071</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
       </c>
       <c r="I14" t="n">
-        <v>8.81</v>
+        <v>0.23</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>0.84</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
@@ -1545,7 +1773,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>554</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1553,31 +1781,31 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F15" t="n">
-        <v>326.5</v>
+        <v>222.5</v>
       </c>
       <c r="G15" t="n">
-        <v>0.003</v>
+        <v>0.028</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
       </c>
       <c r="I15" t="n">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
-        <v>3.12</v>
+        <v>0.72</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
@@ -1586,39 +1814,39 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>654</v>
+        <v>446</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
         <v>0.3</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="G16" t="n">
-        <v>0.005</v>
+        <v>0.018</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
       </c>
       <c r="I16" t="n">
-        <v>2.91</v>
+        <v>5.95</v>
       </c>
       <c r="J16" t="n">
-        <v>2.52</v>
+        <v>5.16</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -1627,39 +1855,39 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>187</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>0.5</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F17" t="n">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="G17" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
       </c>
       <c r="I17" t="n">
-        <v>1.99</v>
+        <v>8.58</v>
       </c>
       <c r="J17" t="n">
-        <v>1.56</v>
+        <v>9.48</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -1668,39 +1896,39 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>371</v>
+        <v>723</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18" t="n">
-        <v>127</v>
+        <v>325.5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.129</v>
+        <v>0.027</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
       </c>
       <c r="I18" t="n">
-        <v>4.49</v>
+        <v>1.04</v>
       </c>
       <c r="J18" t="n">
-        <v>4.68</v>
+        <v>2.88</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
@@ -1709,39 +1937,39 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>128</v>
+        <v>649</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D19" t="n">
         <v>0.4</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F19" t="n">
-        <v>322</v>
+        <v>90.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0.004</v>
+        <v>0.04</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
       </c>
       <c r="I19" t="n">
-        <v>0.43</v>
+        <v>6.36</v>
       </c>
       <c r="J19" t="n">
-        <v>2.52</v>
+        <v>20.16</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
@@ -1750,39 +1978,39 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>323</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F20" t="n">
-        <v>112</v>
+        <v>60.5</v>
       </c>
       <c r="G20" t="n">
-        <v>0.005</v>
+        <v>0.054</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
       </c>
       <c r="I20" t="n">
-        <v>0.18</v>
+        <v>2.91</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>7.8</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
@@ -1791,39 +2019,39 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F21" t="n">
-        <v>166</v>
+        <v>90</v>
       </c>
       <c r="G21" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>0.49</v>
+        <v>1.09</v>
       </c>
       <c r="J21" t="n">
-        <v>0.72</v>
+        <v>2.04</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
@@ -1832,12 +2060,12 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>332</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
         <v>78</v>
@@ -1846,22 +2074,22 @@
         <v>79</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E22" t="s">
         <v>80</v>
       </c>
       <c r="F22" t="n">
-        <v>1298</v>
+        <v>50.5</v>
       </c>
       <c r="G22" t="n">
-        <v>0.001</v>
+        <v>0.03</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
       </c>
       <c r="I22" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="J22" t="n">
         <v>2.04</v>
@@ -1873,12 +2101,12 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>2601</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
         <v>81</v>
@@ -1887,22 +2115,22 @@
         <v>82</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="E23" t="s">
         <v>83</v>
       </c>
       <c r="F23" t="n">
-        <v>864</v>
+        <v>630</v>
       </c>
       <c r="G23" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.61</v>
+        <v>0.77</v>
       </c>
       <c r="J23" t="n">
         <v>0.96</v>
@@ -1914,12 +2142,12 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>1732</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
         <v>84</v>
@@ -1928,25 +2156,25 @@
         <v>85</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="E24" t="s">
         <v>86</v>
       </c>
       <c r="F24" t="n">
-        <v>862</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>0.005</v>
+        <v>0.039</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
       </c>
       <c r="I24" t="n">
-        <v>1.29</v>
+        <v>0.08</v>
       </c>
       <c r="J24" t="n">
-        <v>1.8</v>
+        <v>0.96</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
@@ -1955,12 +2183,12 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1729</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
         <v>87</v>
@@ -1969,25 +2197,25 @@
         <v>88</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E25" t="s">
         <v>89</v>
       </c>
       <c r="F25" t="n">
-        <v>462</v>
+        <v>276.5</v>
       </c>
       <c r="G25" t="n">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
       </c>
       <c r="I25" t="n">
-        <v>0.11</v>
+        <v>8.81</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
@@ -1996,12 +2224,12 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>929</v>
+        <v>554</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
         <v>90</v>
@@ -2010,25 +2238,25 @@
         <v>91</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E26" t="s">
         <v>92</v>
       </c>
       <c r="F26" t="n">
-        <v>83</v>
+        <v>326.5</v>
       </c>
       <c r="G26" t="n">
-        <v>0.014</v>
+        <v>0.003</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
       </c>
       <c r="I26" t="n">
-        <v>0.46</v>
+        <v>1.05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.84</v>
+        <v>3.12</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
@@ -2037,12 +2265,12 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>168</v>
+        <v>654</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
         <v>93</v>
@@ -2051,13 +2279,13 @@
         <v>94</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="E27" t="s">
         <v>95</v>
       </c>
       <c r="F27" t="n">
-        <v>216</v>
+        <v>93</v>
       </c>
       <c r="G27" t="n">
         <v>0.005</v>
@@ -2066,10 +2294,10 @@
         <v>17</v>
       </c>
       <c r="I27" t="n">
-        <v>0.44</v>
+        <v>2.91</v>
       </c>
       <c r="J27" t="n">
-        <v>0.96</v>
+        <v>2.52</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
@@ -2078,7 +2306,7 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>217</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28">
@@ -2092,25 +2320,25 @@
         <v>97</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4</v>
+        <v>6.5</v>
       </c>
       <c r="E28" t="s">
         <v>98</v>
       </c>
       <c r="F28" t="n">
-        <v>349</v>
+        <v>374.5</v>
       </c>
       <c r="G28" t="n">
-        <v>0.129</v>
+        <v>0.019</v>
       </c>
       <c r="H28" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I28" t="n">
-        <v>0.76</v>
+        <v>1.01</v>
       </c>
       <c r="J28" t="n">
-        <v>1.08</v>
+        <v>4.8</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
@@ -2119,12 +2347,12 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>346</v>
+        <v>750</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
         <v>99</v>
@@ -2133,25 +2361,25 @@
         <v>100</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E29" t="s">
         <v>101</v>
       </c>
       <c r="F29" t="n">
-        <v>69</v>
+        <v>370</v>
       </c>
       <c r="G29" t="n">
-        <v>0.025</v>
+        <v>0.002</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.03</v>
+        <v>1.99</v>
       </c>
       <c r="J29" t="n">
-        <v>0.24</v>
+        <v>1.56</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
@@ -2160,12 +2388,12 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>70</v>
+        <v>371</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
         <v>102</v>
@@ -2174,25 +2402,25 @@
         <v>103</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E30" t="s">
         <v>104</v>
       </c>
       <c r="F30" t="n">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="G30" t="n">
-        <v>0.012</v>
+        <v>0.129</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
       </c>
       <c r="I30" t="n">
-        <v>0.75</v>
+        <v>4.49</v>
       </c>
       <c r="J30" t="n">
-        <v>2.4</v>
+        <v>4.68</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
@@ -2201,12 +2429,12 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>102</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
         <v>105</v>
@@ -2215,25 +2443,25 @@
         <v>106</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E31" t="s">
         <v>107</v>
       </c>
       <c r="F31" t="n">
-        <v>438</v>
+        <v>322</v>
       </c>
       <c r="G31" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
       </c>
       <c r="I31" t="n">
-        <v>0.12</v>
+        <v>0.43</v>
       </c>
       <c r="J31" t="n">
-        <v>0.36</v>
+        <v>2.52</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
@@ -2242,12 +2470,12 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>435</v>
+        <v>323</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
         <v>108</v>
@@ -2262,19 +2490,19 @@
         <v>110</v>
       </c>
       <c r="F32" t="n">
-        <v>336</v>
+        <v>112</v>
       </c>
       <c r="G32" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
       </c>
       <c r="I32" t="n">
-        <v>9.49</v>
+        <v>0.18</v>
       </c>
       <c r="J32" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
@@ -2283,7 +2511,7 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>337</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33">
@@ -2297,25 +2525,25 @@
         <v>112</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="E33" t="s">
         <v>113</v>
       </c>
       <c r="F33" t="n">
-        <v>193</v>
+        <v>412</v>
       </c>
       <c r="G33" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
       <c r="H33" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I33" t="n">
-        <v>5.68</v>
+        <v>1.91</v>
       </c>
       <c r="J33" t="n">
-        <v>3.96</v>
+        <v>3</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
@@ -2324,7 +2552,7 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>192</v>
+        <v>413</v>
       </c>
     </row>
     <row r="34">
@@ -2338,25 +2566,25 @@
         <v>115</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="E34" t="s">
         <v>116</v>
       </c>
       <c r="F34" t="n">
-        <v>281</v>
+        <v>805</v>
       </c>
       <c r="G34" t="n">
-        <v>0.007</v>
+        <v>0.078</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
       </c>
       <c r="I34" t="n">
-        <v>0.68</v>
+        <v>2.02</v>
       </c>
       <c r="J34" t="n">
-        <v>1.2</v>
+        <v>2.16</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
@@ -2365,12 +2593,12 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>282</v>
+        <v>831</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
         <v>117</v>
@@ -2379,13 +2607,13 @@
         <v>118</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E35" t="s">
         <v>119</v>
       </c>
       <c r="F35" t="n">
-        <v>332</v>
+        <v>166</v>
       </c>
       <c r="G35" t="n">
         <v>0.006</v>
@@ -2394,10 +2622,10 @@
         <v>17</v>
       </c>
       <c r="I35" t="n">
-        <v>2.38</v>
+        <v>0.49</v>
       </c>
       <c r="J35" t="n">
-        <v>3.36</v>
+        <v>0.72</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
@@ -2406,40 +2634,40 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="B36" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C36" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D36" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="E36" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F36" t="n">
-        <v>96</v>
+        <v>1298</v>
       </c>
       <c r="G36" t="n">
-        <v>0.082</v>
+        <v>0.001</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
       </c>
       <c r="I36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J36" t="n">
         <v>2.04</v>
       </c>
-      <c r="J36" t="n">
-        <v>8.76</v>
-      </c>
       <c r="K36" t="b">
         <v>1</v>
       </c>
@@ -2447,39 +2675,39 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>95</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F37" t="n">
-        <v>26</v>
+        <v>864</v>
       </c>
       <c r="G37" t="n">
-        <v>0.122</v>
+        <v>0.002</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
       </c>
       <c r="I37" t="n">
-        <v>1.72</v>
+        <v>0.61</v>
       </c>
       <c r="J37" t="n">
-        <v>3.36</v>
+        <v>0.96</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
@@ -2488,39 +2716,39 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>27</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="B38" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C38" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="E38" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F38" t="n">
-        <v>77</v>
+        <v>862</v>
       </c>
       <c r="G38" t="n">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
       </c>
       <c r="I38" t="n">
-        <v>0.93</v>
+        <v>1.29</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
@@ -2529,27 +2757,27 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>78</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="B39" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C39" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F39" t="n">
-        <v>214</v>
+        <v>462</v>
       </c>
       <c r="G39" t="n">
         <v>0.005</v>
@@ -2558,10 +2786,10 @@
         <v>17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.47</v>
+        <v>0.11</v>
       </c>
       <c r="J39" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
@@ -2570,39 +2798,39 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>213</v>
+        <v>929</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C40" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D40" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E40" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F40" t="n">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="G40" t="n">
-        <v>0.021</v>
+        <v>0.014</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
       </c>
       <c r="I40" t="n">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="J40" t="n">
-        <v>2.4</v>
+        <v>0.84</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
@@ -2611,39 +2839,39 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>47</v>
+        <v>168</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C41" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="E41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>216</v>
       </c>
       <c r="G41" t="n">
-        <v>0.097</v>
+        <v>0.005</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
       </c>
       <c r="I41" t="n">
-        <v>3.46</v>
+        <v>0.44</v>
       </c>
       <c r="J41" t="n">
-        <v>6.6</v>
+        <v>0.96</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
@@ -2652,39 +2880,39 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>8</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B42" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D42" t="n">
         <v>0.4</v>
       </c>
       <c r="E42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F42" t="n">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="G42" t="n">
-        <v>0.01</v>
+        <v>0.129</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
       </c>
       <c r="I42" t="n">
-        <v>6.39</v>
+        <v>0.76</v>
       </c>
       <c r="J42" t="n">
-        <v>10.92</v>
+        <v>1.08</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
@@ -2693,39 +2921,39 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C43" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F43" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="G43" t="n">
-        <v>0.05</v>
+        <v>0.025</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
       </c>
       <c r="I43" t="n">
-        <v>1.79</v>
+        <v>0.03</v>
       </c>
       <c r="J43" t="n">
-        <v>3.36</v>
+        <v>0.24</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
@@ -2734,39 +2962,39 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B44" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D44" t="n">
         <v>0.3</v>
       </c>
       <c r="E44" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F44" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="G44" t="n">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
       </c>
       <c r="I44" t="n">
-        <v>1.34</v>
+        <v>0.75</v>
       </c>
       <c r="J44" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="K44" t="b">
         <v>1</v>
@@ -2775,7 +3003,7 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45">
@@ -2783,31 +3011,31 @@
         <v>18</v>
       </c>
       <c r="B45" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="E45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F45" t="n">
-        <v>134</v>
+        <v>982</v>
       </c>
       <c r="G45" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H45" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I45" t="n">
-        <v>0.03</v>
+        <v>0.58</v>
       </c>
       <c r="J45" t="n">
-        <v>0.36</v>
+        <v>1.44</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
@@ -2816,39 +3044,39 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>135</v>
+        <v>983</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B46" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C46" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="E46" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F46" t="n">
-        <v>720</v>
+        <v>438</v>
       </c>
       <c r="G46" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
       </c>
       <c r="I46" t="n">
-        <v>4.71</v>
+        <v>0.12</v>
       </c>
       <c r="J46" t="n">
-        <v>8.04</v>
+        <v>0.36</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
@@ -2857,39 +3085,39 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>717</v>
+        <v>435</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C47" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F47" t="n">
-        <v>773</v>
+        <v>336</v>
       </c>
       <c r="G47" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
       </c>
       <c r="I47" t="n">
-        <v>0.37</v>
+        <v>9.49</v>
       </c>
       <c r="J47" t="n">
-        <v>1.56</v>
+        <v>5.4</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
@@ -2898,7 +3126,7 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>774</v>
+        <v>337</v>
       </c>
     </row>
     <row r="48">
@@ -2906,31 +3134,31 @@
         <v>18</v>
       </c>
       <c r="B48" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C48" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D48" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="E48" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F48" t="n">
-        <v>735</v>
+        <v>834</v>
       </c>
       <c r="G48" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H48" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I48" t="n">
-        <v>0.69</v>
+        <v>0.3</v>
       </c>
       <c r="J48" t="n">
-        <v>3.24</v>
+        <v>2.52</v>
       </c>
       <c r="K48" t="b">
         <v>1</v>
@@ -2939,7 +3167,7 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>734</v>
+        <v>833</v>
       </c>
     </row>
     <row r="49">
@@ -2947,19 +3175,19 @@
         <v>18</v>
       </c>
       <c r="B49" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C49" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="E49" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F49" t="n">
-        <v>1100</v>
+        <v>1087</v>
       </c>
       <c r="G49" t="n">
         <v>0.002</v>
@@ -2968,10 +3196,10 @@
         <v>17</v>
       </c>
       <c r="I49" t="n">
-        <v>6.45</v>
+        <v>0.57</v>
       </c>
       <c r="J49" t="n">
-        <v>14.4</v>
+        <v>1.44</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
@@ -2980,7 +3208,7 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>1097</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="50">
@@ -2988,31 +3216,31 @@
         <v>18</v>
       </c>
       <c r="B50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3</v>
+        <v>6.1</v>
       </c>
       <c r="E50" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F50" t="n">
-        <v>498</v>
+        <v>581</v>
       </c>
       <c r="G50" t="n">
-        <v>0.006</v>
+        <v>0.023</v>
       </c>
       <c r="H50" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I50" t="n">
-        <v>1.38</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>2.04</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
@@ -3021,39 +3249,39 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>495</v>
+        <v>580</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B51" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E51" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F51" t="n">
-        <v>257</v>
+        <v>193</v>
       </c>
       <c r="G51" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H51" t="s">
         <v>17</v>
       </c>
       <c r="I51" t="n">
-        <v>6.15</v>
+        <v>5.68</v>
       </c>
       <c r="J51" t="n">
-        <v>9.48</v>
+        <v>3.96</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
@@ -3062,39 +3290,39 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>258</v>
+        <v>192</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B52" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D52" t="n">
         <v>0.3</v>
       </c>
       <c r="E52" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F52" t="n">
-        <v>458</v>
+        <v>281</v>
       </c>
       <c r="G52" t="n">
-        <v>0.059</v>
+        <v>0.007</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
       </c>
       <c r="I52" t="n">
-        <v>2.47</v>
+        <v>0.68</v>
       </c>
       <c r="J52" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
@@ -3103,39 +3331,39 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>453</v>
+        <v>282</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F53" t="n">
-        <v>923</v>
+        <v>332</v>
       </c>
       <c r="G53" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
       </c>
       <c r="I53" t="n">
-        <v>3.76</v>
+        <v>2.38</v>
       </c>
       <c r="J53" t="n">
-        <v>5.4</v>
+        <v>3.36</v>
       </c>
       <c r="K53" t="b">
         <v>1</v>
@@ -3144,39 +3372,39 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>918</v>
+        <v>331</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B54" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C54" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D54" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="E54" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F54" t="n">
-        <v>1012</v>
+        <v>96</v>
       </c>
       <c r="G54" t="n">
-        <v>0.003</v>
+        <v>0.082</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
       </c>
       <c r="I54" t="n">
-        <v>0.08</v>
+        <v>2.04</v>
       </c>
       <c r="J54" t="n">
-        <v>0.72</v>
+        <v>8.76</v>
       </c>
       <c r="K54" t="b">
         <v>1</v>
@@ -3185,47 +3413,1072 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>1211</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" t="s">
+        <v>178</v>
+      </c>
+      <c r="C55" t="s">
+        <v>179</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E55" t="s">
+        <v>180</v>
+      </c>
+      <c r="F55" t="n">
+        <v>26</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="H55" t="s">
+        <v>17</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" t="b">
+        <v>1</v>
+      </c>
+      <c r="M55" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
         <v>18</v>
       </c>
-      <c r="B55" t="s">
-        <v>177</v>
-      </c>
-      <c r="C55" t="s">
-        <v>178</v>
-      </c>
-      <c r="D55" t="n">
+      <c r="B56" t="s">
+        <v>181</v>
+      </c>
+      <c r="C56" t="s">
+        <v>182</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E56" t="s">
+        <v>183</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1131</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H56" t="s">
+        <v>17</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J56" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
+      <c r="L56" t="b">
+        <v>1</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57" t="s">
+        <v>184</v>
+      </c>
+      <c r="C57" t="s">
+        <v>185</v>
+      </c>
+      <c r="D57" t="n">
+        <v>7</v>
+      </c>
+      <c r="E57" t="s">
+        <v>186</v>
+      </c>
+      <c r="F57" t="n">
+        <v>892</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="H57" t="s">
+        <v>38</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="J57" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="K57" t="b">
+        <v>1</v>
+      </c>
+      <c r="L57" t="b">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>13</v>
+      </c>
+      <c r="B58" t="s">
+        <v>187</v>
+      </c>
+      <c r="C58" t="s">
+        <v>188</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E58" t="s">
+        <v>189</v>
+      </c>
+      <c r="F58" t="n">
+        <v>77</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H58" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" t="b">
+        <v>1</v>
+      </c>
+      <c r="L58" t="b">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59" t="s">
+        <v>190</v>
+      </c>
+      <c r="C59" t="s">
+        <v>191</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E59" t="s">
+        <v>192</v>
+      </c>
+      <c r="F59" t="n">
+        <v>438</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H59" t="s">
+        <v>17</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K59" t="b">
+        <v>1</v>
+      </c>
+      <c r="L59" t="b">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>13</v>
+      </c>
+      <c r="B60" t="s">
+        <v>193</v>
+      </c>
+      <c r="C60" t="s">
+        <v>194</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E60" t="s">
+        <v>195</v>
+      </c>
+      <c r="F60" t="n">
+        <v>214</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K60" t="b">
+        <v>1</v>
+      </c>
+      <c r="L60" t="b">
+        <v>1</v>
+      </c>
+      <c r="M60" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>13</v>
+      </c>
+      <c r="B61" t="s">
+        <v>196</v>
+      </c>
+      <c r="C61" t="s">
+        <v>197</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E61" t="s">
+        <v>198</v>
+      </c>
+      <c r="F61" t="n">
+        <v>46</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="H61" t="s">
+        <v>17</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" t="b">
+        <v>1</v>
+      </c>
+      <c r="M61" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>18</v>
+      </c>
+      <c r="B62" t="s">
+        <v>199</v>
+      </c>
+      <c r="C62" t="s">
+        <v>200</v>
+      </c>
+      <c r="D62" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E62" t="s">
+        <v>201</v>
+      </c>
+      <c r="F62" t="n">
+        <v>375</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H62" t="s">
+        <v>38</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="K62" t="b">
+        <v>1</v>
+      </c>
+      <c r="L62" t="b">
+        <v>1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>13</v>
+      </c>
+      <c r="B63" t="s">
+        <v>202</v>
+      </c>
+      <c r="C63" t="s">
+        <v>203</v>
+      </c>
+      <c r="D63" t="n">
         <v>0.3</v>
       </c>
-      <c r="E55" t="s">
-        <v>179</v>
-      </c>
-      <c r="F55" t="n">
+      <c r="E63" t="s">
+        <v>204</v>
+      </c>
+      <c r="F63" t="n">
+        <v>7</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="H63" t="s">
+        <v>17</v>
+      </c>
+      <c r="I63" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="J63" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K63" t="b">
+        <v>1</v>
+      </c>
+      <c r="L63" t="b">
+        <v>1</v>
+      </c>
+      <c r="M63" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64" t="s">
+        <v>205</v>
+      </c>
+      <c r="C64" t="s">
+        <v>206</v>
+      </c>
+      <c r="D64" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E64" t="s">
+        <v>207</v>
+      </c>
+      <c r="F64" t="n">
+        <v>233</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="H64" t="s">
+        <v>38</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K64" t="b">
+        <v>1</v>
+      </c>
+      <c r="L64" t="b">
+        <v>1</v>
+      </c>
+      <c r="M64" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>18</v>
+      </c>
+      <c r="B65" t="s">
+        <v>208</v>
+      </c>
+      <c r="C65" t="s">
+        <v>209</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E65" t="s">
+        <v>210</v>
+      </c>
+      <c r="F65" t="n">
+        <v>765</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H65" t="s">
+        <v>17</v>
+      </c>
+      <c r="I65" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="J65" t="n">
+        <v>9.72</v>
+      </c>
+      <c r="K65" t="b">
+        <v>1</v>
+      </c>
+      <c r="L65" t="b">
+        <v>1</v>
+      </c>
+      <c r="M65" t="n">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B66" t="s">
+        <v>211</v>
+      </c>
+      <c r="C66" t="s">
+        <v>212</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E66" t="s">
+        <v>213</v>
+      </c>
+      <c r="F66" t="n">
+        <v>337</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H66" t="s">
+        <v>17</v>
+      </c>
+      <c r="I66" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="J66" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="K66" t="b">
+        <v>1</v>
+      </c>
+      <c r="L66" t="b">
+        <v>1</v>
+      </c>
+      <c r="M66" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>120</v>
+      </c>
+      <c r="B67" t="s">
+        <v>214</v>
+      </c>
+      <c r="C67" t="s">
+        <v>215</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E67" t="s">
+        <v>216</v>
+      </c>
+      <c r="F67" t="n">
+        <v>41</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H67" t="s">
+        <v>17</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K67" t="b">
+        <v>1</v>
+      </c>
+      <c r="L67" t="b">
+        <v>1</v>
+      </c>
+      <c r="M67" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>13</v>
+      </c>
+      <c r="B68" t="s">
+        <v>217</v>
+      </c>
+      <c r="C68" t="s">
+        <v>218</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E68" t="s">
+        <v>219</v>
+      </c>
+      <c r="F68" t="n">
+        <v>81</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H68" t="s">
+        <v>17</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K68" t="b">
+        <v>1</v>
+      </c>
+      <c r="L68" t="b">
+        <v>1</v>
+      </c>
+      <c r="M68" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69" t="s">
+        <v>220</v>
+      </c>
+      <c r="C69" t="s">
+        <v>221</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E69" t="s">
+        <v>222</v>
+      </c>
+      <c r="F69" t="n">
+        <v>134</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H69" t="s">
+        <v>17</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K69" t="b">
+        <v>1</v>
+      </c>
+      <c r="L69" t="b">
+        <v>1</v>
+      </c>
+      <c r="M69" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>18</v>
+      </c>
+      <c r="B70" t="s">
+        <v>223</v>
+      </c>
+      <c r="C70" t="s">
+        <v>224</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E70" t="s">
+        <v>225</v>
+      </c>
+      <c r="F70" t="n">
+        <v>288</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H70" t="s">
+        <v>17</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K70" t="b">
+        <v>1</v>
+      </c>
+      <c r="L70" t="b">
+        <v>1</v>
+      </c>
+      <c r="M70" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>13</v>
+      </c>
+      <c r="B71" t="s">
+        <v>226</v>
+      </c>
+      <c r="C71" t="s">
+        <v>227</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E71" t="s">
+        <v>228</v>
+      </c>
+      <c r="F71" t="n">
+        <v>720</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H71" t="s">
+        <v>17</v>
+      </c>
+      <c r="I71" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="J71" t="n">
+        <v>8.04</v>
+      </c>
+      <c r="K71" t="b">
+        <v>1</v>
+      </c>
+      <c r="L71" t="b">
+        <v>1</v>
+      </c>
+      <c r="M71" t="n">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>13</v>
+      </c>
+      <c r="B72" t="s">
+        <v>229</v>
+      </c>
+      <c r="C72" t="s">
+        <v>230</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E72" t="s">
+        <v>231</v>
+      </c>
+      <c r="F72" t="n">
+        <v>773</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H72" t="s">
+        <v>17</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K72" t="b">
+        <v>1</v>
+      </c>
+      <c r="L72" t="b">
+        <v>1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>13</v>
+      </c>
+      <c r="B73" t="s">
+        <v>232</v>
+      </c>
+      <c r="C73" t="s">
+        <v>233</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E73" t="s">
+        <v>234</v>
+      </c>
+      <c r="F73" t="n">
+        <v>735</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H73" t="s">
+        <v>17</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="J73" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K73" t="b">
+        <v>1</v>
+      </c>
+      <c r="L73" t="b">
+        <v>1</v>
+      </c>
+      <c r="M73" t="n">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>13</v>
+      </c>
+      <c r="B74" t="s">
+        <v>235</v>
+      </c>
+      <c r="C74" t="s">
+        <v>236</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E74" t="s">
+        <v>237</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H74" t="s">
+        <v>17</v>
+      </c>
+      <c r="I74" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="J74" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K74" t="b">
+        <v>1</v>
+      </c>
+      <c r="L74" t="b">
+        <v>1</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B75" t="s">
+        <v>238</v>
+      </c>
+      <c r="C75" t="s">
+        <v>239</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E75" t="s">
+        <v>240</v>
+      </c>
+      <c r="F75" t="n">
+        <v>498</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H75" t="s">
+        <v>17</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3</v>
+      </c>
+      <c r="K75" t="b">
+        <v>1</v>
+      </c>
+      <c r="L75" t="b">
+        <v>1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>13</v>
+      </c>
+      <c r="B76" t="s">
+        <v>241</v>
+      </c>
+      <c r="C76" t="s">
+        <v>242</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E76" t="s">
+        <v>243</v>
+      </c>
+      <c r="F76" t="n">
+        <v>257</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H76" t="s">
+        <v>17</v>
+      </c>
+      <c r="I76" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="J76" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="K76" t="b">
+        <v>1</v>
+      </c>
+      <c r="L76" t="b">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>13</v>
+      </c>
+      <c r="B77" t="s">
+        <v>244</v>
+      </c>
+      <c r="C77" t="s">
+        <v>245</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E77" t="s">
+        <v>246</v>
+      </c>
+      <c r="F77" t="n">
+        <v>458</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="H77" t="s">
+        <v>17</v>
+      </c>
+      <c r="I77" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="J77" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K77" t="b">
+        <v>1</v>
+      </c>
+      <c r="L77" t="b">
+        <v>1</v>
+      </c>
+      <c r="M77" t="n">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>13</v>
+      </c>
+      <c r="B78" t="s">
+        <v>247</v>
+      </c>
+      <c r="C78" t="s">
+        <v>248</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E78" t="s">
+        <v>249</v>
+      </c>
+      <c r="F78" t="n">
+        <v>923</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H78" t="s">
+        <v>17</v>
+      </c>
+      <c r="I78" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J78" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K78" t="b">
+        <v>1</v>
+      </c>
+      <c r="L78" t="b">
+        <v>1</v>
+      </c>
+      <c r="M78" t="n">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>13</v>
+      </c>
+      <c r="B79" t="s">
+        <v>250</v>
+      </c>
+      <c r="C79" t="s">
+        <v>251</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E79" t="s">
+        <v>252</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1012</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H79" t="s">
+        <v>17</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K79" t="b">
+        <v>1</v>
+      </c>
+      <c r="L79" t="b">
+        <v>1</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>13</v>
+      </c>
+      <c r="B80" t="s">
+        <v>253</v>
+      </c>
+      <c r="C80" t="s">
+        <v>254</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E80" t="s">
+        <v>255</v>
+      </c>
+      <c r="F80" t="n">
         <v>344.5</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G80" t="n">
         <v>0.002</v>
       </c>
-      <c r="H55" t="s">
-        <v>17</v>
-      </c>
-      <c r="I55" t="n">
+      <c r="H80" t="s">
+        <v>17</v>
+      </c>
+      <c r="I80" t="n">
         <v>0.32</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J80" t="n">
         <v>2.04</v>
       </c>
-      <c r="K55" t="b">
-        <v>1</v>
-      </c>
-      <c r="L55" t="b">
-        <v>1</v>
-      </c>
-      <c r="M55" t="n">
+      <c r="K80" t="b">
+        <v>1</v>
+      </c>
+      <c r="L80" t="b">
+        <v>1</v>
+      </c>
+      <c r="M80" t="n">
         <v>688</v>
       </c>
     </row>
@@ -3258,33 +4511,33 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>180</v>
+        <v>256</v>
       </c>
       <c r="C1" t="s">
-        <v>181</v>
+        <v>257</v>
       </c>
       <c r="D1" t="s">
-        <v>182</v>
+        <v>258</v>
       </c>
       <c r="E1" t="s">
-        <v>183</v>
+        <v>259</v>
       </c>
       <c r="F1" t="s">
-        <v>184</v>
+        <v>260</v>
       </c>
       <c r="G1" t="s">
-        <v>185</v>
+        <v>261</v>
       </c>
       <c r="H1" t="s">
-        <v>186</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C2" t="n">
         <v>0.4</v>
@@ -3307,22 +4560,22 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -3333,19 +4586,19 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -3409,28 +4662,28 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>292.5</v>
+        <v>1037.5</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="E2" t="n">
-        <v>1.694</v>
+        <v>0.008</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01</v>
+        <v>6.03</v>
       </c>
       <c r="H2" t="n">
-        <v>0.12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -3438,155 +4691,155 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>205</v>
       </c>
       <c r="C3" t="n">
-        <v>96</v>
+        <v>233</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4</v>
+        <v>7.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.082</v>
+        <v>0.07</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>0.22</v>
       </c>
       <c r="H3" t="n">
-        <v>8.76</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>184</v>
       </c>
       <c r="C4" t="n">
-        <v>1160.5</v>
+        <v>892</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002</v>
+        <v>0.013</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>9.3</v>
+        <v>3.14</v>
       </c>
       <c r="H4" t="n">
-        <v>62.52</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C5" t="n">
-        <v>862</v>
+        <v>374.5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005</v>
+        <v>0.019</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n">
-        <v>1298</v>
+        <v>292.5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001</v>
+        <v>1.694</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>2.18</v>
+        <v>0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>2.04</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="C7" t="n">
-        <v>864</v>
+        <v>581</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002</v>
+        <v>0.023</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>0.61</v>
+        <v>0.9</v>
       </c>
       <c r="H7" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>199</v>
       </c>
       <c r="C8" t="n">
-        <v>83</v>
+        <v>375</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>5.7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.014</v>
+        <v>0.025</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="H8" t="n">
-        <v>0.84</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="9">
@@ -3594,25 +4847,25 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="C9" t="n">
-        <v>735</v>
+        <v>412</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002</v>
+        <v>0.02</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>0.69</v>
+        <v>1.91</v>
       </c>
       <c r="H9" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -3620,25 +4873,25 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>157</v>
       </c>
       <c r="C10" t="n">
-        <v>105.5</v>
+        <v>834</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>0.93</v>
+        <v>0.3</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="11">
@@ -3646,51 +4899,51 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="C11" t="n">
-        <v>216</v>
+        <v>982</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="E11" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>0.44</v>
+        <v>0.58</v>
       </c>
       <c r="H11" t="n">
-        <v>0.96</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>208</v>
       </c>
       <c r="C12" t="n">
-        <v>462</v>
+        <v>765</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>0.11</v>
+        <v>3.82</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6</v>
+        <v>9.72</v>
       </c>
     </row>
     <row r="13">
@@ -3698,51 +4951,51 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>181</v>
       </c>
       <c r="C13" t="n">
-        <v>438</v>
+        <v>1131</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="F13" t="s">
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.12</v>
+        <v>1.26</v>
       </c>
       <c r="H13" t="n">
-        <v>0.36</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="C14" t="n">
-        <v>361</v>
+        <v>96</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="E14" t="n">
-        <v>0.003</v>
+        <v>0.082</v>
       </c>
       <c r="F14" t="s">
         <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>8.58</v>
+        <v>2.04</v>
       </c>
       <c r="H14" t="n">
-        <v>9.48</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="15">
@@ -3750,13 +5003,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>190</v>
       </c>
       <c r="C15" t="n">
-        <v>326.5</v>
+        <v>438</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
         <v>0.003</v>
@@ -3765,10 +5018,10 @@
         <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>1.05</v>
+        <v>0.12</v>
       </c>
       <c r="H15" t="n">
-        <v>3.12</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="16">
@@ -3776,13 +5029,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="C16" t="n">
-        <v>370</v>
+        <v>1106</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="E16" t="n">
         <v>0.002</v>
@@ -3791,10 +5044,10 @@
         <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>1.99</v>
+        <v>0.94</v>
       </c>
       <c r="H16" t="n">
-        <v>1.56</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="17">
@@ -3802,25 +5055,25 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C17" t="n">
-        <v>166</v>
+        <v>630</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="E17" t="n">
-        <v>0.006</v>
+        <v>0.014</v>
       </c>
       <c r="F17" t="s">
         <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>0.49</v>
+        <v>0.77</v>
       </c>
       <c r="H17" t="n">
-        <v>0.72</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="18">
@@ -3828,25 +5081,25 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>123</v>
+        <v>223</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>288</v>
       </c>
       <c r="D18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.5</v>
       </c>
-      <c r="E18" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="F18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.72</v>
-      </c>
       <c r="H18" t="n">
-        <v>3.36</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="19">
@@ -3854,25 +5107,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>32</v>
       </c>
       <c r="C19" t="n">
-        <v>214</v>
+        <v>573.5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="E19" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="F19" t="s">
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="20">
@@ -3880,51 +5133,51 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>1087</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="E20" t="n">
-        <v>0.021</v>
+        <v>0.002</v>
       </c>
       <c r="F20" t="s">
         <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>41</v>
+        <v>1160.5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05</v>
+        <v>0.002</v>
       </c>
       <c r="F21" t="s">
         <v>17</v>
       </c>
       <c r="G21" t="n">
-        <v>1.79</v>
+        <v>9.3</v>
       </c>
       <c r="H21" t="n">
-        <v>3.36</v>
+        <v>62.52</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="266">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -58,6 +58,18 @@
     <t xml:space="preserve">An_der_Kost</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/07/26 18:02:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/07/26 18:46:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/07/26 18:07:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/07/16 12:09:00</t>
   </si>
   <si>
@@ -65,9 +77,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026/07/16 12:54:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
   </si>
   <si>
     <t xml:space="preserve">Wasserstraße_Springorum</t>
@@ -850,8 +859,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M80" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M80"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M81" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M81"/>
   <tableColumns count="13">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -1254,25 +1263,25 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="n">
-        <v>348</v>
+        <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007</v>
+        <v>0.176</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
       </c>
       <c r="I2" t="n">
-        <v>1.17</v>
+        <v>0.06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.04</v>
+        <v>0.72</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
@@ -1281,39 +1290,39 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>694</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
       <c r="F3" t="n">
-        <v>1160.5</v>
+        <v>348</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>9.3</v>
+        <v>1.17</v>
       </c>
       <c r="J3" t="n">
-        <v>62.52</v>
+        <v>5.04</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
@@ -1322,12 +1331,12 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>2322</v>
+        <v>694</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -1336,25 +1345,25 @@
         <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>1160.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.035</v>
+        <v>0.002</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1</v>
+        <v>9.3</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2</v>
+        <v>62.52</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -1363,12 +1372,12 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>67</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1377,25 +1386,25 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>1106</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002</v>
+        <v>0.035</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
       </c>
       <c r="I5" t="n">
-        <v>0.94</v>
+        <v>0.1</v>
       </c>
       <c r="J5" t="n">
-        <v>2.04</v>
+        <v>1.2</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -1404,12 +1413,12 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>2213</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
@@ -1418,25 +1427,25 @@
         <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>292.5</v>
+        <v>1106</v>
       </c>
       <c r="G6" t="n">
-        <v>1.694</v>
+        <v>0.002</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01</v>
+        <v>0.94</v>
       </c>
       <c r="J6" t="n">
-        <v>0.12</v>
+        <v>2.04</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -1445,39 +1454,39 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>586</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E7" t="s">
         <v>33</v>
       </c>
-      <c r="D7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.694</v>
+      </c>
+      <c r="H7" t="s">
         <v>34</v>
       </c>
-      <c r="F7" t="n">
-        <v>573.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="H7" t="s">
-        <v>17</v>
-      </c>
       <c r="I7" t="n">
-        <v>0.46</v>
+        <v>0.01</v>
       </c>
       <c r="J7" t="n">
-        <v>2.16</v>
+        <v>0.12</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -1486,12 +1495,12 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1148</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
         <v>35</v>
@@ -1500,25 +1509,25 @@
         <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="E8" t="s">
         <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>1037.5</v>
+        <v>573.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I8" t="n">
-        <v>6.03</v>
+        <v>0.46</v>
       </c>
       <c r="J8" t="n">
-        <v>21</v>
+        <v>2.16</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -1527,39 +1536,39 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>2076</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
         <v>39</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E9" t="s">
         <v>40</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="n">
+        <v>1037.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H9" t="s">
         <v>41</v>
       </c>
-      <c r="F9" t="n">
-        <v>336</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.069</v>
-      </c>
-      <c r="H9" t="s">
-        <v>17</v>
-      </c>
       <c r="I9" t="n">
-        <v>4.47</v>
+        <v>6.03</v>
       </c>
       <c r="J9" t="n">
-        <v>32.64</v>
+        <v>21</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
@@ -1568,12 +1577,12 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>673</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>42</v>
@@ -1582,25 +1591,25 @@
         <v>43</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="s">
         <v>44</v>
       </c>
       <c r="F10" t="n">
-        <v>282.5</v>
+        <v>336</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006</v>
+        <v>0.069</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
       </c>
       <c r="I10" t="n">
-        <v>1.95</v>
+        <v>4.47</v>
       </c>
       <c r="J10" t="n">
-        <v>9.36</v>
+        <v>32.64</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
@@ -1609,12 +1618,12 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>566</v>
+        <v>673</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
         <v>45</v>
@@ -1623,25 +1632,25 @@
         <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E11" t="s">
         <v>47</v>
       </c>
       <c r="F11" t="n">
-        <v>986</v>
+        <v>282.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="J11" t="n">
-        <v>5.76</v>
+        <v>9.36</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -1650,12 +1659,12 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1973</v>
+        <v>566</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
         <v>48</v>
@@ -1664,25 +1673,25 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E12" t="s">
         <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>105.5</v>
+        <v>986</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
       </c>
       <c r="I12" t="n">
-        <v>0.93</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6</v>
+        <v>5.76</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -1691,12 +1700,12 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>212</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
         <v>51</v>
@@ -1705,25 +1714,25 @@
         <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="E13" t="s">
         <v>53</v>
       </c>
       <c r="F13" t="n">
-        <v>1368.5</v>
+        <v>105.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>0.93</v>
       </c>
       <c r="J13" t="n">
-        <v>1.44</v>
+        <v>3.6</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -1732,12 +1741,12 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>2738</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
         <v>54</v>
@@ -1746,25 +1755,25 @@
         <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
       </c>
       <c r="F14" t="n">
-        <v>50</v>
+        <v>1368.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.071</v>
+        <v>0.005</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
       </c>
       <c r="I14" t="n">
-        <v>0.23</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0.84</v>
+        <v>1.44</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
@@ -1773,12 +1782,12 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>101</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>57</v>
@@ -1787,25 +1796,25 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="E15" t="s">
         <v>59</v>
       </c>
       <c r="F15" t="n">
-        <v>222.5</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>0.028</v>
+        <v>0.071</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="J15" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
@@ -1814,12 +1823,12 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>446</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
         <v>60</v>
@@ -1828,25 +1837,25 @@
         <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="E16" t="s">
         <v>62</v>
       </c>
       <c r="F16" t="n">
-        <v>139</v>
+        <v>222.5</v>
       </c>
       <c r="G16" t="n">
-        <v>0.018</v>
+        <v>0.028</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
       </c>
       <c r="I16" t="n">
-        <v>5.95</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>5.16</v>
+        <v>0.72</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -1855,7 +1864,7 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>279</v>
+        <v>446</v>
       </c>
     </row>
     <row r="17">
@@ -1869,25 +1878,25 @@
         <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E17" t="s">
         <v>65</v>
       </c>
       <c r="F17" t="n">
-        <v>361</v>
+        <v>139</v>
       </c>
       <c r="G17" t="n">
-        <v>0.003</v>
+        <v>0.018</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
       </c>
       <c r="I17" t="n">
-        <v>8.58</v>
+        <v>5.95</v>
       </c>
       <c r="J17" t="n">
-        <v>9.48</v>
+        <v>5.16</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -1896,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>723</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18">
@@ -1910,25 +1919,25 @@
         <v>67</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="n">
-        <v>325.5</v>
+        <v>361</v>
       </c>
       <c r="G18" t="n">
-        <v>0.027</v>
+        <v>0.003</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
       </c>
       <c r="I18" t="n">
-        <v>1.04</v>
+        <v>8.58</v>
       </c>
       <c r="J18" t="n">
-        <v>2.88</v>
+        <v>9.48</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
@@ -1937,7 +1946,7 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>649</v>
+        <v>723</v>
       </c>
     </row>
     <row r="19">
@@ -1951,25 +1960,25 @@
         <v>70</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E19" t="s">
         <v>71</v>
       </c>
       <c r="F19" t="n">
-        <v>90.5</v>
+        <v>325.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0.04</v>
+        <v>0.027</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
       </c>
       <c r="I19" t="n">
-        <v>6.36</v>
+        <v>1.04</v>
       </c>
       <c r="J19" t="n">
-        <v>20.16</v>
+        <v>2.88</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
@@ -1978,7 +1987,7 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>182</v>
+        <v>649</v>
       </c>
     </row>
     <row r="20">
@@ -1992,25 +2001,25 @@
         <v>73</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E20" t="s">
         <v>74</v>
       </c>
       <c r="F20" t="n">
-        <v>60.5</v>
+        <v>90.5</v>
       </c>
       <c r="G20" t="n">
-        <v>0.054</v>
+        <v>0.04</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
       </c>
       <c r="I20" t="n">
-        <v>2.91</v>
+        <v>6.36</v>
       </c>
       <c r="J20" t="n">
-        <v>7.8</v>
+        <v>20.16</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
@@ -2019,7 +2028,7 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>122</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21">
@@ -2033,25 +2042,25 @@
         <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E21" t="s">
         <v>77</v>
       </c>
       <c r="F21" t="n">
-        <v>90</v>
+        <v>60.5</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01</v>
+        <v>0.054</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>1.09</v>
+        <v>2.91</v>
       </c>
       <c r="J21" t="n">
-        <v>2.04</v>
+        <v>7.8</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
@@ -2060,7 +2069,7 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22">
@@ -2074,22 +2083,22 @@
         <v>79</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E22" t="s">
         <v>80</v>
       </c>
       <c r="F22" t="n">
-        <v>50.5</v>
+        <v>90</v>
       </c>
       <c r="G22" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
       </c>
       <c r="I22" t="n">
-        <v>1.89</v>
+        <v>1.09</v>
       </c>
       <c r="J22" t="n">
         <v>2.04</v>
@@ -2101,12 +2110,12 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>102</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
         <v>81</v>
@@ -2115,25 +2124,25 @@
         <v>82</v>
       </c>
       <c r="D23" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="E23" t="s">
         <v>83</v>
       </c>
       <c r="F23" t="n">
-        <v>630</v>
+        <v>50.5</v>
       </c>
       <c r="G23" t="n">
-        <v>0.014</v>
+        <v>0.03</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.77</v>
+        <v>1.89</v>
       </c>
       <c r="J23" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
@@ -2142,12 +2151,12 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>1261</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
         <v>84</v>
@@ -2156,22 +2165,22 @@
         <v>85</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="E24" t="s">
         <v>86</v>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>630</v>
       </c>
       <c r="G24" t="n">
-        <v>0.039</v>
+        <v>0.014</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
       </c>
       <c r="I24" t="n">
-        <v>0.08</v>
+        <v>0.77</v>
       </c>
       <c r="J24" t="n">
         <v>0.96</v>
@@ -2183,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>81</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="25">
@@ -2203,19 +2212,19 @@
         <v>89</v>
       </c>
       <c r="F25" t="n">
-        <v>276.5</v>
+        <v>40</v>
       </c>
       <c r="G25" t="n">
-        <v>0.013</v>
+        <v>0.039</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
       </c>
       <c r="I25" t="n">
-        <v>8.81</v>
+        <v>0.08</v>
       </c>
       <c r="J25" t="n">
-        <v>4.2</v>
+        <v>0.96</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
@@ -2224,7 +2233,7 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>554</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26">
@@ -2238,25 +2247,25 @@
         <v>91</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E26" t="s">
         <v>92</v>
       </c>
       <c r="F26" t="n">
-        <v>326.5</v>
+        <v>276.5</v>
       </c>
       <c r="G26" t="n">
-        <v>0.003</v>
+        <v>0.013</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
       </c>
       <c r="I26" t="n">
-        <v>1.05</v>
+        <v>8.81</v>
       </c>
       <c r="J26" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
@@ -2265,7 +2274,7 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>654</v>
+        <v>554</v>
       </c>
     </row>
     <row r="27">
@@ -2279,25 +2288,25 @@
         <v>94</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E27" t="s">
         <v>95</v>
       </c>
       <c r="F27" t="n">
-        <v>93</v>
+        <v>326.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
       </c>
       <c r="I27" t="n">
-        <v>2.91</v>
+        <v>1.05</v>
       </c>
       <c r="J27" t="n">
-        <v>2.52</v>
+        <v>3.12</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
@@ -2306,12 +2315,12 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>187</v>
+        <v>654</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
         <v>96</v>
@@ -2320,25 +2329,25 @@
         <v>97</v>
       </c>
       <c r="D28" t="n">
-        <v>6.5</v>
+        <v>0.3</v>
       </c>
       <c r="E28" t="s">
         <v>98</v>
       </c>
       <c r="F28" t="n">
-        <v>374.5</v>
+        <v>93</v>
       </c>
       <c r="G28" t="n">
-        <v>0.019</v>
+        <v>0.005</v>
       </c>
       <c r="H28" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I28" t="n">
-        <v>1.01</v>
+        <v>2.91</v>
       </c>
       <c r="J28" t="n">
-        <v>4.8</v>
+        <v>2.52</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
@@ -2347,12 +2356,12 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>750</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
         <v>99</v>
@@ -2361,25 +2370,25 @@
         <v>100</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="E29" t="s">
         <v>101</v>
       </c>
       <c r="F29" t="n">
-        <v>370</v>
+        <v>374.5</v>
       </c>
       <c r="G29" t="n">
-        <v>0.002</v>
+        <v>0.019</v>
       </c>
       <c r="H29" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I29" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="J29" t="n">
-        <v>1.56</v>
+        <v>4.8</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
@@ -2388,7 +2397,7 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>371</v>
+        <v>750</v>
       </c>
     </row>
     <row r="30">
@@ -2402,25 +2411,25 @@
         <v>103</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E30" t="s">
         <v>104</v>
       </c>
       <c r="F30" t="n">
-        <v>127</v>
+        <v>370</v>
       </c>
       <c r="G30" t="n">
-        <v>0.129</v>
+        <v>0.002</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
       </c>
       <c r="I30" t="n">
-        <v>4.49</v>
+        <v>1.99</v>
       </c>
       <c r="J30" t="n">
-        <v>4.68</v>
+        <v>1.56</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
@@ -2429,7 +2438,7 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>128</v>
+        <v>371</v>
       </c>
     </row>
     <row r="31">
@@ -2449,19 +2458,19 @@
         <v>107</v>
       </c>
       <c r="F31" t="n">
-        <v>322</v>
+        <v>127</v>
       </c>
       <c r="G31" t="n">
-        <v>0.004</v>
+        <v>0.129</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
       </c>
       <c r="I31" t="n">
-        <v>0.43</v>
+        <v>4.49</v>
       </c>
       <c r="J31" t="n">
-        <v>2.52</v>
+        <v>4.68</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
@@ -2470,7 +2479,7 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>323</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32">
@@ -2490,19 +2499,19 @@
         <v>110</v>
       </c>
       <c r="F32" t="n">
-        <v>112</v>
+        <v>322</v>
       </c>
       <c r="G32" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
       </c>
       <c r="I32" t="n">
-        <v>0.18</v>
+        <v>0.43</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6</v>
+        <v>2.52</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
@@ -2511,12 +2520,12 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>113</v>
+        <v>323</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
         <v>111</v>
@@ -2525,25 +2534,25 @@
         <v>112</v>
       </c>
       <c r="D33" t="n">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
       <c r="E33" t="s">
         <v>113</v>
       </c>
       <c r="F33" t="n">
-        <v>412</v>
+        <v>112</v>
       </c>
       <c r="G33" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="H33" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I33" t="n">
-        <v>1.91</v>
+        <v>0.18</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
@@ -2552,12 +2561,12 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>413</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B34" t="s">
         <v>114</v>
@@ -2566,25 +2575,25 @@
         <v>115</v>
       </c>
       <c r="D34" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="E34" t="s">
         <v>116</v>
       </c>
       <c r="F34" t="n">
-        <v>805</v>
+        <v>412</v>
       </c>
       <c r="G34" t="n">
-        <v>0.078</v>
+        <v>0.02</v>
       </c>
       <c r="H34" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I34" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="J34" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
@@ -2593,12 +2602,12 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>831</v>
+        <v>413</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
         <v>117</v>
@@ -2607,25 +2616,25 @@
         <v>118</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="E35" t="s">
         <v>119</v>
       </c>
       <c r="F35" t="n">
-        <v>166</v>
+        <v>805</v>
       </c>
       <c r="G35" t="n">
-        <v>0.006</v>
+        <v>0.078</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
       </c>
       <c r="I35" t="n">
-        <v>0.49</v>
+        <v>2.02</v>
       </c>
       <c r="J35" t="n">
-        <v>0.72</v>
+        <v>2.16</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
@@ -2634,39 +2643,39 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>332</v>
+        <v>831</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" t="s">
         <v>120</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>121</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E36" t="s">
         <v>122</v>
       </c>
-      <c r="D36" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E36" t="s">
-        <v>123</v>
-      </c>
       <c r="F36" t="n">
-        <v>1298</v>
+        <v>166</v>
       </c>
       <c r="G36" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
       </c>
       <c r="I36" t="n">
-        <v>2.18</v>
+        <v>0.49</v>
       </c>
       <c r="J36" t="n">
-        <v>2.04</v>
+        <v>0.72</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
@@ -2675,12 +2684,12 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>2601</v>
+        <v>332</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B37" t="s">
         <v>124</v>
@@ -2695,19 +2704,19 @@
         <v>126</v>
       </c>
       <c r="F37" t="n">
-        <v>864</v>
+        <v>1298</v>
       </c>
       <c r="G37" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
       </c>
       <c r="I37" t="n">
-        <v>0.61</v>
+        <v>2.18</v>
       </c>
       <c r="J37" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
@@ -2716,12 +2725,12 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>1732</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B38" t="s">
         <v>127</v>
@@ -2730,25 +2739,25 @@
         <v>128</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E38" t="s">
         <v>129</v>
       </c>
       <c r="F38" t="n">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G38" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
       </c>
       <c r="I38" t="n">
-        <v>1.29</v>
+        <v>0.61</v>
       </c>
       <c r="J38" t="n">
-        <v>1.8</v>
+        <v>0.96</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
@@ -2757,12 +2766,12 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>1729</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B39" t="s">
         <v>130</v>
@@ -2771,13 +2780,13 @@
         <v>131</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E39" t="s">
         <v>132</v>
       </c>
       <c r="F39" t="n">
-        <v>462</v>
+        <v>862</v>
       </c>
       <c r="G39" t="n">
         <v>0.005</v>
@@ -2786,10 +2795,10 @@
         <v>17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.11</v>
+        <v>1.29</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
@@ -2798,12 +2807,12 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>929</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B40" t="s">
         <v>133</v>
@@ -2812,25 +2821,25 @@
         <v>134</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E40" t="s">
         <v>135</v>
       </c>
       <c r="F40" t="n">
-        <v>83</v>
+        <v>462</v>
       </c>
       <c r="G40" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
       </c>
       <c r="I40" t="n">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="J40" t="n">
-        <v>0.84</v>
+        <v>0.6</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
@@ -2839,12 +2848,12 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>168</v>
+        <v>929</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="B41" t="s">
         <v>136</v>
@@ -2853,25 +2862,25 @@
         <v>137</v>
       </c>
       <c r="D41" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E41" t="s">
         <v>138</v>
       </c>
       <c r="F41" t="n">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="G41" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
       </c>
       <c r="I41" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="J41" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
@@ -2880,7 +2889,7 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>217</v>
+        <v>168</v>
       </c>
     </row>
     <row r="42">
@@ -2894,25 +2903,25 @@
         <v>140</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E42" t="s">
         <v>141</v>
       </c>
       <c r="F42" t="n">
-        <v>349</v>
+        <v>216</v>
       </c>
       <c r="G42" t="n">
-        <v>0.129</v>
+        <v>0.005</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
       </c>
       <c r="I42" t="n">
-        <v>0.76</v>
+        <v>0.44</v>
       </c>
       <c r="J42" t="n">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
@@ -2921,12 +2930,12 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>346</v>
+        <v>217</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
         <v>142</v>
@@ -2941,19 +2950,19 @@
         <v>144</v>
       </c>
       <c r="F43" t="n">
-        <v>69</v>
+        <v>349</v>
       </c>
       <c r="G43" t="n">
-        <v>0.025</v>
+        <v>0.129</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
       </c>
       <c r="I43" t="n">
-        <v>0.03</v>
+        <v>0.76</v>
       </c>
       <c r="J43" t="n">
-        <v>0.24</v>
+        <v>1.08</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
@@ -2962,12 +2971,12 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>70</v>
+        <v>346</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="B44" t="s">
         <v>145</v>
@@ -2976,25 +2985,25 @@
         <v>146</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E44" t="s">
         <v>147</v>
       </c>
       <c r="F44" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="G44" t="n">
-        <v>0.012</v>
+        <v>0.025</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
       </c>
       <c r="I44" t="n">
-        <v>0.75</v>
+        <v>0.03</v>
       </c>
       <c r="J44" t="n">
-        <v>2.4</v>
+        <v>0.24</v>
       </c>
       <c r="K44" t="b">
         <v>1</v>
@@ -3003,12 +3012,12 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B45" t="s">
         <v>148</v>
@@ -3017,25 +3026,25 @@
         <v>149</v>
       </c>
       <c r="D45" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="E45" t="s">
         <v>150</v>
       </c>
       <c r="F45" t="n">
-        <v>982</v>
+        <v>101</v>
       </c>
       <c r="G45" t="n">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
       <c r="H45" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I45" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="J45" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
@@ -3044,12 +3053,12 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>983</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B46" t="s">
         <v>151</v>
@@ -3058,25 +3067,25 @@
         <v>152</v>
       </c>
       <c r="D46" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="E46" t="s">
         <v>153</v>
       </c>
       <c r="F46" t="n">
-        <v>438</v>
+        <v>982</v>
       </c>
       <c r="G46" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
       <c r="H46" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I46" t="n">
-        <v>0.12</v>
+        <v>0.58</v>
       </c>
       <c r="J46" t="n">
-        <v>0.36</v>
+        <v>1.44</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
@@ -3085,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>435</v>
+        <v>983</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3108,25 @@
         <v>155</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E47" t="s">
         <v>156</v>
       </c>
       <c r="F47" t="n">
-        <v>336</v>
+        <v>438</v>
       </c>
       <c r="G47" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
       </c>
       <c r="I47" t="n">
-        <v>9.49</v>
+        <v>0.12</v>
       </c>
       <c r="J47" t="n">
-        <v>5.4</v>
+        <v>0.36</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
@@ -3126,12 +3135,12 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>337</v>
+        <v>435</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B48" t="s">
         <v>157</v>
@@ -3140,25 +3149,25 @@
         <v>158</v>
       </c>
       <c r="D48" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="E48" t="s">
         <v>159</v>
       </c>
       <c r="F48" t="n">
-        <v>834</v>
+        <v>336</v>
       </c>
       <c r="G48" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="H48" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3</v>
+        <v>9.49</v>
       </c>
       <c r="J48" t="n">
-        <v>2.52</v>
+        <v>5.4</v>
       </c>
       <c r="K48" t="b">
         <v>1</v>
@@ -3167,12 +3176,12 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>833</v>
+        <v>337</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
         <v>160</v>
@@ -3181,25 +3190,25 @@
         <v>161</v>
       </c>
       <c r="D49" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="E49" t="s">
         <v>162</v>
       </c>
       <c r="F49" t="n">
-        <v>1087</v>
+        <v>834</v>
       </c>
       <c r="G49" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H49" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I49" t="n">
-        <v>0.57</v>
+        <v>0.3</v>
       </c>
       <c r="J49" t="n">
-        <v>1.44</v>
+        <v>2.52</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
@@ -3208,12 +3217,12 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>1084</v>
+        <v>833</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B50" t="s">
         <v>163</v>
@@ -3222,25 +3231,25 @@
         <v>164</v>
       </c>
       <c r="D50" t="n">
-        <v>6.1</v>
+        <v>1.2</v>
       </c>
       <c r="E50" t="s">
         <v>165</v>
       </c>
       <c r="F50" t="n">
-        <v>581</v>
+        <v>1087</v>
       </c>
       <c r="G50" t="n">
-        <v>0.023</v>
+        <v>0.002</v>
       </c>
       <c r="H50" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>0.57</v>
       </c>
       <c r="J50" t="n">
-        <v>2.04</v>
+        <v>1.44</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
@@ -3249,12 +3258,12 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>580</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B51" t="s">
         <v>166</v>
@@ -3263,25 +3272,25 @@
         <v>167</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3</v>
+        <v>6.1</v>
       </c>
       <c r="E51" t="s">
         <v>168</v>
       </c>
       <c r="F51" t="n">
-        <v>193</v>
+        <v>581</v>
       </c>
       <c r="G51" t="n">
-        <v>0.008</v>
+        <v>0.023</v>
       </c>
       <c r="H51" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I51" t="n">
-        <v>5.68</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
-        <v>3.96</v>
+        <v>2.04</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
@@ -3290,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>192</v>
+        <v>580</v>
       </c>
     </row>
     <row r="52">
@@ -3310,19 +3319,19 @@
         <v>171</v>
       </c>
       <c r="F52" t="n">
-        <v>281</v>
+        <v>193</v>
       </c>
       <c r="G52" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
       </c>
       <c r="I52" t="n">
-        <v>0.68</v>
+        <v>5.68</v>
       </c>
       <c r="J52" t="n">
-        <v>1.2</v>
+        <v>3.96</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
@@ -3331,7 +3340,7 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>282</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53">
@@ -3345,25 +3354,25 @@
         <v>173</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E53" t="s">
         <v>174</v>
       </c>
       <c r="F53" t="n">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="G53" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
       </c>
       <c r="I53" t="n">
-        <v>2.38</v>
+        <v>0.68</v>
       </c>
       <c r="J53" t="n">
-        <v>3.36</v>
+        <v>1.2</v>
       </c>
       <c r="K53" t="b">
         <v>1</v>
@@ -3372,7 +3381,7 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>331</v>
+        <v>282</v>
       </c>
     </row>
     <row r="54">
@@ -3386,25 +3395,25 @@
         <v>176</v>
       </c>
       <c r="D54" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="E54" t="s">
         <v>177</v>
       </c>
       <c r="F54" t="n">
-        <v>96</v>
+        <v>332</v>
       </c>
       <c r="G54" t="n">
-        <v>0.082</v>
+        <v>0.006</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
       </c>
       <c r="I54" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="J54" t="n">
-        <v>8.76</v>
+        <v>3.36</v>
       </c>
       <c r="K54" t="b">
         <v>1</v>
@@ -3413,7 +3422,7 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>95</v>
+        <v>331</v>
       </c>
     </row>
     <row r="55">
@@ -3427,25 +3436,25 @@
         <v>179</v>
       </c>
       <c r="D55" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="E55" t="s">
         <v>180</v>
       </c>
       <c r="F55" t="n">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="G55" t="n">
-        <v>0.122</v>
+        <v>0.082</v>
       </c>
       <c r="H55" t="s">
         <v>17</v>
       </c>
       <c r="I55" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="J55" t="n">
-        <v>3.36</v>
+        <v>8.76</v>
       </c>
       <c r="K55" t="b">
         <v>1</v>
@@ -3454,12 +3463,12 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>27</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B56" t="s">
         <v>181</v>
@@ -3468,25 +3477,25 @@
         <v>182</v>
       </c>
       <c r="D56" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E56" t="s">
         <v>183</v>
       </c>
       <c r="F56" t="n">
-        <v>1131</v>
+        <v>26</v>
       </c>
       <c r="G56" t="n">
-        <v>0.002</v>
+        <v>0.122</v>
       </c>
       <c r="H56" t="s">
         <v>17</v>
       </c>
       <c r="I56" t="n">
-        <v>1.26</v>
+        <v>1.72</v>
       </c>
       <c r="J56" t="n">
-        <v>8.4</v>
+        <v>3.36</v>
       </c>
       <c r="K56" t="b">
         <v>1</v>
@@ -3495,12 +3504,12 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>1128</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B57" t="s">
         <v>184</v>
@@ -3509,25 +3518,25 @@
         <v>185</v>
       </c>
       <c r="D57" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="E57" t="s">
         <v>186</v>
       </c>
       <c r="F57" t="n">
-        <v>892</v>
+        <v>1131</v>
       </c>
       <c r="G57" t="n">
-        <v>0.013</v>
+        <v>0.002</v>
       </c>
       <c r="H57" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I57" t="n">
-        <v>3.14</v>
+        <v>1.26</v>
       </c>
       <c r="J57" t="n">
-        <v>7.44</v>
+        <v>8.4</v>
       </c>
       <c r="K57" t="b">
         <v>1</v>
@@ -3536,12 +3545,12 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>891</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B58" t="s">
         <v>187</v>
@@ -3550,25 +3559,25 @@
         <v>188</v>
       </c>
       <c r="D58" t="n">
-        <v>0.4</v>
+        <v>7</v>
       </c>
       <c r="E58" t="s">
         <v>189</v>
       </c>
       <c r="F58" t="n">
-        <v>77</v>
+        <v>892</v>
       </c>
       <c r="G58" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="H58" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I58" t="n">
-        <v>0.93</v>
+        <v>3.14</v>
       </c>
       <c r="J58" t="n">
-        <v>3</v>
+        <v>7.44</v>
       </c>
       <c r="K58" t="b">
         <v>1</v>
@@ -3577,12 +3586,12 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>78</v>
+        <v>891</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B59" t="s">
         <v>190</v>
@@ -3591,25 +3600,25 @@
         <v>191</v>
       </c>
       <c r="D59" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="E59" t="s">
         <v>192</v>
       </c>
       <c r="F59" t="n">
-        <v>438</v>
+        <v>77</v>
       </c>
       <c r="G59" t="n">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="H59" t="s">
         <v>17</v>
       </c>
       <c r="I59" t="n">
-        <v>0.12</v>
+        <v>0.93</v>
       </c>
       <c r="J59" t="n">
-        <v>0.48</v>
+        <v>3</v>
       </c>
       <c r="K59" t="b">
         <v>1</v>
@@ -3618,12 +3627,12 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>437</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B60" t="s">
         <v>193</v>
@@ -3632,25 +3641,25 @@
         <v>194</v>
       </c>
       <c r="D60" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="E60" t="s">
         <v>195</v>
       </c>
       <c r="F60" t="n">
-        <v>214</v>
+        <v>438</v>
       </c>
       <c r="G60" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="H60" t="s">
         <v>17</v>
       </c>
       <c r="I60" t="n">
-        <v>0.47</v>
+        <v>0.12</v>
       </c>
       <c r="J60" t="n">
-        <v>1.2</v>
+        <v>0.48</v>
       </c>
       <c r="K60" t="b">
         <v>1</v>
@@ -3659,7 +3668,7 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>213</v>
+        <v>437</v>
       </c>
     </row>
     <row r="61">
@@ -3679,19 +3688,19 @@
         <v>198</v>
       </c>
       <c r="F61" t="n">
-        <v>46</v>
+        <v>214</v>
       </c>
       <c r="G61" t="n">
-        <v>0.021</v>
+        <v>0.005</v>
       </c>
       <c r="H61" t="s">
         <v>17</v>
       </c>
       <c r="I61" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="J61" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="K61" t="b">
         <v>1</v>
@@ -3700,12 +3709,12 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>47</v>
+        <v>213</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B62" t="s">
         <v>199</v>
@@ -3714,25 +3723,25 @@
         <v>200</v>
       </c>
       <c r="D62" t="n">
-        <v>5.7</v>
+        <v>0.5</v>
       </c>
       <c r="E62" t="s">
         <v>201</v>
       </c>
       <c r="F62" t="n">
-        <v>375</v>
+        <v>46</v>
       </c>
       <c r="G62" t="n">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
       <c r="H62" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I62" t="n">
-        <v>0.32</v>
+        <v>0.52</v>
       </c>
       <c r="J62" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="K62" t="b">
         <v>1</v>
@@ -3741,12 +3750,12 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>372</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B63" t="s">
         <v>202</v>
@@ -3755,25 +3764,25 @@
         <v>203</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3</v>
+        <v>5.7</v>
       </c>
       <c r="E63" t="s">
         <v>204</v>
       </c>
       <c r="F63" t="n">
-        <v>7</v>
+        <v>375</v>
       </c>
       <c r="G63" t="n">
-        <v>0.097</v>
+        <v>0.025</v>
       </c>
       <c r="H63" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I63" t="n">
-        <v>3.46</v>
+        <v>0.32</v>
       </c>
       <c r="J63" t="n">
-        <v>6.6</v>
+        <v>1.68</v>
       </c>
       <c r="K63" t="b">
         <v>1</v>
@@ -3782,12 +3791,12 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>8</v>
+        <v>372</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B64" t="s">
         <v>205</v>
@@ -3796,25 +3805,25 @@
         <v>206</v>
       </c>
       <c r="D64" t="n">
-        <v>7.1</v>
+        <v>0.3</v>
       </c>
       <c r="E64" t="s">
         <v>207</v>
       </c>
       <c r="F64" t="n">
-        <v>233</v>
+        <v>7</v>
       </c>
       <c r="G64" t="n">
-        <v>0.07</v>
+        <v>0.097</v>
       </c>
       <c r="H64" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I64" t="n">
-        <v>0.22</v>
+        <v>3.46</v>
       </c>
       <c r="J64" t="n">
-        <v>2.16</v>
+        <v>6.6</v>
       </c>
       <c r="K64" t="b">
         <v>1</v>
@@ -3823,12 +3832,12 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>232</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B65" t="s">
         <v>208</v>
@@ -3837,25 +3846,25 @@
         <v>209</v>
       </c>
       <c r="D65" t="n">
-        <v>1.9</v>
+        <v>7.1</v>
       </c>
       <c r="E65" t="s">
         <v>210</v>
       </c>
       <c r="F65" t="n">
-        <v>765</v>
+        <v>233</v>
       </c>
       <c r="G65" t="n">
-        <v>0.004</v>
+        <v>0.07</v>
       </c>
       <c r="H65" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I65" t="n">
-        <v>3.82</v>
+        <v>0.22</v>
       </c>
       <c r="J65" t="n">
-        <v>9.72</v>
+        <v>2.16</v>
       </c>
       <c r="K65" t="b">
         <v>1</v>
@@ -3864,12 +3873,12 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>764</v>
+        <v>232</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B66" t="s">
         <v>211</v>
@@ -3878,25 +3887,25 @@
         <v>212</v>
       </c>
       <c r="D66" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="E66" t="s">
         <v>213</v>
       </c>
       <c r="F66" t="n">
-        <v>337</v>
+        <v>765</v>
       </c>
       <c r="G66" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="H66" t="s">
         <v>17</v>
       </c>
       <c r="I66" t="n">
-        <v>6.39</v>
+        <v>3.82</v>
       </c>
       <c r="J66" t="n">
-        <v>10.92</v>
+        <v>9.72</v>
       </c>
       <c r="K66" t="b">
         <v>1</v>
@@ -3905,12 +3914,12 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>336</v>
+        <v>764</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="B67" t="s">
         <v>214</v>
@@ -3919,25 +3928,25 @@
         <v>215</v>
       </c>
       <c r="D67" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E67" t="s">
         <v>216</v>
       </c>
       <c r="F67" t="n">
-        <v>41</v>
+        <v>337</v>
       </c>
       <c r="G67" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H67" t="s">
         <v>17</v>
       </c>
       <c r="I67" t="n">
-        <v>1.79</v>
+        <v>6.39</v>
       </c>
       <c r="J67" t="n">
-        <v>3.36</v>
+        <v>10.92</v>
       </c>
       <c r="K67" t="b">
         <v>1</v>
@@ -3946,12 +3955,12 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>42</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="B68" t="s">
         <v>217</v>
@@ -3960,25 +3969,25 @@
         <v>218</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E68" t="s">
         <v>219</v>
       </c>
       <c r="F68" t="n">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="G68" t="n">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="H68" t="s">
         <v>17</v>
       </c>
       <c r="I68" t="n">
-        <v>1.34</v>
+        <v>1.79</v>
       </c>
       <c r="J68" t="n">
-        <v>1.2</v>
+        <v>3.36</v>
       </c>
       <c r="K68" t="b">
         <v>1</v>
@@ -3987,7 +3996,7 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69">
@@ -4007,19 +4016,19 @@
         <v>222</v>
       </c>
       <c r="F69" t="n">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="G69" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H69" t="s">
         <v>17</v>
       </c>
       <c r="I69" t="n">
-        <v>0.03</v>
+        <v>1.34</v>
       </c>
       <c r="J69" t="n">
-        <v>0.36</v>
+        <v>1.2</v>
       </c>
       <c r="K69" t="b">
         <v>1</v>
@@ -4028,12 +4037,12 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>135</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B70" t="s">
         <v>223</v>
@@ -4042,25 +4051,25 @@
         <v>224</v>
       </c>
       <c r="D70" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="E70" t="s">
         <v>225</v>
       </c>
       <c r="F70" t="n">
-        <v>288</v>
+        <v>134</v>
       </c>
       <c r="G70" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="H70" t="s">
         <v>17</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>0.03</v>
       </c>
       <c r="J70" t="n">
-        <v>2.16</v>
+        <v>0.36</v>
       </c>
       <c r="K70" t="b">
         <v>1</v>
@@ -4069,12 +4078,12 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>285</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B71" t="s">
         <v>226</v>
@@ -4083,25 +4092,25 @@
         <v>227</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="E71" t="s">
         <v>228</v>
       </c>
       <c r="F71" t="n">
-        <v>720</v>
+        <v>288</v>
       </c>
       <c r="G71" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H71" t="s">
         <v>17</v>
       </c>
       <c r="I71" t="n">
-        <v>4.71</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
-        <v>8.04</v>
+        <v>2.16</v>
       </c>
       <c r="K71" t="b">
         <v>1</v>
@@ -4110,7 +4119,7 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>717</v>
+        <v>285</v>
       </c>
     </row>
     <row r="72">
@@ -4130,19 +4139,19 @@
         <v>231</v>
       </c>
       <c r="F72" t="n">
-        <v>773</v>
+        <v>720</v>
       </c>
       <c r="G72" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
       </c>
       <c r="I72" t="n">
-        <v>0.37</v>
+        <v>4.71</v>
       </c>
       <c r="J72" t="n">
-        <v>1.56</v>
+        <v>8.04</v>
       </c>
       <c r="K72" t="b">
         <v>1</v>
@@ -4151,7 +4160,7 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>774</v>
+        <v>717</v>
       </c>
     </row>
     <row r="73">
@@ -4165,25 +4174,25 @@
         <v>233</v>
       </c>
       <c r="D73" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E73" t="s">
         <v>234</v>
       </c>
       <c r="F73" t="n">
-        <v>735</v>
+        <v>773</v>
       </c>
       <c r="G73" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
       </c>
       <c r="I73" t="n">
-        <v>0.69</v>
+        <v>0.37</v>
       </c>
       <c r="J73" t="n">
-        <v>3.24</v>
+        <v>1.56</v>
       </c>
       <c r="K73" t="b">
         <v>1</v>
@@ -4192,7 +4201,7 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>734</v>
+        <v>774</v>
       </c>
     </row>
     <row r="74">
@@ -4206,13 +4215,13 @@
         <v>236</v>
       </c>
       <c r="D74" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E74" t="s">
         <v>237</v>
       </c>
       <c r="F74" t="n">
-        <v>1100</v>
+        <v>735</v>
       </c>
       <c r="G74" t="n">
         <v>0.002</v>
@@ -4221,10 +4230,10 @@
         <v>17</v>
       </c>
       <c r="I74" t="n">
-        <v>6.45</v>
+        <v>0.69</v>
       </c>
       <c r="J74" t="n">
-        <v>14.4</v>
+        <v>3.24</v>
       </c>
       <c r="K74" t="b">
         <v>1</v>
@@ -4233,7 +4242,7 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>1097</v>
+        <v>734</v>
       </c>
     </row>
     <row r="75">
@@ -4247,25 +4256,25 @@
         <v>239</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E75" t="s">
         <v>240</v>
       </c>
       <c r="F75" t="n">
-        <v>498</v>
+        <v>1100</v>
       </c>
       <c r="G75" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="H75" t="s">
         <v>17</v>
       </c>
       <c r="I75" t="n">
-        <v>1.38</v>
+        <v>6.45</v>
       </c>
       <c r="J75" t="n">
-        <v>3</v>
+        <v>14.4</v>
       </c>
       <c r="K75" t="b">
         <v>1</v>
@@ -4274,7 +4283,7 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>495</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="76">
@@ -4288,25 +4297,25 @@
         <v>242</v>
       </c>
       <c r="D76" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E76" t="s">
         <v>243</v>
       </c>
       <c r="F76" t="n">
-        <v>257</v>
+        <v>498</v>
       </c>
       <c r="G76" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="H76" t="s">
         <v>17</v>
       </c>
       <c r="I76" t="n">
-        <v>6.15</v>
+        <v>1.38</v>
       </c>
       <c r="J76" t="n">
-        <v>9.48</v>
+        <v>3</v>
       </c>
       <c r="K76" t="b">
         <v>1</v>
@@ -4315,7 +4324,7 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>258</v>
+        <v>495</v>
       </c>
     </row>
     <row r="77">
@@ -4329,25 +4338,25 @@
         <v>245</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E77" t="s">
         <v>246</v>
       </c>
       <c r="F77" t="n">
-        <v>458</v>
+        <v>257</v>
       </c>
       <c r="G77" t="n">
-        <v>0.059</v>
+        <v>0.003</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
       </c>
       <c r="I77" t="n">
-        <v>2.47</v>
+        <v>6.15</v>
       </c>
       <c r="J77" t="n">
-        <v>7.2</v>
+        <v>9.48</v>
       </c>
       <c r="K77" t="b">
         <v>1</v>
@@ -4356,7 +4365,7 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>453</v>
+        <v>258</v>
       </c>
     </row>
     <row r="78">
@@ -4376,19 +4385,19 @@
         <v>249</v>
       </c>
       <c r="F78" t="n">
-        <v>923</v>
+        <v>458</v>
       </c>
       <c r="G78" t="n">
-        <v>0.002</v>
+        <v>0.059</v>
       </c>
       <c r="H78" t="s">
         <v>17</v>
       </c>
       <c r="I78" t="n">
-        <v>3.76</v>
+        <v>2.47</v>
       </c>
       <c r="J78" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="K78" t="b">
         <v>1</v>
@@ -4397,7 +4406,7 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>918</v>
+        <v>453</v>
       </c>
     </row>
     <row r="79">
@@ -4411,25 +4420,25 @@
         <v>251</v>
       </c>
       <c r="D79" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E79" t="s">
         <v>252</v>
       </c>
       <c r="F79" t="n">
-        <v>1012</v>
+        <v>923</v>
       </c>
       <c r="G79" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
       </c>
       <c r="I79" t="n">
-        <v>0.08</v>
+        <v>3.76</v>
       </c>
       <c r="J79" t="n">
-        <v>0.72</v>
+        <v>5.4</v>
       </c>
       <c r="K79" t="b">
         <v>1</v>
@@ -4438,7 +4447,7 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>1211</v>
+        <v>918</v>
       </c>
     </row>
     <row r="80">
@@ -4452,33 +4461,74 @@
         <v>254</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E80" t="s">
         <v>255</v>
       </c>
       <c r="F80" t="n">
+        <v>1012</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H80" t="s">
+        <v>17</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K80" t="b">
+        <v>1</v>
+      </c>
+      <c r="L80" t="b">
+        <v>1</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>13</v>
+      </c>
+      <c r="B81" t="s">
+        <v>256</v>
+      </c>
+      <c r="C81" t="s">
+        <v>257</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E81" t="s">
+        <v>258</v>
+      </c>
+      <c r="F81" t="n">
         <v>344.5</v>
       </c>
-      <c r="G80" t="n">
+      <c r="G81" t="n">
         <v>0.002</v>
       </c>
-      <c r="H80" t="s">
-        <v>17</v>
-      </c>
-      <c r="I80" t="n">
+      <c r="H81" t="s">
+        <v>17</v>
+      </c>
+      <c r="I81" t="n">
         <v>0.32</v>
       </c>
-      <c r="J80" t="n">
+      <c r="J81" t="n">
         <v>2.04</v>
       </c>
-      <c r="K80" t="b">
-        <v>1</v>
-      </c>
-      <c r="L80" t="b">
-        <v>1</v>
-      </c>
-      <c r="M80" t="n">
+      <c r="K81" t="b">
+        <v>1</v>
+      </c>
+      <c r="L81" t="b">
+        <v>1</v>
+      </c>
+      <c r="M81" t="n">
         <v>688</v>
       </c>
     </row>
@@ -4511,25 +4561,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2">
@@ -4537,7 +4587,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
         <v>0.4</v>
@@ -4560,7 +4610,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>24</v>
@@ -4586,7 +4636,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B4" t="n">
         <v>7</v>
@@ -4662,10 +4712,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C2" t="n">
         <v>1037.5</v>
@@ -4677,7 +4727,7 @@
         <v>0.008</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
         <v>6.03</v>
@@ -4688,10 +4738,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C3" t="n">
         <v>233</v>
@@ -4703,7 +4753,7 @@
         <v>0.07</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
         <v>0.22</v>
@@ -4714,10 +4764,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C4" t="n">
         <v>892</v>
@@ -4729,7 +4779,7 @@
         <v>0.013</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
         <v>3.14</v>
@@ -4740,10 +4790,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C5" t="n">
         <v>374.5</v>
@@ -4755,7 +4805,7 @@
         <v>0.019</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
         <v>1.01</v>
@@ -4766,10 +4816,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C6" t="n">
         <v>292.5</v>
@@ -4781,7 +4831,7 @@
         <v>1.694</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
         <v>0.01</v>
@@ -4792,10 +4842,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C7" t="n">
         <v>581</v>
@@ -4807,7 +4857,7 @@
         <v>0.023</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
         <v>0.9</v>
@@ -4818,10 +4868,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C8" t="n">
         <v>375</v>
@@ -4833,7 +4883,7 @@
         <v>0.025</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G8" t="n">
         <v>0.32</v>
@@ -4844,10 +4894,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C9" t="n">
         <v>412</v>
@@ -4859,7 +4909,7 @@
         <v>0.02</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
         <v>1.91</v>
@@ -4870,10 +4920,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C10" t="n">
         <v>834</v>
@@ -4885,7 +4935,7 @@
         <v>0.005</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
         <v>0.3</v>
@@ -4896,10 +4946,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C11" t="n">
         <v>982</v>
@@ -4911,7 +4961,7 @@
         <v>0.003</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
         <v>0.58</v>
@@ -4922,10 +4972,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C12" t="n">
         <v>765</v>
@@ -4948,10 +4998,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C13" t="n">
         <v>1131</v>
@@ -4977,7 +5027,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C14" t="n">
         <v>96</v>
@@ -5000,10 +5050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C15" t="n">
         <v>438</v>
@@ -5026,10 +5076,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C16" t="n">
         <v>1106</v>
@@ -5052,10 +5102,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C17" t="n">
         <v>630</v>
@@ -5078,10 +5128,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C18" t="n">
         <v>288</v>
@@ -5104,10 +5154,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
         <v>573.5</v>
@@ -5130,10 +5180,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C20" t="n">
         <v>1087</v>
@@ -5156,10 +5206,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C21" t="n">
         <v>1160.5</v>

--- a/data/output/all_detected_events.xlsx
+++ b/data/output/all_detected_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="251">
   <si>
     <t xml:space="preserve">station</t>
   </si>
@@ -58,6 +58,345 @@
     <t xml:space="preserve">An_der_Kost</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/07/26 18:02:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/07/26 18:46:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/07/26 18:07:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Königsallee_Springorum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/07/02 10:19:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/07/03 09:17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/07/02 14:05:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/30 16:22:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/07/01 09:28:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/07/01 06:10:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/21 01:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/21 02:21:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/21 01:55:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/12 07:38:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/12 08:02:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/12 07:45:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wasserstraße_Springorum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/10 23:22:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/11 17:48:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/11 08:03:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/10 16:52:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/10 17:13:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/10 17:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/08 20:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/08 20:18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/08 20:07:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/08 14:41:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/08 17:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/08 15:11:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/06 18:56:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/06 23:48:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/06 18:59:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sturzflut-Ereignis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/06 07:15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/06 16:50:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/06 13:46:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/02 10:29:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/03 10:01:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06/02 19:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/31 03:41:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/31 05:35:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/31 04:49:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/19 16:02:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/20 10:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/20 04:04:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/18 16:51:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/19 02:00:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/18 20:11:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/13 08:08:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/13 12:09:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/13 08:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/11 06:13:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/11 08:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/11 07:53:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/11 00:16:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/11 05:04:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/11 02:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/05 11:55:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/05 19:19:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05/05 13:24:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/19 00:24:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/19 02:08:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/19 01:05:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/16 17:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/17 09:25:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/17 01:12:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 21:52:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 22:05:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 21:58:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 19:15:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 20:22:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04/11 20:07:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/30 04:32:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/30 05:01:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/30 04:45:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 22:32:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 23:48:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/29 23:18:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/28 06:59:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/28 09:41:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/28 09:07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/14 08:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/14 09:54:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/14 08:54:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 05:51:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 12:06:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03/11 11:31:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regenereignis / Natürlich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/23 21:51:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/24 05:24:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/24 03:24:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 21:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 22:19:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 21:55:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 17:16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 19:47:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 17:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 09:59:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 15:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 11:53:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 00:10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 01:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/22 00:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 09:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 11:51:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 11:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 04:48:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 11:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 08:24:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/18 13:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/19 02:52:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02/18 13:41:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/02/16 13:25:00</t>
   </si>
   <si>
@@ -67,19 +406,346 @@
     <t xml:space="preserve">2026/02/16 14:46:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Leichter Regen / Unterhalb DWD-Schwelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/02/11 09:52:00</t>
+    <t xml:space="preserve">2026/02/11 15:54:00</t>
   </si>
   <si>
     <t xml:space="preserve">2026/02/11 18:28:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/02/11 15:24:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sturzflut-Ereignis</t>
+    <t xml:space="preserve">2026/02/11 16:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/14 04:17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/14 11:18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/14 06:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/09 10:51:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/09 17:49:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/09 13:14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/08 22:17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/09 02:28:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/09 01:23:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/07 17:01:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/07 18:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01/07 17:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/08 18:37:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/09 04:02:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/08 19:50:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/07 16:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/07 22:41:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/07 20:06:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/06 03:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/06 05:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/06 03:41:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/04 00:25:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/04 02:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/04 01:16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/02 06:11:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/02 10:22:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/02 07:16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/28 07:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/28 10:25:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/28 08:06:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/17 13:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/17 15:39:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/17 13:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/15 00:51:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/15 01:25:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/15 00:55:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/10 21:33:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/10 23:23:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/10 21:57:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/01 13:10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/01 14:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/01 13:38:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/29 22:54:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/30 01:01:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/29 23:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/28 06:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/28 10:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/28 08:36:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/25 14:59:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/25 15:15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/25 15:09:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 16:56:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 17:45:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 17:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 13:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 14:49:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 14:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 03:37:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 03:45:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 03:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/22 15:53:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 10:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/23 04:45:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 15:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/05 09:39:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 20:19:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 05:29:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 11:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 08:28:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/03 21:35:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 00:40:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/03 23:55:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/03 15:22:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 13:10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/04 00:26:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/03 11:33:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/03 14:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/03 12:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/02 15:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/03 09:12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10/03 03:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/26 06:12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/26 22:50:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/26 22:02:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/25 16:38:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/25 17:04:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/25 16:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/22 15:04:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/23 09:18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/23 04:06:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 15:14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/22 11:23:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/22 07:18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/20 15:53:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 14:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/21 00:49:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/14 22:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/15 16:32:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/15 10:02:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/14 04:49:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/14 08:34:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/14 07:24:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/13 06:13:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/14 02:33:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/13 21:37:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/09 02:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/10 00:47:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/09 05:21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/05 08:36:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/06 05:47:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/05 11:25:00</t>
   </si>
   <si>
     <t xml:space="preserve">Ereignisse</t>
@@ -148,8 +814,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M3" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M76" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M76"/>
   <tableColumns count="13">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -170,8 +836,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:H2" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:H4" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H4"/>
   <tableColumns count="8">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="Ereignisse"/>
@@ -187,8 +853,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:H3" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:H21" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H21"/>
   <tableColumns count="8">
     <tableColumn id="1" name="station"/>
     <tableColumn id="2" name="start_time"/>
@@ -485,7 +1151,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="19.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="19.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
@@ -552,22 +1218,22 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.54</v>
+        <v>0.91</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="n">
-        <v>168</v>
+        <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007</v>
+        <v>0.177</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
       </c>
       <c r="I2" t="n">
-        <v>0.49</v>
+        <v>0.06</v>
       </c>
       <c r="J2" t="n">
         <v>0.72</v>
@@ -579,48 +1245,3041 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>338</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1378</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="n">
-        <v>238.58</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="n">
-        <v>516</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.718</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1026</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1106</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="n">
         <v>21</v>
       </c>
-      <c r="I3" t="n">
+      <c r="G8" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" t="n">
+        <v>18</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="E11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.683</v>
+      </c>
+      <c r="H11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" t="n">
+        <v>575</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1411.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2824</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" t="n">
+        <v>114</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="H14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H15" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" t="n">
+        <v>549</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" t="n">
+        <v>241</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="H17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" t="n">
+        <v>139</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E19" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H19" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" t="n">
+        <v>444</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.009</v>
+      </c>
+      <c r="H20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="J20" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" t="n">
+        <v>104</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E22" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" t="n">
+        <v>985</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H22" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E23" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" t="n">
+        <v>13</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="H23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" t="n">
+        <v>67</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H24" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="J24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E25" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="H25" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E26" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" t="n">
+        <v>76</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E27" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H27" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E28" t="s">
+        <v>98</v>
+      </c>
+      <c r="F28" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="H28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="E29" t="s">
+        <v>101</v>
+      </c>
+      <c r="F29" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="H29" t="s">
+        <v>102</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E30" t="s">
+        <v>105</v>
+      </c>
+      <c r="F30" t="n">
+        <v>453</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H30" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E31" t="s">
+        <v>108</v>
+      </c>
+      <c r="F31" t="n">
+        <v>37</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="H31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E32" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" t="n">
+        <v>151</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="H32" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E33" t="s">
+        <v>114</v>
+      </c>
+      <c r="F33" t="n">
+        <v>322</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E34" t="s">
+        <v>117</v>
+      </c>
+      <c r="F34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H34" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" t="s">
+        <v>118</v>
+      </c>
+      <c r="C35" t="s">
+        <v>119</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E35" t="s">
+        <v>120</v>
+      </c>
+      <c r="F35" t="n">
+        <v>140</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H35" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" t="s">
+        <v>121</v>
+      </c>
+      <c r="C36" t="s">
+        <v>122</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E36" t="s">
+        <v>123</v>
+      </c>
+      <c r="F36" t="n">
+        <v>412</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H36" t="s">
+        <v>102</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" t="s">
+        <v>124</v>
+      </c>
+      <c r="C37" t="s">
+        <v>125</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E37" t="s">
+        <v>126</v>
+      </c>
+      <c r="F37" t="n">
+        <v>805</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="H37" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38" t="s">
+        <v>128</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E38" t="s">
+        <v>129</v>
+      </c>
+      <c r="F38" t="n">
+        <v>168</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H38" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>130</v>
+      </c>
+      <c r="C39" t="s">
+        <v>131</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E39" t="s">
+        <v>132</v>
+      </c>
+      <c r="F39" t="n">
+        <v>154</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H39" t="s">
+        <v>17</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="b">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" t="s">
+        <v>133</v>
+      </c>
+      <c r="C40" t="s">
+        <v>134</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E40" t="s">
+        <v>135</v>
+      </c>
+      <c r="F40" t="n">
+        <v>421</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H40" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41" t="s">
+        <v>137</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E41" t="s">
+        <v>138</v>
+      </c>
+      <c r="F41" t="n">
+        <v>418</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H41" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="b">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E42" t="s">
+        <v>141</v>
+      </c>
+      <c r="F42" t="n">
+        <v>251</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H42" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="b">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" t="s">
+        <v>142</v>
+      </c>
+      <c r="C43" t="s">
+        <v>143</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E43" t="s">
+        <v>144</v>
+      </c>
+      <c r="F43" t="n">
+        <v>105</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H43" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" t="s">
+        <v>145</v>
+      </c>
+      <c r="C44" t="s">
+        <v>146</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E44" t="s">
+        <v>147</v>
+      </c>
+      <c r="F44" t="n">
+        <v>565</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H44" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" t="s">
+        <v>149</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F45" t="n">
+        <v>367</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="J45" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" t="s">
+        <v>151</v>
+      </c>
+      <c r="C46" t="s">
+        <v>152</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E46" t="s">
+        <v>153</v>
+      </c>
+      <c r="F46" t="n">
+        <v>122</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="H46" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" t="s">
+        <v>154</v>
+      </c>
+      <c r="C47" t="s">
+        <v>155</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E47" t="s">
+        <v>156</v>
+      </c>
+      <c r="F47" t="n">
+        <v>116</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H47" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K47" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" t="b">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" t="s">
+        <v>157</v>
+      </c>
+      <c r="C48" t="s">
+        <v>158</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E48" t="s">
+        <v>159</v>
+      </c>
+      <c r="F48" t="n">
+        <v>251</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H48" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="J48" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" t="b">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" t="s">
+        <v>160</v>
+      </c>
+      <c r="C49" t="s">
+        <v>161</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E49" t="s">
+        <v>162</v>
+      </c>
+      <c r="F49" t="n">
+        <v>178</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.009</v>
+      </c>
+      <c r="H49" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="K49" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" t="b">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50" t="s">
+        <v>163</v>
+      </c>
+      <c r="C50" t="s">
+        <v>164</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E50" t="s">
+        <v>165</v>
+      </c>
+      <c r="F50" t="n">
+        <v>130</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.084</v>
+      </c>
+      <c r="H50" t="s">
+        <v>17</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" t="b">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" t="s">
+        <v>167</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E51" t="s">
+        <v>168</v>
+      </c>
+      <c r="F51" t="n">
+        <v>34</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="H51" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="J51" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
+      </c>
+      <c r="L51" t="b">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52" t="s">
+        <v>169</v>
+      </c>
+      <c r="C52" t="s">
+        <v>170</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E52" t="s">
+        <v>171</v>
+      </c>
+      <c r="F52" t="n">
+        <v>110</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H52" t="s">
+        <v>17</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J52" t="n">
+        <v>9.72</v>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
+      <c r="L52" t="b">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>13</v>
+      </c>
+      <c r="B53" t="s">
+        <v>172</v>
+      </c>
+      <c r="C53" t="s">
+        <v>173</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E53" t="s">
+        <v>174</v>
+      </c>
+      <c r="F53" t="n">
+        <v>80</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="H53" t="s">
+        <v>17</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" t="b">
+        <v>1</v>
+      </c>
+      <c r="M53" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>13</v>
+      </c>
+      <c r="B54" t="s">
+        <v>175</v>
+      </c>
+      <c r="C54" t="s">
+        <v>176</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E54" t="s">
+        <v>177</v>
+      </c>
+      <c r="F54" t="n">
+        <v>127</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="H54" t="s">
+        <v>17</v>
+      </c>
+      <c r="I54" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
+      <c r="L54" t="b">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" t="s">
+        <v>178</v>
+      </c>
+      <c r="C55" t="s">
+        <v>179</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E55" t="s">
+        <v>180</v>
+      </c>
+      <c r="F55" t="n">
+        <v>219</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H55" t="s">
+        <v>17</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J55" t="n">
         <v>1.2</v>
       </c>
-      <c r="J3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1034</v>
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" t="b">
+        <v>1</v>
+      </c>
+      <c r="M55" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B56" t="s">
+        <v>181</v>
+      </c>
+      <c r="C56" t="s">
+        <v>182</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E56" t="s">
+        <v>183</v>
+      </c>
+      <c r="F56" t="n">
+        <v>16</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="H56" t="s">
+        <v>17</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J56" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
+      <c r="L56" t="b">
+        <v>1</v>
+      </c>
+      <c r="M56" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>13</v>
+      </c>
+      <c r="B57" t="s">
+        <v>184</v>
+      </c>
+      <c r="C57" t="s">
+        <v>185</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E57" t="s">
+        <v>186</v>
+      </c>
+      <c r="F57" t="n">
+        <v>49</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="H57" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K57" t="b">
+        <v>1</v>
+      </c>
+      <c r="L57" t="b">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>13</v>
+      </c>
+      <c r="B58" t="s">
+        <v>187</v>
+      </c>
+      <c r="C58" t="s">
+        <v>188</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>189</v>
+      </c>
+      <c r="F58" t="n">
+        <v>78</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H58" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K58" t="b">
+        <v>1</v>
+      </c>
+      <c r="L58" t="b">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>13</v>
+      </c>
+      <c r="B59" t="s">
+        <v>190</v>
+      </c>
+      <c r="C59" t="s">
+        <v>191</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E59" t="s">
+        <v>192</v>
+      </c>
+      <c r="F59" t="n">
+        <v>8</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="H59" t="s">
+        <v>17</v>
+      </c>
+      <c r="I59" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="J59" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K59" t="b">
+        <v>1</v>
+      </c>
+      <c r="L59" t="b">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>18</v>
+      </c>
+      <c r="B60" t="s">
+        <v>193</v>
+      </c>
+      <c r="C60" t="s">
+        <v>194</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E60" t="s">
+        <v>195</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1107</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="J60" t="n">
+        <v>9.12</v>
+      </c>
+      <c r="K60" t="b">
+        <v>1</v>
+      </c>
+      <c r="L60" t="b">
+        <v>1</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61" t="s">
+        <v>196</v>
+      </c>
+      <c r="C61" t="s">
+        <v>197</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E61" t="s">
+        <v>198</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1098</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H61" t="s">
+        <v>17</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" t="b">
+        <v>1</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62" t="s">
+        <v>199</v>
+      </c>
+      <c r="C62" t="s">
+        <v>200</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E62" t="s">
+        <v>201</v>
+      </c>
+      <c r="F62" t="n">
+        <v>363</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H62" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="J62" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="K62" t="b">
+        <v>1</v>
+      </c>
+      <c r="L62" t="b">
+        <v>1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>13</v>
+      </c>
+      <c r="B63" t="s">
+        <v>202</v>
+      </c>
+      <c r="C63" t="s">
+        <v>203</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E63" t="s">
+        <v>204</v>
+      </c>
+      <c r="F63" t="n">
+        <v>185</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H63" t="s">
+        <v>17</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K63" t="b">
+        <v>1</v>
+      </c>
+      <c r="L63" t="b">
+        <v>1</v>
+      </c>
+      <c r="M63" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64" t="s">
+        <v>205</v>
+      </c>
+      <c r="C64" t="s">
+        <v>206</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E64" t="s">
+        <v>207</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1308</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H64" t="s">
+        <v>17</v>
+      </c>
+      <c r="I64" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="J64" t="n">
+        <v>9.72</v>
+      </c>
+      <c r="K64" t="b">
+        <v>1</v>
+      </c>
+      <c r="L64" t="b">
+        <v>1</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>18</v>
+      </c>
+      <c r="B65" t="s">
+        <v>208</v>
+      </c>
+      <c r="C65" t="s">
+        <v>209</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E65" t="s">
+        <v>210</v>
+      </c>
+      <c r="F65" t="n">
+        <v>168</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H65" t="s">
+        <v>17</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J65" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K65" t="b">
+        <v>1</v>
+      </c>
+      <c r="L65" t="b">
+        <v>1</v>
+      </c>
+      <c r="M65" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>18</v>
+      </c>
+      <c r="B66" t="s">
+        <v>211</v>
+      </c>
+      <c r="C66" t="s">
+        <v>212</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E66" t="s">
+        <v>213</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1061</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H66" t="s">
+        <v>17</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K66" t="b">
+        <v>1</v>
+      </c>
+      <c r="L66" t="b">
+        <v>1</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>13</v>
+      </c>
+      <c r="B67" t="s">
+        <v>214</v>
+      </c>
+      <c r="C67" t="s">
+        <v>215</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E67" t="s">
+        <v>216</v>
+      </c>
+      <c r="F67" t="n">
+        <v>998</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="s">
+        <v>17</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J67" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="K67" t="b">
+        <v>1</v>
+      </c>
+      <c r="L67" t="b">
+        <v>1</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>13</v>
+      </c>
+      <c r="B68" t="s">
+        <v>217</v>
+      </c>
+      <c r="C68" t="s">
+        <v>218</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E68" t="s">
+        <v>219</v>
+      </c>
+      <c r="F68" t="n">
+        <v>26</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="H68" t="s">
+        <v>17</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J68" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="K68" t="b">
+        <v>1</v>
+      </c>
+      <c r="L68" t="b">
+        <v>1</v>
+      </c>
+      <c r="M68" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>18</v>
+      </c>
+      <c r="B69" t="s">
+        <v>220</v>
+      </c>
+      <c r="C69" t="s">
+        <v>221</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="E69" t="s">
+        <v>222</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1094</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H69" t="s">
+        <v>17</v>
+      </c>
+      <c r="I69" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="K69" t="b">
+        <v>1</v>
+      </c>
+      <c r="L69" t="b">
+        <v>1</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>18</v>
+      </c>
+      <c r="B70" t="s">
+        <v>223</v>
+      </c>
+      <c r="C70" t="s">
+        <v>224</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E70" t="s">
+        <v>225</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1209</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H70" t="s">
+        <v>17</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K70" t="b">
+        <v>1</v>
+      </c>
+      <c r="L70" t="b">
+        <v>1</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>18</v>
+      </c>
+      <c r="B71" t="s">
+        <v>226</v>
+      </c>
+      <c r="C71" t="s">
+        <v>227</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="E71" t="s">
+        <v>228</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1335</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H71" t="s">
+        <v>17</v>
+      </c>
+      <c r="I71" t="n">
+        <v>4</v>
+      </c>
+      <c r="J71" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="K71" t="b">
+        <v>1</v>
+      </c>
+      <c r="L71" t="b">
+        <v>1</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>13</v>
+      </c>
+      <c r="B72" t="s">
+        <v>229</v>
+      </c>
+      <c r="C72" t="s">
+        <v>230</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E72" t="s">
+        <v>231</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1054</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H72" t="s">
+        <v>17</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J72" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K72" t="b">
+        <v>1</v>
+      </c>
+      <c r="L72" t="b">
+        <v>1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>13</v>
+      </c>
+      <c r="B73" t="s">
+        <v>232</v>
+      </c>
+      <c r="C73" t="s">
+        <v>233</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E73" t="s">
+        <v>234</v>
+      </c>
+      <c r="F73" t="n">
+        <v>225</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H73" t="s">
+        <v>17</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J73" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K73" t="b">
+        <v>1</v>
+      </c>
+      <c r="L73" t="b">
+        <v>1</v>
+      </c>
+      <c r="M73" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>13</v>
+      </c>
+      <c r="B74" t="s">
+        <v>235</v>
+      </c>
+      <c r="C74" t="s">
+        <v>236</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E74" t="s">
+        <v>237</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="s">
+        <v>17</v>
+      </c>
+      <c r="I74" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="J74" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K74" t="b">
+        <v>1</v>
+      </c>
+      <c r="L74" t="b">
+        <v>1</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B75" t="s">
+        <v>238</v>
+      </c>
+      <c r="C75" t="s">
+        <v>239</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E75" t="s">
+        <v>240</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1337</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H75" t="s">
+        <v>17</v>
+      </c>
+      <c r="I75" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="K75" t="b">
+        <v>1</v>
+      </c>
+      <c r="L75" t="b">
+        <v>1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>13</v>
+      </c>
+      <c r="B76" t="s">
+        <v>241</v>
+      </c>
+      <c r="C76" t="s">
+        <v>242</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E76" t="s">
+        <v>243</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1271</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H76" t="s">
+        <v>17</v>
+      </c>
+      <c r="I76" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="J76" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K76" t="b">
+        <v>1</v>
+      </c>
+      <c r="L76" t="b">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1276</v>
       </c>
     </row>
   </sheetData>
@@ -637,7 +4296,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
@@ -652,25 +4311,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>244</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>245</v>
       </c>
       <c r="D1" t="s">
-        <v>24</v>
+        <v>246</v>
       </c>
       <c r="E1" t="s">
-        <v>25</v>
+        <v>247</v>
       </c>
       <c r="F1" t="s">
-        <v>26</v>
+        <v>248</v>
       </c>
       <c r="G1" t="s">
-        <v>27</v>
+        <v>249</v>
       </c>
       <c r="H1" t="s">
-        <v>28</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2">
@@ -678,16 +4337,16 @@
         <v>13</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="C2" t="n">
-        <v>119.6</v>
+        <v>0.4</v>
       </c>
       <c r="D2" t="n">
-        <v>238.58</v>
+        <v>1.44</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -696,6 +4355,58 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -713,7 +4424,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="19.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
@@ -751,54 +4462,522 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="C2" t="n">
-        <v>516</v>
+        <v>374.5</v>
       </c>
       <c r="D2" t="n">
-        <v>238.58</v>
+        <v>6.53</v>
       </c>
       <c r="E2" t="n">
-        <v>0.718</v>
+        <v>0.019</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="H2" t="n">
-        <v>2.88</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.683</v>
+      </c>
+      <c r="F3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" t="n">
+        <v>412</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1098</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1335</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" t="n">
+        <v>130</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.084</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8.76</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>205</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1308</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9.72</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1106</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1120</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="n">
+        <v>575</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1107</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="H12" t="n">
+        <v>9.12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" t="n">
+        <v>805</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="F13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1411.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="n">
+        <v>549</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H15" t="n">
+        <v>10.68</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1378</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1026</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="n">
-        <v>168</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="C18" t="n">
+        <v>44</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="F18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H18" t="n">
         <v>0.72</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>223</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1209</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" t="n">
+        <v>241</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>211</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1061</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.04</v>
       </c>
     </row>
   </sheetData>
